--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -9679,16 +9679,16 @@
         <v>6324105879</v>
       </c>
       <c r="D404" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E404" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F404" t="str">
         <v>РФ</v>
       </c>
       <c r="G404">
-        <v>46153</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="405">
@@ -9702,16 +9702,16 @@
         <v>6324105879</v>
       </c>
       <c r="D405" t="str">
-        <v>EADAS</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E405" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F405" t="str">
         <v>РФ</v>
       </c>
       <c r="G405">
-        <v>46064</v>
+        <v>47187</v>
       </c>
     </row>
     <row r="406">
@@ -9725,7 +9725,7 @@
         <v>6324105879</v>
       </c>
       <c r="D406" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E406" t="str">
         <v>ISO 9001:2015</v>
@@ -9739,16 +9739,16 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>ББС ШТАМП</v>
+        <v>ПКФ Полюс</v>
       </c>
       <c r="B407" t="str">
         <v>ООО</v>
       </c>
       <c r="C407" t="str">
-        <v>6324105879</v>
+        <v>1648002641</v>
       </c>
       <c r="D407" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E407" t="str">
         <v>ISO 9001:2015</v>
@@ -9757,7 +9757,7 @@
         <v>РФ</v>
       </c>
       <c r="G407">
-        <v>47187</v>
+        <v>46746</v>
       </c>
     </row>
     <row r="408">
@@ -9771,27 +9771,27 @@
         <v>1648002641</v>
       </c>
       <c r="D408" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E408" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F408" t="str">
         <v>РФ</v>
       </c>
       <c r="G408">
-        <v>46746</v>
+        <v>46345</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>ПКФ Полюс</v>
+        <v>РАСКАМ</v>
       </c>
       <c r="B409" t="str">
         <v>ООО</v>
       </c>
       <c r="C409" t="str">
-        <v>1648002641</v>
+        <v>1650339258</v>
       </c>
       <c r="D409" t="str">
         <v>EADAS</v>
@@ -9803,7 +9803,7 @@
         <v>РФ</v>
       </c>
       <c r="G409">
-        <v>46345</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="410">
@@ -9817,16 +9817,16 @@
         <v>1650339258</v>
       </c>
       <c r="D410" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E410" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F410" t="str">
         <v>РФ</v>
       </c>
       <c r="G410">
-        <v>46059</v>
+        <v>46865</v>
       </c>
     </row>
     <row r="411">
@@ -9843,7 +9843,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E411" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2018</v>
       </c>
       <c r="F411" t="str">
         <v>РФ</v>
@@ -9854,25 +9854,25 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>РАСКАМ</v>
+        <v>ПКФ Полюс-Альфа</v>
       </c>
       <c r="B412" t="str">
         <v>ООО</v>
       </c>
       <c r="C412" t="str">
-        <v>1650339258</v>
+        <v>1648005321</v>
       </c>
       <c r="D412" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E412" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F412" t="str">
         <v>РФ</v>
       </c>
       <c r="G412">
-        <v>46865</v>
+        <v>46746</v>
       </c>
     </row>
     <row r="413">
@@ -9886,39 +9886,39 @@
         <v>1648005321</v>
       </c>
       <c r="D413" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E413" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F413" t="str">
         <v>РФ</v>
       </c>
       <c r="G413">
-        <v>46746</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ПКФ Полюс-Альфа</v>
+        <v>Завод имени А.М. Тарасова (ЗиТ)</v>
       </c>
       <c r="B414" t="str">
-        <v>ООО</v>
+        <v>ПАО</v>
       </c>
       <c r="C414" t="str">
-        <v>1648005321</v>
+        <v>6319017480</v>
       </c>
       <c r="D414" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E414" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F414" t="str">
         <v>РФ</v>
       </c>
       <c r="G414">
-        <v>46332</v>
+        <v>46898</v>
       </c>
     </row>
     <row r="415">
@@ -9932,7 +9932,7 @@
         <v>6319017480</v>
       </c>
       <c r="D415" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E415" t="str">
         <v>ISO 9001:2015</v>
@@ -9955,27 +9955,27 @@
         <v>6319017480</v>
       </c>
       <c r="D416" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E416" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F416" t="str">
         <v>РФ</v>
       </c>
       <c r="G416">
-        <v>46898</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Завод имени А.М. Тарасова (ЗиТ)</v>
+        <v>Татнефть-Пресскомпозит</v>
       </c>
       <c r="B417" t="str">
-        <v>ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C417" t="str">
-        <v>6319017480</v>
+        <v>1644062664</v>
       </c>
       <c r="D417" t="str">
         <v>EADAS</v>
@@ -9987,7 +9987,7 @@
         <v>РФ</v>
       </c>
       <c r="G417">
-        <v>46115</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="418">
@@ -10001,16 +10001,16 @@
         <v>1644062664</v>
       </c>
       <c r="D418" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E418" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F418" t="str">
         <v>РФ</v>
       </c>
       <c r="G418">
-        <v>46192</v>
+        <v>46988</v>
       </c>
     </row>
     <row r="419">
@@ -10024,16 +10024,16 @@
         <v>1644062664</v>
       </c>
       <c r="D419" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E419" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F419" t="str">
         <v>РФ</v>
       </c>
       <c r="G419">
-        <v>46988</v>
+        <v>47148</v>
       </c>
     </row>
     <row r="420">
@@ -10047,16 +10047,16 @@
         <v>1644062664</v>
       </c>
       <c r="D420" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E420" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F420" t="str">
         <v>РФ</v>
       </c>
       <c r="G420">
-        <v>47148</v>
+        <v>47160</v>
       </c>
     </row>
     <row r="421">
@@ -10070,7 +10070,7 @@
         <v>1644062664</v>
       </c>
       <c r="D421" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E421" t="str">
         <v>ISO 9001:2015</v>
@@ -10084,13 +10084,13 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Татнефть-Пресскомпозит</v>
+        <v>БИФОРМ ПЛЮС</v>
       </c>
       <c r="B422" t="str">
         <v>ООО</v>
       </c>
       <c r="C422" t="str">
-        <v>1644062664</v>
+        <v>1650306566</v>
       </c>
       <c r="D422" t="str">
         <v>ESYD (IAF)</v>
@@ -10102,7 +10102,7 @@
         <v>РФ</v>
       </c>
       <c r="G422">
-        <v>47160</v>
+        <v>47080</v>
       </c>
     </row>
     <row r="423">
@@ -10116,7 +10116,7 @@
         <v>1650306566</v>
       </c>
       <c r="D423" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E423" t="str">
         <v>ISO 9001:2015</v>
@@ -10139,27 +10139,27 @@
         <v>1650306566</v>
       </c>
       <c r="D424" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E424" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F424" t="str">
         <v>РФ</v>
       </c>
       <c r="G424">
-        <v>47080</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>БИФОРМ ПЛЮС</v>
+        <v>Блик</v>
       </c>
       <c r="B425" t="str">
         <v>ООО</v>
       </c>
       <c r="C425" t="str">
-        <v>1650306566</v>
+        <v>1650248931</v>
       </c>
       <c r="D425" t="str">
         <v>EADAS</v>
@@ -10171,7 +10171,7 @@
         <v>РФ</v>
       </c>
       <c r="G425">
-        <v>46199</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="426">
@@ -10185,16 +10185,16 @@
         <v>1650248931</v>
       </c>
       <c r="D426" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E426" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F426" t="str">
         <v>РФ</v>
       </c>
       <c r="G426">
-        <v>46170</v>
+        <v>46950</v>
       </c>
     </row>
     <row r="427">
@@ -10211,7 +10211,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E427" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F427" t="str">
         <v>РФ</v>
@@ -10222,25 +10222,25 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Блик</v>
+        <v>Электрокабель Кольчугинский завод</v>
       </c>
       <c r="B428" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C428" t="str">
-        <v>1650248931</v>
+        <v>3306007697</v>
       </c>
       <c r="D428" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E428" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F428" t="str">
         <v>РФ</v>
       </c>
       <c r="G428">
-        <v>46950</v>
+        <v>46191</v>
       </c>
     </row>
     <row r="429">
@@ -10254,39 +10254,39 @@
         <v>3306007697</v>
       </c>
       <c r="D429" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E429" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F429" t="str">
         <v>РФ</v>
       </c>
       <c r="G429">
-        <v>46191</v>
+        <v>47004</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Электрокабель Кольчугинский завод</v>
+        <v>ВАТИ-АВТО</v>
       </c>
       <c r="B430" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C430" t="str">
-        <v>3306007697</v>
+        <v>3435133516</v>
       </c>
       <c r="D430" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E430" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F430" t="str">
         <v>РФ</v>
       </c>
       <c r="G430">
-        <v>47004</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="431">
@@ -10300,39 +10300,39 @@
         <v>3435133516</v>
       </c>
       <c r="D431" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E431" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2018</v>
       </c>
       <c r="F431" t="str">
         <v>РФ</v>
       </c>
       <c r="G431">
-        <v>46100</v>
+        <v>46887</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>ВАТИ-АВТО</v>
+        <v>Дейвон Спринг энд Сит</v>
       </c>
       <c r="B432" t="str">
         <v>ООО</v>
       </c>
       <c r="C432" t="str">
-        <v>3435133516</v>
+        <v>6324043421</v>
       </c>
       <c r="D432" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E432" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F432" t="str">
         <v>РФ</v>
       </c>
       <c r="G432">
-        <v>46887</v>
+        <v>46464</v>
       </c>
     </row>
     <row r="433">
@@ -10346,39 +10346,39 @@
         <v>6324043421</v>
       </c>
       <c r="D433" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E433" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F433" t="str">
         <v>РФ</v>
       </c>
       <c r="G433">
-        <v>46464</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Дейвон Спринг энд Сит</v>
+        <v>Стекло-сервис</v>
       </c>
       <c r="B434" t="str">
         <v>ООО</v>
       </c>
       <c r="C434" t="str">
-        <v>6324043421</v>
+        <v>7719539002</v>
       </c>
       <c r="D434" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E434" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F434" t="str">
         <v>РФ</v>
       </c>
       <c r="G434">
-        <v>45959</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="435">
@@ -10392,16 +10392,16 @@
         <v>7719539002</v>
       </c>
       <c r="D435" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E435" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F435" t="str">
         <v>РФ</v>
       </c>
       <c r="G435">
-        <v>46215</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="436">
@@ -10415,21 +10415,21 @@
         <v>7719539002</v>
       </c>
       <c r="D436" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E436" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F436" t="str">
         <v>РФ</v>
       </c>
       <c r="G436">
-        <v>46268</v>
+        <v>47086</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Стекло-сервис</v>
+        <v>Филиал Стекло-сервис Индустриальный парк Формула света</v>
       </c>
       <c r="B437" t="str">
         <v>ООО</v>
@@ -10438,16 +10438,16 @@
         <v>7719539002</v>
       </c>
       <c r="D437" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E437" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F437" t="str">
         <v>РФ</v>
       </c>
       <c r="G437">
-        <v>47086</v>
+        <v>46381</v>
       </c>
     </row>
     <row r="438">
@@ -10461,39 +10461,39 @@
         <v>7719539002</v>
       </c>
       <c r="D438" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E438" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F438" t="str">
         <v>РФ</v>
       </c>
       <c r="G438">
-        <v>46381</v>
+        <v>46397</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Филиал Стекло-сервис Индустриальный парк Формула света</v>
+        <v>Производственное объединение Пензенский завод Электромехизмерение</v>
       </c>
       <c r="B439" t="str">
         <v>ООО</v>
       </c>
       <c r="C439" t="str">
-        <v>7719539002</v>
+        <v>5835105370</v>
       </c>
       <c r="D439" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E439" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F439" t="str">
         <v>РФ</v>
       </c>
       <c r="G439">
-        <v>46397</v>
+        <v>47010</v>
       </c>
     </row>
     <row r="440">
@@ -10507,7 +10507,7 @@
         <v>5835105370</v>
       </c>
       <c r="D440" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E440" t="str">
         <v>ISO 9001:2015</v>
@@ -10530,50 +10530,50 @@
         <v>5835105370</v>
       </c>
       <c r="D441" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E441" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F441" t="str">
         <v>РФ</v>
       </c>
       <c r="G441">
-        <v>47010</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Производственное объединение Пензенский завод Электромехизмерение</v>
+        <v>Научно-производственное предприятие Волга Медикал</v>
       </c>
       <c r="B442" t="str">
         <v>ООО</v>
       </c>
       <c r="C442" t="str">
-        <v>5835105370</v>
+        <v>5259086766</v>
       </c>
       <c r="D442" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E442" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F442" t="str">
         <v>РФ</v>
       </c>
       <c r="G442">
-        <v>46248</v>
+        <v>46563</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Научно-производственное предприятие Волга Медикал</v>
+        <v>ИНТРА</v>
       </c>
       <c r="B443" t="str">
         <v>ООО</v>
       </c>
       <c r="C443" t="str">
-        <v>5259086766</v>
+        <v>6321453211</v>
       </c>
       <c r="D443" t="str">
         <v>UKAS (IAF)</v>
@@ -10585,21 +10585,21 @@
         <v>РФ</v>
       </c>
       <c r="G443">
-        <v>46563</v>
+        <v>46362</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>ИНТРА</v>
+        <v>Апекс Групп</v>
       </c>
       <c r="B444" t="str">
         <v>ООО</v>
       </c>
       <c r="C444" t="str">
-        <v>6321453211</v>
+        <v>7453131043</v>
       </c>
       <c r="D444" t="str">
-        <v>UKAS (IAF)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E444" t="str">
         <v>ISO 9001:2015</v>
@@ -10608,7 +10608,7 @@
         <v>РФ</v>
       </c>
       <c r="G444">
-        <v>46362</v>
+        <v>47031</v>
       </c>
     </row>
     <row r="445">
@@ -10622,7 +10622,7 @@
         <v>7453131043</v>
       </c>
       <c r="D445" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E445" t="str">
         <v>ISO 9001:2015</v>
@@ -10645,39 +10645,39 @@
         <v>7453131043</v>
       </c>
       <c r="D446" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E446" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F446" t="str">
         <v>РФ</v>
       </c>
       <c r="G446">
-        <v>47031</v>
+        <v>47085</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Апекс Групп</v>
+        <v>КНАУФ ПЕНОПЛАСТ</v>
       </c>
       <c r="B447" t="str">
         <v>ООО</v>
       </c>
       <c r="C447" t="str">
-        <v>7453131043</v>
+        <v>7817034384</v>
       </c>
       <c r="D447" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E447" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F447" t="str">
         <v>РФ</v>
       </c>
       <c r="G447">
-        <v>47085</v>
+        <v>47077</v>
       </c>
     </row>
     <row r="448">
@@ -10691,27 +10691,27 @@
         <v>7817034384</v>
       </c>
       <c r="D448" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E448" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F448" t="str">
         <v>РФ</v>
       </c>
       <c r="G448">
-        <v>47077</v>
+        <v>46336</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>КНАУФ ПЕНОПЛАСТ</v>
+        <v>СГЛ</v>
       </c>
       <c r="B449" t="str">
         <v>ООО</v>
       </c>
       <c r="C449" t="str">
-        <v>7817034384</v>
+        <v>6674224819</v>
       </c>
       <c r="D449" t="str">
         <v>EADAS</v>
@@ -10723,18 +10723,18 @@
         <v>РФ</v>
       </c>
       <c r="G449">
-        <v>46336</v>
+        <v>46175</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>СГЛ</v>
+        <v>НПЦ Электропитание</v>
       </c>
       <c r="B450" t="str">
         <v>ООО</v>
       </c>
       <c r="C450" t="str">
-        <v>6674224819</v>
+        <v>5835005992</v>
       </c>
       <c r="D450" t="str">
         <v>EADAS</v>
@@ -10746,53 +10746,53 @@
         <v>РФ</v>
       </c>
       <c r="G450">
-        <v>46175</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>НПЦ Электропитание</v>
+        <v>Ульяновский Приборо-Ремонтный Завод</v>
       </c>
       <c r="B451" t="str">
         <v>ООО</v>
       </c>
       <c r="C451" t="str">
-        <v>5835005992</v>
+        <v>7325057468</v>
       </c>
       <c r="D451" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E451" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F451" t="str">
         <v>РФ</v>
       </c>
       <c r="G451">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Ульяновский Приборо-Ремонтный Завод</v>
+        <v>Кузнечный завод тяжелых штамповок (КЗТШ)</v>
       </c>
       <c r="B452" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C452" t="str">
-        <v>7325057468</v>
+        <v>600038921</v>
       </c>
       <c r="D452" t="str">
         <v>UKAS (IAF)</v>
       </c>
       <c r="E452" t="str">
-        <v>ISO 9001:2015</v>
+        <v>IATF 16949:2016</v>
       </c>
       <c r="F452" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G452">
-        <v>46170</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="453">
@@ -10806,50 +10806,50 @@
         <v>600038921</v>
       </c>
       <c r="D453" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E453" t="str">
-        <v>IATF 16949:2016</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F453" t="str">
         <v>РБ</v>
       </c>
       <c r="G453">
-        <v>46143</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Кузнечный завод тяжелых штамповок (КЗТШ)</v>
+        <v>Оренбургский Радиатор</v>
       </c>
       <c r="B454" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C454" t="str">
-        <v>600038921</v>
+        <v>5612030402</v>
       </c>
       <c r="D454" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E454" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F454" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G454">
-        <v>46071</v>
+        <v>46504</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Оренбургский Радиатор</v>
+        <v>Компания СМД</v>
       </c>
       <c r="B455" t="str">
         <v>ООО</v>
       </c>
       <c r="C455" t="str">
-        <v>5612030402</v>
+        <v>6323102610</v>
       </c>
       <c r="D455" t="str">
         <v>UKAS (IAF)</v>
@@ -10861,7 +10861,7 @@
         <v>РФ</v>
       </c>
       <c r="G455">
-        <v>46504</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="456">
@@ -10875,16 +10875,16 @@
         <v>6323102610</v>
       </c>
       <c r="D456" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E456" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F456" t="str">
         <v>РФ</v>
       </c>
       <c r="G456">
-        <v>46054</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="457">
@@ -10898,39 +10898,39 @@
         <v>6323102610</v>
       </c>
       <c r="D457" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E457" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F457" t="str">
         <v>РФ</v>
       </c>
       <c r="G457">
-        <v>46082</v>
+        <v>46562</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Компания СМД</v>
+        <v>Прогресс-Плюс</v>
       </c>
       <c r="B458" t="str">
         <v>ООО</v>
       </c>
       <c r="C458" t="str">
-        <v>6323102610</v>
+        <v>1651091962</v>
       </c>
       <c r="D458" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E458" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F458" t="str">
         <v>РФ</v>
       </c>
       <c r="G458">
-        <v>46562</v>
+        <v>46336</v>
       </c>
     </row>
     <row r="459">
@@ -10944,16 +10944,16 @@
         <v>1651091962</v>
       </c>
       <c r="D459" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E459" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F459" t="str">
         <v>РФ</v>
       </c>
       <c r="G459">
-        <v>46336</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="460">
@@ -10967,39 +10967,39 @@
         <v>1651091962</v>
       </c>
       <c r="D460" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E460" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F460" t="str">
         <v>РФ</v>
       </c>
       <c r="G460">
-        <v>46297</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Прогресс-Плюс</v>
+        <v>МЕКА</v>
       </c>
       <c r="B461" t="str">
         <v>ООО</v>
       </c>
       <c r="C461" t="str">
-        <v>1651091962</v>
+        <v>7802719681</v>
       </c>
       <c r="D461" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E461" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F461" t="str">
         <v>РФ</v>
       </c>
       <c r="G461">
-        <v>46341</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="462">
@@ -11013,50 +11013,50 @@
         <v>7802719681</v>
       </c>
       <c r="D462" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E462" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F462" t="str">
         <v>РФ</v>
       </c>
       <c r="G462">
-        <v>46110</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>МЕКА</v>
+        <v>Татнефть</v>
       </c>
       <c r="B463" t="str">
-        <v>ООО</v>
+        <v>ЦОБ ПАО</v>
       </c>
       <c r="C463" t="str">
-        <v>7802719681</v>
+        <v>1644003838</v>
       </c>
       <c r="D463" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E463" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F463" t="str">
         <v>РФ</v>
       </c>
       <c r="G463">
-        <v>46111</v>
+        <v>46556</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Татнефть</v>
+        <v>Научно-производственное объединение СтарЛайн</v>
       </c>
       <c r="B464" t="str">
-        <v>ЦОБ ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C464" t="str">
-        <v>1644003838</v>
+        <v>7802728654</v>
       </c>
       <c r="D464" t="str">
         <v>UKAS (IAF)</v>
@@ -11068,7 +11068,7 @@
         <v>РФ</v>
       </c>
       <c r="G464">
-        <v>46556</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="465">
@@ -11082,10 +11082,10 @@
         <v>7802728654</v>
       </c>
       <c r="D465" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E465" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F465" t="str">
         <v>РФ</v>
@@ -11096,36 +11096,36 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Научно-производственное объединение СтарЛайн</v>
+        <v>КОБА Автомотив РУС</v>
       </c>
       <c r="B466" t="str">
         <v>ООО</v>
       </c>
       <c r="C466" t="str">
-        <v>7802728654</v>
+        <v>6376020295</v>
       </c>
       <c r="D466" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E466" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F466" t="str">
         <v>РФ</v>
       </c>
       <c r="G466">
-        <v>46268</v>
+        <v>46675</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>КОБА Автомотив РУС</v>
+        <v>СЛОН-АВТО</v>
       </c>
       <c r="B467" t="str">
         <v>ООО</v>
       </c>
       <c r="C467" t="str">
-        <v>6376020295</v>
+        <v>6323111661</v>
       </c>
       <c r="D467" t="str">
         <v>UKAS (IAF)</v>
@@ -11137,7 +11137,7 @@
         <v>РФ</v>
       </c>
       <c r="G467">
-        <v>46675</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="468">
@@ -11151,16 +11151,16 @@
         <v>6323111661</v>
       </c>
       <c r="D468" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E468" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F468" t="str">
         <v>РФ</v>
       </c>
       <c r="G468">
-        <v>46305</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="469">
@@ -11174,39 +11174,39 @@
         <v>6323111661</v>
       </c>
       <c r="D469" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E469" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F469" t="str">
         <v>РФ</v>
       </c>
       <c r="G469">
-        <v>46286</v>
+        <v>46354</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>СЛОН-АВТО</v>
+        <v>Глобал Электрик Системс</v>
       </c>
       <c r="B470" t="str">
         <v>ООО</v>
       </c>
       <c r="C470" t="str">
-        <v>6323111661</v>
+        <v>7804522306</v>
       </c>
       <c r="D470" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E470" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F470" t="str">
         <v>РФ</v>
       </c>
       <c r="G470">
-        <v>46354</v>
+        <v>46369</v>
       </c>
     </row>
     <row r="471">
@@ -11220,16 +11220,16 @@
         <v>7804522306</v>
       </c>
       <c r="D471" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E471" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F471" t="str">
         <v>РФ</v>
       </c>
       <c r="G471">
-        <v>46369</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="472">
@@ -11243,39 +11243,39 @@
         <v>7804522306</v>
       </c>
       <c r="D472" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E472" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2018</v>
       </c>
       <c r="F472" t="str">
         <v>РФ</v>
       </c>
       <c r="G472">
-        <v>46357</v>
+        <v>46381</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Глобал Электрик Системс</v>
+        <v>Первоуральский Автоагрегатный завод</v>
       </c>
       <c r="B473" t="str">
         <v>ООО</v>
       </c>
       <c r="C473" t="str">
-        <v>7804522306</v>
+        <v>6684011136</v>
       </c>
       <c r="D473" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E473" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F473" t="str">
         <v>РФ</v>
       </c>
       <c r="G473">
-        <v>46381</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="474">
@@ -11289,16 +11289,16 @@
         <v>6684011136</v>
       </c>
       <c r="D474" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E474" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F474" t="str">
         <v>РФ</v>
       </c>
       <c r="G474">
-        <v>46316</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="475">
@@ -11312,39 +11312,39 @@
         <v>6684011136</v>
       </c>
       <c r="D475" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E475" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F475" t="str">
         <v>РФ</v>
       </c>
       <c r="G475">
-        <v>46303</v>
+        <v>47098</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Первоуральский Автоагрегатный завод</v>
+        <v>Сарансккабель-Оптика</v>
       </c>
       <c r="B476" t="str">
         <v>ООО</v>
       </c>
       <c r="C476" t="str">
-        <v>6684011136</v>
+        <v>1327153649</v>
       </c>
       <c r="D476" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E476" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F476" t="str">
         <v>РФ</v>
       </c>
       <c r="G476">
-        <v>47098</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="477">
@@ -11358,44 +11358,44 @@
         <v>1327153649</v>
       </c>
       <c r="D477" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E477" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F477" t="str">
         <v>РФ</v>
       </c>
       <c r="G477">
-        <v>46317</v>
+        <v>46444</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Сарансккабель-Оптика</v>
+        <v>Аккумулятор Инноваций</v>
       </c>
       <c r="B478" t="str">
         <v>ООО</v>
       </c>
       <c r="C478" t="str">
-        <v>1327153649</v>
+        <v>6321431240</v>
       </c>
       <c r="D478" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E478" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F478" t="str">
         <v>РФ</v>
       </c>
       <c r="G478">
-        <v>46444</v>
+        <v>47180</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Аккумулятор Инноваций</v>
+        <v>Аккумулятор инноваций</v>
       </c>
       <c r="B479" t="str">
         <v>ООО</v>
@@ -11404,7 +11404,7 @@
         <v>6321431240</v>
       </c>
       <c r="D479" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E479" t="str">
         <v>ISO 9001:2015</v>
@@ -11413,136 +11413,136 @@
         <v>РФ</v>
       </c>
       <c r="G479">
-        <v>46098</v>
+        <v>47180</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Аккумулятор Инноваций</v>
+        <v>Научно-исследовательский институт электронной техники (НИИЭТ)</v>
       </c>
       <c r="B480" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C480" t="str">
-        <v>6321431240</v>
+        <v>3661057900</v>
       </c>
       <c r="D480" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E480" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F480" t="str">
         <v>РФ</v>
       </c>
       <c r="G480">
-        <v>47180</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Аккумулятор инноваций</v>
+        <v>Научно-исследовательский институт электронной техники (НИИЭТ)</v>
       </c>
       <c r="B481" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C481" t="str">
-        <v>6321431240</v>
+        <v>3661057900</v>
       </c>
       <c r="D481" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E481" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2018</v>
       </c>
       <c r="F481" t="str">
         <v>РФ</v>
       </c>
       <c r="G481">
-        <v>47180</v>
+        <v>46929</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Научно-исследовательский институт электронной техники (НИИЭТ)</v>
+        <v>Северо-Западная Промышленная Корпорация (СЗПК)</v>
       </c>
       <c r="B482" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C482" t="str">
-        <v>3661057900</v>
+        <v>7802319490</v>
       </c>
       <c r="D482" t="str">
-        <v>EADAS</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E482" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F482" t="str">
         <v>РФ</v>
       </c>
       <c r="G482">
-        <v>46107</v>
+        <v>46778</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Научно-исследовательский институт электронной техники (НИИЭТ)</v>
+        <v>Северо-Западная Промышленная Корпорация (СЗПК)</v>
       </c>
       <c r="B483" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C483" t="str">
-        <v>3661057900</v>
+        <v>7802319490</v>
       </c>
       <c r="D483" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E483" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F483" t="str">
         <v>РФ</v>
       </c>
       <c r="G483">
-        <v>46929</v>
+        <v>46778</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Северо-Западная Промышленная Корпорация (СЗПК)</v>
+        <v>BBF Эстония (СЗПК)</v>
       </c>
       <c r="B484" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C484" t="str">
-        <v>7802319490</v>
+        <v/>
       </c>
       <c r="D484" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E484" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F484" t="str">
-        <v>РФ</v>
+        <v>Estonia</v>
       </c>
       <c r="G484">
-        <v>46778</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Северо-Западная Промышленная Корпорация (СЗПК)</v>
+        <v>Димитровградский вентильный завод</v>
       </c>
       <c r="B485" t="str">
         <v>ООО</v>
       </c>
       <c r="C485" t="str">
-        <v>7802319490</v>
+        <v>7302004420</v>
       </c>
       <c r="D485" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E485" t="str">
         <v>ISO 9001:2015</v>
@@ -11551,44 +11551,44 @@
         <v>РФ</v>
       </c>
       <c r="G485">
-        <v>46778</v>
+        <v>46834</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>BBF Эстония (СЗПК)</v>
+        <v>Димитровградский вентильный завод</v>
       </c>
       <c r="B486" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C486" t="str">
-        <v/>
+        <v>7302004420</v>
       </c>
       <c r="D486" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E486" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F486" t="str">
-        <v>Estonia</v>
+        <v>РФ</v>
       </c>
       <c r="G486">
-        <v>46218</v>
+        <v>46834</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Димитровградский вентильный завод</v>
+        <v>Старооскольский завод автотракторного электрооборудования им. А.М. мамонова (СОАТЭ)</v>
       </c>
       <c r="B487" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C487" t="str">
-        <v>7302004420</v>
+        <v>3128000673</v>
       </c>
       <c r="D487" t="str">
-        <v>IAS (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E487" t="str">
         <v>ISO 9001:2015</v>
@@ -11597,30 +11597,30 @@
         <v>РФ</v>
       </c>
       <c r="G487">
-        <v>46834</v>
+        <v>46576</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Димитровградский вентильный завод</v>
+        <v>Старооскольский завод автотракторного электрооборудования им. А.М. мамонова (СОАТЭ)</v>
       </c>
       <c r="B488" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C488" t="str">
-        <v>7302004420</v>
+        <v>3128000673</v>
       </c>
       <c r="D488" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E488" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F488" t="str">
         <v>РФ</v>
       </c>
       <c r="G488">
-        <v>46834</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="489">
@@ -11634,10 +11634,10 @@
         <v>3128000673</v>
       </c>
       <c r="D489" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E489" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2018</v>
       </c>
       <c r="F489" t="str">
         <v>РФ</v>
@@ -11648,48 +11648,48 @@
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Старооскольский завод автотракторного электрооборудования им. А.М. мамонова (СОАТЭ)</v>
+        <v>Государственный Рязанский приборный завод</v>
       </c>
       <c r="B490" t="str">
         <v>АО</v>
       </c>
       <c r="C490" t="str">
-        <v>3128000673</v>
+        <v>6234098539</v>
       </c>
       <c r="D490" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E490" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F490" t="str">
         <v>РФ</v>
       </c>
       <c r="G490">
-        <v>46080</v>
+        <v>46463</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Старооскольский завод автотракторного электрооборудования им. А.М. мамонова (СОАТЭ)</v>
+        <v>Государственный Рязанский приборный завод</v>
       </c>
       <c r="B491" t="str">
         <v>АО</v>
       </c>
       <c r="C491" t="str">
-        <v>3128000673</v>
+        <v>6234098539</v>
       </c>
       <c r="D491" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E491" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F491" t="str">
         <v>РФ</v>
       </c>
       <c r="G491">
-        <v>46576</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="492">
@@ -11703,10 +11703,10 @@
         <v>6234098539</v>
       </c>
       <c r="D492" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E492" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2018</v>
       </c>
       <c r="F492" t="str">
         <v>РФ</v>
@@ -11717,62 +11717,62 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Государственный Рязанский приборный завод</v>
+        <v>ТерроСтрой</v>
       </c>
       <c r="B493" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C493" t="str">
-        <v>6234098539</v>
+        <v>6678032593</v>
       </c>
       <c r="D493" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E493" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F493" t="str">
         <v>РФ</v>
       </c>
       <c r="G493">
-        <v>46009</v>
+        <v>46920</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Государственный Рязанский приборный завод</v>
+        <v>ТерроСтрой</v>
       </c>
       <c r="B494" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C494" t="str">
-        <v>6234098539</v>
+        <v>6678032593</v>
       </c>
       <c r="D494" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E494" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F494" t="str">
         <v>РФ</v>
       </c>
       <c r="G494">
-        <v>46463</v>
+        <v>46920</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>ТерроСтрой</v>
+        <v>Пермцветмет</v>
       </c>
       <c r="B495" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C495" t="str">
-        <v>6678032593</v>
+        <v>5906043394</v>
       </c>
       <c r="D495" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E495" t="str">
         <v>ISO 9001:2015</v>
@@ -11781,30 +11781,30 @@
         <v>РФ</v>
       </c>
       <c r="G495">
-        <v>46920</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>ТерроСтрой</v>
+        <v>Пермцветмет</v>
       </c>
       <c r="B496" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C496" t="str">
-        <v>6678032593</v>
+        <v>5906043394</v>
       </c>
       <c r="D496" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E496" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F496" t="str">
         <v>РФ</v>
       </c>
       <c r="G496">
-        <v>46920</v>
+        <v>46844</v>
       </c>
     </row>
     <row r="497">
@@ -11818,16 +11818,16 @@
         <v>5906043394</v>
       </c>
       <c r="D497" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E497" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F497" t="str">
         <v>РФ</v>
       </c>
       <c r="G497">
-        <v>46520</v>
+        <v>46844</v>
       </c>
     </row>
     <row r="498">
@@ -11841,16 +11841,16 @@
         <v>5906043394</v>
       </c>
       <c r="D498" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E498" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F498" t="str">
         <v>РФ</v>
       </c>
       <c r="G498">
-        <v>46844</v>
+        <v>46440</v>
       </c>
     </row>
     <row r="499">
@@ -11864,67 +11864,67 @@
         <v>5906043394</v>
       </c>
       <c r="D499" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E499" t="str">
-        <v>ISO 14001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F499" t="str">
         <v>РФ</v>
       </c>
       <c r="G499">
-        <v>46844</v>
+        <v>46548</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Пермцветмет</v>
+        <v>ВОЛЬТ-СПБ</v>
       </c>
       <c r="B500" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C500" t="str">
-        <v>5906043394</v>
+        <v>7810582416</v>
       </c>
       <c r="D500" t="str">
-        <v>UKAS (IAF)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E500" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F500" t="str">
         <v>РФ</v>
       </c>
       <c r="G500">
-        <v>46440</v>
+        <v>46905</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Пермцветмет</v>
+        <v>ВОЛЬТ-СПБ</v>
       </c>
       <c r="B501" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C501" t="str">
-        <v>5906043394</v>
+        <v>7810582416</v>
       </c>
       <c r="D501" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E501" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F501" t="str">
         <v>РФ</v>
       </c>
       <c r="G501">
-        <v>46548</v>
+        <v>46905</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>ВОЛЬТ-СПБ</v>
+        <v>ООО "ВОЛЬТ-СПБ"</v>
       </c>
       <c r="B502" t="str">
         <v>ООО</v>
@@ -11933,30 +11933,30 @@
         <v>7810582416</v>
       </c>
       <c r="D502" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E502" t="str">
-        <v>ISO 9001:2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F502" t="str">
         <v>РФ</v>
       </c>
       <c r="G502">
-        <v>46905</v>
+        <v>46901</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>ВОЛЬТ-СПБ</v>
+        <v>БАС Аутомотив Системс РУС</v>
       </c>
       <c r="B503" t="str">
         <v>ООО</v>
       </c>
       <c r="C503" t="str">
-        <v>7810582416</v>
+        <v>6321360461</v>
       </c>
       <c r="D503" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E503" t="str">
         <v>ISO 9001:2015</v>
@@ -11965,113 +11965,113 @@
         <v>РФ</v>
       </c>
       <c r="G503">
-        <v>46905</v>
+        <v>46582</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>ООО "ВОЛЬТ-СПБ"</v>
+        <v>БАС Аутомотив Системс РУС</v>
       </c>
       <c r="B504" t="str">
         <v>ООО</v>
       </c>
       <c r="C504" t="str">
-        <v>7810582416</v>
+        <v>6321360461</v>
       </c>
       <c r="D504" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>EADAS</v>
       </c>
       <c r="E504" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F504" t="str">
         <v>РФ</v>
       </c>
       <c r="G504">
-        <v>46901</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>БАС Аутомотив Системс РУС</v>
+        <v>Торсион-Д</v>
       </c>
       <c r="B505" t="str">
         <v>ООО</v>
       </c>
       <c r="C505" t="str">
-        <v>6321360461</v>
+        <v>7329023043</v>
       </c>
       <c r="D505" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E505" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F505" t="str">
         <v>РФ</v>
       </c>
       <c r="G505">
-        <v>46582</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>БАС Аутомотив Системс РУС</v>
+        <v>Торсион-Д</v>
       </c>
       <c r="B506" t="str">
         <v>ООО</v>
       </c>
       <c r="C506" t="str">
-        <v>6321360461</v>
+        <v>7329023043</v>
       </c>
       <c r="D506" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E506" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F506" t="str">
         <v>РФ</v>
       </c>
       <c r="G506">
-        <v>46108</v>
+        <v>46722</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Торсион-Д</v>
+        <v>МЦЕНСКИЙ ЛИТЕЙНЫЙ ЗАВОД</v>
       </c>
       <c r="B507" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C507" t="str">
-        <v>7329023043</v>
+        <v>5703008860</v>
       </c>
       <c r="D507" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E507" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2018</v>
       </c>
       <c r="F507" t="str">
         <v>РФ</v>
       </c>
       <c r="G507">
-        <v>46182</v>
+        <v>46480</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Торсион-Д</v>
+        <v>МЦЕНСКИЙ ЛИТЕЙНЫЙ ЗАВОД</v>
       </c>
       <c r="B508" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C508" t="str">
-        <v>7329023043</v>
+        <v>5703008860</v>
       </c>
       <c r="D508" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>NABCB (IAF)</v>
       </c>
       <c r="E508" t="str">
         <v>ISO 9001:2015</v>
@@ -12080,7 +12080,7 @@
         <v>РФ</v>
       </c>
       <c r="G508">
-        <v>46722</v>
+        <v>46852</v>
       </c>
     </row>
     <row r="509">
@@ -12097,13 +12097,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E509" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F509" t="str">
         <v>РФ</v>
       </c>
       <c r="G509">
-        <v>46480</v>
+        <v>46852</v>
       </c>
     </row>
     <row r="510">
@@ -12117,62 +12117,62 @@
         <v>5703008860</v>
       </c>
       <c r="D510" t="str">
-        <v>NABCB (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E510" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F510" t="str">
         <v>РФ</v>
       </c>
       <c r="G510">
-        <v>46852</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>МЦЕНСКИЙ ЛИТЕЙНЫЙ ЗАВОД</v>
+        <v>АББА</v>
       </c>
       <c r="B511" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C511" t="str">
-        <v>5703008860</v>
+        <v>2904009346</v>
       </c>
       <c r="D511" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E511" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F511" t="str">
         <v>РФ</v>
       </c>
       <c r="G511">
-        <v>46852</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>МЦЕНСКИЙ ЛИТЕЙНЫЙ ЗАВОД</v>
+        <v>АББА</v>
       </c>
       <c r="B512" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C512" t="str">
-        <v>5703008860</v>
+        <v>2904009346</v>
       </c>
       <c r="D512" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E512" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F512" t="str">
         <v>РФ</v>
       </c>
       <c r="G512">
-        <v>46093</v>
+        <v>46712</v>
       </c>
     </row>
     <row r="513">
@@ -12186,96 +12186,96 @@
         <v>2904009346</v>
       </c>
       <c r="D513" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E513" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F513" t="str">
         <v>РФ</v>
       </c>
       <c r="G513">
-        <v>46241</v>
+        <v>46589</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>АББА</v>
+        <v>ОАО "Борисовский завод автоагрегатов" - БЗА</v>
       </c>
       <c r="B514" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C514" t="str">
-        <v>2904009346</v>
+        <v>600012164</v>
       </c>
       <c r="D514" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E514" t="str">
-        <v>ISO 9001:2015</v>
+        <v>IATF 16949:2016</v>
       </c>
       <c r="F514" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G514">
-        <v>46712</v>
+        <v>46556</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>АББА</v>
+        <v>ОАО "Борисовский завод автоагрегатов" - БЗА</v>
       </c>
       <c r="B515" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C515" t="str">
-        <v>2904009346</v>
+        <v>600012164</v>
       </c>
       <c r="D515" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E515" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F515" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G515">
-        <v>46589</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>ОАО "Борисовский завод автоагрегатов" - БЗА</v>
+        <v>Завод Атлант</v>
       </c>
       <c r="B516" t="str">
-        <v>ОАО</v>
+        <v>АО</v>
       </c>
       <c r="C516" t="str">
-        <v>600012164</v>
+        <v>2607000333</v>
       </c>
       <c r="D516" t="str">
         <v>UKAS (IAF)</v>
       </c>
       <c r="E516" t="str">
-        <v>IATF 16949:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F516" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G516">
-        <v>46556</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>ОАО "Борисовский завод автоагрегатов" - БЗА</v>
+        <v>Завод Атлант</v>
       </c>
       <c r="B517" t="str">
-        <v>ОАО</v>
+        <v>АО</v>
       </c>
       <c r="C517" t="str">
-        <v>600012164</v>
+        <v>2607000333</v>
       </c>
       <c r="D517" t="str">
         <v>EADAS</v>
@@ -12284,24 +12284,24 @@
         <v>16949: 2016</v>
       </c>
       <c r="F517" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G517">
-        <v>46101</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Завод Атлант</v>
+        <v>ТатхимПласт</v>
       </c>
       <c r="B518" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C518" t="str">
-        <v>2607000333</v>
+        <v>1655217729</v>
       </c>
       <c r="D518" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E518" t="str">
         <v>ISO 9001:2015</v>
@@ -12310,30 +12310,30 @@
         <v>РФ</v>
       </c>
       <c r="G518">
-        <v>46660</v>
+        <v>46722</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Завод Атлант</v>
+        <v>ТатхимПласт</v>
       </c>
       <c r="B519" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C519" t="str">
-        <v>2607000333</v>
+        <v>1655217729</v>
       </c>
       <c r="D519" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E519" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F519" t="str">
         <v>РФ</v>
       </c>
       <c r="G519">
-        <v>46226</v>
+        <v>46722</v>
       </c>
     </row>
     <row r="520">
@@ -12347,50 +12347,50 @@
         <v>1655217729</v>
       </c>
       <c r="D520" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E520" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F520" t="str">
         <v>РФ</v>
       </c>
       <c r="G520">
-        <v>46722</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>ТатхимПласт</v>
+        <v>ОАО «БАТЭ» - управляющая компания холдинга «Автокомпоненты»</v>
       </c>
       <c r="B521" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C521" t="str">
-        <v>1655217729</v>
+        <v>600017855</v>
       </c>
       <c r="D521" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E521" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>IATF 16949:2016</v>
       </c>
       <c r="F521" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G521">
-        <v>46722</v>
+        <v>46667</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>ТатхимПласт</v>
+        <v>ОАО «БАТЭ» - управляющая компания холдинга «Автокомпоненты»</v>
       </c>
       <c r="B522" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C522" t="str">
-        <v>1655217729</v>
+        <v>600017855</v>
       </c>
       <c r="D522" t="str">
         <v>EADAS</v>
@@ -12399,44 +12399,44 @@
         <v>16949: 2016</v>
       </c>
       <c r="F522" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G522">
-        <v>46295</v>
+        <v>46191</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>ОАО «БАТЭ» - управляющая компания холдинга «Автокомпоненты»</v>
+        <v>Деталь-Ресурс</v>
       </c>
       <c r="B523" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C523" t="str">
-        <v>600017855</v>
+        <v>6382060673</v>
       </c>
       <c r="D523" t="str">
         <v>UKAS (IAF)</v>
       </c>
       <c r="E523" t="str">
-        <v>IATF 16949:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F523" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G523">
-        <v>46667</v>
+        <v>46681</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>ОАО «БАТЭ» - управляющая компания холдинга «Автокомпоненты»</v>
+        <v>Деталь-Ресурс</v>
       </c>
       <c r="B524" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C524" t="str">
-        <v>600017855</v>
+        <v>6382060673</v>
       </c>
       <c r="D524" t="str">
         <v>EADAS</v>
@@ -12445,10 +12445,10 @@
         <v>16949: 2016</v>
       </c>
       <c r="F524" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G524">
-        <v>46191</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="525">
@@ -12462,96 +12462,96 @@
         <v>6382060673</v>
       </c>
       <c r="D525" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E525" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F525" t="str">
         <v>РФ</v>
       </c>
       <c r="G525">
-        <v>46681</v>
+        <v>46999</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Деталь-Ресурс</v>
+        <v>ВМ Авто</v>
       </c>
       <c r="B526" t="str">
         <v>ООО</v>
       </c>
       <c r="C526" t="str">
-        <v>6382060673</v>
+        <v>6316145927</v>
       </c>
       <c r="D526" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E526" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F526" t="str">
         <v>РФ</v>
       </c>
       <c r="G526">
-        <v>46213</v>
+        <v>46688</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Деталь-Ресурс</v>
+        <v>ВМ Авто</v>
       </c>
       <c r="B527" t="str">
         <v>ООО</v>
       </c>
       <c r="C527" t="str">
-        <v>6382060673</v>
+        <v>6316145927</v>
       </c>
       <c r="D527" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E527" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F527" t="str">
         <v>РФ</v>
       </c>
       <c r="G527">
-        <v>46999</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>ВМ Авто</v>
+        <v>Торговый дом ТехноКорд</v>
       </c>
       <c r="B528" t="str">
         <v>ООО</v>
       </c>
       <c r="C528" t="str">
-        <v>6316145927</v>
+        <v>9717022519</v>
       </c>
       <c r="D528" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E528" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F528" t="str">
         <v>РФ</v>
       </c>
       <c r="G528">
-        <v>46688</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>ВМ Авто</v>
+        <v>ПО ЛУЗАР</v>
       </c>
       <c r="B529" t="str">
         <v>ООО</v>
       </c>
       <c r="C529" t="str">
-        <v>6316145927</v>
+        <v>7816485433</v>
       </c>
       <c r="D529" t="str">
         <v>EADAS</v>
@@ -12563,30 +12563,30 @@
         <v>РФ</v>
       </c>
       <c r="G529">
-        <v>46211</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Торговый дом ТехноКорд</v>
+        <v>ПО ЛУЗАР</v>
       </c>
       <c r="B530" t="str">
         <v>ООО</v>
       </c>
       <c r="C530" t="str">
-        <v>9717022519</v>
+        <v>7816485433</v>
       </c>
       <c r="D530" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E530" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F530" t="str">
         <v>РФ</v>
       </c>
       <c r="G530">
-        <v>46280</v>
+        <v>46857</v>
       </c>
     </row>
     <row r="531">
@@ -12600,73 +12600,73 @@
         <v>7816485433</v>
       </c>
       <c r="D531" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E531" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F531" t="str">
         <v>РФ</v>
       </c>
       <c r="G531">
-        <v>46102</v>
+        <v>46857</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>ПО ЛУЗАР</v>
+        <v>Промтехнологии</v>
       </c>
       <c r="B532" t="str">
         <v>ООО</v>
       </c>
       <c r="C532" t="str">
-        <v>7816485433</v>
+        <v>7415088326</v>
       </c>
       <c r="D532" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E532" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F532" t="str">
         <v>РФ</v>
       </c>
       <c r="G532">
-        <v>46857</v>
+        <v>46443</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>ПО ЛУЗАР</v>
+        <v>Промтехнологии</v>
       </c>
       <c r="B533" t="str">
         <v>ООО</v>
       </c>
       <c r="C533" t="str">
-        <v>7816485433</v>
+        <v>7415088326</v>
       </c>
       <c r="D533" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E533" t="str">
-        <v>ISO 9001:2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F533" t="str">
         <v>РФ</v>
       </c>
       <c r="G533">
-        <v>46857</v>
+        <v>46436</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Промтехнологии</v>
+        <v>АРХАНГЕЛЬСКИЙ ФАНЕРНЫЙ ЗАВОД</v>
       </c>
       <c r="B534" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C534" t="str">
-        <v>7415088326</v>
+        <v>2903004722</v>
       </c>
       <c r="D534" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -12678,30 +12678,30 @@
         <v>РФ</v>
       </c>
       <c r="G534">
-        <v>46443</v>
+        <v>47190</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Промтехнологии</v>
+        <v>АРХАНГЕЛЬСКИЙ ФАНЕРНЫЙ ЗАВОД</v>
       </c>
       <c r="B535" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C535" t="str">
-        <v>7415088326</v>
+        <v>2903004722</v>
       </c>
       <c r="D535" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E535" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F535" t="str">
         <v>РФ</v>
       </c>
       <c r="G535">
-        <v>46436</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="536">
@@ -12715,16 +12715,16 @@
         <v>2903004722</v>
       </c>
       <c r="D536" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E536" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F536" t="str">
         <v>РФ</v>
       </c>
       <c r="G536">
-        <v>47190</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="537">
@@ -14909,7 +14909,7 @@
         <v>РБ</v>
       </c>
       <c r="G631">
-        <v>46360</v>
+        <v>47195</v>
       </c>
     </row>
     <row r="632">
@@ -21472,7 +21472,7 @@
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>Линдэйли</v>
+        <v>ехлаб</v>
       </c>
       <c r="B917" t="str">
         <v>ООО</v>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1384"/>
+  <dimension ref="A1:G1386"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9067,7 +9067,7 @@
         <v>РФ</v>
       </c>
       <c r="G377">
-        <v>45974</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="378">
@@ -10728,7 +10728,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Ульяновский Приборо-Ремонтный Завод</v>
+        <v>Ульяновский Приборо-Ремонтный Завод (УПРЗ)</v>
       </c>
       <c r="B450" t="str">
         <v>ООО</v>
@@ -12936,25 +12936,25 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Нижнекамскнефтехим</v>
+        <v>СИБУР Холдинг</v>
       </c>
       <c r="B546" t="str">
         <v>ПАО</v>
       </c>
       <c r="C546" t="str">
-        <v>1651000010</v>
+        <v>7727547261</v>
       </c>
       <c r="D546" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E546" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F546" t="str">
         <v>РФ</v>
       </c>
       <c r="G546">
-        <v>46367</v>
+        <v>47189</v>
       </c>
     </row>
     <row r="547">
@@ -12968,16 +12968,16 @@
         <v>1651000010</v>
       </c>
       <c r="D547" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E547" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F547" t="str">
         <v>РФ</v>
       </c>
       <c r="G547">
-        <v>46467</v>
+        <v>46367</v>
       </c>
     </row>
     <row r="548">
@@ -12994,36 +12994,36 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E548" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ГОСТ Р 58139-2018</v>
       </c>
       <c r="F548" t="str">
         <v>РФ</v>
       </c>
       <c r="G548">
-        <v>47189</v>
+        <v>46467</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Номатекс</v>
+        <v>Нижнекамскнефтехим</v>
       </c>
       <c r="B549" t="str">
-        <v>ООО</v>
+        <v>ПАО</v>
       </c>
       <c r="C549" t="str">
-        <v>7310006830</v>
+        <v>1651000010</v>
       </c>
       <c r="D549" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E549" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F549" t="str">
         <v>РФ</v>
       </c>
       <c r="G549">
-        <v>46837</v>
+        <v>47189</v>
       </c>
     </row>
     <row r="550">
@@ -13037,7 +13037,7 @@
         <v>7310006830</v>
       </c>
       <c r="D550" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E550" t="str">
         <v>ISO 9001:2015</v>
@@ -13060,27 +13060,27 @@
         <v>7310006830</v>
       </c>
       <c r="D551" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E551" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F551" t="str">
         <v>РФ</v>
       </c>
       <c r="G551">
-        <v>46373</v>
+        <v>46837</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>АвтоТрейд</v>
+        <v>Номатекс</v>
       </c>
       <c r="B552" t="str">
         <v>ООО</v>
       </c>
       <c r="C552" t="str">
-        <v>7703644467</v>
+        <v>7310006830</v>
       </c>
       <c r="D552" t="str">
         <v>EADAS</v>
@@ -13106,16 +13106,16 @@
         <v>7703644467</v>
       </c>
       <c r="D553" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E553" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F553" t="str">
         <v>РФ</v>
       </c>
       <c r="G553">
-        <v>46853</v>
+        <v>46373</v>
       </c>
     </row>
     <row r="554">
@@ -13132,7 +13132,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E554" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F554" t="str">
         <v>РФ</v>
@@ -13143,25 +13143,25 @@
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Теком</v>
+        <v>АвтоТрейд</v>
       </c>
       <c r="B555" t="str">
         <v>ООО</v>
       </c>
       <c r="C555" t="str">
-        <v>7806531031</v>
+        <v>7703644467</v>
       </c>
       <c r="D555" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E555" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2018</v>
       </c>
       <c r="F555" t="str">
         <v>РФ</v>
       </c>
       <c r="G555">
-        <v>46963</v>
+        <v>46853</v>
       </c>
     </row>
     <row r="556">
@@ -13175,7 +13175,7 @@
         <v>7806531031</v>
       </c>
       <c r="D556" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E556" t="str">
         <v>ISO 9001:2015</v>
@@ -13198,16 +13198,16 @@
         <v>7806531031</v>
       </c>
       <c r="D557" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E557" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F557" t="str">
         <v>РФ</v>
       </c>
       <c r="G557">
-        <v>46164</v>
+        <v>46963</v>
       </c>
     </row>
     <row r="558">
@@ -13221,62 +13221,62 @@
         <v>7806531031</v>
       </c>
       <c r="D558" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E558" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F558" t="str">
         <v>РФ</v>
       </c>
       <c r="G558">
-        <v>46929</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Аксиома</v>
+        <v>Теком</v>
       </c>
       <c r="B559" t="str">
         <v>ООО</v>
       </c>
       <c r="C559" t="str">
-        <v>6382058258</v>
+        <v>7806531031</v>
       </c>
       <c r="D559" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E559" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F559" t="str">
         <v>РФ</v>
       </c>
       <c r="G559">
-        <v>46218</v>
+        <v>46929</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Россети Московский регион</v>
+        <v>Аксиома</v>
       </c>
       <c r="B560" t="str">
-        <v>ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C560" t="str">
-        <v>5036065113</v>
+        <v>6382058258</v>
       </c>
       <c r="D560" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E560" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F560" t="str">
         <v>РФ</v>
       </c>
       <c r="G560">
-        <v>47096</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="561">
@@ -13290,7 +13290,7 @@
         <v>5036065113</v>
       </c>
       <c r="D561" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E561" t="str">
         <v>ISO 14001:2015</v>
@@ -13304,39 +13304,39 @@
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Диммоторс</v>
+        <v>Россети Московский регион</v>
       </c>
       <c r="B562" t="str">
-        <v>ООО</v>
+        <v>ПАО</v>
       </c>
       <c r="C562" t="str">
-        <v>7300002788</v>
+        <v>5036065113</v>
       </c>
       <c r="D562" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E562" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F562" t="str">
         <v>РФ</v>
       </c>
       <c r="G562">
-        <v>46310</v>
+        <v>47096</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>МВ Кингисепп</v>
+        <v>Диммоторс</v>
       </c>
       <c r="B563" t="str">
         <v>ООО</v>
       </c>
       <c r="C563" t="str">
-        <v>4707023842</v>
+        <v>7300002788</v>
       </c>
       <c r="D563" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E563" t="str">
         <v>ISO 9001:2015</v>
@@ -13345,7 +13345,7 @@
         <v>РФ</v>
       </c>
       <c r="G563">
-        <v>46968</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="564">
@@ -13359,7 +13359,7 @@
         <v>4707023842</v>
       </c>
       <c r="D564" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E564" t="str">
         <v>ISO 9001:2015</v>
@@ -13382,16 +13382,16 @@
         <v>4707023842</v>
       </c>
       <c r="D565" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E565" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F565" t="str">
         <v>РФ</v>
       </c>
       <c r="G565">
-        <v>46592</v>
+        <v>46968</v>
       </c>
     </row>
     <row r="566">
@@ -13408,13 +13408,13 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E566" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F566" t="str">
         <v>РФ</v>
       </c>
       <c r="G566">
-        <v>46581</v>
+        <v>46592</v>
       </c>
     </row>
     <row r="567">
@@ -13428,16 +13428,16 @@
         <v>4707023842</v>
       </c>
       <c r="D567" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E567" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F567" t="str">
         <v>РФ</v>
       </c>
       <c r="G567">
-        <v>46156</v>
+        <v>46581</v>
       </c>
     </row>
     <row r="568">
@@ -13451,16 +13451,16 @@
         <v>4707023842</v>
       </c>
       <c r="D568" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E568" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F568" t="str">
         <v>РФ</v>
       </c>
       <c r="G568">
-        <v>46925</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="569">
@@ -13477,13 +13477,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E569" t="str">
-        <v>ГОСТ Р ИСО 14001-2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F569" t="str">
         <v>РФ</v>
       </c>
       <c r="G569">
-        <v>46882</v>
+        <v>46925</v>
       </c>
     </row>
     <row r="570">
@@ -13500,7 +13500,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E570" t="str">
-        <v>ГОСТ Р ИСО 45001-2020</v>
+        <v>ГОСТ Р ИСО 14001-2016</v>
       </c>
       <c r="F570" t="str">
         <v>РФ</v>
@@ -13511,48 +13511,48 @@
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>ПК Движение качества</v>
+        <v>МВ Кингисепп</v>
       </c>
       <c r="B571" t="str">
         <v>ООО</v>
       </c>
       <c r="C571" t="str">
-        <v>5252000576</v>
+        <v>4707023842</v>
       </c>
       <c r="D571" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E571" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 45001-2020</v>
       </c>
       <c r="F571" t="str">
         <v>РФ</v>
       </c>
       <c r="G571">
-        <v>46496</v>
+        <v>46882</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Кедр</v>
+        <v>ПК Движение качества</v>
       </c>
       <c r="B572" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C572" t="str">
-        <v>7415003234</v>
+        <v>5252000576</v>
       </c>
       <c r="D572" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E572" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F572" t="str">
         <v>РФ</v>
       </c>
       <c r="G572">
-        <v>46183</v>
+        <v>46496</v>
       </c>
     </row>
     <row r="573">
@@ -13566,16 +13566,16 @@
         <v>7415003234</v>
       </c>
       <c r="D573" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E573" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F573" t="str">
         <v>РФ</v>
       </c>
       <c r="G573">
-        <v>47010</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="574">
@@ -13589,53 +13589,53 @@
         <v>7415003234</v>
       </c>
       <c r="D574" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E574" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F574" t="str">
         <v>РФ</v>
       </c>
       <c r="G574">
-        <v>46980</v>
+        <v>47010</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Автомотозапчасть</v>
+        <v>Кедр</v>
       </c>
       <c r="B575" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C575" t="str">
-        <v>9909429837</v>
+        <v>7415003234</v>
       </c>
       <c r="D575" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E575" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F575" t="str">
         <v>РФ</v>
       </c>
       <c r="G575">
-        <v>46498</v>
+        <v>46980</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Бергауф Строительные Технологии</v>
+        <v>Автомотозапчасть</v>
       </c>
       <c r="B576" t="str">
         <v>ООО</v>
       </c>
       <c r="C576" t="str">
-        <v>6670045047</v>
+        <v>9909429837</v>
       </c>
       <c r="D576" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E576" t="str">
         <v>ISO 9001:2015</v>
@@ -13644,7 +13644,7 @@
         <v>РФ</v>
       </c>
       <c r="G576">
-        <v>47073</v>
+        <v>46498</v>
       </c>
     </row>
     <row r="577">
@@ -13658,7 +13658,7 @@
         <v>6670045047</v>
       </c>
       <c r="D577" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E577" t="str">
         <v>ISO 9001:2015</v>
@@ -13672,16 +13672,16 @@
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Асфальтобетонный завод №1</v>
+        <v>Бергауф Строительные Технологии</v>
       </c>
       <c r="B578" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C578" t="str">
-        <v>7804016807</v>
+        <v>6670045047</v>
       </c>
       <c r="D578" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E578" t="str">
         <v>ISO 9001:2015</v>
@@ -13690,7 +13690,7 @@
         <v>РФ</v>
       </c>
       <c r="G578">
-        <v>46644</v>
+        <v>47073</v>
       </c>
     </row>
     <row r="579">
@@ -13704,39 +13704,39 @@
         <v>7804016807</v>
       </c>
       <c r="D579" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E579" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F579" t="str">
         <v>РФ</v>
       </c>
       <c r="G579">
-        <v>46263</v>
+        <v>46644</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Ярославский технический углерод имени В.Ю. Орлова</v>
+        <v>Асфальтобетонный завод №1</v>
       </c>
       <c r="B580" t="str">
         <v>АО</v>
       </c>
       <c r="C580" t="str">
-        <v>7605000714</v>
+        <v>7804016807</v>
       </c>
       <c r="D580" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E580" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F580" t="str">
         <v>РФ</v>
       </c>
       <c r="G580">
-        <v>46663</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="581">
@@ -13750,16 +13750,16 @@
         <v>7605000714</v>
       </c>
       <c r="D581" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E581" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F581" t="str">
         <v>РФ</v>
       </c>
       <c r="G581">
-        <v>47013</v>
+        <v>46663</v>
       </c>
     </row>
     <row r="582">
@@ -13773,7 +13773,7 @@
         <v>7605000714</v>
       </c>
       <c r="D582" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E582" t="str">
         <v>ISO 14001:2015</v>
@@ -13787,36 +13787,36 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Межрегиональный центр стерилизационных технологий Акцентр</v>
+        <v>Ярославский технический углерод имени В.Ю. Орлова</v>
       </c>
       <c r="B583" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C583" t="str">
-        <v>3703048393</v>
+        <v>7605000714</v>
       </c>
       <c r="D583" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E583" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F583" t="str">
         <v>РФ</v>
       </c>
       <c r="G583">
-        <v>46653</v>
+        <v>47013</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>АКЦЕНТР СЕВЕРО-ЗАПАД</v>
+        <v>Межрегиональный центр стерилизационных технологий Акцентр</v>
       </c>
       <c r="B584" t="str">
         <v>ООО</v>
       </c>
       <c r="C584" t="str">
-        <v>7707370545</v>
+        <v>3703048393</v>
       </c>
       <c r="D584" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -13833,13 +13833,13 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>АКЦЕНТР ГРУПП</v>
+        <v>АКЦЕНТР СЕВЕРО-ЗАПАД</v>
       </c>
       <c r="B585" t="str">
         <v>ООО</v>
       </c>
       <c r="C585" t="str">
-        <v>7817085357</v>
+        <v>7707370545</v>
       </c>
       <c r="D585" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -13856,25 +13856,25 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Акцентр Технологии обработки</v>
+        <v>АКЦЕНТР ГРУПП</v>
       </c>
       <c r="B586" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C586" t="str">
-        <v>5027237550</v>
+        <v>7817085357</v>
       </c>
       <c r="D586" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E586" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F586" t="str">
         <v>РФ</v>
       </c>
       <c r="G586">
-        <v>47110</v>
+        <v>46653</v>
       </c>
     </row>
     <row r="587">
@@ -13888,7 +13888,7 @@
         <v>5027237550</v>
       </c>
       <c r="D587" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E587" t="str">
         <v>ISO 9001:2015</v>
@@ -13914,70 +13914,70 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E588" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F588" t="str">
         <v>РФ</v>
       </c>
       <c r="G588">
-        <v>47103</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>ПАНДЭКС</v>
+        <v>Акцентр Технологии обработки</v>
       </c>
       <c r="B589" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C589" t="str">
-        <v>7804660183</v>
+        <v>5027237550</v>
       </c>
       <c r="D589" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E589" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F589" t="str">
         <v>РФ</v>
       </c>
       <c r="G589">
-        <v>46590</v>
+        <v>47103</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Строительный торговый дом Петрович</v>
+        <v>ПАНДЭКС</v>
       </c>
       <c r="B590" t="str">
         <v>ООО</v>
       </c>
       <c r="C590" t="str">
-        <v>7802348846</v>
+        <v>7804660183</v>
       </c>
       <c r="D590" t="str">
-        <v>NABCB (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E590" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F590" t="str">
         <v>РФ</v>
       </c>
       <c r="G590">
-        <v>46365</v>
+        <v>46590</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Силта</v>
+        <v>Строительный торговый дом Петрович</v>
       </c>
       <c r="B591" t="str">
         <v>ООО</v>
       </c>
       <c r="C591" t="str">
-        <v>7816486638</v>
+        <v>7802348846</v>
       </c>
       <c r="D591" t="str">
         <v>NABCB (IAF)</v>
@@ -13994,16 +13994,16 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>ПСС</v>
+        <v>Силта</v>
       </c>
       <c r="B592" t="str">
         <v>ООО</v>
       </c>
       <c r="C592" t="str">
-        <v>7816592996</v>
+        <v>7816486638</v>
       </c>
       <c r="D592" t="str">
-        <v>TURKAK (Турция)</v>
+        <v>NABCB (IAF)</v>
       </c>
       <c r="E592" t="str">
         <v>ISO 9001:2015</v>
@@ -14012,21 +14012,21 @@
         <v>РФ</v>
       </c>
       <c r="G592">
-        <v>46366</v>
+        <v>46365</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>М.Н.Балтика</v>
+        <v>ПСС</v>
       </c>
       <c r="B593" t="str">
         <v>ООО</v>
       </c>
       <c r="C593" t="str">
-        <v>3907023326</v>
+        <v>7816592996</v>
       </c>
       <c r="D593" t="str">
-        <v>UKAS (IAF)</v>
+        <v>TURKAK (Турция)</v>
       </c>
       <c r="E593" t="str">
         <v>ISO 9001:2015</v>
@@ -14035,21 +14035,21 @@
         <v>РФ</v>
       </c>
       <c r="G593">
-        <v>46193</v>
+        <v>46366</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Арман</v>
+        <v>М.Н.Балтика</v>
       </c>
       <c r="B594" t="str">
         <v>ООО</v>
       </c>
       <c r="C594" t="str">
-        <v>7805298463</v>
+        <v>3907023326</v>
       </c>
       <c r="D594" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E594" t="str">
         <v>ISO 9001:2015</v>
@@ -14058,7 +14058,7 @@
         <v>РФ</v>
       </c>
       <c r="G594">
-        <v>46630</v>
+        <v>46193</v>
       </c>
     </row>
     <row r="595">
@@ -14072,7 +14072,7 @@
         <v>7805298463</v>
       </c>
       <c r="D595" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E595" t="str">
         <v>ISO 9001:2015</v>
@@ -14086,16 +14086,16 @@
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Армтел</v>
+        <v>Арман</v>
       </c>
       <c r="B596" t="str">
         <v>ООО</v>
       </c>
       <c r="C596" t="str">
-        <v>7810803665</v>
+        <v>7805298463</v>
       </c>
       <c r="D596" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E596" t="str">
         <v>ISO 9001:2015</v>
@@ -14104,7 +14104,7 @@
         <v>РФ</v>
       </c>
       <c r="G596">
-        <v>46260</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="597">
@@ -14118,7 +14118,7 @@
         <v>7810803665</v>
       </c>
       <c r="D597" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E597" t="str">
         <v>ISO 9001:2015</v>
@@ -14141,16 +14141,16 @@
         <v>7810803665</v>
       </c>
       <c r="D598" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E598" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F598" t="str">
         <v>РФ</v>
       </c>
       <c r="G598">
-        <v>46989</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="599">
@@ -14164,7 +14164,7 @@
         <v>7810803665</v>
       </c>
       <c r="D599" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E599" t="str">
         <v>ISO 45001:2018</v>
@@ -14178,25 +14178,25 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Armtel Engineering Private Limited</v>
+        <v>Армтел</v>
       </c>
       <c r="B600" t="str">
-        <v>LTD</v>
+        <v>ООО</v>
       </c>
       <c r="C600" t="str">
-        <v>09AAWCA1561B1ZO</v>
+        <v>7810803665</v>
       </c>
       <c r="D600" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E600" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F600" t="str">
-        <v>India</v>
+        <v>РФ</v>
       </c>
       <c r="G600">
-        <v>46282</v>
+        <v>46989</v>
       </c>
     </row>
     <row r="601">
@@ -19549,7 +19549,7 @@
         <v/>
       </c>
       <c r="D833" t="str">
-        <v>UKAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E833" t="str">
         <v>ISO 9001:2015</v>
@@ -19558,7 +19558,7 @@
         <v>Estonia</v>
       </c>
       <c r="G833">
-        <v>46043</v>
+        <v>47199</v>
       </c>
     </row>
     <row r="834">
@@ -19575,10 +19575,10 @@
         <v/>
       </c>
       <c r="E834" t="str">
-        <v>ISO 9001:2015</v>
+        <v/>
       </c>
       <c r="F834" t="str">
-        <v>Estonia</v>
+        <v/>
       </c>
       <c r="G834" t="str">
         <v/>
@@ -32236,9 +32236,55 @@
         <v>3/2/29</v>
       </c>
     </row>
+    <row r="1385">
+      <c r="A1385" t="str">
+        <v>Инновационный центр КАМАЗ</v>
+      </c>
+      <c r="B1385" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1385" t="str">
+        <v>7801204062</v>
+      </c>
+      <c r="D1385" t="str">
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+      </c>
+      <c r="E1385" t="str">
+        <v>ГОСТ Р ИСО 9001-2015</v>
+      </c>
+      <c r="F1385" t="str">
+        <v/>
+      </c>
+      <c r="G1385" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="str">
+        <v>Инновационный центр КАМАЗ</v>
+      </c>
+      <c r="B1386" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1386" t="str">
+        <v>7801204062</v>
+      </c>
+      <c r="D1386" t="str">
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+      </c>
+      <c r="E1386" t="str">
+        <v>ГОСТ Р 58139-2024</v>
+      </c>
+      <c r="F1386" t="str">
+        <v/>
+      </c>
+      <c r="G1386" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1384"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1386"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -15506,8 +15506,8 @@
       <c r="F657" t="str">
         <v>РФ</v>
       </c>
-      <c r="G657" t="str">
-        <v>08.21.2026</v>
+      <c r="G657">
+        <v>46254</v>
       </c>
     </row>
     <row r="658">
@@ -15529,8 +15529,8 @@
       <c r="F658" t="str">
         <v>РФ</v>
       </c>
-      <c r="G658" t="str">
-        <v>08.21.2026</v>
+      <c r="G658">
+        <v>46254</v>
       </c>
     </row>
     <row r="659">
@@ -15552,8 +15552,8 @@
       <c r="F659" t="str">
         <v>РФ</v>
       </c>
-      <c r="G659" t="str">
-        <v>08.21.2026</v>
+      <c r="G659">
+        <v>46254</v>
       </c>
     </row>
     <row r="660">
@@ -15576,7 +15576,7 @@
         <v>РФ</v>
       </c>
       <c r="G660">
-        <v>47331</v>
+        <v>47125</v>
       </c>
     </row>
     <row r="661">
@@ -15599,7 +15599,7 @@
         <v>РФ</v>
       </c>
       <c r="G661">
-        <v>47331</v>
+        <v>47125</v>
       </c>
     </row>
     <row r="662">
@@ -15622,7 +15622,7 @@
         <v>РФ</v>
       </c>
       <c r="G662">
-        <v>46911</v>
+        <v>46939</v>
       </c>
     </row>
     <row r="663">
@@ -15645,7 +15645,7 @@
         <v>РФ</v>
       </c>
       <c r="G663">
-        <v>46911</v>
+        <v>46939</v>
       </c>
     </row>
     <row r="664">
@@ -15668,7 +15668,7 @@
         <v>РФ</v>
       </c>
       <c r="G664">
-        <v>46880</v>
+        <v>46938</v>
       </c>
     </row>
     <row r="665">
@@ -15691,7 +15691,7 @@
         <v>РФ</v>
       </c>
       <c r="G665">
-        <v>46911</v>
+        <v>46939</v>
       </c>
     </row>
     <row r="666">
@@ -15805,8 +15805,8 @@
       <c r="F670" t="str">
         <v>CYPRUS</v>
       </c>
-      <c r="G670" t="str">
-        <v>08.19.2026</v>
+      <c r="G670">
+        <v>46252</v>
       </c>
     </row>
     <row r="671">
@@ -15828,8 +15828,8 @@
       <c r="F671" t="str">
         <v>CYPRUS</v>
       </c>
-      <c r="G671" t="str">
-        <v>08.19.2026</v>
+      <c r="G671">
+        <v>46252</v>
       </c>
     </row>
     <row r="672">
@@ -15851,8 +15851,8 @@
       <c r="F672" t="str">
         <v>CYPRUS</v>
       </c>
-      <c r="G672" t="str">
-        <v>08.19.2026</v>
+      <c r="G672">
+        <v>46252</v>
       </c>
     </row>
     <row r="673">
@@ -15920,8 +15920,8 @@
       <c r="F675" t="str">
         <v>РФ</v>
       </c>
-      <c r="G675" t="str">
-        <v>02.13.2026</v>
+      <c r="G675">
+        <v>46065</v>
       </c>
     </row>
     <row r="676">
@@ -15943,8 +15943,8 @@
       <c r="F676" t="str">
         <v>РФ</v>
       </c>
-      <c r="G676" t="str">
-        <v>04.13.2026</v>
+      <c r="G676">
+        <v>46124</v>
       </c>
     </row>
     <row r="677">
@@ -16289,7 +16289,7 @@
         <v>РФ</v>
       </c>
       <c r="G691">
-        <v>46205</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="692">
@@ -16357,8 +16357,8 @@
       <c r="F694" t="str">
         <v>РФ</v>
       </c>
-      <c r="G694" t="str">
-        <v>05.15.2027</v>
+      <c r="G694">
+        <v>46521</v>
       </c>
     </row>
     <row r="695">
@@ -17047,8 +17047,8 @@
       <c r="F724" t="str">
         <v>РФ</v>
       </c>
-      <c r="G724" t="str">
-        <v>07.13.2026</v>
+      <c r="G724">
+        <v>46215</v>
       </c>
     </row>
     <row r="725">
@@ -17347,8 +17347,8 @@
       <c r="F737" t="str">
         <v>РФ</v>
       </c>
-      <c r="G737" t="str">
-        <v>02.15.2026</v>
+      <c r="G737">
+        <v>46067</v>
       </c>
     </row>
     <row r="738">
@@ -17508,8 +17508,8 @@
       <c r="F744" t="str">
         <v>РФ</v>
       </c>
-      <c r="G744" t="str">
-        <v>05.16.2026</v>
+      <c r="G744">
+        <v>46157</v>
       </c>
     </row>
     <row r="745">
@@ -17577,8 +17577,8 @@
       <c r="F747" t="str">
         <v>РФ</v>
       </c>
-      <c r="G747" t="str">
-        <v>05.24.2026</v>
+      <c r="G747">
+        <v>46165</v>
       </c>
     </row>
     <row r="748">
@@ -17739,7 +17739,7 @@
         <v>РБ</v>
       </c>
       <c r="G754">
-        <v>46607</v>
+        <v>46606</v>
       </c>
     </row>
     <row r="755">
@@ -17762,7 +17762,7 @@
         <v>РБ</v>
       </c>
       <c r="G755">
-        <v>46607</v>
+        <v>46606</v>
       </c>
     </row>
     <row r="756">
@@ -18003,7 +18003,7 @@
         <v>АО</v>
       </c>
       <c r="C766" t="str">
-        <v>9.9114E+11</v>
+        <v>991140001226</v>
       </c>
       <c r="D766" t="str">
         <v>ESYD (IAF)</v>
@@ -18061,7 +18061,7 @@
         <v>KZ</v>
       </c>
       <c r="G768">
-        <v>46086</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="769">
@@ -18084,7 +18084,7 @@
         <v>KZ</v>
       </c>
       <c r="G769">
-        <v>46086</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="770">
@@ -18107,7 +18107,7 @@
         <v>KZ</v>
       </c>
       <c r="G770">
-        <v>46086</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="771">
@@ -19005,8 +19005,8 @@
       <c r="F809" t="str">
         <v>KZ</v>
       </c>
-      <c r="G809" t="str">
-        <v>07.18.2026</v>
+      <c r="G809">
+        <v>46220</v>
       </c>
     </row>
     <row r="810">
@@ -19868,7 +19868,7 @@
         <v>LLC</v>
       </c>
       <c r="C847" t="str">
-        <v>2.21612E+11</v>
+        <v>221611608288</v>
       </c>
       <c r="D847" t="str">
         <v>UKAS (IAF)</v>
@@ -20673,7 +20673,7 @@
         <v>LLC</v>
       </c>
       <c r="C882" t="str">
-        <v>3.4156E+11</v>
+        <v>341559908255</v>
       </c>
       <c r="D882" t="str">
         <v>UKAS (IAF)</v>
@@ -22731,8 +22731,8 @@
       <c r="F971" t="str">
         <v>РФ</v>
       </c>
-      <c r="G971" t="str">
-        <v>01.29.2028</v>
+      <c r="G971">
+        <v>46780</v>
       </c>
     </row>
     <row r="972">
@@ -23030,8 +23030,8 @@
       <c r="F984" t="str">
         <v>РФ</v>
       </c>
-      <c r="G984" t="str">
-        <v>02.27.2028</v>
+      <c r="G984">
+        <v>46809</v>
       </c>
     </row>
     <row r="985">
@@ -23054,7 +23054,7 @@
         <v>РФ</v>
       </c>
       <c r="G985">
-        <v>47090</v>
+        <v>46823</v>
       </c>
     </row>
     <row r="986">
@@ -26872,7 +26872,7 @@
         <v>РФ</v>
       </c>
       <c r="G1151">
-        <v>46454</v>
+        <v>46601</v>
       </c>
     </row>
     <row r="1152">
@@ -26894,8 +26894,8 @@
       <c r="F1152" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1152" t="str">
-        <v>09.19.2027</v>
+      <c r="G1152">
+        <v>46648</v>
       </c>
     </row>
     <row r="1153">
@@ -26917,8 +26917,8 @@
       <c r="F1153" t="str">
         <v>Lithuania</v>
       </c>
-      <c r="G1153" t="str">
-        <v>09.22.2027</v>
+      <c r="G1153">
+        <v>46651</v>
       </c>
     </row>
     <row r="1154">
@@ -26940,8 +26940,8 @@
       <c r="F1154" t="str">
         <v>Lithuania</v>
       </c>
-      <c r="G1154" t="str">
-        <v>05.24.2028</v>
+      <c r="G1154">
+        <v>46896</v>
       </c>
     </row>
     <row r="1155">
@@ -26963,8 +26963,8 @@
       <c r="F1155" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1155" t="str">
-        <v>05.26.2028</v>
+      <c r="G1155">
+        <v>46898</v>
       </c>
     </row>
     <row r="1156">
@@ -26986,8 +26986,8 @@
       <c r="F1156" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1156" t="str">
-        <v>12.29.2027</v>
+      <c r="G1156">
+        <v>46749</v>
       </c>
     </row>
     <row r="1157">
@@ -27009,8 +27009,8 @@
       <c r="F1157" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1157" t="str">
-        <v>12.29.2027</v>
+      <c r="G1157">
+        <v>46749</v>
       </c>
     </row>
     <row r="1158">
@@ -27032,8 +27032,8 @@
       <c r="F1158" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1158" t="str">
-        <v>12.29.2027</v>
+      <c r="G1158">
+        <v>46749</v>
       </c>
     </row>
     <row r="1159">
@@ -27055,8 +27055,8 @@
       <c r="F1159" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1159" t="str">
-        <v>12.29.2027</v>
+      <c r="G1159">
+        <v>46749</v>
       </c>
     </row>
     <row r="1160">
@@ -27079,7 +27079,7 @@
         <v>РФ</v>
       </c>
       <c r="G1160">
-        <v>46480</v>
+        <v>46449</v>
       </c>
     </row>
     <row r="1161">
@@ -27101,8 +27101,8 @@
       <c r="F1161" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1161" t="str">
-        <v>01.23.2028</v>
+      <c r="G1161">
+        <v>46774</v>
       </c>
     </row>
     <row r="1162">
@@ -27125,7 +27125,7 @@
         <v>РФ</v>
       </c>
       <c r="G1162">
-        <v>46789</v>
+        <v>46905</v>
       </c>
     </row>
     <row r="1163">
@@ -27148,7 +27148,7 @@
         <v>РФ</v>
       </c>
       <c r="G1163">
-        <v>46879</v>
+        <v>46908</v>
       </c>
     </row>
     <row r="1164">
@@ -27170,8 +27170,8 @@
       <c r="F1164" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1164" t="str">
-        <v>08.15.2028</v>
+      <c r="G1164">
+        <v>46979</v>
       </c>
     </row>
     <row r="1165">
@@ -27193,8 +27193,8 @@
       <c r="F1165" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1165" t="str">
-        <v>11.29.2028</v>
+      <c r="G1165">
+        <v>47085</v>
       </c>
     </row>
     <row r="1166">
@@ -27217,7 +27217,7 @@
         <v>РФ</v>
       </c>
       <c r="G1166">
-        <v>46054</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="1167">
@@ -27239,8 +27239,8 @@
       <c r="F1167" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1167" t="str">
-        <v>01.22.2027</v>
+      <c r="G1167">
+        <v>46408</v>
       </c>
     </row>
     <row r="1168">
@@ -27262,8 +27262,8 @@
       <c r="F1168" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1168" t="str">
-        <v>01.24.2027</v>
+      <c r="G1168">
+        <v>46410</v>
       </c>
     </row>
     <row r="1169">
@@ -27285,8 +27285,8 @@
       <c r="F1169" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1169" t="str">
-        <v>01.24.2027</v>
+      <c r="G1169">
+        <v>46410</v>
       </c>
     </row>
     <row r="1170">
@@ -27308,8 +27308,8 @@
       <c r="F1170" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1170" t="str">
-        <v>10.22.2026</v>
+      <c r="G1170">
+        <v>46316</v>
       </c>
     </row>
     <row r="1171">
@@ -27331,8 +27331,8 @@
       <c r="F1171" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1171" t="str">
-        <v>02.15.2027</v>
+      <c r="G1171">
+        <v>46432</v>
       </c>
     </row>
     <row r="1172">
@@ -27354,8 +27354,8 @@
       <c r="F1172" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1172" t="str">
-        <v>03.29.2026</v>
+      <c r="G1172">
+        <v>46109</v>
       </c>
     </row>
     <row r="1173">
@@ -27378,7 +27378,7 @@
         <v>РФ</v>
       </c>
       <c r="G1173">
-        <v>46695</v>
+        <v>46487</v>
       </c>
     </row>
     <row r="1174">
@@ -27400,8 +27400,8 @@
       <c r="F1174" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1174" t="str">
-        <v>05.23.2026</v>
+      <c r="G1174">
+        <v>46164</v>
       </c>
     </row>
     <row r="1175">
@@ -27424,7 +27424,7 @@
         <v>РФ</v>
       </c>
       <c r="G1175">
-        <v>46333</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="1176">
@@ -27447,7 +27447,7 @@
         <v>РФ</v>
       </c>
       <c r="G1176">
-        <v>46303</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="1177">
@@ -27469,8 +27469,8 @@
       <c r="F1177" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1177" t="str">
-        <v>08.31.2026</v>
+      <c r="G1177">
+        <v>46264</v>
       </c>
     </row>
     <row r="1178">
@@ -27492,8 +27492,8 @@
       <c r="F1178" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1178" t="str">
-        <v>10.31.2026</v>
+      <c r="G1178">
+        <v>46325</v>
       </c>
     </row>
     <row r="1179">
@@ -27515,8 +27515,8 @@
       <c r="F1179" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1179" t="str">
-        <v>07.26.2026</v>
+      <c r="G1179">
+        <v>46228</v>
       </c>
     </row>
     <row r="1180">
@@ -27538,8 +27538,8 @@
       <c r="F1180" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1180" t="str">
-        <v>05.29.2026</v>
+      <c r="G1180">
+        <v>46170</v>
       </c>
     </row>
     <row r="1181">
@@ -27561,8 +27561,8 @@
       <c r="F1181" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1181" t="str">
-        <v>03.24.2026</v>
+      <c r="G1181">
+        <v>46104</v>
       </c>
     </row>
     <row r="1182">
@@ -27585,7 +27585,7 @@
         <v>РФ</v>
       </c>
       <c r="G1182">
-        <v>46117</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="1183">
@@ -27608,7 +27608,7 @@
         <v>РФ</v>
       </c>
       <c r="G1183">
-        <v>46272</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="1184">
@@ -27630,8 +27630,8 @@
       <c r="F1184" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1184" t="str">
-        <v>06.27.2026</v>
+      <c r="G1184">
+        <v>46199</v>
       </c>
     </row>
     <row r="1185">
@@ -27653,8 +27653,8 @@
       <c r="F1185" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1185" t="str">
-        <v>09.25.2026</v>
+      <c r="G1185">
+        <v>46289</v>
       </c>
     </row>
     <row r="1186">
@@ -27676,8 +27676,8 @@
       <c r="F1186" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1186" t="str">
-        <v>09.19.2026</v>
+      <c r="G1186">
+        <v>46283</v>
       </c>
     </row>
     <row r="1187">
@@ -27699,8 +27699,8 @@
       <c r="F1187" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1187" t="str">
-        <v>09.19.2026</v>
+      <c r="G1187">
+        <v>46283</v>
       </c>
     </row>
     <row r="1188">
@@ -27722,8 +27722,8 @@
       <c r="F1188" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1188" t="str">
-        <v>10.16.2026</v>
+      <c r="G1188">
+        <v>46310</v>
       </c>
     </row>
     <row r="1189">
@@ -27745,8 +27745,8 @@
       <c r="F1189" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1189" t="str">
-        <v>07.25.2026</v>
+      <c r="G1189">
+        <v>46227</v>
       </c>
     </row>
     <row r="1190">
@@ -27791,8 +27791,8 @@
       <c r="F1191" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1191" t="str">
-        <v>08.13.2026</v>
+      <c r="G1191">
+        <v>46246</v>
       </c>
     </row>
     <row r="1192">
@@ -27815,7 +27815,7 @@
         <v>РФ</v>
       </c>
       <c r="G1192">
-        <v>46275</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1193">
@@ -27837,8 +27837,8 @@
       <c r="F1193" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1193" t="str">
-        <v>09.24.2026</v>
+      <c r="G1193">
+        <v>46288</v>
       </c>
     </row>
     <row r="1194">
@@ -27860,8 +27860,8 @@
       <c r="F1194" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1194" t="str">
-        <v>11.15.2026</v>
+      <c r="G1194">
+        <v>46340</v>
       </c>
     </row>
     <row r="1195">
@@ -27883,8 +27883,8 @@
       <c r="F1195" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1195" t="str">
-        <v>10.25.2026</v>
+      <c r="G1195">
+        <v>46319</v>
       </c>
     </row>
     <row r="1196">
@@ -27907,7 +27907,7 @@
         <v>РФ</v>
       </c>
       <c r="G1196">
-        <v>46296</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="1197">
@@ -27930,7 +27930,7 @@
         <v>РФ</v>
       </c>
       <c r="G1197">
-        <v>46479</v>
+        <v>46421</v>
       </c>
     </row>
     <row r="1198">
@@ -27952,8 +27952,8 @@
       <c r="F1198" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1198" t="str">
-        <v>10.31.2025</v>
+      <c r="G1198">
+        <v>45960</v>
       </c>
     </row>
     <row r="1199">
@@ -27975,8 +27975,8 @@
       <c r="F1199" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1199" t="str">
-        <v>01.22.2027</v>
+      <c r="G1199">
+        <v>46408</v>
       </c>
     </row>
     <row r="1200">
@@ -27998,8 +27998,8 @@
       <c r="F1200" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1200" t="str">
-        <v>12.19.2026</v>
+      <c r="G1200">
+        <v>46374</v>
       </c>
     </row>
     <row r="1201">
@@ -28022,7 +28022,7 @@
         <v>РФ</v>
       </c>
       <c r="G1201">
-        <v>46144</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="1202">
@@ -28045,7 +28045,7 @@
         <v>РФ</v>
       </c>
       <c r="G1202">
-        <v>46511</v>
+        <v>46481</v>
       </c>
     </row>
     <row r="1203">
@@ -28067,8 +28067,8 @@
       <c r="F1203" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1203" t="str">
-        <v>10.14.2027</v>
+      <c r="G1203">
+        <v>46673</v>
       </c>
     </row>
     <row r="1204">
@@ -28091,7 +28091,7 @@
         <v>РФ</v>
       </c>
       <c r="G1204">
-        <v>46573</v>
+        <v>46513</v>
       </c>
     </row>
     <row r="1205">
@@ -28113,8 +28113,8 @@
       <c r="F1205" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1205" t="str">
-        <v>07.30.2027</v>
+      <c r="G1205">
+        <v>46597</v>
       </c>
     </row>
     <row r="1206">
@@ -28136,8 +28136,8 @@
       <c r="F1206" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1206" t="str">
-        <v>07.25.2027</v>
+      <c r="G1206">
+        <v>46592</v>
       </c>
     </row>
     <row r="1207">
@@ -28160,7 +28160,7 @@
         <v>РФ</v>
       </c>
       <c r="G1207">
-        <v>46458</v>
+        <v>46723</v>
       </c>
     </row>
     <row r="1208">
@@ -28182,8 +28182,8 @@
       <c r="F1208" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1208" t="str">
-        <v>10.28.2026</v>
+      <c r="G1208">
+        <v>46322</v>
       </c>
     </row>
     <row r="1209">
@@ -28205,8 +28205,8 @@
       <c r="F1209" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1209" t="str">
-        <v>10.28.2026</v>
+      <c r="G1209">
+        <v>46322</v>
       </c>
     </row>
     <row r="1210">
@@ -28228,8 +28228,8 @@
       <c r="F1210" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1210" t="str">
-        <v>12.23.2027</v>
+      <c r="G1210">
+        <v>46743</v>
       </c>
     </row>
     <row r="1211">
@@ -28251,8 +28251,8 @@
       <c r="F1211" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1211" t="str">
-        <v>11.30.2026</v>
+      <c r="G1211">
+        <v>46355</v>
       </c>
     </row>
     <row r="1212">
@@ -28274,8 +28274,8 @@
       <c r="F1212" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1212" t="str">
-        <v>09.23.2027</v>
+      <c r="G1212">
+        <v>46652</v>
       </c>
     </row>
     <row r="1213">
@@ -28297,8 +28297,8 @@
       <c r="F1213" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1213" t="str">
-        <v>01.15.2028</v>
+      <c r="G1213">
+        <v>46766</v>
       </c>
     </row>
     <row r="1214">
@@ -28320,8 +28320,8 @@
       <c r="F1214" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1214" t="str">
-        <v>05.15.2028</v>
+      <c r="G1214">
+        <v>46887</v>
       </c>
     </row>
     <row r="1215">
@@ -28343,8 +28343,8 @@
       <c r="F1215" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1215" t="str">
-        <v>12.29.2027</v>
+      <c r="G1215">
+        <v>46749</v>
       </c>
     </row>
     <row r="1216">
@@ -28366,8 +28366,8 @@
       <c r="F1216" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1216" t="str">
-        <v>01.23.2028</v>
+      <c r="G1216">
+        <v>46774</v>
       </c>
     </row>
     <row r="1217">
@@ -28389,8 +28389,8 @@
       <c r="F1217" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1217" t="str">
-        <v>12.24.2026</v>
+      <c r="G1217">
+        <v>46379</v>
       </c>
     </row>
     <row r="1218">
@@ -28413,7 +28413,7 @@
         <v>РФ</v>
       </c>
       <c r="G1218">
-        <v>46338</v>
+        <v>46366</v>
       </c>
     </row>
     <row r="1219">
@@ -28424,7 +28424,7 @@
         <v>ТОО</v>
       </c>
       <c r="C1219" t="str">
-        <v>2.2104E+11</v>
+        <v>221040014631</v>
       </c>
       <c r="D1219" t="str">
         <v>ESYD (IAF)</v>
@@ -28436,7 +28436,7 @@
         <v>KZ</v>
       </c>
       <c r="G1219">
-        <v>46733</v>
+        <v>46732</v>
       </c>
     </row>
     <row r="1220">
@@ -28458,8 +28458,8 @@
       <c r="F1220" t="str">
         <v>KZ</v>
       </c>
-      <c r="G1220" t="str">
-        <v>12.26.2027</v>
+      <c r="G1220">
+        <v>46746</v>
       </c>
     </row>
     <row r="1221">
@@ -28481,8 +28481,8 @@
       <c r="F1221" t="str">
         <v>KZ</v>
       </c>
-      <c r="G1221" t="str">
-        <v>12.23.2027</v>
+      <c r="G1221">
+        <v>46743</v>
       </c>
     </row>
     <row r="1222">
@@ -28527,8 +28527,8 @@
       <c r="F1223" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1223" t="str">
-        <v>12.15.2028</v>
+      <c r="G1223">
+        <v>47101</v>
       </c>
     </row>
     <row r="1224">
@@ -28550,8 +28550,8 @@
       <c r="F1224" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1224" t="str">
-        <v>04.28.2028</v>
+      <c r="G1224">
+        <v>46870</v>
       </c>
     </row>
     <row r="1225">
@@ -28573,8 +28573,8 @@
       <c r="F1225" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1225" t="str">
-        <v>03.28.2027</v>
+      <c r="G1225">
+        <v>46473</v>
       </c>
     </row>
     <row r="1226">
@@ -28643,7 +28643,7 @@
         <v>UZ</v>
       </c>
       <c r="G1228">
-        <v>46816</v>
+        <v>46845</v>
       </c>
     </row>
     <row r="1229">
@@ -28665,8 +28665,8 @@
       <c r="F1229" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1229" t="str">
-        <v>03.26.2028</v>
+      <c r="G1229">
+        <v>46837</v>
       </c>
     </row>
     <row r="1230">
@@ -28688,8 +28688,8 @@
       <c r="F1230" t="str">
         <v>KZ</v>
       </c>
-      <c r="G1230" t="str">
-        <v>04.16.2028</v>
+      <c r="G1230">
+        <v>46858</v>
       </c>
     </row>
     <row r="1231">
@@ -28711,8 +28711,8 @@
       <c r="F1231" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1231" t="str">
-        <v>05.19.2028</v>
+      <c r="G1231">
+        <v>46891</v>
       </c>
     </row>
     <row r="1232">
@@ -28734,8 +28734,8 @@
       <c r="F1232" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1232" t="str">
-        <v>05.16.2028</v>
+      <c r="G1232">
+        <v>46888</v>
       </c>
     </row>
     <row r="1233">
@@ -28757,8 +28757,8 @@
       <c r="F1233" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1233" t="str">
-        <v>05.19.2028</v>
+      <c r="G1233">
+        <v>46891</v>
       </c>
     </row>
     <row r="1234">
@@ -28780,8 +28780,8 @@
       <c r="F1234" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1234" t="str">
-        <v>08.31.2028</v>
+      <c r="G1234">
+        <v>46995</v>
       </c>
     </row>
     <row r="1235">
@@ -28803,8 +28803,8 @@
       <c r="F1235" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1235" t="str">
-        <v>10.13.2028</v>
+      <c r="G1235">
+        <v>47038</v>
       </c>
     </row>
     <row r="1236">
@@ -28826,8 +28826,8 @@
       <c r="F1236" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1236" t="str">
-        <v>07.27.2028</v>
+      <c r="G1236">
+        <v>46960</v>
       </c>
     </row>
     <row r="1237">
@@ -28849,8 +28849,8 @@
       <c r="F1237" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1237" t="str">
-        <v>07.27.2028</v>
+      <c r="G1237">
+        <v>46960</v>
       </c>
     </row>
     <row r="1238">
@@ -28872,8 +28872,8 @@
       <c r="F1238" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1238" t="str">
-        <v>10.30.2028</v>
+      <c r="G1238">
+        <v>47055</v>
       </c>
     </row>
     <row r="1239">
@@ -28895,8 +28895,8 @@
       <c r="F1239" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1239" t="str">
-        <v>08.28.2028</v>
+      <c r="G1239">
+        <v>46992</v>
       </c>
     </row>
     <row r="1240">
@@ -28919,7 +28919,7 @@
         <v>UZ</v>
       </c>
       <c r="G1240">
-        <v>47005</v>
+        <v>47004</v>
       </c>
     </row>
     <row r="1241">
@@ -28941,8 +28941,8 @@
       <c r="F1241" t="str">
         <v>РБ</v>
       </c>
-      <c r="G1241" t="str">
-        <v>10.19.2028</v>
+      <c r="G1241">
+        <v>47044</v>
       </c>
     </row>
     <row r="1242">
@@ -28964,8 +28964,8 @@
       <c r="F1242" t="str">
         <v>РБ</v>
       </c>
-      <c r="G1242" t="str">
-        <v>10.19.2028</v>
+      <c r="G1242">
+        <v>47044</v>
       </c>
     </row>
     <row r="1243">
@@ -29056,8 +29056,8 @@
       <c r="F1246" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1246" t="str">
-        <v>10.29.2028</v>
+      <c r="G1246">
+        <v>47054</v>
       </c>
     </row>
     <row r="1247">
@@ -29079,8 +29079,8 @@
       <c r="F1247" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1247" t="str">
-        <v>09.16.2028</v>
+      <c r="G1247">
+        <v>47011</v>
       </c>
     </row>
     <row r="1248">
@@ -29102,8 +29102,8 @@
       <c r="F1248" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1248" t="str">
-        <v>11.17.2028</v>
+      <c r="G1248">
+        <v>47073</v>
       </c>
     </row>
     <row r="1249">
@@ -29125,8 +29125,8 @@
       <c r="F1249" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1249" t="str">
-        <v>11.16.2028</v>
+      <c r="G1249">
+        <v>47072</v>
       </c>
     </row>
     <row r="1250">
@@ -29148,8 +29148,8 @@
       <c r="F1250" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1250" t="str">
-        <v>10.28.2028</v>
+      <c r="G1250">
+        <v>47053</v>
       </c>
     </row>
     <row r="1251">
@@ -29171,8 +29171,8 @@
       <c r="F1251" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1251" t="str">
-        <v>10.29.2028</v>
+      <c r="G1251">
+        <v>47054</v>
       </c>
     </row>
     <row r="1252">
@@ -29194,8 +29194,8 @@
       <c r="F1252" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1252" t="str">
-        <v>10.30.2028</v>
+      <c r="G1252">
+        <v>47055</v>
       </c>
     </row>
     <row r="1253">
@@ -29218,7 +29218,7 @@
         <v>РФ</v>
       </c>
       <c r="G1253">
-        <v>46883</v>
+        <v>47030</v>
       </c>
     </row>
     <row r="1254">
@@ -29240,8 +29240,8 @@
       <c r="F1254" t="str">
         <v>РБ</v>
       </c>
-      <c r="G1254" t="str">
-        <v>10.22.2028</v>
+      <c r="G1254">
+        <v>47047</v>
       </c>
     </row>
     <row r="1255">
@@ -29263,8 +29263,8 @@
       <c r="F1255" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1255" t="str">
-        <v>12.19.2028</v>
+      <c r="G1255">
+        <v>47105</v>
       </c>
     </row>
     <row r="1256">
@@ -29287,7 +29287,7 @@
         <v>РФ</v>
       </c>
       <c r="G1256">
-        <v>45759</v>
+        <v>45994</v>
       </c>
     </row>
     <row r="1257">
@@ -29310,7 +29310,7 @@
         <v>KZ</v>
       </c>
       <c r="G1257">
-        <v>46572</v>
+        <v>46483</v>
       </c>
     </row>
     <row r="1258">
@@ -29333,7 +29333,7 @@
         <v>UZ</v>
       </c>
       <c r="G1258">
-        <v>46912</v>
+        <v>46970</v>
       </c>
     </row>
     <row r="1259">
@@ -29356,7 +29356,7 @@
         <v>UZ</v>
       </c>
       <c r="G1259">
-        <v>47064</v>
+        <v>46944</v>
       </c>
     </row>
     <row r="1260">
@@ -29378,8 +29378,8 @@
       <c r="F1260" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1260" t="str">
-        <v>09.20.2028</v>
+      <c r="G1260">
+        <v>47015</v>
       </c>
     </row>
     <row r="1261">
@@ -29401,8 +29401,8 @@
       <c r="F1261" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1261" t="str">
-        <v>08.20.2027</v>
+      <c r="G1261">
+        <v>46618</v>
       </c>
     </row>
     <row r="1262">
@@ -29424,8 +29424,8 @@
       <c r="F1262" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1262" t="str">
-        <v>09.25.2027</v>
+      <c r="G1262">
+        <v>46654</v>
       </c>
     </row>
     <row r="1263">
@@ -29448,7 +29448,7 @@
         <v>РФ</v>
       </c>
       <c r="G1263">
-        <v>46609</v>
+        <v>46667</v>
       </c>
     </row>
     <row r="1264">
@@ -29470,8 +29470,8 @@
       <c r="F1264" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1264" t="str">
-        <v>10.23.2027</v>
+      <c r="G1264">
+        <v>46682</v>
       </c>
     </row>
     <row r="1265">
@@ -29493,8 +29493,8 @@
       <c r="F1265" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1265" t="str">
-        <v>11.28.2027</v>
+      <c r="G1265">
+        <v>46718</v>
       </c>
     </row>
     <row r="1266">
@@ -29517,7 +29517,7 @@
         <v>РФ</v>
       </c>
       <c r="G1266">
-        <v>46672</v>
+        <v>46730</v>
       </c>
     </row>
     <row r="1267">
@@ -29539,8 +29539,8 @@
       <c r="F1267" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1267" t="str">
-        <v>03.13.2028</v>
+      <c r="G1267">
+        <v>46824</v>
       </c>
     </row>
     <row r="1268">
@@ -29562,8 +29562,8 @@
       <c r="F1268" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1268" t="str">
-        <v>04.13.2028</v>
+      <c r="G1268">
+        <v>46855</v>
       </c>
     </row>
     <row r="1269">
@@ -29585,8 +29585,8 @@
       <c r="F1269" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1269" t="str">
-        <v>05.13.2027</v>
+      <c r="G1269">
+        <v>46519</v>
       </c>
     </row>
     <row r="1270">
@@ -29608,8 +29608,8 @@
       <c r="F1270" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1270" t="str">
-        <v>05.27.2028</v>
+      <c r="G1270">
+        <v>46899</v>
       </c>
     </row>
     <row r="1271">
@@ -29631,8 +29631,8 @@
       <c r="F1271" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1271" t="str">
-        <v>05.27.2028</v>
+      <c r="G1271">
+        <v>46899</v>
       </c>
     </row>
     <row r="1272">
@@ -29654,8 +29654,8 @@
       <c r="F1272" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1272" t="str">
-        <v>06.17.2028</v>
+      <c r="G1272">
+        <v>46920</v>
       </c>
     </row>
     <row r="1273">
@@ -29677,8 +29677,8 @@
       <c r="F1273" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1273" t="str">
-        <v>06.30.2028</v>
+      <c r="G1273">
+        <v>46933</v>
       </c>
     </row>
     <row r="1274">
@@ -29700,8 +29700,8 @@
       <c r="F1274" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1274" t="str">
-        <v>12.24.2028</v>
+      <c r="G1274">
+        <v>47110</v>
       </c>
     </row>
     <row r="1275">
@@ -29724,7 +29724,7 @@
         <v>РФ</v>
       </c>
       <c r="G1275">
-        <v>46424</v>
+        <v>46539</v>
       </c>
     </row>
     <row r="1276">
@@ -29747,7 +29747,7 @@
         <v>РФ</v>
       </c>
       <c r="G1276">
-        <v>46605</v>
+        <v>46545</v>
       </c>
     </row>
     <row r="1277">
@@ -29770,7 +29770,7 @@
         <v>РФ</v>
       </c>
       <c r="G1277">
-        <v>46212</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="1278">
@@ -29792,8 +29792,8 @@
       <c r="F1278" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1278" t="str">
-        <v>08.31.2026</v>
+      <c r="G1278">
+        <v>46264</v>
       </c>
     </row>
     <row r="1279">
@@ -29815,8 +29815,8 @@
       <c r="F1279" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1279" t="str">
-        <v>02.25.2028</v>
+      <c r="G1279">
+        <v>46807</v>
       </c>
     </row>
     <row r="1280">
@@ -29838,8 +29838,8 @@
       <c r="F1280" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1280" t="str">
-        <v>09.13.2026</v>
+      <c r="G1280">
+        <v>46277</v>
       </c>
     </row>
     <row r="1281">
@@ -29862,7 +29862,7 @@
         <v>РФ</v>
       </c>
       <c r="G1281">
-        <v>46117</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="1282">
@@ -29884,8 +29884,8 @@
       <c r="F1282" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1282" t="str">
-        <v>03.24.2027</v>
+      <c r="G1282">
+        <v>46469</v>
       </c>
     </row>
     <row r="1283">
@@ -29907,8 +29907,8 @@
       <c r="F1283" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1283" t="str">
-        <v>06.29.2027</v>
+      <c r="G1283">
+        <v>46566</v>
       </c>
     </row>
     <row r="1284">
@@ -29930,8 +29930,8 @@
       <c r="F1284" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1284" t="str">
-        <v>10.13.2027</v>
+      <c r="G1284">
+        <v>46672</v>
       </c>
     </row>
     <row r="1285" xml:space="preserve">
@@ -29954,8 +29954,8 @@
       <c r="F1285" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1285" t="str">
-        <v>09.23.2027</v>
+      <c r="G1285">
+        <v>46652</v>
       </c>
     </row>
     <row r="1286" xml:space="preserve">
@@ -29978,8 +29978,8 @@
       <c r="F1286" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1286" t="str">
-        <v>11.18.2027</v>
+      <c r="G1286">
+        <v>46708</v>
       </c>
     </row>
     <row r="1287">
@@ -30001,8 +30001,8 @@
       <c r="F1287" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1287" t="str">
-        <v>12.15.2028</v>
+      <c r="G1287">
+        <v>47101</v>
       </c>
     </row>
     <row r="1288">
@@ -30024,8 +30024,8 @@
       <c r="F1288" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1288" t="str">
-        <v>02.27.2028</v>
+      <c r="G1288">
+        <v>46809</v>
       </c>
     </row>
     <row r="1289">
@@ -30047,8 +30047,8 @@
       <c r="F1289" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1289" t="str">
-        <v>05.13.2027</v>
+      <c r="G1289">
+        <v>46519</v>
       </c>
     </row>
     <row r="1290">
@@ -30070,8 +30070,8 @@
       <c r="F1290" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1290" t="str">
-        <v>06.23.2028</v>
+      <c r="G1290">
+        <v>46926</v>
       </c>
     </row>
     <row r="1291">
@@ -30093,8 +30093,8 @@
       <c r="F1291" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1291" t="str">
-        <v>05.25.2028</v>
+      <c r="G1291">
+        <v>46897</v>
       </c>
     </row>
     <row r="1292">
@@ -30116,8 +30116,8 @@
       <c r="F1292" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1292" t="str">
-        <v>02.21.2026</v>
+      <c r="G1292">
+        <v>46073</v>
       </c>
     </row>
     <row r="1293">
@@ -30139,8 +30139,8 @@
       <c r="F1293" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1293" t="str">
-        <v>10.13.2028</v>
+      <c r="G1293">
+        <v>47038</v>
       </c>
     </row>
     <row r="1294">
@@ -30163,7 +30163,7 @@
         <v>РФ</v>
       </c>
       <c r="G1294">
-        <v>46244</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="1295">
@@ -30231,8 +30231,8 @@
       <c r="F1297" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1297" t="str">
-        <v>09.29.2028</v>
+      <c r="G1297">
+        <v>47024</v>
       </c>
     </row>
     <row r="1298">
@@ -30254,8 +30254,8 @@
       <c r="F1298" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1298" t="str">
-        <v>09.29.2028</v>
+      <c r="G1298">
+        <v>47024</v>
       </c>
     </row>
     <row r="1299">
@@ -30277,8 +30277,8 @@
       <c r="F1299" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1299" t="str">
-        <v>09.29.2028</v>
+      <c r="G1299">
+        <v>47024</v>
       </c>
     </row>
     <row r="1300">
@@ -30300,8 +30300,8 @@
       <c r="F1300" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1300" t="str">
-        <v>09.29.2028</v>
+      <c r="G1300">
+        <v>47024</v>
       </c>
     </row>
     <row r="1301">
@@ -30323,8 +30323,8 @@
       <c r="F1301" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1301" t="str">
-        <v>09.29.2028</v>
+      <c r="G1301">
+        <v>47024</v>
       </c>
     </row>
     <row r="1302">
@@ -30346,8 +30346,8 @@
       <c r="F1302" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1302" t="str">
-        <v>09.29.2028</v>
+      <c r="G1302">
+        <v>47024</v>
       </c>
     </row>
     <row r="1303">
@@ -30369,8 +30369,8 @@
       <c r="F1303" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1303" t="str">
-        <v>09.27.2028</v>
+      <c r="G1303">
+        <v>47022</v>
       </c>
     </row>
     <row r="1304">
@@ -30392,8 +30392,8 @@
       <c r="F1304" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1304" t="str">
-        <v>09.27.2028</v>
+      <c r="G1304">
+        <v>47022</v>
       </c>
     </row>
     <row r="1305">
@@ -30415,8 +30415,8 @@
       <c r="F1305" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1305" t="str">
-        <v>09.27.2028</v>
+      <c r="G1305">
+        <v>47022</v>
       </c>
     </row>
     <row r="1306">
@@ -30968,7 +30968,7 @@
         <v>РФ</v>
       </c>
       <c r="G1329">
-        <v>47007</v>
+        <v>47065</v>
       </c>
     </row>
     <row r="1330">
@@ -30991,7 +30991,7 @@
         <v>РФ</v>
       </c>
       <c r="G1330">
-        <v>47007</v>
+        <v>47065</v>
       </c>
     </row>
     <row r="1331">
@@ -31014,7 +31014,7 @@
         <v>РФ</v>
       </c>
       <c r="G1331">
-        <v>46486</v>
+        <v>46633</v>
       </c>
     </row>
     <row r="1332">
@@ -31037,7 +31037,7 @@
         <v>РФ</v>
       </c>
       <c r="G1332">
-        <v>46486</v>
+        <v>46633</v>
       </c>
     </row>
     <row r="1333">
@@ -31060,7 +31060,7 @@
         <v>РФ</v>
       </c>
       <c r="G1333">
-        <v>46486</v>
+        <v>46633</v>
       </c>
     </row>
     <row r="1334">
@@ -31083,7 +31083,7 @@
         <v>РФ</v>
       </c>
       <c r="G1334">
-        <v>46486</v>
+        <v>46633</v>
       </c>
     </row>
     <row r="1335">
@@ -31105,8 +31105,8 @@
       <c r="F1335" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1335" t="str">
-        <v>08.21.2026</v>
+      <c r="G1335">
+        <v>46254</v>
       </c>
     </row>
     <row r="1336">
@@ -31128,8 +31128,8 @@
       <c r="F1336" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1336" t="str">
-        <v>10.13.2028</v>
+      <c r="G1336">
+        <v>47038</v>
       </c>
     </row>
     <row r="1337">
@@ -31151,8 +31151,8 @@
       <c r="F1337" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1337" t="str">
-        <v>10.13.2028</v>
+      <c r="G1337">
+        <v>47038</v>
       </c>
     </row>
     <row r="1338">
@@ -31174,8 +31174,8 @@
       <c r="F1338" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1338" t="str">
-        <v>10.28.2026</v>
+      <c r="G1338">
+        <v>46322</v>
       </c>
     </row>
     <row r="1339">
@@ -31198,7 +31198,7 @@
         <v>РФ</v>
       </c>
       <c r="G1339">
-        <v>46946</v>
+        <v>47093</v>
       </c>
     </row>
     <row r="1340">
@@ -31220,8 +31220,8 @@
       <c r="F1340" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1340" t="str">
-        <v>11.16.2028</v>
+      <c r="G1340">
+        <v>47072</v>
       </c>
     </row>
     <row r="1341">
@@ -31243,8 +31243,8 @@
       <c r="F1341" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1341" t="str">
-        <v>12.25.2028</v>
+      <c r="G1341">
+        <v>47111</v>
       </c>
     </row>
     <row r="1342">
@@ -31266,8 +31266,8 @@
       <c r="F1342" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1342" t="str">
-        <v>12.25.2028</v>
+      <c r="G1342">
+        <v>47111</v>
       </c>
     </row>
     <row r="1343">
@@ -31289,8 +31289,8 @@
       <c r="F1343" t="str">
         <v>UZ</v>
       </c>
-      <c r="G1343" t="str">
-        <v>12.23.2028</v>
+      <c r="G1343">
+        <v>47109</v>
       </c>
     </row>
     <row r="1344">
@@ -31312,8 +31312,8 @@
       <c r="F1344" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1344" t="str">
-        <v>11.17.2028</v>
+      <c r="G1344">
+        <v>47073</v>
       </c>
     </row>
     <row r="1345">
@@ -31336,7 +31336,7 @@
         <v>РФ</v>
       </c>
       <c r="G1345">
-        <v>46672</v>
+        <v>46730</v>
       </c>
     </row>
     <row r="1346">
@@ -31359,7 +31359,7 @@
         <v>РФ</v>
       </c>
       <c r="G1346">
-        <v>46882</v>
+        <v>47000</v>
       </c>
     </row>
     <row r="1347">
@@ -32118,7 +32118,7 @@
         <v>РФ</v>
       </c>
       <c r="G1379">
-        <v>46943</v>
+        <v>47002</v>
       </c>
     </row>
     <row r="1380">
@@ -32141,7 +32141,7 @@
         <v>РБ</v>
       </c>
       <c r="G1380">
-        <v>47151</v>
+        <v>47150</v>
       </c>
     </row>
     <row r="1381">
@@ -32164,7 +32164,7 @@
         <v>РБ</v>
       </c>
       <c r="G1381">
-        <v>47151</v>
+        <v>47150</v>
       </c>
     </row>
     <row r="1382">
@@ -32187,7 +32187,7 @@
         <v>РФ</v>
       </c>
       <c r="G1382">
-        <v>47152</v>
+        <v>47178</v>
       </c>
     </row>
     <row r="1383">
@@ -32210,7 +32210,7 @@
         <v>РФ</v>
       </c>
       <c r="G1383">
-        <v>47152</v>
+        <v>47178</v>
       </c>
     </row>
     <row r="1384">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -12471,7 +12471,7 @@
         <v>РФ</v>
       </c>
       <c r="G525">
-        <v>46102</v>
+        <v>46444</v>
       </c>
     </row>
     <row r="526">
@@ -31149,7 +31149,7 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1337" t="str">
-        <v>РФ</v>
+        <v/>
       </c>
       <c r="G1337">
         <v>47039</v>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -16450,7 +16450,7 @@
         <v>РФ</v>
       </c>
       <c r="G698">
-        <v>46058</v>
+        <v>46422</v>
       </c>
     </row>
     <row r="699">
@@ -16467,13 +16467,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E699" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F699" t="str">
         <v>РФ</v>
       </c>
       <c r="G699">
-        <v>46115</v>
+        <v>47209</v>
       </c>
     </row>
     <row r="700">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -8400,7 +8400,7 @@
         <v>РФ</v>
       </c>
       <c r="G348">
-        <v>46052</v>
+        <v>46413</v>
       </c>
     </row>
     <row r="349">
@@ -9941,7 +9941,7 @@
         <v>РФ</v>
       </c>
       <c r="G415">
-        <v>46115</v>
+        <v>46451</v>
       </c>
     </row>
     <row r="416">
@@ -31818,8 +31818,8 @@
       <c r="F1366" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1366" t="str">
-        <v/>
+      <c r="G1366">
+        <v>47213</v>
       </c>
     </row>
     <row r="1367">
@@ -31836,13 +31836,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1367" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1367" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1367" t="str">
-        <v/>
+      <c r="G1367">
+        <v>47213</v>
       </c>
     </row>
     <row r="1368">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -12062,7 +12062,7 @@
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>ОАО "Борисовский завод автоагрегатов" - БЗА</v>
+        <v>"Борисовский завод агрегатов" - БЗА</v>
       </c>
       <c r="B508" t="str">
         <v>ОАО</v>
@@ -12085,7 +12085,7 @@
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>мэнергокомплект</v>
+        <v>"Борисовский завод агрегатов" - БЗА</v>
       </c>
       <c r="B509" t="str">
         <v>ОАО</v>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>ОАО "Борисовский завод автоагрегатов" - БЗА</v>
+        <v>"Борисовский завод агрегатов" - БЗА</v>
       </c>
       <c r="B510" t="str">
         <v>ОАО</v>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -32437,7 +32437,7 @@
         <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1393" t="str">
-        <v/>
+        <v>РФ</v>
       </c>
       <c r="G1393" t="str">
         <v/>
@@ -32460,7 +32460,7 @@
         <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1394" t="str">
-        <v/>
+        <v>РФ</v>
       </c>
       <c r="G1394" t="str">
         <v/>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1408"/>
+  <dimension ref="A1:G1411"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -32169,7 +32169,7 @@
     </row>
     <row r="1382">
       <c r="A1382" t="str">
-        <v>"КраМЗ"</v>
+        <v>Красноярский металлургический завод ("КраМЗ")</v>
       </c>
       <c r="B1382" t="str">
         <v>ООО</v>
@@ -32192,7 +32192,7 @@
     </row>
     <row r="1383">
       <c r="A1383" t="str">
-        <v>"КраМЗ"</v>
+        <v>Красноярский металлургический завод ("КраМЗ")</v>
       </c>
       <c r="B1383" t="str">
         <v>ООО</v>
@@ -32201,73 +32201,73 @@
         <v>2465043748</v>
       </c>
       <c r="D1383" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1383" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1383" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1383" t="str">
-        <v/>
+      <c r="G1383">
+        <v>47110</v>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="str">
-        <v>"ЭЛАРА"</v>
+        <v>Красноярский металлургический завод ("КраМЗ")</v>
       </c>
       <c r="B1384" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1384" t="str">
-        <v>2129017646</v>
+        <v>2465043748</v>
       </c>
       <c r="D1384" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1384" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1384" t="str">
         <v>РФ</v>
       </c>
       <c r="G1384">
-        <v>46980</v>
+        <v>47242</v>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="str">
-        <v>"ЭЛАРА"</v>
+        <v>Красноярский металлургический завод ("КраМЗ")</v>
       </c>
       <c r="B1385" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1385" t="str">
-        <v>2129017646</v>
+        <v>2465043748</v>
       </c>
       <c r="D1385" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1385" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1385" t="str">
         <v>РФ</v>
       </c>
       <c r="G1385">
-        <v>46574</v>
+        <v>47242</v>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="str">
-        <v>"Газпром проектирование"</v>
+        <v>"ЭЛАРА"</v>
       </c>
       <c r="B1386" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1386" t="str">
-        <v>0560022871</v>
+        <v>2129017646</v>
       </c>
       <c r="D1386" t="str">
         <v>ESYD (IAF)</v>
@@ -32279,18 +32279,18 @@
         <v>РФ</v>
       </c>
       <c r="G1386">
-        <v>47003</v>
+        <v>46980</v>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="str">
-        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
+        <v>"ЭЛАРА"</v>
       </c>
       <c r="B1387" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1387" t="str">
-        <v>190918566</v>
+        <v>2129017646</v>
       </c>
       <c r="D1387" t="str">
         <v>ESYD (IAF)</v>
@@ -32299,79 +32299,79 @@
         <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1387" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1387">
-        <v>47151</v>
+        <v>46574</v>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="str">
-        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
+        <v>"Газпром проектирование"</v>
       </c>
       <c r="B1388" t="str">
         <v>ООО</v>
       </c>
       <c r="C1388" t="str">
-        <v>190918566</v>
+        <v>0560022871</v>
       </c>
       <c r="D1388" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1388" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1388" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1388">
-        <v>47151</v>
+        <v>47003</v>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="str">
-        <v>Аутолайт Технолоджи</v>
+        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
       </c>
       <c r="B1389" t="str">
         <v>ООО</v>
       </c>
       <c r="C1389" t="str">
-        <v>6230025811</v>
+        <v>190918566</v>
       </c>
       <c r="D1389" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1389" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1389" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1389">
-        <v>47179</v>
+        <v>47151</v>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="str">
-        <v>Аутолайт Технолоджи</v>
+        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
       </c>
       <c r="B1390" t="str">
         <v>ООО</v>
       </c>
       <c r="C1390" t="str">
-        <v>6230025811</v>
+        <v>190918566</v>
       </c>
       <c r="D1390" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1390" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1390" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1390">
-        <v>47229</v>
+        <v>47151</v>
       </c>
     </row>
     <row r="1391">
@@ -32385,16 +32385,16 @@
         <v>6230025811</v>
       </c>
       <c r="D1391" t="str">
-        <v>EADAS</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1391" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1391" t="str">
         <v>РФ</v>
       </c>
       <c r="G1391">
-        <v>46430</v>
+        <v>47179</v>
       </c>
     </row>
     <row r="1392">
@@ -32411,76 +32411,76 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1392" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1392" t="str">
         <v>РФ</v>
       </c>
       <c r="G1392">
-        <v>47179</v>
+        <v>47229</v>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="str">
-        <v>Инновационный центр КАМАЗ</v>
+        <v>Аутолайт Технолоджи</v>
       </c>
       <c r="B1393" t="str">
         <v>ООО</v>
       </c>
       <c r="C1393" t="str">
-        <v>7801204062</v>
+        <v>6230025811</v>
       </c>
       <c r="D1393" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1393" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1393" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1393" t="str">
-        <v/>
+      <c r="G1393">
+        <v>46430</v>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="str">
-        <v>Инновационный центр КАМАЗ</v>
+        <v>Аутолайт Технолоджи</v>
       </c>
       <c r="B1394" t="str">
         <v>ООО</v>
       </c>
       <c r="C1394" t="str">
-        <v>7801204062</v>
+        <v>6230025811</v>
       </c>
       <c r="D1394" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1394" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1394" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1394" t="str">
-        <v/>
+      <c r="G1394">
+        <v>47179</v>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="str">
-        <v>АкваПромМеталл</v>
+        <v>Инновационный центр КАМАЗ</v>
       </c>
       <c r="B1395" t="str">
         <v>ООО</v>
       </c>
       <c r="C1395" t="str">
-        <v/>
+        <v>7801204062</v>
       </c>
       <c r="D1395" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1395" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1395" t="str">
         <v>РФ</v>
@@ -32491,19 +32491,19 @@
     </row>
     <row r="1396">
       <c r="A1396" t="str">
-        <v>ПО "ХСК"</v>
+        <v>Инновационный центр КАМАЗ</v>
       </c>
       <c r="B1396" t="str">
         <v>ООО</v>
       </c>
       <c r="C1396" t="str">
-        <v/>
+        <v>7801204062</v>
       </c>
       <c r="D1396" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1396" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1396" t="str">
         <v>РФ</v>
@@ -32514,7 +32514,7 @@
     </row>
     <row r="1397">
       <c r="A1397" t="str">
-        <v>ПО "ХСК"</v>
+        <v>АкваПромМеталл</v>
       </c>
       <c r="B1397" t="str">
         <v>ООО</v>
@@ -32523,7 +32523,7 @@
         <v/>
       </c>
       <c r="D1397" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1397" t="str">
         <v>ISO 9001:2015</v>
@@ -32537,7 +32537,7 @@
     </row>
     <row r="1398">
       <c r="A1398" t="str">
-        <v>СЗЭМО ЗВ ТДМ</v>
+        <v>ПО "ХСК"</v>
       </c>
       <c r="B1398" t="str">
         <v>ООО</v>
@@ -32546,7 +32546,7 @@
         <v/>
       </c>
       <c r="D1398" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1398" t="str">
         <v>ISO 9001:2015</v>
@@ -32560,7 +32560,7 @@
     </row>
     <row r="1399">
       <c r="A1399" t="str">
-        <v>РМЗ ГХК</v>
+        <v>ПО "ХСК"</v>
       </c>
       <c r="B1399" t="str">
         <v>ООО</v>
@@ -32569,7 +32569,7 @@
         <v/>
       </c>
       <c r="D1399" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1399" t="str">
         <v>ISO 9001:2015</v>
@@ -32583,7 +32583,7 @@
     </row>
     <row r="1400">
       <c r="A1400" t="str">
-        <v>ЦДЭС</v>
+        <v>СЗЭМО ЗВ ТДМ</v>
       </c>
       <c r="B1400" t="str">
         <v>ООО</v>
@@ -32606,7 +32606,7 @@
     </row>
     <row r="1401">
       <c r="A1401" t="str">
-        <v>УЗСА</v>
+        <v>РМЗ ГХК</v>
       </c>
       <c r="B1401" t="str">
         <v>ООО</v>
@@ -32615,7 +32615,7 @@
         <v/>
       </c>
       <c r="D1401" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1401" t="str">
         <v>ISO 9001:2015</v>
@@ -32629,7 +32629,7 @@
     </row>
     <row r="1402">
       <c r="A1402" t="str">
-        <v>УЗСА</v>
+        <v>ЦДЭС</v>
       </c>
       <c r="B1402" t="str">
         <v>ООО</v>
@@ -32638,7 +32638,7 @@
         <v/>
       </c>
       <c r="D1402" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1402" t="str">
         <v>ISO 9001:2015</v>
@@ -32652,7 +32652,7 @@
     </row>
     <row r="1403">
       <c r="A1403" t="str">
-        <v>УЗТПА</v>
+        <v>УЗСА</v>
       </c>
       <c r="B1403" t="str">
         <v>ООО</v>
@@ -32675,7 +32675,7 @@
     </row>
     <row r="1404">
       <c r="A1404" t="str">
-        <v>УЗТПА</v>
+        <v>УЗСА</v>
       </c>
       <c r="B1404" t="str">
         <v>ООО</v>
@@ -32698,16 +32698,16 @@
     </row>
     <row r="1405">
       <c r="A1405" t="str">
-        <v>НПО Спецматериалов</v>
+        <v>УЗТПА</v>
       </c>
       <c r="B1405" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1405" t="str">
         <v/>
       </c>
       <c r="D1405" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1405" t="str">
         <v>ISO 9001:2015</v>
@@ -32721,7 +32721,7 @@
     </row>
     <row r="1406">
       <c r="A1406" t="str">
-        <v>ТПТ</v>
+        <v>УЗТПА</v>
       </c>
       <c r="B1406" t="str">
         <v>ООО</v>
@@ -32744,16 +32744,16 @@
     </row>
     <row r="1407">
       <c r="A1407" t="str">
-        <v>СЗМА СПИК</v>
+        <v>НПО Спецматериалов</v>
       </c>
       <c r="B1407" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1407" t="str">
         <v/>
       </c>
       <c r="D1407" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1407" t="str">
         <v>ISO 9001:2015</v>
@@ -32767,16 +32767,16 @@
     </row>
     <row r="1408">
       <c r="A1408" t="str">
-        <v>ТоМеЗ</v>
+        <v>ТПТ</v>
       </c>
       <c r="B1408" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1408" t="str">
         <v/>
       </c>
       <c r="D1408" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1408" t="str">
         <v>ISO 9001:2015</v>
@@ -32788,9 +32788,78 @@
         <v/>
       </c>
     </row>
+    <row r="1409">
+      <c r="A1409" t="str">
+        <v>СЗМА СПИК</v>
+      </c>
+      <c r="B1409" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1409" t="str">
+        <v/>
+      </c>
+      <c r="D1409" t="str">
+        <v>O’ZAKK (IAF)</v>
+      </c>
+      <c r="E1409" t="str">
+        <v>ISO 9001:2015</v>
+      </c>
+      <c r="F1409" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1409" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="str">
+        <v>ТоМеЗ</v>
+      </c>
+      <c r="B1410" t="str">
+        <v>АО</v>
+      </c>
+      <c r="C1410" t="str">
+        <v/>
+      </c>
+      <c r="D1410" t="str">
+        <v>O’ZAKK (IAF)</v>
+      </c>
+      <c r="E1410" t="str">
+        <v>ISO 9001:2015</v>
+      </c>
+      <c r="F1410" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1410" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="str">
+        <v>Красноярский металлургический завод</v>
+      </c>
+      <c r="B1411" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1411" t="str">
+        <v/>
+      </c>
+      <c r="D1411" t="str">
+        <v/>
+      </c>
+      <c r="E1411" t="str">
+        <v/>
+      </c>
+      <c r="F1411" t="str">
+        <v/>
+      </c>
+      <c r="G1411" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1408"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1406"/>
+  <dimension ref="A1:G1400"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -29798,25 +29798,25 @@
     </row>
     <row r="1279">
       <c r="A1279" t="str">
-        <v>Петроаналитика</v>
+        <v>ЛЮМЭКС</v>
       </c>
       <c r="B1279" t="str">
         <v>ООО</v>
       </c>
       <c r="C1279" t="str">
-        <v>7805523334</v>
+        <v>7816033050</v>
       </c>
       <c r="D1279" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>EGAC (QME)</v>
       </c>
       <c r="E1279" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1279" t="str">
         <v>РФ</v>
       </c>
       <c r="G1279">
-        <v>45830</v>
+        <v>46540</v>
       </c>
     </row>
     <row r="1280">
@@ -29830,39 +29830,39 @@
         <v>7816033050</v>
       </c>
       <c r="D1280" t="str">
-        <v>EGAC (QME)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1280" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1280" t="str">
         <v>РФ</v>
       </c>
       <c r="G1280">
-        <v>46540</v>
+        <v>46546</v>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="str">
-        <v>ЛЮМЭКС</v>
+        <v>Химсталькомплект (ХСК)</v>
       </c>
       <c r="B1281" t="str">
         <v>ООО</v>
       </c>
       <c r="C1281" t="str">
-        <v>7816033050</v>
+        <v>7422046285</v>
       </c>
       <c r="D1281" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EGAC (QME)</v>
       </c>
       <c r="E1281" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1281" t="str">
         <v>РФ</v>
       </c>
       <c r="G1281">
-        <v>46546</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="1282">
@@ -29876,39 +29876,39 @@
         <v>7422046285</v>
       </c>
       <c r="D1282" t="str">
-        <v>EGAC (QME)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1282" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1282" t="str">
         <v>РФ</v>
       </c>
       <c r="G1282">
-        <v>46265</v>
+        <v>46808</v>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="str">
-        <v>Химсталькомплект (ХСК)</v>
+        <v>Группа компаний "ЛЮМЭКС Инструментс"</v>
       </c>
       <c r="B1283" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1283" t="str">
-        <v>7422046285</v>
+        <v>7801472150</v>
       </c>
       <c r="D1283" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>JASANZ (SAI Global)</v>
       </c>
       <c r="E1283" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1283" t="str">
         <v>РФ</v>
       </c>
       <c r="G1283">
-        <v>46808</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="1284">
@@ -29922,27 +29922,27 @@
         <v>7801472150</v>
       </c>
       <c r="D1284" t="str">
-        <v>JASANZ (SAI Global)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1284" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1284" t="str">
         <v>РФ</v>
       </c>
       <c r="G1284">
-        <v>46278</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="str">
-        <v>Группа компаний "ЛЮМЭКС Инструментс"</v>
+        <v>ЗВЕЗДА-Комплексные энергетические решения</v>
       </c>
       <c r="B1285" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1285" t="str">
-        <v>7801472150</v>
+        <v>7811717360</v>
       </c>
       <c r="D1285" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -29954,18 +29954,18 @@
         <v>РФ</v>
       </c>
       <c r="G1285">
-        <v>46146</v>
+        <v>46470</v>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="str">
-        <v>ЗВЕЗДА-Комплексные энергетические решения</v>
+        <v>СИЭЛ</v>
       </c>
       <c r="B1286" t="str">
         <v>ООО</v>
       </c>
       <c r="C1286" t="str">
-        <v>7811717360</v>
+        <v>7810742885</v>
       </c>
       <c r="D1286" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -29977,41 +29977,41 @@
         <v>РФ</v>
       </c>
       <c r="G1286">
-        <v>46470</v>
+        <v>46673</v>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="str">
-        <v>ЗВЕЗДА-Комплексные энергетические решения</v>
+        <v>Газпром диагностика</v>
       </c>
       <c r="B1287" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1287" t="str">
-        <v>7811717360</v>
+        <v>4345083100</v>
       </c>
       <c r="D1287" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1287" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1287" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1287" t="str">
-        <v/>
+      <c r="G1287">
+        <v>47102</v>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="str">
-        <v>СИЭЛ</v>
+        <v>БП Морские Системы</v>
       </c>
       <c r="B1288" t="str">
         <v>ООО</v>
       </c>
       <c r="C1288" t="str">
-        <v>7810742885</v>
+        <v>7801726319</v>
       </c>
       <c r="D1288" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -30023,21 +30023,21 @@
         <v>РФ</v>
       </c>
       <c r="G1288">
-        <v>46673</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="str">
-        <v>Газпром диагностика</v>
+        <v>Статус</v>
       </c>
       <c r="B1289" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1289" t="str">
-        <v>4345083100</v>
+        <v>7413025257</v>
       </c>
       <c r="D1289" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1289" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -30046,21 +30046,21 @@
         <v>РФ</v>
       </c>
       <c r="G1289">
-        <v>47102</v>
+        <v>46927</v>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="str">
-        <v>БП Морские Системы</v>
+        <v>ТЭК-Консалтинг</v>
       </c>
       <c r="B1290" t="str">
         <v>ООО</v>
       </c>
       <c r="C1290" t="str">
-        <v>7801726319</v>
+        <v>7804185393</v>
       </c>
       <c r="D1290" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1290" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -30069,18 +30069,18 @@
         <v>РФ</v>
       </c>
       <c r="G1290">
-        <v>46520</v>
+        <v>46898</v>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="str">
-        <v>Статус</v>
+        <v>ГидроТехАтом</v>
       </c>
       <c r="B1291" t="str">
         <v>ООО</v>
       </c>
       <c r="C1291" t="str">
-        <v>7413025257</v>
+        <v>1831123035</v>
       </c>
       <c r="D1291" t="str">
         <v>РОСАТОМРЕГИСТР</v>
@@ -30092,21 +30092,21 @@
         <v>РФ</v>
       </c>
       <c r="G1291">
-        <v>46927</v>
+        <v>47168</v>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="str">
-        <v>ТЭК-Консалтинг</v>
+        <v>НАМИ инновационные компоненты</v>
       </c>
       <c r="B1292" t="str">
         <v>ООО</v>
       </c>
       <c r="C1292" t="str">
-        <v>7804185393</v>
+        <v>6330056813</v>
       </c>
       <c r="D1292" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1292" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -30115,87 +30115,87 @@
         <v>РФ</v>
       </c>
       <c r="G1292">
-        <v>46898</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="str">
-        <v>ГидроТехАтом</v>
+        <v>НАМИ инновационные компоненты</v>
       </c>
       <c r="B1293" t="str">
         <v>ООО</v>
       </c>
       <c r="C1293" t="str">
-        <v>1831123035</v>
+        <v>6330056813</v>
       </c>
       <c r="D1293" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>EADAS</v>
       </c>
       <c r="E1293" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1293" t="str">
         <v>РФ</v>
       </c>
       <c r="G1293">
-        <v>47168</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="str">
-        <v>НАМИ инновационные компоненты</v>
+        <v>Европейский мужчина и его здоровье</v>
       </c>
       <c r="B1294" t="str">
         <v>ООО</v>
       </c>
       <c r="C1294" t="str">
-        <v>6330056813</v>
+        <v>7811447106</v>
       </c>
       <c r="D1294" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1294" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1294" t="str">
         <v>РФ</v>
       </c>
       <c r="G1294">
-        <v>47039</v>
+        <v>47115</v>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="str">
-        <v>НАМИ инновационные компоненты</v>
+        <v>Европейский мужчина и его здоровье</v>
       </c>
       <c r="B1295" t="str">
         <v>ООО</v>
       </c>
       <c r="C1295" t="str">
-        <v>6330056813</v>
+        <v>7811447106</v>
       </c>
       <c r="D1295" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1295" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1295" t="str">
         <v>РФ</v>
       </c>
       <c r="G1295">
-        <v>46303</v>
+        <v>47115</v>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="str">
-        <v>Европейский мужчина и его здоровье</v>
+        <v>Газпром Линде Инжиниринг (ГЛ Инжиниринг)</v>
       </c>
       <c r="B1296" t="str">
         <v>ООО</v>
       </c>
       <c r="C1296" t="str">
-        <v>7811447106</v>
+        <v>0266023912</v>
       </c>
       <c r="D1296" t="str">
         <v>ESYD (IAF)</v>
@@ -30207,18 +30207,18 @@
         <v>РФ</v>
       </c>
       <c r="G1296">
-        <v>47115</v>
+        <v>47025</v>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="str">
-        <v>Европейский мужчина и его здоровье</v>
+        <v>Газпром Линде Инжиниринг (ГЛ Инжиниринг)</v>
       </c>
       <c r="B1297" t="str">
         <v>ООО</v>
       </c>
       <c r="C1297" t="str">
-        <v>7811447106</v>
+        <v>0266023912</v>
       </c>
       <c r="D1297" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -30230,7 +30230,7 @@
         <v>РФ</v>
       </c>
       <c r="G1297">
-        <v>47115</v>
+        <v>47025</v>
       </c>
     </row>
     <row r="1298">
@@ -30247,7 +30247,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1298" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1298" t="str">
         <v>РФ</v>
@@ -30270,7 +30270,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1299" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1299" t="str">
         <v>РФ</v>
@@ -30293,7 +30293,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1300" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1300" t="str">
         <v>РФ</v>
@@ -30316,7 +30316,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1301" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1301" t="str">
         <v>РФ</v>
@@ -30336,16 +30336,16 @@
         <v>0266023912</v>
       </c>
       <c r="D1302" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1302" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1302" t="str">
         <v>РФ</v>
       </c>
       <c r="G1302">
-        <v>47025</v>
+        <v>47023</v>
       </c>
     </row>
     <row r="1303">
@@ -30359,16 +30359,16 @@
         <v>0266023912</v>
       </c>
       <c r="D1303" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1303" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ГОСТ Р ИСО 14001-2016</v>
       </c>
       <c r="F1303" t="str">
         <v>РФ</v>
       </c>
       <c r="G1303">
-        <v>47025</v>
+        <v>47023</v>
       </c>
     </row>
     <row r="1304">
@@ -30385,7 +30385,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1304" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р ИСО 45001-2020</v>
       </c>
       <c r="F1304" t="str">
         <v>РФ</v>
@@ -30405,62 +30405,62 @@
         <v>0266023912</v>
       </c>
       <c r="D1305" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1305" t="str">
-        <v>ГОСТ Р ИСО 14001-2016</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1305" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1305">
-        <v>47023</v>
+      <c r="G1305" t="str">
+        <v/>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="str">
-        <v>Газпром Линде Инжиниринг (ГЛ Инжиниринг)</v>
+        <v>Сарштедт</v>
       </c>
       <c r="B1306" t="str">
         <v>ООО</v>
       </c>
       <c r="C1306" t="str">
-        <v>0266023912</v>
+        <v>6037008575</v>
       </c>
       <c r="D1306" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>NABCB (IAF)</v>
       </c>
       <c r="E1306" t="str">
-        <v>ГОСТ Р ИСО 45001-2020</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1306" t="str">
         <v>РФ</v>
       </c>
       <c r="G1306">
-        <v>47023</v>
+        <v>47076</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="str">
-        <v>Газпром Линде Инжиниринг (ГЛ Инжиниринг)</v>
+        <v>Сарштедт</v>
       </c>
       <c r="B1307" t="str">
         <v>ООО</v>
       </c>
       <c r="C1307" t="str">
-        <v>0266023912</v>
+        <v>6037008575</v>
       </c>
       <c r="D1307" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1307" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1307" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1307" t="str">
-        <v/>
+      <c r="G1307">
+        <v>47076</v>
       </c>
     </row>
     <row r="1308">
@@ -30474,62 +30474,62 @@
         <v>6037008575</v>
       </c>
       <c r="D1308" t="str">
-        <v>NABCB (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1308" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1308" t="str">
         <v>РФ</v>
       </c>
       <c r="G1308">
-        <v>47076</v>
+        <v>46748</v>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="str">
-        <v>Сарштедт</v>
+        <v>Бора Пак</v>
       </c>
       <c r="B1309" t="str">
         <v>ООО</v>
       </c>
       <c r="C1309" t="str">
-        <v>6037008575</v>
+        <v>6315626314</v>
       </c>
       <c r="D1309" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1309" t="str">
-        <v>ISO 13485:2016</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1309" t="str">
         <v>РФ</v>
       </c>
       <c r="G1309">
-        <v>47076</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="str">
-        <v>Сарштедт</v>
+        <v>Бора Пак</v>
       </c>
       <c r="B1310" t="str">
         <v>ООО</v>
       </c>
       <c r="C1310" t="str">
-        <v>6037008575</v>
+        <v>6315626314</v>
       </c>
       <c r="D1310" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1310" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1310" t="str">
         <v>РФ</v>
       </c>
       <c r="G1310">
-        <v>46748</v>
+        <v>47086</v>
       </c>
     </row>
     <row r="1311">
@@ -30543,50 +30543,50 @@
         <v>6315626314</v>
       </c>
       <c r="D1311" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1311" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1311" t="str">
         <v>РФ</v>
       </c>
       <c r="G1311">
-        <v>46274</v>
+        <v>47086</v>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="str">
-        <v>Бора Пак</v>
+        <v>Научно-производственный центр Горноспасательные технологии</v>
       </c>
       <c r="B1312" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1312" t="str">
-        <v>6315626314</v>
+        <v>6672163631</v>
       </c>
       <c r="D1312" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1312" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1312" t="str">
         <v>РФ</v>
       </c>
       <c r="G1312">
-        <v>47086</v>
+        <v>47070</v>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="str">
-        <v>Бора Пак</v>
+        <v>Научно-производственный центр Горноспасательные технологии</v>
       </c>
       <c r="B1313" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1313" t="str">
-        <v>6315626314</v>
+        <v>6672163631</v>
       </c>
       <c r="D1313" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -30598,12 +30598,12 @@
         <v>РФ</v>
       </c>
       <c r="G1313">
-        <v>47086</v>
+        <v>47070</v>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="str">
-        <v>Научно-производственный центр Горноспасательные технологии</v>
+        <v>Научно-производственный центр "Горноспасательные технологии"</v>
       </c>
       <c r="B1314" t="str">
         <v>АО</v>
@@ -30612,30 +30612,30 @@
         <v>6672163631</v>
       </c>
       <c r="D1314" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1314" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1314" t="str">
         <v>РФ</v>
       </c>
       <c r="G1314">
-        <v>47070</v>
+        <v>47100</v>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="str">
-        <v>Научно-производственный центр Горноспасательные технологии</v>
+        <v>Джойсон Сейфти Системс Рус</v>
       </c>
       <c r="B1315" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1315" t="str">
-        <v>6672163631</v>
+        <v>7325097407</v>
       </c>
       <c r="D1315" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1315" t="str">
         <v>ISO 9001:2015</v>
@@ -30644,30 +30644,30 @@
         <v>РФ</v>
       </c>
       <c r="G1315">
-        <v>47070</v>
+        <v>47097</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="str">
-        <v>Научно-производственный центр "Горноспасательные технологии"</v>
+        <v>Джойсон Сейфти Системс Рус</v>
       </c>
       <c r="B1316" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1316" t="str">
-        <v>6672163631</v>
+        <v>7325097407</v>
       </c>
       <c r="D1316" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1316" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1316" t="str">
         <v>РФ</v>
       </c>
       <c r="G1316">
-        <v>47100</v>
+        <v>47097</v>
       </c>
     </row>
     <row r="1317">
@@ -30684,13 +30684,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1317" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1317" t="str">
         <v>РФ</v>
       </c>
       <c r="G1317">
-        <v>47097</v>
+        <v>47166</v>
       </c>
     </row>
     <row r="1318">
@@ -30707,13 +30707,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1318" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1318" t="str">
         <v>РФ</v>
       </c>
       <c r="G1318">
-        <v>47097</v>
+        <v>47166</v>
       </c>
     </row>
     <row r="1319">
@@ -30730,7 +30730,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1319" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1319" t="str">
         <v>РФ</v>
@@ -30753,7 +30753,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1320" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1320" t="str">
         <v>РФ</v>
@@ -30773,16 +30773,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1321" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1321" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1321" t="str">
         <v>РФ</v>
       </c>
       <c r="G1321">
-        <v>47166</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1322">
@@ -30796,16 +30796,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1322" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1322" t="str">
-        <v>ISO 45001:2018</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1322" t="str">
         <v>РФ</v>
       </c>
       <c r="G1322">
-        <v>47166</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="1323">
@@ -30822,7 +30822,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1323" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1323" t="str">
         <v>РФ</v>
@@ -30833,62 +30833,62 @@
     </row>
     <row r="1324">
       <c r="A1324" t="str">
-        <v>Джойсон Сейфти Системс Рус</v>
+        <v>ТЛТ ПРОФ</v>
       </c>
       <c r="B1324" t="str">
         <v>ООО</v>
       </c>
       <c r="C1324" t="str">
-        <v>7325097407</v>
+        <v>6321273480</v>
       </c>
       <c r="D1324" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1324" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1324" t="str">
         <v>РФ</v>
       </c>
       <c r="G1324">
-        <v>46178</v>
+        <v>46844</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="str">
-        <v>Джойсон Сейфти Системс Рус</v>
+        <v>ТЛТ ПРОФ</v>
       </c>
       <c r="B1325" t="str">
         <v>ООО</v>
       </c>
       <c r="C1325" t="str">
-        <v>7325097407</v>
+        <v>6321273480</v>
       </c>
       <c r="D1325" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1325" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1325" t="str">
         <v>РФ</v>
       </c>
       <c r="G1325">
-        <v>46982</v>
+        <v>46844</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="str">
-        <v>ТЛТ ПРОФ</v>
+        <v>ТрансАвтоСвет</v>
       </c>
       <c r="B1326" t="str">
         <v>ООО</v>
       </c>
       <c r="C1326" t="str">
-        <v>6321273480</v>
+        <v>7328075313</v>
       </c>
       <c r="D1326" t="str">
-        <v>ESYD (IAF)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1326" t="str">
         <v>ISO 9001:2015</v>
@@ -30897,18 +30897,18 @@
         <v>РФ</v>
       </c>
       <c r="G1326">
-        <v>46844</v>
+        <v>47046</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="str">
-        <v>ТЛТ ПРОФ</v>
+        <v>ТрансАвтоСвет</v>
       </c>
       <c r="B1327" t="str">
         <v>ООО</v>
       </c>
       <c r="C1327" t="str">
-        <v>6321273480</v>
+        <v>7328075313</v>
       </c>
       <c r="D1327" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -30920,21 +30920,21 @@
         <v>РФ</v>
       </c>
       <c r="G1327">
-        <v>46844</v>
+        <v>47046</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="str">
-        <v>ТрансАвтоСвет</v>
+        <v>Борский стекольный завод</v>
       </c>
       <c r="B1328" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1328" t="str">
-        <v>7328075313</v>
+        <v>5246002261</v>
       </c>
       <c r="D1328" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1328" t="str">
         <v>ISO 9001:2015</v>
@@ -30943,18 +30943,18 @@
         <v>РФ</v>
       </c>
       <c r="G1328">
-        <v>47046</v>
+        <v>47066</v>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="str">
-        <v>ТрансАвтоСвет</v>
+        <v>Борский стекольный завод</v>
       </c>
       <c r="B1329" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1329" t="str">
-        <v>7328075313</v>
+        <v>5246002261</v>
       </c>
       <c r="D1329" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -30966,7 +30966,7 @@
         <v>РФ</v>
       </c>
       <c r="G1329">
-        <v>47046</v>
+        <v>47066</v>
       </c>
     </row>
     <row r="1330">
@@ -30983,13 +30983,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1330" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1330" t="str">
         <v>РФ</v>
       </c>
       <c r="G1330">
-        <v>47066</v>
+        <v>46634</v>
       </c>
     </row>
     <row r="1331">
@@ -31006,13 +31006,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1331" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1331" t="str">
         <v>РФ</v>
       </c>
       <c r="G1331">
-        <v>47066</v>
+        <v>46634</v>
       </c>
     </row>
     <row r="1332">
@@ -31029,7 +31029,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1332" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1332" t="str">
         <v>РФ</v>
@@ -31052,7 +31052,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1333" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1333" t="str">
         <v>РФ</v>
@@ -31072,329 +31072,329 @@
         <v>5246002261</v>
       </c>
       <c r="D1334" t="str">
-        <v>ESYD (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1334" t="str">
-        <v>ISO 45001:2018</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1334" t="str">
         <v>РФ</v>
       </c>
       <c r="G1334">
-        <v>46634</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="str">
-        <v>Борский стекольный завод</v>
+        <v>ПРОМЭНЕРГОКОМПЛЕКТ</v>
       </c>
       <c r="B1335" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1335" t="str">
-        <v>5246002261</v>
+        <v>5262222391</v>
       </c>
       <c r="D1335" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1335" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1335" t="str">
         <v>РФ</v>
       </c>
       <c r="G1335">
-        <v>46634</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="str">
-        <v>Борский стекольный завод</v>
+        <v>ПРОМЭНЕРГОКОМПЛЕКТ</v>
       </c>
       <c r="B1336" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1336" t="str">
-        <v>5246002261</v>
+        <v>5262222391</v>
       </c>
       <c r="D1336" t="str">
-        <v>EADAS</v>
+        <v>ECA (APAC)</v>
       </c>
       <c r="E1336" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1336" t="str">
         <v>РФ</v>
       </c>
       <c r="G1336">
-        <v>46255</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="str">
-        <v>ПРОМЭНЕРГОКОМПЛЕКТ</v>
+        <v>НПФ "Евродеталь"</v>
       </c>
       <c r="B1337" t="str">
         <v>ООО</v>
       </c>
       <c r="C1337" t="str">
-        <v>5262222391</v>
+        <v>1834054140</v>
       </c>
       <c r="D1337" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1337" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1337" t="str">
         <v>РФ</v>
       </c>
       <c r="G1337">
-        <v>47039</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="str">
-        <v>ПРОМЭНЕРГОКОМПЛЕКТ</v>
+        <v>АйСиЭл Системные Технологии</v>
       </c>
       <c r="B1338" t="str">
         <v>ООО</v>
       </c>
       <c r="C1338" t="str">
-        <v>5262222391</v>
+        <v>1615012203</v>
       </c>
       <c r="D1338" t="str">
-        <v>ECA (APAC)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1338" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1338" t="str">
         <v>РФ</v>
       </c>
       <c r="G1338">
-        <v>47039</v>
+        <v>47094</v>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="str">
-        <v>НПФ "Евродеталь"</v>
+        <v>МЕДИН-Н</v>
       </c>
       <c r="B1339" t="str">
         <v>ООО</v>
       </c>
       <c r="C1339" t="str">
-        <v>1834054140</v>
+        <v>6662112620</v>
       </c>
       <c r="D1339" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1339" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1339" t="str">
         <v>РФ</v>
       </c>
       <c r="G1339">
-        <v>46323</v>
+        <v>47073</v>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="str">
-        <v>АйСиЭл Системные Технологии</v>
+        <v>МЕТТЕХ</v>
       </c>
       <c r="B1340" t="str">
         <v>ООО</v>
       </c>
       <c r="C1340" t="str">
-        <v>1615012203</v>
+        <v>7806591143</v>
       </c>
       <c r="D1340" t="str">
-        <v>ESYD (IAF)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1340" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1340" t="str">
         <v>РФ</v>
       </c>
       <c r="G1340">
-        <v>47094</v>
+        <v>47112</v>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="str">
-        <v>МЕДИН-Н</v>
+        <v>МЕТТЕХ</v>
       </c>
       <c r="B1341" t="str">
         <v>ООО</v>
       </c>
       <c r="C1341" t="str">
-        <v>6662112620</v>
+        <v>7806591143</v>
       </c>
       <c r="D1341" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1341" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1341" t="str">
         <v>РФ</v>
       </c>
       <c r="G1341">
-        <v>47073</v>
+        <v>47112</v>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="str">
-        <v>МЕТТЕХ</v>
+        <v>Birinchi rezinotexnika zavodi</v>
       </c>
       <c r="B1342" t="str">
-        <v>ООО</v>
+        <v>ИП ООО</v>
       </c>
       <c r="C1342" t="str">
-        <v>7806591143</v>
+        <v>301938570</v>
       </c>
       <c r="D1342" t="str">
-        <v>IAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1342" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1342" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1342">
-        <v>47112</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="str">
-        <v>МЕТТЕХ</v>
+        <v>Тюменский завод ЗСГ</v>
       </c>
       <c r="B1343" t="str">
         <v>ООО</v>
       </c>
       <c r="C1343" t="str">
-        <v>7806591143</v>
+        <v>7203412108</v>
       </c>
       <c r="D1343" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1343" t="str">
-        <v>ISO 9001:2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1343" t="str">
         <v>РФ</v>
       </c>
       <c r="G1343">
-        <v>47112</v>
+        <v>47074</v>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="str">
-        <v>Birinchi rezinotexnika zavodi</v>
+        <v>Электронмаш Инжиниринг</v>
       </c>
       <c r="B1344" t="str">
-        <v>ИП ООО</v>
+        <v>ООО</v>
       </c>
       <c r="C1344" t="str">
-        <v>301938570</v>
+        <v>7802428812</v>
       </c>
       <c r="D1344" t="str">
-        <v>ESYD (IAF)</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1344" t="str">
-        <v>ISO 45001:2018</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1344" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1344">
-        <v>47110</v>
+        <v>46731</v>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="str">
-        <v>Тюменский завод ЗСГ</v>
+        <v>Нефтегаздеталь</v>
       </c>
       <c r="B1345" t="str">
         <v>ООО</v>
       </c>
       <c r="C1345" t="str">
-        <v>7203412108</v>
+        <v>3661081734</v>
       </c>
       <c r="D1345" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1345" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1345" t="str">
         <v>РФ</v>
       </c>
       <c r="G1345">
-        <v>47074</v>
+        <v>47001</v>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="str">
-        <v>Электронмаш Инжиниринг</v>
+        <v>Богословский кабельный завод</v>
       </c>
       <c r="B1346" t="str">
         <v>ООО</v>
       </c>
       <c r="C1346" t="str">
-        <v>7802428812</v>
+        <v>6617026384</v>
       </c>
       <c r="D1346" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1346" t="str">
-        <v>S.QS.07-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1346" t="str">
         <v>РФ</v>
       </c>
       <c r="G1346">
-        <v>46731</v>
+        <v>47087</v>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="str">
-        <v>Нефтегаздеталь</v>
+        <v>Богословский кабельный завод</v>
       </c>
       <c r="B1347" t="str">
         <v>ООО</v>
       </c>
       <c r="C1347" t="str">
-        <v>3661081734</v>
+        <v>6617026384</v>
       </c>
       <c r="D1347" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1347" t="str">
-        <v>S.QS.07-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1347" t="str">
         <v>РФ</v>
       </c>
       <c r="G1347">
-        <v>47001</v>
+        <v>47087</v>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="str">
-        <v>Богословский кабельный завод</v>
+        <v>Аутолив</v>
       </c>
       <c r="B1348" t="str">
         <v>ООО</v>
       </c>
       <c r="C1348" t="str">
-        <v>6617026384</v>
+        <v>4703105420</v>
       </c>
       <c r="D1348" t="str">
-        <v>ESYD (IAF)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1348" t="str">
         <v>ISO 9001:2015</v>
@@ -31408,13 +31408,13 @@
     </row>
     <row r="1349">
       <c r="A1349" t="str">
-        <v>Богословский кабельный завод</v>
+        <v>Аутолив</v>
       </c>
       <c r="B1349" t="str">
         <v>ООО</v>
       </c>
       <c r="C1349" t="str">
-        <v>6617026384</v>
+        <v>4703105420</v>
       </c>
       <c r="D1349" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -31440,16 +31440,16 @@
         <v>4703105420</v>
       </c>
       <c r="D1350" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1350" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1350" t="str">
         <v>РФ</v>
       </c>
       <c r="G1350">
-        <v>47087</v>
+        <v>47101</v>
       </c>
     </row>
     <row r="1351">
@@ -31463,62 +31463,62 @@
         <v>4703105420</v>
       </c>
       <c r="D1351" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1351" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1351" t="str">
         <v>РФ</v>
       </c>
       <c r="G1351">
-        <v>47087</v>
+        <v>45980</v>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="str">
-        <v>Аутолив</v>
+        <v>ASTEL</v>
       </c>
       <c r="B1352" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1352" t="str">
-        <v>4703105420</v>
+        <v>11140001666</v>
       </c>
       <c r="D1352" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1352" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1352" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1352">
-        <v>47101</v>
+        <v>46629</v>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="str">
-        <v>Аутолив</v>
+        <v>ASTEL</v>
       </c>
       <c r="B1353" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1353" t="str">
-        <v>4703105420</v>
+        <v>11140001666</v>
       </c>
       <c r="D1353" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1353" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 27001:2013</v>
       </c>
       <c r="F1353" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1353">
-        <v>45980</v>
+        <v>46643</v>
       </c>
     </row>
     <row r="1354">
@@ -31535,82 +31535,82 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1354" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 20000-1:2018</v>
       </c>
       <c r="F1354" t="str">
         <v>KZ</v>
       </c>
       <c r="G1354">
-        <v>46629</v>
+        <v>46643</v>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="str">
-        <v>ASTEL</v>
+        <v>Федеральное государственное бюджетное образовательное учреждение высшего образования «Тульский государственный педагогический университет им. Л.Н. Толстого», Научно-исследовательский институт химических, фармацевтических и биотехнологий, Научно-производственный центр</v>
       </c>
       <c r="B1355" t="str">
-        <v>АО</v>
+        <v>ФГБОУ ВО</v>
       </c>
       <c r="C1355" t="str">
-        <v>11140001666</v>
+        <v>7107030811</v>
       </c>
       <c r="D1355" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1355" t="str">
-        <v>ISO 27001:2013</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1355" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1355">
-        <v>46643</v>
+        <v>47101</v>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="str">
-        <v>ASTEL</v>
+        <v>«УЗЛЫ И МЕХАНИЗМЫ КУЗОВА АВТОМОБИЛЯ» (ООО «УМКА»)</v>
       </c>
       <c r="B1356" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1356" t="str">
-        <v>11140001666</v>
+        <v>6382061684</v>
       </c>
       <c r="D1356" t="str">
-        <v>UKAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1356" t="str">
-        <v>ISO 20000-1:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1356" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1356">
-        <v>46643</v>
+        <v>47094</v>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="str">
-        <v>Федеральное государственное бюджетное образовательное учреждение высшего образования «Тульский государственный педагогический университет им. Л.Н. Толстого», Научно-исследовательский институт химических, фармацевтических и биотехнологий, Научно-производственный центр</v>
+        <v>«УЗЛЫ И МЕХАНИЗМЫ КУЗОВА АВТОМОБИЛЯ» (ООО «УМКА»)</v>
       </c>
       <c r="B1357" t="str">
-        <v>ФГБОУ ВО</v>
+        <v>ООО</v>
       </c>
       <c r="C1357" t="str">
-        <v>7107030811</v>
+        <v>6382061684</v>
       </c>
       <c r="D1357" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1357" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1357" t="str">
         <v>РФ</v>
       </c>
       <c r="G1357">
-        <v>47101</v>
+        <v>47094</v>
       </c>
     </row>
     <row r="1358">
@@ -31624,16 +31624,16 @@
         <v>6382061684</v>
       </c>
       <c r="D1358" t="str">
-        <v>ESYD (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1358" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1358" t="str">
         <v>РФ</v>
       </c>
       <c r="G1358">
-        <v>47094</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="1359">
@@ -31650,59 +31650,59 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1359" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1359" t="str">
         <v>РФ</v>
       </c>
       <c r="G1359">
-        <v>47094</v>
+        <v>47175</v>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="str">
-        <v>«УЗЛЫ И МЕХАНИЗМЫ КУЗОВА АВТОМОБИЛЯ» (ООО «УМКА»)</v>
+        <v>РУСАЛ Ачинский Глиноземный Комбинат</v>
       </c>
       <c r="B1360" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1360" t="str">
-        <v>6382061684</v>
+        <v>2443005570</v>
       </c>
       <c r="D1360" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1360" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1360" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1360">
-        <v>46318</v>
+      <c r="G1360" t="str">
+        <v/>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="str">
-        <v>«УЗЛЫ И МЕХАНИЗМЫ КУЗОВА АВТОМОБИЛЯ» (ООО «УМКА»)</v>
+        <v>РУСАЛ Ачинский Глиноземный Комбинат</v>
       </c>
       <c r="B1361" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1361" t="str">
-        <v>6382061684</v>
+        <v>2443005570</v>
       </c>
       <c r="D1361" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1361" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1361" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1361">
-        <v>47175</v>
+      <c r="G1361" t="str">
+        <v/>
       </c>
     </row>
     <row r="1362">
@@ -31719,13 +31719,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1362" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1362" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1362" t="str">
-        <v/>
+      <c r="G1362">
+        <v>47097</v>
       </c>
     </row>
     <row r="1363">
@@ -31742,13 +31742,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1363" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1363" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1363" t="str">
-        <v/>
+      <c r="G1363">
+        <v>47097</v>
       </c>
     </row>
     <row r="1364">
@@ -31765,13 +31765,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1364" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1364" t="str">
         <v>РФ</v>
       </c>
       <c r="G1364">
-        <v>47097</v>
+        <v>47213</v>
       </c>
     </row>
     <row r="1365">
@@ -31788,59 +31788,59 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1365" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1365" t="str">
         <v>РФ</v>
       </c>
       <c r="G1365">
-        <v>47097</v>
+        <v>47213</v>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="str">
-        <v>РУСАЛ Ачинский Глиноземный Комбинат</v>
+        <v>ENTER STEEL</v>
       </c>
       <c r="B1366" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1366" t="str">
-        <v>2443005570</v>
+        <v>306574437</v>
       </c>
       <c r="D1366" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1366" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1366" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1366">
-        <v>47213</v>
+        <v>UZ</v>
+      </c>
+      <c r="G1366" t="str">
+        <v/>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="str">
-        <v>РУСАЛ Ачинский Глиноземный Комбинат</v>
+        <v>ENTER STEEL</v>
       </c>
       <c r="B1367" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1367" t="str">
-        <v>2443005570</v>
+        <v>306574437</v>
       </c>
       <c r="D1367" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1367" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1367" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1367">
-        <v>47213</v>
+        <v>UZ</v>
+      </c>
+      <c r="G1367" t="str">
+        <v/>
       </c>
     </row>
     <row r="1368">
@@ -31857,7 +31857,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1368" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1368" t="str">
         <v>UZ</v>
@@ -31868,19 +31868,19 @@
     </row>
     <row r="1369">
       <c r="A1369" t="str">
-        <v>ENTER STEEL</v>
+        <v>SAVDONI RIVOJLANTIRISH KOMPANIYASI</v>
       </c>
       <c r="B1369" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1369" t="str">
-        <v>306574437</v>
+        <v>306303488</v>
       </c>
       <c r="D1369" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1369" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 37001:2016</v>
       </c>
       <c r="F1369" t="str">
         <v>UZ</v>
@@ -31891,19 +31891,19 @@
     </row>
     <row r="1370">
       <c r="A1370" t="str">
-        <v>ENTER STEEL</v>
+        <v>Unitel</v>
       </c>
       <c r="B1370" t="str">
         <v>ООО</v>
       </c>
       <c r="C1370" t="str">
-        <v>306574437</v>
+        <v>201838002</v>
       </c>
       <c r="D1370" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1370" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1370" t="str">
         <v>UZ</v>
@@ -31914,22 +31914,22 @@
     </row>
     <row r="1371">
       <c r="A1371" t="str">
-        <v>SAVDONI RIVOJLANTIRISH KOMPANIYASI</v>
+        <v>«СХП «РАССВЕТ»</v>
       </c>
       <c r="B1371" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1371" t="str">
-        <v>306303488</v>
+        <v>2625027835</v>
       </c>
       <c r="D1371" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1371" t="str">
-        <v>ISO 37001:2016</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1371" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1371" t="str">
         <v/>
@@ -31937,13 +31937,13 @@
     </row>
     <row r="1372">
       <c r="A1372" t="str">
-        <v>Unitel</v>
+        <v>Завод по производству винто-рулевых колонок Сапфир</v>
       </c>
       <c r="B1372" t="str">
         <v>ООО</v>
       </c>
       <c r="C1372" t="str">
-        <v>201838002</v>
+        <v>2503032563</v>
       </c>
       <c r="D1372" t="str">
         <v>ESYD (IAF)</v>
@@ -31952,7 +31952,7 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1372" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1372" t="str">
         <v/>
@@ -31960,36 +31960,36 @@
     </row>
     <row r="1373">
       <c r="A1373" t="str">
-        <v>«СХП «РАССВЕТ»</v>
+        <v>GDC Services and Solutions d.o.o.</v>
       </c>
       <c r="B1373" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1373" t="str">
-        <v>2625027835</v>
+        <v/>
       </c>
       <c r="D1373" t="str">
-        <v>ESYD (IAF)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1373" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1373" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1373" t="str">
-        <v/>
+        <v>Serbia</v>
+      </c>
+      <c r="G1373">
+        <v>47101</v>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="str">
-        <v>Завод по производству винто-рулевых колонок Сапфир</v>
+        <v>Красноярский металлургический завод ("КраМЗ")</v>
       </c>
       <c r="B1374" t="str">
         <v>ООО</v>
       </c>
       <c r="C1374" t="str">
-        <v>2503032563</v>
+        <v>2465043748</v>
       </c>
       <c r="D1374" t="str">
         <v>ESYD (IAF)</v>
@@ -32000,31 +32000,31 @@
       <c r="F1374" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1374" t="str">
-        <v/>
+      <c r="G1374">
+        <v>47110</v>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="str">
-        <v>GDC Services and Solutions d.o.o.</v>
+        <v>Красноярский металлургический завод ("КраМЗ")</v>
       </c>
       <c r="B1375" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1375" t="str">
-        <v/>
+        <v>2465043748</v>
       </c>
       <c r="D1375" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1375" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1375" t="str">
-        <v>Serbia</v>
+        <v>РФ</v>
       </c>
       <c r="G1375">
-        <v>47101</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="1376">
@@ -32041,13 +32041,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1376" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1376" t="str">
         <v>РФ</v>
       </c>
       <c r="G1376">
-        <v>47110</v>
+        <v>47242</v>
       </c>
     </row>
     <row r="1377">
@@ -32064,70 +32064,70 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1377" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1377" t="str">
         <v>РФ</v>
       </c>
       <c r="G1377">
-        <v>47110</v>
+        <v>47242</v>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="str">
-        <v>Красноярский металлургический завод ("КраМЗ")</v>
+        <v>"ЭЛАРА"</v>
       </c>
       <c r="B1378" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1378" t="str">
-        <v>2465043748</v>
+        <v>2129017646</v>
       </c>
       <c r="D1378" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1378" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1378" t="str">
         <v>РФ</v>
       </c>
       <c r="G1378">
-        <v>47242</v>
+        <v>46980</v>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="str">
-        <v>Красноярский металлургический завод ("КраМЗ")</v>
+        <v>"ЭЛАРА"</v>
       </c>
       <c r="B1379" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1379" t="str">
-        <v>2465043748</v>
+        <v>2129017646</v>
       </c>
       <c r="D1379" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1379" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1379" t="str">
         <v>РФ</v>
       </c>
       <c r="G1379">
-        <v>47242</v>
+        <v>46574</v>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="str">
-        <v>"ЭЛАРА"</v>
+        <v>"Газпром проектирование"</v>
       </c>
       <c r="B1380" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1380" t="str">
-        <v>2129017646</v>
+        <v>0560022871</v>
       </c>
       <c r="D1380" t="str">
         <v>ESYD (IAF)</v>
@@ -32139,18 +32139,18 @@
         <v>РФ</v>
       </c>
       <c r="G1380">
-        <v>46980</v>
+        <v>47003</v>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="str">
-        <v>"ЭЛАРА"</v>
+        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
       </c>
       <c r="B1381" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1381" t="str">
-        <v>2129017646</v>
+        <v>190918566</v>
       </c>
       <c r="D1381" t="str">
         <v>ESYD (IAF)</v>
@@ -32159,79 +32159,79 @@
         <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1381" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1381">
-        <v>46574</v>
+        <v>47151</v>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="str">
-        <v>"Газпром проектирование"</v>
+        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
       </c>
       <c r="B1382" t="str">
         <v>ООО</v>
       </c>
       <c r="C1382" t="str">
-        <v>0560022871</v>
+        <v>190918566</v>
       </c>
       <c r="D1382" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1382" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1382" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1382">
-        <v>47003</v>
+        <v>47151</v>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="str">
-        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
+        <v>Аутолайт Технолоджи</v>
       </c>
       <c r="B1383" t="str">
         <v>ООО</v>
       </c>
       <c r="C1383" t="str">
-        <v>190918566</v>
+        <v>6230025811</v>
       </c>
       <c r="D1383" t="str">
-        <v>ESYD (IAF)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1383" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1383" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1383">
-        <v>47151</v>
+        <v>47179</v>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="str">
-        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
+        <v>Аутолайт Технолоджи</v>
       </c>
       <c r="B1384" t="str">
         <v>ООО</v>
       </c>
       <c r="C1384" t="str">
-        <v>190918566</v>
+        <v>6230025811</v>
       </c>
       <c r="D1384" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1384" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1384" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1384">
-        <v>47151</v>
+        <v>47229</v>
       </c>
     </row>
     <row r="1385">
@@ -32245,16 +32245,16 @@
         <v>6230025811</v>
       </c>
       <c r="D1385" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1385" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1385" t="str">
         <v>РФ</v>
       </c>
       <c r="G1385">
-        <v>47179</v>
+        <v>46430</v>
       </c>
     </row>
     <row r="1386">
@@ -32271,76 +32271,76 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1386" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1386" t="str">
         <v>РФ</v>
       </c>
       <c r="G1386">
-        <v>47229</v>
+        <v>47179</v>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="str">
-        <v>Аутолайт Технолоджи</v>
+        <v>Инновационный центр КАМАЗ</v>
       </c>
       <c r="B1387" t="str">
         <v>ООО</v>
       </c>
       <c r="C1387" t="str">
-        <v>6230025811</v>
+        <v>7801204062</v>
       </c>
       <c r="D1387" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1387" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1387" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1387">
-        <v>46430</v>
+      <c r="G1387" t="str">
+        <v/>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="str">
-        <v>Аутолайт Технолоджи</v>
+        <v>Инновационный центр КАМАЗ</v>
       </c>
       <c r="B1388" t="str">
         <v>ООО</v>
       </c>
       <c r="C1388" t="str">
-        <v>6230025811</v>
+        <v>7801204062</v>
       </c>
       <c r="D1388" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1388" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1388" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1388">
-        <v>47179</v>
+      <c r="G1388" t="str">
+        <v/>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="str">
-        <v>Инновационный центр КАМАЗ</v>
+        <v>АкваПромМеталл</v>
       </c>
       <c r="B1389" t="str">
         <v>ООО</v>
       </c>
       <c r="C1389" t="str">
-        <v>7801204062</v>
+        <v>7807240772</v>
       </c>
       <c r="D1389" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1389" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1389" t="str">
         <v>РФ</v>
@@ -32351,36 +32351,36 @@
     </row>
     <row r="1390">
       <c r="A1390" t="str">
-        <v>Инновационный центр КАМАЗ</v>
+        <v>СЗЭМО ЗАВОД ВЕНТИЛЯТОР ТДМ</v>
       </c>
       <c r="B1390" t="str">
         <v>ООО</v>
       </c>
       <c r="C1390" t="str">
-        <v>7801204062</v>
+        <v>7811513824</v>
       </c>
       <c r="D1390" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1390" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1390" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1390" t="str">
-        <v/>
+      <c r="G1390">
+        <v>46810</v>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="str">
-        <v>АкваПромМеталл</v>
+        <v>РЕМОНТНО-МЕХАНИЧЕСКИЙ ЗАВОД ГОРНО-ХИМИЧЕСКОГО КОМБИНАТА (РМЗ ГХК)</v>
       </c>
       <c r="B1391" t="str">
         <v>ООО</v>
       </c>
       <c r="C1391" t="str">
-        <v>7807240772</v>
+        <v>2452201891</v>
       </c>
       <c r="D1391" t="str">
         <v>РОСАТОМРЕГИСТР</v>
@@ -32397,13 +32397,13 @@
     </row>
     <row r="1392">
       <c r="A1392" t="str">
-        <v>СЗЭМО ЗАВОД ВЕНТИЛЯТОР ТДМ</v>
+        <v>Центр диагностики, экспертизы и сертификации (ЦДЭС)</v>
       </c>
       <c r="B1392" t="str">
         <v>ООО</v>
       </c>
       <c r="C1392" t="str">
-        <v>7811513824</v>
+        <v>7839346161</v>
       </c>
       <c r="D1392" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -32415,21 +32415,21 @@
         <v>РФ</v>
       </c>
       <c r="G1392">
-        <v>46810</v>
+        <v>46567</v>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="str">
-        <v>РЕМОНТНО-МЕХАНИЧЕСКИЙ ЗАВОД ГОРНО-ХИМИЧЕСКОГО КОМБИНАТА (РМЗ ГХК)</v>
+        <v>Уральский завод специального арматуростроения (УЗСА)</v>
       </c>
       <c r="B1393" t="str">
         <v>ООО</v>
       </c>
       <c r="C1393" t="str">
-        <v>2452201891</v>
+        <v>7451403608</v>
       </c>
       <c r="D1393" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1393" t="str">
         <v>ISO 9001:2015</v>
@@ -32437,88 +32437,90 @@
       <c r="F1393" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1393" t="str">
-        <v/>
+      <c r="G1393">
+        <v>46900</v>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="str">
-        <v>Центр диагностики, экспертизы и сертификации (ЦДЭС)</v>
+        <v>Угрешский завод трубопроводной арматуры (УЗТПА)</v>
       </c>
       <c r="B1394" t="str">
         <v>ООО</v>
       </c>
       <c r="C1394" t="str">
-        <v>7839346161</v>
+        <v>5056009251</v>
       </c>
       <c r="D1394" t="str">
+        <v>O’ZAKK (IAF)</v>
+      </c>
+      <c r="E1394" t="str">
+        <v>ISO 9001:2015</v>
+      </c>
+      <c r="F1394" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1394">
+        <v>46900</v>
+      </c>
+    </row>
+    <row r="1395" xml:space="preserve">
+      <c r="A1395" t="str" xml:space="preserve">
+        <v xml:space="preserve">Научно-_x000d_
+производственное объединение специальных материалов (НПО Спецматериалов)</v>
+      </c>
+      <c r="B1395" t="str">
+        <v>АО</v>
+      </c>
+      <c r="C1395" t="str">
+        <v>7806125671</v>
+      </c>
+      <c r="D1395" t="str">
+        <v>РОСАТОМРЕГИСТР</v>
+      </c>
+      <c r="E1395" t="str">
+        <v>ГОСТ Р ИСО 9001-2015</v>
+      </c>
+      <c r="F1395" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1395">
+        <v>46709</v>
+      </c>
+    </row>
+    <row r="1396" xml:space="preserve">
+      <c r="A1396" t="str" xml:space="preserve">
+        <v xml:space="preserve">Научно-_x000d_
+производственное объединение специальных материалов (НПО Спецматериалов)</v>
+      </c>
+      <c r="B1396" t="str">
+        <v>АО</v>
+      </c>
+      <c r="C1396" t="str">
+        <v>7806125671</v>
+      </c>
+      <c r="D1396" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
-      <c r="E1394" t="str">
+      <c r="E1396" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
-      <c r="F1394" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1394">
-        <v>46567</v>
-      </c>
-    </row>
-    <row r="1395">
-      <c r="A1395" t="str">
-        <v>Уральский завод специального арматуростроения (УЗСА)</v>
-      </c>
-      <c r="B1395" t="str">
-        <v>ООО</v>
-      </c>
-      <c r="C1395" t="str">
-        <v>7451403608</v>
-      </c>
-      <c r="D1395" t="str">
-        <v>O’ZAKK (IAF)</v>
-      </c>
-      <c r="E1395" t="str">
-        <v>ISO 9001:2015</v>
-      </c>
-      <c r="F1395" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1395">
-        <v>46900</v>
-      </c>
-    </row>
-    <row r="1396">
-      <c r="A1396" t="str">
-        <v>Уральский завод специального арматуростроения (УЗСА)</v>
-      </c>
-      <c r="B1396" t="str">
-        <v>ООО</v>
-      </c>
-      <c r="C1396" t="str">
-        <v>7451403608</v>
-      </c>
-      <c r="D1396" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
-      </c>
-      <c r="E1396" t="str">
-        <v>СТО Газпром 9001-2018</v>
-      </c>
       <c r="F1396" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1396" t="str">
-        <v/>
+      <c r="G1396">
+        <v>46655</v>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="str">
-        <v>Угрешский завод трубопроводной арматуры (УЗТПА)</v>
+        <v>Специализированная инжиниринговая компания Севзапмонтажавтоматика (СЗМА СПИК)</v>
       </c>
       <c r="B1397" t="str">
         <v>ООО</v>
       </c>
       <c r="C1397" t="str">
-        <v>5056009251</v>
+        <v>7801715500</v>
       </c>
       <c r="D1397" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -32530,221 +32532,81 @@
         <v>РФ</v>
       </c>
       <c r="G1397">
-        <v>46900</v>
+        <v>46921</v>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="str">
-        <v>Угрешский завод трубопроводной арматуры (УЗТПА)</v>
+        <v>Тосненский механический завод (ТоМеЗ)</v>
       </c>
       <c r="B1398" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1398" t="str">
-        <v>5056009251</v>
+        <v>4716002824</v>
       </c>
       <c r="D1398" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1398" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1398" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1398" t="str">
+      <c r="G1398">
+        <v>46619</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="str">
+        <v>Трубопроводные покрытия и технологии (ТПТ)</v>
+      </c>
+      <c r="B1399" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1399" t="str">
+        <v>3435308501</v>
+      </c>
+      <c r="D1399" t="str">
+        <v>EGAC (QME)</v>
+      </c>
+      <c r="E1399" t="str">
+        <v>ISO 9001:2015</v>
+      </c>
+      <c r="F1399" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1399">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="str">
+        <v>Ладуга</v>
+      </c>
+      <c r="B1400" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1400" t="str">
+        <v>6321369143</v>
+      </c>
+      <c r="D1400" t="str">
         <v/>
       </c>
-    </row>
-    <row r="1399" xml:space="preserve">
-      <c r="A1399" t="str" xml:space="preserve">
-        <v xml:space="preserve">Научно-_x000d_
-производственное объединение специальных материалов (НПО Спецматериалов)</v>
-      </c>
-      <c r="B1399" t="str">
-        <v>АО</v>
-      </c>
-      <c r="C1399" t="str">
-        <v>7806125671</v>
-      </c>
-      <c r="D1399" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
-      </c>
-      <c r="E1399" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
-      </c>
-      <c r="F1399" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1399">
-        <v>46709</v>
-      </c>
-    </row>
-    <row r="1400" xml:space="preserve">
-      <c r="A1400" t="str" xml:space="preserve">
-        <v xml:space="preserve">Научно-_x000d_
-производственное объединение специальных материалов (НПО Спецматериалов)</v>
-      </c>
-      <c r="B1400" t="str">
-        <v>АО</v>
-      </c>
-      <c r="C1400" t="str">
-        <v>7806125671</v>
-      </c>
-      <c r="D1400" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
-      </c>
       <c r="E1400" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v/>
       </c>
       <c r="F1400" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1400">
-        <v>46655</v>
-      </c>
-    </row>
-    <row r="1401">
-      <c r="A1401" t="str">
-        <v>Специализированная инжиниринговая компания Севзапмонтажавтоматика (СЗМА СПИК)</v>
-      </c>
-      <c r="B1401" t="str">
-        <v>ООО</v>
-      </c>
-      <c r="C1401" t="str">
-        <v>7801715500</v>
-      </c>
-      <c r="D1401" t="str">
-        <v>O’ZAKK (IAF)</v>
-      </c>
-      <c r="E1401" t="str">
-        <v>ISO 9001:2015</v>
-      </c>
-      <c r="F1401" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1401">
-        <v>46921</v>
-      </c>
-    </row>
-    <row r="1402">
-      <c r="A1402" t="str">
-        <v>Тосненский механический завод (ТоМеЗ)</v>
-      </c>
-      <c r="B1402" t="str">
-        <v>АО</v>
-      </c>
-      <c r="C1402" t="str">
-        <v>4716002824</v>
-      </c>
-      <c r="D1402" t="str">
-        <v>O’ZAKK (IAF)</v>
-      </c>
-      <c r="E1402" t="str">
-        <v>ISO 9001:2015</v>
-      </c>
-      <c r="F1402" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1402">
-        <v>46619</v>
-      </c>
-    </row>
-    <row r="1403">
-      <c r="A1403" t="str">
-        <v>Трубопроводные покрытия и технологии (ТПТ)</v>
-      </c>
-      <c r="B1403" t="str">
-        <v>ООО</v>
-      </c>
-      <c r="C1403" t="str">
-        <v>3435308501</v>
-      </c>
-      <c r="D1403" t="str">
-        <v>EGAC (QME)</v>
-      </c>
-      <c r="E1403" t="str">
-        <v>ISO 9001:2015</v>
-      </c>
-      <c r="F1403" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1403">
-        <v>46272</v>
-      </c>
-    </row>
-    <row r="1404">
-      <c r="A1404" t="str">
-        <v>Трубопроводные покрытия и технологии (ТПТ)</v>
-      </c>
-      <c r="B1404" t="str">
-        <v>ООО</v>
-      </c>
-      <c r="C1404" t="str">
-        <v>3435308501</v>
-      </c>
-      <c r="D1404" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
-      </c>
-      <c r="E1404" t="str">
-        <v>СТО Газпром 9001-2018</v>
-      </c>
-      <c r="F1404" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1404" t="str">
         <v/>
       </c>
-    </row>
-    <row r="1405">
-      <c r="A1405" t="str">
-        <v>Хакель</v>
-      </c>
-      <c r="B1405" t="str">
-        <v>АО</v>
-      </c>
-      <c r="C1405" t="str">
-        <v/>
-      </c>
-      <c r="D1405" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
-      </c>
-      <c r="E1405" t="str">
-        <v>СТО Газпром 9001-2018</v>
-      </c>
-      <c r="F1405" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1405" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1406">
-      <c r="A1406" t="str">
-        <v>Ладуга</v>
-      </c>
-      <c r="B1406" t="str">
-        <v>ООО</v>
-      </c>
-      <c r="C1406" t="str">
-        <v>6321369143</v>
-      </c>
-      <c r="D1406" t="str">
-        <v/>
-      </c>
-      <c r="E1406" t="str">
-        <v/>
-      </c>
-      <c r="F1406" t="str">
-        <v/>
-      </c>
-      <c r="G1406" t="str">
+      <c r="G1400" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1406"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1400"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -3860,7 +3860,7 @@
         <v>200167349</v>
       </c>
       <c r="D151" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E151" t="str">
         <v>ISO 45001:2018</v>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1375"/>
+  <dimension ref="A1:G1376"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -32029,9 +32029,32 @@
         <v>47270</v>
       </c>
     </row>
+    <row r="1376">
+      <c r="A1376" t="str">
+        <v>АВТОКОЛОРИТ</v>
+      </c>
+      <c r="B1376" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1376" t="str">
+        <v>6320092604</v>
+      </c>
+      <c r="D1376" t="str">
+        <v>ESYD (IAF)</v>
+      </c>
+      <c r="E1376" t="str">
+        <v>ISO 9001:2015</v>
+      </c>
+      <c r="F1376" t="str">
+        <v/>
+      </c>
+      <c r="G1376" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1375"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1376"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1378"/>
+  <dimension ref="A1:G1380"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -32098,9 +32098,55 @@
         <v/>
       </c>
     </row>
+    <row r="1379">
+      <c r="A1379" t="str">
+        <v>ХЕНДЭ СТИЛ РУС</v>
+      </c>
+      <c r="B1379" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1379" t="str">
+        <v>7813442054</v>
+      </c>
+      <c r="D1379" t="str">
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+      </c>
+      <c r="E1379" t="str">
+        <v>ГОСТ Р ИСО 9001-2015</v>
+      </c>
+      <c r="F1379" t="str">
+        <v/>
+      </c>
+      <c r="G1379" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="str">
+        <v>ХЕНДЭ СТИЛ РУС</v>
+      </c>
+      <c r="B1380" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1380" t="str">
+        <v>7813442054</v>
+      </c>
+      <c r="D1380" t="str">
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+      </c>
+      <c r="E1380" t="str">
+        <v>ГОСТ Р 58139-2024</v>
+      </c>
+      <c r="F1380" t="str">
+        <v/>
+      </c>
+      <c r="G1380" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1378"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1380"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -31724,8 +31724,8 @@
       <c r="F1362" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1362" t="str">
-        <v/>
+      <c r="G1362">
+        <v>47286</v>
       </c>
     </row>
     <row r="1363">
@@ -31747,8 +31747,8 @@
       <c r="F1363" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1363" t="str">
-        <v/>
+      <c r="G1363">
+        <v>47286</v>
       </c>
     </row>
     <row r="1364">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1382"/>
+  <dimension ref="A1:G1383"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -32115,7 +32115,7 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1379" t="str">
-        <v/>
+        <v>РФ</v>
       </c>
       <c r="G1379" t="str">
         <v/>
@@ -32138,7 +32138,7 @@
         <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1380" t="str">
-        <v/>
+        <v>РФ</v>
       </c>
       <c r="G1380" t="str">
         <v/>
@@ -32161,7 +32161,7 @@
         <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1381" t="str">
-        <v/>
+        <v>РФ</v>
       </c>
       <c r="G1381" t="str">
         <v/>
@@ -32190,9 +32190,32 @@
         <v>46521</v>
       </c>
     </row>
+    <row r="1383">
+      <c r="A1383" t="str">
+        <v>Сваркер</v>
+      </c>
+      <c r="B1383" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1383" t="str">
+        <v>6686156088</v>
+      </c>
+      <c r="D1383" t="str">
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+      </c>
+      <c r="E1383" t="str">
+        <v>ГОСТ Р ИСО 9001-2015</v>
+      </c>
+      <c r="F1383" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1383" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1382"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1383"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -482,7 +482,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E4" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F4" t="str">
         <v>РФ</v>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -7204,12 +7204,12 @@
         <v>РФ</v>
       </c>
       <c r="G296">
-        <v>46409</v>
+        <v>46479</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>АВТОКОМПОНЕНТ ФОРМАТ ТОЛЬЯТТИ-ИНТЕРЬЕРЫ</v>
+        <v>Автокомпонент Формат Тольятти - Интерьеры (АФТ-Интерьеры)</v>
       </c>
       <c r="B297" t="str">
         <v>АО</v>
@@ -32273,7 +32273,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1386" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1386" t="str">
         <v>РБ</v>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -32416,8 +32416,8 @@
       <c r="F1392" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1392" t="str">
-        <v/>
+      <c r="G1392">
+        <v>47314</v>
       </c>
     </row>
     <row r="1393">
@@ -32439,8 +32439,8 @@
       <c r="F1393" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1393" t="str">
-        <v/>
+      <c r="G1393">
+        <v>47314</v>
       </c>
     </row>
     <row r="1394">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -11758,7 +11758,7 @@
         <v>Estonia</v>
       </c>
       <c r="G494">
-        <v>46218</v>
+        <v>47313</v>
       </c>
     </row>
     <row r="495">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1395"/>
+  <dimension ref="A1:G1407"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8400,7 +8400,7 @@
         <v>РФ</v>
       </c>
       <c r="G348">
-        <v>46197</v>
+        <v>46562</v>
       </c>
     </row>
     <row r="349">
@@ -22962,18 +22962,18 @@
         <v>РФ</v>
       </c>
       <c r="G981">
-        <v>45948</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>ООО "Газпром Трансгаз Нижний Новгород"</v>
+        <v>ЗАО "АлтайСпецИзделия"</v>
       </c>
       <c r="B982" t="str">
-        <v>ООО</v>
+        <v>ЗАО</v>
       </c>
       <c r="C982" t="str">
-        <v>5260080007</v>
+        <v>2224130666</v>
       </c>
       <c r="D982" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -22985,18 +22985,18 @@
         <v>РФ</v>
       </c>
       <c r="G982">
-        <v>46069</v>
+        <v>47187</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>ЗАО "АлтайСпецИзделия"</v>
+        <v>ООО "Этирекс"</v>
       </c>
       <c r="B983" t="str">
-        <v>ЗАО</v>
+        <v>ООО</v>
       </c>
       <c r="C983" t="str">
-        <v>2224130666</v>
+        <v>7715350670</v>
       </c>
       <c r="D983" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -23008,18 +23008,18 @@
         <v>РФ</v>
       </c>
       <c r="G983">
-        <v>46094</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>ООО "Этирекс"</v>
+        <v>ООО "КомплектСнаб"</v>
       </c>
       <c r="B984" t="str">
         <v>ООО</v>
       </c>
       <c r="C984" t="str">
-        <v>7715350670</v>
+        <v>4501124406</v>
       </c>
       <c r="D984" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -23031,18 +23031,18 @@
         <v>РФ</v>
       </c>
       <c r="G984">
-        <v>46234</v>
+        <v>46384</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>ООО "Политехформ М"</v>
+        <v>ООО "Гео-проект"</v>
       </c>
       <c r="B985" t="str">
         <v>ООО</v>
       </c>
       <c r="C985" t="str">
-        <v>7724187733</v>
+        <v>7839418049</v>
       </c>
       <c r="D985" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -23054,18 +23054,18 @@
         <v>РФ</v>
       </c>
       <c r="G985">
-        <v>46283</v>
+        <v>46464</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>АО "Синарский трубный завод"</v>
+        <v>ООО "ТСЗП"</v>
       </c>
       <c r="B986" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C986" t="str">
-        <v>6612000551</v>
+        <v>7719193993</v>
       </c>
       <c r="D986" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -23077,18 +23077,18 @@
         <v>РФ</v>
       </c>
       <c r="G986">
-        <v>46384</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>ООО "КомплектСнаб"</v>
+        <v>ООО "Автоматические пожарные системы"</v>
       </c>
       <c r="B987" t="str">
         <v>ООО</v>
       </c>
       <c r="C987" t="str">
-        <v>4501124406</v>
+        <v>7743790249</v>
       </c>
       <c r="D987" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -23100,18 +23100,18 @@
         <v>РФ</v>
       </c>
       <c r="G987">
-        <v>46384</v>
+        <v>46696</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>ООО "Гео-проект"</v>
+        <v>Георесурс-КБ</v>
       </c>
       <c r="B988" t="str">
         <v>ООО</v>
       </c>
       <c r="C988" t="str">
-        <v>7839418049</v>
+        <v>6452946595</v>
       </c>
       <c r="D988" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -23123,18 +23123,18 @@
         <v>РФ</v>
       </c>
       <c r="G988">
-        <v>46464</v>
+        <v>46558</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>ООО "ТСЗП"</v>
+        <v>ПластПроектСтрой</v>
       </c>
       <c r="B989" t="str">
         <v>ООО</v>
       </c>
       <c r="C989" t="str">
-        <v>7719193993</v>
+        <v>7813637092</v>
       </c>
       <c r="D989" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -23146,18 +23146,18 @@
         <v>РФ</v>
       </c>
       <c r="G989">
-        <v>46478</v>
+        <v>46810</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>ООО "Автоматические пожарные системы"</v>
+        <v>ЧЗТО</v>
       </c>
       <c r="B990" t="str">
         <v>ООО</v>
       </c>
       <c r="C990" t="str">
-        <v>7743790249</v>
+        <v>7449010286</v>
       </c>
       <c r="D990" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -23169,182 +23169,182 @@
         <v>РФ</v>
       </c>
       <c r="G990">
-        <v>46696</v>
+        <v>46824</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>Георесурс-КБ</v>
+        <v>Деловые решения и технологии</v>
       </c>
       <c r="B991" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C991" t="str">
-        <v>6452946595</v>
+        <v>7703097990</v>
       </c>
       <c r="D991" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E991" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F991" t="str">
         <v>РФ</v>
       </c>
       <c r="G991">
-        <v>46558</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>ПластПроектСтрой</v>
+        <v>Деловые решения и технологии</v>
       </c>
       <c r="B992" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C992" t="str">
-        <v>7813637092</v>
+        <v>7703097990</v>
       </c>
       <c r="D992" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E992" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F992" t="str">
         <v>РФ</v>
       </c>
       <c r="G992">
-        <v>46810</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>ЧЗТО</v>
+        <v>Техно Драйв</v>
       </c>
       <c r="B993" t="str">
         <v>ООО</v>
       </c>
       <c r="C993" t="str">
-        <v>7449010286</v>
+        <v>7451385726</v>
       </c>
       <c r="D993" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E993" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F993" t="str">
         <v>РФ</v>
       </c>
       <c r="G993">
-        <v>46824</v>
+        <v>46534</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>Деловые решения и технологии</v>
+        <v>Техно Драйв</v>
       </c>
       <c r="B994" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C994" t="str">
-        <v>7703097990</v>
+        <v>7451385726</v>
       </c>
       <c r="D994" t="str">
-        <v>ESYD (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E994" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F994" t="str">
         <v>РФ</v>
       </c>
       <c r="G994">
-        <v>46478</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>Деловые решения и технологии</v>
+        <v>Кинельагропласт</v>
       </c>
       <c r="B995" t="str">
         <v>АО</v>
       </c>
       <c r="C995" t="str">
-        <v>7703097990</v>
+        <v>6371000295</v>
       </c>
       <c r="D995" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E995" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F995" t="str">
         <v>РФ</v>
       </c>
       <c r="G995">
-        <v>46478</v>
+        <v>46594</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>Техно Драйв</v>
+        <v>Кинельагропласт</v>
       </c>
       <c r="B996" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C996" t="str">
-        <v>7451385726</v>
+        <v>6371000295</v>
       </c>
       <c r="D996" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E996" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F996" t="str">
         <v>РФ</v>
       </c>
       <c r="G996">
-        <v>46534</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>Техно Драйв</v>
+        <v>Техлаб</v>
       </c>
       <c r="B997" t="str">
         <v>ООО</v>
       </c>
       <c r="C997" t="str">
-        <v>7451385726</v>
+        <v>7805539408</v>
       </c>
       <c r="D997" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E997" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F997" t="str">
         <v>РФ</v>
       </c>
       <c r="G997">
-        <v>46297</v>
+        <v>46519</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>Кинельагропласт</v>
+        <v>ХАЙЕР ИНДАСТРИ РУС</v>
       </c>
       <c r="B998" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C998" t="str">
-        <v>6371000295</v>
+        <v>1650371043</v>
       </c>
       <c r="D998" t="str">
-        <v>UKAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E998" t="str">
         <v>ISO 9001:2015</v>
@@ -23353,67 +23353,67 @@
         <v>РФ</v>
       </c>
       <c r="G998">
-        <v>46594</v>
+        <v>47004</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>Кинельагропласт</v>
+        <v>ХАЙЕР ИНДАСТРИ РУС</v>
       </c>
       <c r="B999" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C999" t="str">
-        <v>6371000295</v>
+        <v>1650371043</v>
       </c>
       <c r="D999" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E999" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F999" t="str">
         <v>РФ</v>
       </c>
       <c r="G999">
-        <v>46157</v>
+        <v>47004</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>Техлаб</v>
+        <v>МСС-КИП Автоматика</v>
       </c>
       <c r="B1000" t="str">
-        <v>ООО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1000" t="str">
-        <v>7805539408</v>
+        <v>101240018331</v>
       </c>
       <c r="D1000" t="str">
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1000" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1000" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1000">
-        <v>46519</v>
+        <v>46643</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>ХАЙЕР ИНДАСТРИ РУС</v>
+        <v>ИНАРКТИКА Северо-Запад</v>
       </c>
       <c r="B1001" t="str">
         <v>ООО</v>
       </c>
       <c r="C1001" t="str">
-        <v>1650371043</v>
+        <v>7722607816</v>
       </c>
       <c r="D1001" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1001" t="str">
         <v>ISO 9001:2015</v>
@@ -23422,64 +23422,64 @@
         <v>РФ</v>
       </c>
       <c r="G1001">
-        <v>47004</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>ХАЙЕР ИНДАСТРИ РУС</v>
+        <v>СП ООО «Milk Euro Food»</v>
       </c>
       <c r="B1002" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1002" t="str">
-        <v>1650371043</v>
+        <v/>
       </c>
       <c r="D1002" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1002" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1002" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1002">
-        <v>47004</v>
+        <v>46604</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>МСС-КИП Автоматика</v>
+        <v>СП ООО «Milk Euro Food»</v>
       </c>
       <c r="B1003" t="str">
-        <v>ТОО</v>
+        <v/>
       </c>
       <c r="C1003" t="str">
-        <v>101240018331</v>
+        <v/>
       </c>
       <c r="D1003" t="str">
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1003" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1003" t="str">
-        <v>KZ</v>
+        <v>UZ</v>
       </c>
       <c r="G1003">
-        <v>46643</v>
+        <v>46644</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>ИНАРКТИКА Северо-Запад</v>
+        <v>Общество с ограниченной ответственностью «Промышленная химия»</v>
       </c>
       <c r="B1004" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1004" t="str">
-        <v>7722607816</v>
+        <v/>
       </c>
       <c r="D1004" t="str">
         <v>UKAS (IAF)</v>
@@ -23491,12 +23491,12 @@
         <v>РФ</v>
       </c>
       <c r="G1004">
-        <v>46171</v>
+        <v>46613</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>СП ООО «Milk Euro Food»</v>
+        <v>DT BUILDING</v>
       </c>
       <c r="B1005" t="str">
         <v/>
@@ -23511,15 +23511,15 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1005" t="str">
-        <v>UZ</v>
+        <v>Bulgaria</v>
       </c>
       <c r="G1005">
-        <v>46604</v>
+        <v>46640</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>СП ООО «Milk Euro Food»</v>
+        <v>DT BUILDING</v>
       </c>
       <c r="B1006" t="str">
         <v/>
@@ -23531,18 +23531,18 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1006" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1006" t="str">
-        <v>UZ</v>
+        <v>Bulgaria</v>
       </c>
       <c r="G1006">
-        <v>46644</v>
+        <v>46640</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>Общество с ограниченной ответственностью «Промышленная химия»</v>
+        <v>Государственное учреждение "Центр безопасности фармацевтической продукции"</v>
       </c>
       <c r="B1007" t="str">
         <v/>
@@ -23557,21 +23557,21 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1007" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1007">
-        <v>46613</v>
+        <v>46716</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>DT BUILDING</v>
+        <v>ЛИДЕР-АВ</v>
       </c>
       <c r="B1008" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1008" t="str">
-        <v/>
+        <v>5049025534</v>
       </c>
       <c r="D1008" t="str">
         <v>UKAS (IAF)</v>
@@ -23580,90 +23580,90 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1008" t="str">
-        <v>Bulgaria</v>
+        <v>РФ</v>
       </c>
       <c r="G1008">
-        <v>46640</v>
+        <v>46528</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>DT BUILDING</v>
+        <v>ПФ Авангард-А</v>
       </c>
       <c r="B1009" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1009" t="str">
-        <v/>
+        <v>6382098652</v>
       </c>
       <c r="D1009" t="str">
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1009" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1009" t="str">
-        <v>Bulgaria</v>
+        <v>РФ</v>
       </c>
       <c r="G1009">
-        <v>46640</v>
+        <v>46575</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>Государственное учреждение "Центр безопасности фармацевтической продукции"</v>
+        <v>ПФ Авангард-А</v>
       </c>
       <c r="B1010" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1010" t="str">
-        <v/>
+        <v>6382098652</v>
       </c>
       <c r="D1010" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1010" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1010" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1010">
-        <v>46716</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>ЛИДЕР-АВ</v>
+        <v>Ассоциация Медицины и Аналитики</v>
       </c>
       <c r="B1011" t="str">
         <v>ООО</v>
       </c>
       <c r="C1011" t="str">
-        <v>5049025534</v>
+        <v>7801223114</v>
       </c>
       <c r="D1011" t="str">
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1011" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1011" t="str">
         <v>РФ</v>
       </c>
       <c r="G1011">
-        <v>46528</v>
+        <v>46622</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>ПФ Авангард-А</v>
+        <v>Айрос-Систем</v>
       </c>
       <c r="B1012" t="str">
         <v>ООО</v>
       </c>
       <c r="C1012" t="str">
-        <v>6382098652</v>
+        <v>7804691720</v>
       </c>
       <c r="D1012" t="str">
         <v>UKAS (IAF)</v>
@@ -23675,64 +23675,64 @@
         <v>РФ</v>
       </c>
       <c r="G1012">
-        <v>46575</v>
+        <v>46622</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>ПФ Авангард-А</v>
+        <v>БорМаш</v>
       </c>
       <c r="B1013" t="str">
         <v>ООО</v>
       </c>
       <c r="C1013" t="str">
-        <v>6382098652</v>
+        <v>3604011804</v>
       </c>
       <c r="D1013" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1013" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1013" t="str">
         <v>РФ</v>
       </c>
       <c r="G1013">
-        <v>46206</v>
+        <v>46625</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>Ассоциация Медицины и Аналитики</v>
+        <v>БорМаш</v>
       </c>
       <c r="B1014" t="str">
         <v>ООО</v>
       </c>
       <c r="C1014" t="str">
-        <v>7801223114</v>
+        <v>3604011804</v>
       </c>
       <c r="D1014" t="str">
-        <v>UKAS (IAF)</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1014" t="str">
-        <v>ISO 13485:2016</v>
+        <v>S.QS.01-2020</v>
       </c>
       <c r="F1014" t="str">
         <v>РФ</v>
       </c>
       <c r="G1014">
-        <v>46622</v>
+        <v>46474</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>Айрос-Систем</v>
+        <v>FELUCCA MARITIME SERVICES</v>
       </c>
       <c r="B1015" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1015" t="str">
-        <v>7804691720</v>
+        <v/>
       </c>
       <c r="D1015" t="str">
         <v>UKAS (IAF)</v>
@@ -23741,21 +23741,21 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1015" t="str">
-        <v>РФ</v>
+        <v>UAE</v>
       </c>
       <c r="G1015">
-        <v>46622</v>
+        <v>46654</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>БорМаш</v>
+        <v>ОБЪЕДИНЕННАЯ КОМПАНИЯ РУСАЛ АНОДНАЯ ФАБРИКА</v>
       </c>
       <c r="B1016" t="str">
         <v>ООО</v>
       </c>
       <c r="C1016" t="str">
-        <v>3604011804</v>
+        <v>7709788673</v>
       </c>
       <c r="D1016" t="str">
         <v>UKAS (IAF)</v>
@@ -23767,67 +23767,67 @@
         <v>РФ</v>
       </c>
       <c r="G1016">
-        <v>46625</v>
+        <v>46597</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>БорМаш</v>
+        <v>Мегатехника СПб</v>
       </c>
       <c r="B1017" t="str">
         <v>ООО</v>
       </c>
       <c r="C1017" t="str">
-        <v>3604011804</v>
+        <v>7801399929</v>
       </c>
       <c r="D1017" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1017" t="str">
-        <v>S.QS.01-2020</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1017" t="str">
         <v>РФ</v>
       </c>
       <c r="G1017">
-        <v>46474</v>
+        <v>46793</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>FELUCCA MARITIME SERVICES</v>
+        <v>Мегатехника СПб</v>
       </c>
       <c r="B1018" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1018" t="str">
-        <v/>
+        <v>7801399929</v>
       </c>
       <c r="D1018" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1018" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1018" t="str">
-        <v>UAE</v>
+        <v>РФ</v>
       </c>
       <c r="G1018">
-        <v>46654</v>
+        <v>46773</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>ОБЪЕДИНЕННАЯ КОМПАНИЯ РУСАЛ АНОДНАЯ ФАБРИКА</v>
+        <v>Мегатехника СПб</v>
       </c>
       <c r="B1019" t="str">
         <v>ООО</v>
       </c>
       <c r="C1019" t="str">
-        <v>7709788673</v>
+        <v>7801399929</v>
       </c>
       <c r="D1019" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1019" t="str">
         <v>ISO 9001:2015</v>
@@ -23836,44 +23836,44 @@
         <v>РФ</v>
       </c>
       <c r="G1019">
-        <v>46597</v>
+        <v>46773</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>Мегатехника СПб</v>
+        <v>ORIENT BULKER EXPRESS SHIP MANAGEMENT</v>
       </c>
       <c r="B1020" t="str">
-        <v>ООО</v>
+        <v>LLC</v>
       </c>
       <c r="C1020" t="str">
-        <v>7801399929</v>
+        <v/>
       </c>
       <c r="D1020" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1020" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1020" t="str">
-        <v>РФ</v>
+        <v>UAE</v>
       </c>
       <c r="G1020">
-        <v>46793</v>
+        <v>46669</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>Мегатехника СПб</v>
+        <v>Электронстандарт-прибор</v>
       </c>
       <c r="B1021" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1021" t="str">
-        <v>7801399929</v>
+        <v>7816145170</v>
       </c>
       <c r="D1021" t="str">
-        <v>EGAC (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1021" t="str">
         <v>ISO 9001:2015</v>
@@ -23882,21 +23882,21 @@
         <v>РФ</v>
       </c>
       <c r="G1021">
-        <v>46773</v>
+        <v>46596</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>Мегатехника СПб</v>
+        <v>НАУЧНО-ПРОИЗВОДСТВЕННОЕ ПРЕДПРИЯТИЕ «РАДАР ММС»</v>
       </c>
       <c r="B1022" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1022" t="str">
-        <v>7801399929</v>
+        <v>7814027653</v>
       </c>
       <c r="D1022" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1022" t="str">
         <v>ISO 9001:2015</v>
@@ -23905,340 +23905,340 @@
         <v>РФ</v>
       </c>
       <c r="G1022">
-        <v>46773</v>
+        <v>46669</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>ORIENT BULKER EXPRESS SHIP MANAGEMENT</v>
+        <v>НАУЧНО-ПРОИЗВОДСТВЕННОЕ ПРЕДПРИЯТИЕ «РАДАР ММС»</v>
       </c>
       <c r="B1023" t="str">
-        <v>LLC</v>
+        <v>АО</v>
       </c>
       <c r="C1023" t="str">
-        <v/>
+        <v>7814027653</v>
       </c>
       <c r="D1023" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1023" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1023" t="str">
-        <v>UAE</v>
+        <v>РФ</v>
       </c>
       <c r="G1023">
-        <v>46669</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>Электронстандарт-прибор</v>
+        <v>НАУЧНО-ПРОИЗВОДСТВЕННОЕ ПРЕДПРИЯТИЕ «РАДАР ММС»</v>
       </c>
       <c r="B1024" t="str">
         <v>АО</v>
       </c>
       <c r="C1024" t="str">
-        <v>7816145170</v>
+        <v>7814027653</v>
       </c>
       <c r="D1024" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1024" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1024" t="str">
         <v>РФ</v>
       </c>
       <c r="G1024">
-        <v>46596</v>
+        <v>46710</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>НАУЧНО-ПРОИЗВОДСТВЕННОЕ ПРЕДПРИЯТИЕ «РАДАР ММС»</v>
+        <v>СКТ-сервис</v>
       </c>
       <c r="B1025" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1025" t="str">
-        <v>7814027653</v>
+        <v>6027207282</v>
       </c>
       <c r="D1025" t="str">
-        <v>ESYD (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1025" t="str">
-        <v>ISO 9001:2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1025" t="str">
         <v>РФ</v>
       </c>
       <c r="G1025">
-        <v>46669</v>
+        <v>46864</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>НАУЧНО-ПРОИЗВОДСТВЕННОЕ ПРЕДПРИЯТИЕ «РАДАР ММС»</v>
+        <v>Общество с ограниченной ответственностью "ИЛМАКС" Завод по производству строительных материалов</v>
       </c>
       <c r="B1026" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1026" t="str">
-        <v>7814027653</v>
+        <v>100070995</v>
       </c>
       <c r="D1026" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1026" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1026" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1026">
-        <v>46260</v>
+        <v>46729</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>НАУЧНО-ПРОИЗВОДСТВЕННОЕ ПРЕДПРИЯТИЕ «РАДАР ММС»</v>
+        <v>Кандрашин А.В</v>
       </c>
       <c r="B1027" t="str">
-        <v>АО</v>
+        <v>ИП</v>
       </c>
       <c r="C1027" t="str">
-        <v>7814027653</v>
+        <v>632106359952</v>
       </c>
       <c r="D1027" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1027" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1027" t="str">
         <v>РФ</v>
       </c>
       <c r="G1027">
-        <v>46710</v>
+        <v>46730</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>СКТ-сервис</v>
+        <v>Шумихинский завод подшипниковых иглороликов</v>
       </c>
       <c r="B1028" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1028" t="str">
-        <v>6027207282</v>
+        <v>4524000693</v>
       </c>
       <c r="D1028" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>EADAS</v>
       </c>
       <c r="E1028" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1028" t="str">
         <v>РФ</v>
       </c>
       <c r="G1028">
-        <v>46864</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>Общество с ограниченной ответственностью "ИЛМАКС" Завод по производству строительных материалов</v>
+        <v>Шумихинский завод подшипниковых иглороликов</v>
       </c>
       <c r="B1029" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1029" t="str">
-        <v>100070995</v>
+        <v>4524000693</v>
       </c>
       <c r="D1029" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1029" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1029" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1029">
-        <v>46729</v>
+        <v>46717</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>Кандрашин А.В</v>
+        <v>СМТ</v>
       </c>
       <c r="B1030" t="str">
-        <v>ИП</v>
+        <v>ООО</v>
       </c>
       <c r="C1030" t="str">
-        <v>632106359952</v>
+        <v>7838510490</v>
       </c>
       <c r="D1030" t="str">
-        <v>EGAC (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1030" t="str">
-        <v>ISO 9001:2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1030" t="str">
         <v>РФ</v>
       </c>
       <c r="G1030">
-        <v>46730</v>
+        <v>46575</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>Шумихинский завод подшипниковых иглороликов</v>
+        <v>Технология</v>
       </c>
       <c r="B1031" t="str">
-        <v>ОАО</v>
+        <v>АО</v>
       </c>
       <c r="C1031" t="str">
-        <v>4524000693</v>
+        <v>1828007328</v>
       </c>
       <c r="D1031" t="str">
-        <v>EADAS</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1031" t="str">
-        <v>16949: 2016</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1031" t="str">
         <v>РФ</v>
       </c>
       <c r="G1031">
-        <v>46227</v>
+        <v>46866</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>Шумихинский завод подшипниковых иглороликов</v>
+        <v>Steam Line Middle East Shipping</v>
       </c>
       <c r="B1032" t="str">
-        <v>ОАО</v>
+        <v/>
       </c>
       <c r="C1032" t="str">
-        <v>4524000693</v>
+        <v/>
       </c>
       <c r="D1032" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1032" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1032" t="str">
-        <v>РФ</v>
+        <v>UAE</v>
       </c>
       <c r="G1032">
-        <v>46717</v>
+        <v>46719</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>СМТ</v>
+        <v>Верейский механический завод</v>
       </c>
       <c r="B1033" t="str">
         <v>ООО</v>
       </c>
       <c r="C1033" t="str">
-        <v>7838510490</v>
+        <v>5030090040</v>
       </c>
       <c r="D1033" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1033" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>S.QS.01-2020</v>
       </c>
       <c r="F1033" t="str">
         <v>РФ</v>
       </c>
       <c r="G1033">
-        <v>46575</v>
+        <v>46362</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>Технология</v>
+        <v>ТМС-групп</v>
       </c>
       <c r="B1034" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1034" t="str">
-        <v>1828007328</v>
+        <v>1644034949</v>
       </c>
       <c r="D1034" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1034" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>S.QS.01-2020</v>
       </c>
       <c r="F1034" t="str">
         <v>РФ</v>
       </c>
       <c r="G1034">
-        <v>46866</v>
+        <v>46467</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>Steam Line Middle East Shipping</v>
+        <v>Титан-Энерго</v>
       </c>
       <c r="B1035" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1035" t="str">
-        <v/>
+        <v>8610024374</v>
       </c>
       <c r="D1035" t="str">
-        <v>UKAS (IAF)</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1035" t="str">
-        <v>ISO 9001:2015</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1035" t="str">
-        <v>UAE</v>
+        <v>РФ</v>
       </c>
       <c r="G1035">
-        <v>46719</v>
+        <v>46699</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>Верейский механический завод</v>
+        <v>СРЗ</v>
       </c>
       <c r="B1036" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1036" t="str">
-        <v>5030090040</v>
+        <v>6317126596</v>
       </c>
       <c r="D1036" t="str">
         <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1036" t="str">
-        <v>S.QS.01-2020</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1036" t="str">
         <v>РФ</v>
       </c>
       <c r="G1036">
-        <v>46362</v>
+        <v>46692</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>ТМС-групп</v>
+        <v>ПСА</v>
       </c>
       <c r="B1037" t="str">
         <v>ООО</v>
       </c>
       <c r="C1037" t="str">
-        <v>1644034949</v>
+        <v>7017462729</v>
       </c>
       <c r="D1037" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -24250,64 +24250,64 @@
         <v>РФ</v>
       </c>
       <c r="G1037">
-        <v>46467</v>
+        <v>46502</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>Титан-Энерго</v>
+        <v>ГК «ЛИМАН»</v>
       </c>
       <c r="B1038" t="str">
         <v>ООО</v>
       </c>
       <c r="C1038" t="str">
-        <v>8610024374</v>
+        <v>7811438750</v>
       </c>
       <c r="D1038" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1038" t="str">
-        <v>S.QS.07-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1038" t="str">
         <v>РФ</v>
       </c>
       <c r="G1038">
-        <v>46699</v>
+        <v>46837</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>СРЗ</v>
+        <v>ГК «ЛИМАН»</v>
       </c>
       <c r="B1039" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1039" t="str">
-        <v>6317126596</v>
+        <v>7811438750</v>
       </c>
       <c r="D1039" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1039" t="str">
-        <v>S.QS.07-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1039" t="str">
         <v>РФ</v>
       </c>
       <c r="G1039">
-        <v>46692</v>
+        <v>46837</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>ПСА</v>
+        <v>ЗМК-Сибирь</v>
       </c>
       <c r="B1040" t="str">
         <v>ООО</v>
       </c>
       <c r="C1040" t="str">
-        <v>7017462729</v>
+        <v>5505217893</v>
       </c>
       <c r="D1040" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -24319,168 +24319,168 @@
         <v>РФ</v>
       </c>
       <c r="G1040">
-        <v>46502</v>
+        <v>46440</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>ГК «ЛИМАН»</v>
+        <v>Б2Б центр</v>
       </c>
       <c r="B1041" t="str">
         <v>ООО</v>
       </c>
       <c r="C1041" t="str">
-        <v>7811438750</v>
+        <v>5034051080</v>
       </c>
       <c r="D1041" t="str">
-        <v>ESYD (IAF)</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1041" t="str">
-        <v>ISO 9001:2015</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1041" t="str">
         <v>РФ</v>
       </c>
       <c r="G1041">
-        <v>46837</v>
+        <v>46677</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>ГК «ЛИМАН»</v>
+        <v>Nikolov S.r.l.</v>
       </c>
       <c r="B1042" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1042" t="str">
-        <v>7811438750</v>
+        <v/>
       </c>
       <c r="D1042" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Accredia</v>
       </c>
       <c r="E1042" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1042" t="str">
-        <v>РФ</v>
+        <v>IT</v>
       </c>
       <c r="G1042">
-        <v>46837</v>
+        <v>46769</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>ЗМК-Сибирь</v>
+        <v>M C G 8 LLC</v>
       </c>
       <c r="B1043" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1043" t="str">
-        <v>5505217893</v>
+        <v/>
       </c>
       <c r="D1043" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1043" t="str">
-        <v>S.QS.01-2020</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1043" t="str">
-        <v>РФ</v>
+        <v>Georgia</v>
       </c>
       <c r="G1043">
-        <v>46440</v>
+        <v>46766</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>Б2Б центр</v>
+        <v>ТДМК</v>
       </c>
       <c r="B1044" t="str">
         <v>ООО</v>
       </c>
       <c r="C1044" t="str">
-        <v>5034051080</v>
+        <v>6321191904</v>
       </c>
       <c r="D1044" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1044" t="str">
-        <v>S.QS.07-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1044" t="str">
         <v>РФ</v>
       </c>
       <c r="G1044">
-        <v>46677</v>
+        <v>46760</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>Nikolov S.r.l.</v>
+        <v>НаноМед</v>
       </c>
       <c r="B1045" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1045" t="str">
-        <v/>
+        <v>5837044394</v>
       </c>
       <c r="D1045" t="str">
-        <v>Accredia</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1045" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1045" t="str">
-        <v>IT</v>
+        <v>РФ</v>
       </c>
       <c r="G1045">
-        <v>46769</v>
+        <v>46781</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>M C G 8 LLC</v>
+        <v>НаноМед</v>
       </c>
       <c r="B1046" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1046" t="str">
-        <v/>
+        <v>5837044394</v>
       </c>
       <c r="D1046" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1046" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1046" t="str">
-        <v>Georgia</v>
+        <v>РФ</v>
       </c>
       <c r="G1046">
-        <v>46766</v>
+        <v>46781</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>ТДМК</v>
+        <v>НаноМед</v>
       </c>
       <c r="B1047" t="str">
         <v>ООО</v>
       </c>
       <c r="C1047" t="str">
-        <v>6321191904</v>
+        <v>5837044394</v>
       </c>
       <c r="D1047" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1047" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1047" t="str">
         <v>РФ</v>
       </c>
       <c r="G1047">
-        <v>46760</v>
+        <v>46822</v>
       </c>
     </row>
     <row r="1048">
@@ -24494,257 +24494,257 @@
         <v>5837044394</v>
       </c>
       <c r="D1048" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1048" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1048" t="str">
         <v>РФ</v>
       </c>
       <c r="G1048">
-        <v>46781</v>
+        <v>46822</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>НаноМед</v>
+        <v>ТЕХНОЛОГИЧЕСКИЕ ПЛЕНКИ</v>
       </c>
       <c r="B1049" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1049" t="str">
-        <v>5837044394</v>
+        <v>5246058666</v>
       </c>
       <c r="D1049" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1049" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1049" t="str">
         <v>РФ</v>
       </c>
       <c r="G1049">
-        <v>46781</v>
+        <v>47112</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>НаноМед</v>
+        <v>ТЕХНОЛОГИЧЕСКИЕ ПЛЕНКИ</v>
       </c>
       <c r="B1050" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1050" t="str">
-        <v>5837044394</v>
+        <v>5246058666</v>
       </c>
       <c r="D1050" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1050" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1050" t="str">
         <v>РФ</v>
       </c>
       <c r="G1050">
-        <v>46822</v>
+        <v>47112</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>НаноМед</v>
+        <v>Шарпинская</v>
       </c>
       <c r="B1051" t="str">
         <v>ООО</v>
       </c>
       <c r="C1051" t="str">
-        <v>5837044394</v>
+        <v>3801142563</v>
       </c>
       <c r="D1051" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1051" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1051" t="str">
         <v>РФ</v>
       </c>
       <c r="G1051">
-        <v>46822</v>
+        <v>46736</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>ТЕХНОЛОГИЧЕСКИЕ ПЛЕНКИ</v>
+        <v>Автогидроусилитель</v>
       </c>
       <c r="B1052" t="str">
-        <v>АО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1052" t="str">
-        <v>5246058666</v>
+        <v>600009233</v>
       </c>
       <c r="D1052" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1052" t="str">
-        <v>ISO 9001:2015</v>
+        <v>IATF 16949:2016</v>
       </c>
       <c r="F1052" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1052">
-        <v>47112</v>
+        <v>46597</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>ТЕХНОЛОГИЧЕСКИЕ ПЛЕНКИ</v>
+        <v>Автогидроусилитель</v>
       </c>
       <c r="B1053" t="str">
-        <v>АО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1053" t="str">
-        <v>5246058666</v>
+        <v>600009233</v>
       </c>
       <c r="D1053" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1053" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1053" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1053">
-        <v>47112</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>Шарпинская</v>
+        <v>ЛАДАПЛАСТ-Т</v>
       </c>
       <c r="B1054" t="str">
         <v>ООО</v>
       </c>
       <c r="C1054" t="str">
-        <v>3801142563</v>
+        <v>6321231498</v>
       </c>
       <c r="D1054" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1054" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1054" t="str">
         <v>РФ</v>
       </c>
       <c r="G1054">
-        <v>46736</v>
+        <v>46731</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>Автогидроусилитель</v>
+        <v>ЛАДАПЛАСТ-Т</v>
       </c>
       <c r="B1055" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1055" t="str">
-        <v>600009233</v>
+        <v>6321231498</v>
       </c>
       <c r="D1055" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1055" t="str">
-        <v>IATF 16949:2016</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1055" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1055">
-        <v>46597</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>Автогидроусилитель</v>
+        <v>АксТим</v>
       </c>
       <c r="B1056" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1056" t="str">
-        <v>600009233</v>
+        <v>7705476338</v>
       </c>
       <c r="D1056" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1056" t="str">
-        <v>16949: 2016</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1056" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1056">
-        <v>46101</v>
+        <v>47038</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>ЛАДАПЛАСТ-Т</v>
+        <v>АксТим Тех</v>
       </c>
       <c r="B1057" t="str">
         <v>ООО</v>
       </c>
       <c r="C1057" t="str">
-        <v>6321231498</v>
+        <v>6950259732</v>
       </c>
       <c r="D1057" t="str">
-        <v>EGAC (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1057" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1057" t="str">
         <v>РФ</v>
       </c>
       <c r="G1057">
-        <v>46731</v>
+        <v>47038</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>ЛАДАПЛАСТ-Т</v>
+        <v>Аксеникс Инновации</v>
       </c>
       <c r="B1058" t="str">
         <v>ООО</v>
       </c>
       <c r="C1058" t="str">
-        <v>6321231498</v>
+        <v>9731109240</v>
       </c>
       <c r="D1058" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1058" t="str">
-        <v>16949: 2016</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1058" t="str">
         <v>РФ</v>
       </c>
       <c r="G1058">
-        <v>46318</v>
+        <v>47038</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>АксТим</v>
+        <v>Аксеникс Нейрокод</v>
       </c>
       <c r="B1059" t="str">
         <v>ООО</v>
       </c>
       <c r="C1059" t="str">
-        <v>7705476338</v>
+        <v>9731136116</v>
       </c>
       <c r="D1059" t="str">
         <v>ESYD (IAF)</v>
@@ -24761,13 +24761,13 @@
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>АксТим Тех</v>
+        <v>Аксеникс Инсайт</v>
       </c>
       <c r="B1060" t="str">
         <v>ООО</v>
       </c>
       <c r="C1060" t="str">
-        <v>6950259732</v>
+        <v>9731121783</v>
       </c>
       <c r="D1060" t="str">
         <v>ESYD (IAF)</v>
@@ -24779,21 +24779,21 @@
         <v>РФ</v>
       </c>
       <c r="G1060">
-        <v>47038</v>
+        <v>47041</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>Аксеникс Инновации</v>
+        <v>АксТим</v>
       </c>
       <c r="B1061" t="str">
         <v>ООО</v>
       </c>
       <c r="C1061" t="str">
-        <v>9731109240</v>
+        <v>7705476338</v>
       </c>
       <c r="D1061" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1061" t="str">
         <v>ISO/IEC 27001:2022</v>
@@ -24807,16 +24807,16 @@
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>Аксеникс Нейрокод</v>
+        <v>АксТим Тех</v>
       </c>
       <c r="B1062" t="str">
         <v>ООО</v>
       </c>
       <c r="C1062" t="str">
-        <v>9731136116</v>
+        <v>6950259732</v>
       </c>
       <c r="D1062" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1062" t="str">
         <v>ISO/IEC 27001:2022</v>
@@ -24830,16 +24830,16 @@
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>Аксеникс Инсайт</v>
+        <v>Аксеникс Инновации</v>
       </c>
       <c r="B1063" t="str">
         <v>ООО</v>
       </c>
       <c r="C1063" t="str">
-        <v>9731121783</v>
+        <v>9731109240</v>
       </c>
       <c r="D1063" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1063" t="str">
         <v>ISO/IEC 27001:2022</v>
@@ -24848,18 +24848,18 @@
         <v>РФ</v>
       </c>
       <c r="G1063">
-        <v>47041</v>
+        <v>47038</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>АксТим</v>
+        <v>Аксеникс Нейрокод</v>
       </c>
       <c r="B1064" t="str">
         <v>ООО</v>
       </c>
       <c r="C1064" t="str">
-        <v>7705476338</v>
+        <v>9731136116</v>
       </c>
       <c r="D1064" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -24876,13 +24876,13 @@
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>АксТим Тех</v>
+        <v>Аксеникс Инсайт</v>
       </c>
       <c r="B1065" t="str">
         <v>ООО</v>
       </c>
       <c r="C1065" t="str">
-        <v>6950259732</v>
+        <v>9731121783</v>
       </c>
       <c r="D1065" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -24894,90 +24894,90 @@
         <v>РФ</v>
       </c>
       <c r="G1065">
-        <v>47038</v>
+        <v>47041</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>Аксеникс Инновации</v>
+        <v>КАТЮША ПРИНТ</v>
       </c>
       <c r="B1066" t="str">
         <v>ООО</v>
       </c>
       <c r="C1066" t="str">
-        <v>9731109240</v>
+        <v>9703037297</v>
       </c>
       <c r="D1066" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1066" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1066" t="str">
         <v>РФ</v>
       </c>
       <c r="G1066">
-        <v>47038</v>
+        <v>46729</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>Аксеникс Нейрокод</v>
+        <v>КАТЮША ПРИНТ</v>
       </c>
       <c r="B1067" t="str">
         <v>ООО</v>
       </c>
       <c r="C1067" t="str">
-        <v>9731136116</v>
+        <v>9703037297</v>
       </c>
       <c r="D1067" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1067" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1067" t="str">
         <v>РФ</v>
       </c>
       <c r="G1067">
-        <v>47038</v>
+        <v>46729</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>Аксеникс Инсайт</v>
+        <v>КАТЮША ПРИНТ</v>
       </c>
       <c r="B1068" t="str">
         <v>ООО</v>
       </c>
       <c r="C1068" t="str">
-        <v>9731121783</v>
+        <v>9703037297</v>
       </c>
       <c r="D1068" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1068" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1068" t="str">
         <v>РФ</v>
       </c>
       <c r="G1068">
-        <v>47041</v>
+        <v>46787</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>КАТЮША ПРИНТ</v>
+        <v>НПП Спектр-ТП</v>
       </c>
       <c r="B1069" t="str">
         <v>ООО</v>
       </c>
       <c r="C1069" t="str">
-        <v>9703037297</v>
+        <v>6415003465</v>
       </c>
       <c r="D1069" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1069" t="str">
         <v>ISO 9001:2015</v>
@@ -24986,53 +24986,53 @@
         <v>РФ</v>
       </c>
       <c r="G1069">
-        <v>46729</v>
+        <v>46744</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>КАТЮША ПРИНТ</v>
+        <v>НПП Спектр-ТП</v>
       </c>
       <c r="B1070" t="str">
         <v>ООО</v>
       </c>
       <c r="C1070" t="str">
-        <v>9703037297</v>
+        <v>6415003465</v>
       </c>
       <c r="D1070" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1070" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1070" t="str">
         <v>РФ</v>
       </c>
       <c r="G1070">
-        <v>46729</v>
+        <v>46744</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>КАТЮША ПРИНТ</v>
+        <v>НПП Спектр-ТП</v>
       </c>
       <c r="B1071" t="str">
         <v>ООО</v>
       </c>
       <c r="C1071" t="str">
-        <v>9703037297</v>
+        <v>6415003465</v>
       </c>
       <c r="D1071" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1071" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1071" t="str">
         <v>РФ</v>
       </c>
       <c r="G1071">
-        <v>46787</v>
+        <v>46744</v>
       </c>
     </row>
     <row r="1072">
@@ -25046,10 +25046,10 @@
         <v>6415003465</v>
       </c>
       <c r="D1072" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1072" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1072" t="str">
         <v>РФ</v>
@@ -25060,36 +25060,36 @@
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>НПП Спектр-ТП</v>
+        <v>ВМПАВТО</v>
       </c>
       <c r="B1073" t="str">
         <v>ООО</v>
       </c>
       <c r="C1073" t="str">
-        <v>6415003465</v>
+        <v>7814069526</v>
       </c>
       <c r="D1073" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1073" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1073" t="str">
         <v>РФ</v>
       </c>
       <c r="G1073">
-        <v>46744</v>
+        <v>46849</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>НПП Спектр-ТП</v>
+        <v>ВМПАВТО</v>
       </c>
       <c r="B1074" t="str">
         <v>ООО</v>
       </c>
       <c r="C1074" t="str">
-        <v>6415003465</v>
+        <v>7814069526</v>
       </c>
       <c r="D1074" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -25101,44 +25101,44 @@
         <v>РФ</v>
       </c>
       <c r="G1074">
-        <v>46744</v>
+        <v>46849</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>НПП Спектр-ТП</v>
+        <v>смазка.ру</v>
       </c>
       <c r="B1075" t="str">
         <v>ООО</v>
       </c>
       <c r="C1075" t="str">
-        <v>6415003465</v>
+        <v>7805276082</v>
       </c>
       <c r="D1075" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1075" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1075" t="str">
         <v>РФ</v>
       </c>
       <c r="G1075">
-        <v>46744</v>
+        <v>46846</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>ВМПАВТО</v>
+        <v>смазка.ру</v>
       </c>
       <c r="B1076" t="str">
         <v>ООО</v>
       </c>
       <c r="C1076" t="str">
-        <v>7814069526</v>
+        <v>7805276082</v>
       </c>
       <c r="D1076" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1076" t="str">
         <v>ISO 9001:2015</v>
@@ -25147,21 +25147,21 @@
         <v>РФ</v>
       </c>
       <c r="G1076">
-        <v>46849</v>
+        <v>46846</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>ВМПАВТО</v>
+        <v>Лайтинг Солюшнс</v>
       </c>
       <c r="B1077" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1077" t="str">
-        <v>7814069526</v>
+        <v>7720906560</v>
       </c>
       <c r="D1077" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1077" t="str">
         <v>ISO 9001:2015</v>
@@ -25170,21 +25170,21 @@
         <v>РФ</v>
       </c>
       <c r="G1077">
-        <v>46849</v>
+        <v>46806</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>смазка.ру</v>
+        <v>Лайтинг Солюшнс</v>
       </c>
       <c r="B1078" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1078" t="str">
-        <v>7805276082</v>
+        <v>7720906560</v>
       </c>
       <c r="D1078" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1078" t="str">
         <v>ISO 9001:2015</v>
@@ -25193,41 +25193,41 @@
         <v>РФ</v>
       </c>
       <c r="G1078">
-        <v>46846</v>
+        <v>46806</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>смазка.ру</v>
+        <v>Лайтинг Солюшнс</v>
       </c>
       <c r="B1079" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1079" t="str">
-        <v>7805276082</v>
+        <v>7720906560</v>
       </c>
       <c r="D1079" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1079" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1079" t="str">
         <v>РФ</v>
       </c>
       <c r="G1079">
-        <v>46846</v>
+        <v>46423</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>Лайтинг Солюшнс</v>
+        <v>"АРТ ДЕКО БИЛД" ЕООД</v>
       </c>
       <c r="B1080" t="str">
-        <v>АО</v>
+        <v/>
       </c>
       <c r="C1080" t="str">
-        <v>7720906560</v>
+        <v/>
       </c>
       <c r="D1080" t="str">
         <v>IAS (IAF)</v>
@@ -25236,148 +25236,148 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1080" t="str">
-        <v>РФ</v>
+        <v>Bulgaria</v>
       </c>
       <c r="G1080">
-        <v>46806</v>
+        <v>46788</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>Лайтинг Солюшнс</v>
+        <v>"АРТ ДЕКО БИЛД" ЕООД</v>
       </c>
       <c r="B1081" t="str">
-        <v>АО</v>
+        <v/>
       </c>
       <c r="C1081" t="str">
-        <v>7720906560</v>
+        <v/>
       </c>
       <c r="D1081" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1081" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1081" t="str">
-        <v>РФ</v>
+        <v>Bulgaria</v>
       </c>
       <c r="G1081">
-        <v>46806</v>
+        <v>46787</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>Лайтинг Солюшнс</v>
+        <v>"АРТ ДЕКО БИЛД" ЕООД</v>
       </c>
       <c r="B1082" t="str">
-        <v>АО</v>
+        <v/>
       </c>
       <c r="C1082" t="str">
-        <v>7720906560</v>
+        <v/>
       </c>
       <c r="D1082" t="str">
-        <v>EADAS</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1082" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1082" t="str">
-        <v>РФ</v>
+        <v>Bulgaria</v>
       </c>
       <c r="G1082">
-        <v>46423</v>
+        <v>46787</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>"АРТ ДЕКО БИЛД" ЕООД</v>
+        <v>Предприятие "Трубопласт"</v>
       </c>
       <c r="B1083" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1083" t="str">
-        <v/>
+        <v>6661044752</v>
       </c>
       <c r="D1083" t="str">
-        <v>IAS (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1083" t="str">
-        <v>ISO 9001:2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1083" t="str">
-        <v>Bulgaria</v>
+        <v>РФ</v>
       </c>
       <c r="G1083">
-        <v>46788</v>
+        <v>46857</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>"АРТ ДЕКО БИЛД" ЕООД</v>
+        <v>"Карачевский завод "Электродеталь"</v>
       </c>
       <c r="B1084" t="str">
-        <v/>
+        <v>АО</v>
       </c>
       <c r="C1084" t="str">
-        <v/>
+        <v>3254511340</v>
       </c>
       <c r="D1084" t="str">
-        <v>IAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1084" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1084" t="str">
-        <v>Bulgaria</v>
+        <v>РФ</v>
       </c>
       <c r="G1084">
-        <v>46787</v>
+        <v>47033</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>"АРТ ДЕКО БИЛД" ЕООД</v>
+        <v>"Карачевский завод "Электродеталь"</v>
       </c>
       <c r="B1085" t="str">
-        <v/>
+        <v>АО</v>
       </c>
       <c r="C1085" t="str">
-        <v/>
+        <v>3254511340</v>
       </c>
       <c r="D1085" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1085" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1085" t="str">
-        <v>Bulgaria</v>
+        <v>РФ</v>
       </c>
       <c r="G1085">
-        <v>46787</v>
+        <v>47033</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>Предприятие "Трубопласт"</v>
+        <v>"Карачевский завод "Электродеталь"</v>
       </c>
       <c r="B1086" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1086" t="str">
-        <v>6661044752</v>
+        <v>3254511340</v>
       </c>
       <c r="D1086" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>EADAS</v>
       </c>
       <c r="E1086" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1086" t="str">
         <v>РФ</v>
       </c>
       <c r="G1086">
-        <v>46857</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="1087">
@@ -25391,16 +25391,16 @@
         <v>3254511340</v>
       </c>
       <c r="D1087" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1087" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1087" t="str">
         <v>РФ</v>
       </c>
       <c r="G1087">
-        <v>47033</v>
+        <v>47035</v>
       </c>
     </row>
     <row r="1088">
@@ -25414,85 +25414,85 @@
         <v>3254511340</v>
       </c>
       <c r="D1088" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1088" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1088" t="str">
         <v>РФ</v>
       </c>
       <c r="G1088">
-        <v>47033</v>
+        <v>47035</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>"Карачевский завод "Электродеталь"</v>
+        <v>QazAlPack</v>
       </c>
       <c r="B1089" t="str">
-        <v>АО</v>
+        <v>LLP</v>
       </c>
       <c r="C1089" t="str">
-        <v>3254511340</v>
+        <v>191140029675</v>
       </c>
       <c r="D1089" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1089" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1089" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1089">
-        <v>46206</v>
+        <v>46823</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>"Карачевский завод "Электродеталь"</v>
+        <v>QazAlPack</v>
       </c>
       <c r="B1090" t="str">
-        <v>АО</v>
+        <v>LLP</v>
       </c>
       <c r="C1090" t="str">
-        <v>3254511340</v>
+        <v>191140029675</v>
       </c>
       <c r="D1090" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1090" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1090" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1090">
-        <v>47035</v>
+        <v>46824</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>"Карачевский завод "Электродеталь"</v>
+        <v>QazAlPack</v>
       </c>
       <c r="B1091" t="str">
-        <v>АО</v>
+        <v>LLP</v>
       </c>
       <c r="C1091" t="str">
-        <v>3254511340</v>
+        <v>191140029675</v>
       </c>
       <c r="D1091" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1091" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1091" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1091">
-        <v>47035</v>
+        <v>46824</v>
       </c>
     </row>
     <row r="1092">
@@ -25509,82 +25509,82 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1092" t="str">
-        <v>ISO 9001:2015</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1092" t="str">
         <v>KZ</v>
       </c>
       <c r="G1092">
-        <v>46823</v>
+        <v>46891</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>QazAlPack</v>
+        <v>Транспортные интерьерные системы</v>
       </c>
       <c r="B1093" t="str">
-        <v>LLP</v>
+        <v>ООО</v>
       </c>
       <c r="C1093" t="str">
-        <v>191140029675</v>
+        <v>6230126270</v>
       </c>
       <c r="D1093" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1093" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1093" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1093">
-        <v>46824</v>
+        <v>47049</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>QazAlPack</v>
+        <v>Транспортные интерьерные системы</v>
       </c>
       <c r="B1094" t="str">
-        <v>LLP</v>
+        <v>ООО</v>
       </c>
       <c r="C1094" t="str">
-        <v>191140029675</v>
+        <v>6230126270</v>
       </c>
       <c r="D1094" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1094" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1094" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1094">
-        <v>46824</v>
+        <v>47049</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>QazAlPack</v>
+        <v>Транспортные интерьерные системы</v>
       </c>
       <c r="B1095" t="str">
-        <v>LLP</v>
+        <v>ООО</v>
       </c>
       <c r="C1095" t="str">
-        <v>191140029675</v>
+        <v>6230126270</v>
       </c>
       <c r="D1095" t="str">
-        <v>ESYD (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1095" t="str">
-        <v>FSSC 22000</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1095" t="str">
-        <v>KZ</v>
-      </c>
-      <c r="G1095">
-        <v>46891</v>
+        <v>РФ</v>
+      </c>
+      <c r="G1095" t="str">
+        <v>с 2026 года</v>
       </c>
     </row>
     <row r="1096">
@@ -25598,73 +25598,73 @@
         <v>6230126270</v>
       </c>
       <c r="D1096" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1096" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1096" t="str">
         <v>РФ</v>
       </c>
       <c r="G1096">
-        <v>47049</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>Транспортные интерьерные системы</v>
+        <v>СмартЭмСис</v>
       </c>
       <c r="B1097" t="str">
         <v>ООО</v>
       </c>
       <c r="C1097" t="str">
-        <v>6230126270</v>
+        <v>7725781700</v>
       </c>
       <c r="D1097" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1097" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1097" t="str">
         <v>РФ</v>
       </c>
       <c r="G1097">
-        <v>47049</v>
+        <v>47035</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>Транспортные интерьерные системы</v>
+        <v>ТехноТерм-Саратов</v>
       </c>
       <c r="B1098" t="str">
         <v>ООО</v>
       </c>
       <c r="C1098" t="str">
-        <v>6230126270</v>
+        <v>6453132158</v>
       </c>
       <c r="D1098" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1098" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1098" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1098" t="str">
-        <v>с 2026 года</v>
+      <c r="G1098">
+        <v>46983</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>Транспортные интерьерные системы</v>
+        <v>Энергия М</v>
       </c>
       <c r="B1099" t="str">
         <v>ООО</v>
       </c>
       <c r="C1099" t="str">
-        <v>6230126270</v>
+        <v>7736365613</v>
       </c>
       <c r="D1099" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -25676,150 +25676,150 @@
         <v>РФ</v>
       </c>
       <c r="G1099">
-        <v>47039</v>
+        <v>46941</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>СмартЭмСис</v>
+        <v>ЛП-Трим</v>
       </c>
       <c r="B1100" t="str">
         <v>ООО</v>
       </c>
       <c r="C1100" t="str">
-        <v>7725781700</v>
+        <v>6321173535</v>
       </c>
       <c r="D1100" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1100" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1100" t="str">
         <v>РФ</v>
       </c>
       <c r="G1100">
-        <v>47035</v>
+        <v>46877</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>ТехноТерм-Саратов</v>
+        <v>ЛП-Трим</v>
       </c>
       <c r="B1101" t="str">
         <v>ООО</v>
       </c>
       <c r="C1101" t="str">
-        <v>6453132158</v>
+        <v>6321173535</v>
       </c>
       <c r="D1101" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1101" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1101" t="str">
         <v>РФ</v>
       </c>
       <c r="G1101">
-        <v>46983</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>Энергия М</v>
+        <v>ЛП-Трим</v>
       </c>
       <c r="B1102" t="str">
         <v>ООО</v>
       </c>
       <c r="C1102" t="str">
-        <v>7736365613</v>
+        <v>6321173535</v>
       </c>
       <c r="D1102" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1102" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1102" t="str">
         <v>РФ</v>
       </c>
       <c r="G1102">
-        <v>46941</v>
+        <v>46877</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>ЛП-Трим</v>
+        <v>“TRIDAN” Ltd.</v>
       </c>
       <c r="B1103" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1103" t="str">
-        <v>6321173535</v>
+        <v/>
       </c>
       <c r="D1103" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1103" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1103" t="str">
-        <v>РФ</v>
+        <v>Bulgaria</v>
       </c>
       <c r="G1103">
-        <v>46877</v>
+        <v>46907</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>ЛП-Трим</v>
+        <v>VOYNOV LTD</v>
       </c>
       <c r="B1104" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1104" t="str">
-        <v>6321173535</v>
+        <v/>
       </c>
       <c r="D1104" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1104" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1104" t="str">
-        <v>РФ</v>
+        <v>Bulgaria</v>
       </c>
       <c r="G1104">
-        <v>46478</v>
+        <v>46857</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>ЛП-Трим</v>
+        <v>VOYNOV LTD</v>
       </c>
       <c r="B1105" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1105" t="str">
-        <v>6321173535</v>
+        <v/>
       </c>
       <c r="D1105" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1105" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1105" t="str">
-        <v>РФ</v>
+        <v>Bulgaria</v>
       </c>
       <c r="G1105">
-        <v>46877</v>
+        <v>46899</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>“TRIDAN” Ltd.</v>
+        <v>ADS Sea center LTD.</v>
       </c>
       <c r="B1106" t="str">
         <v/>
@@ -25837,136 +25837,136 @@
         <v>Bulgaria</v>
       </c>
       <c r="G1106">
-        <v>46907</v>
+        <v>46824</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>VOYNOV LTD</v>
+        <v>Инновационно-внедренческий центр радиационной стерилизации Уральского Федерального Университета имени первого Президента России Б.Н.Ельцина</v>
       </c>
       <c r="B1107" t="str">
-        <v/>
+        <v>ФГАОУ ВО</v>
       </c>
       <c r="C1107" t="str">
-        <v/>
+        <v>6660003190</v>
       </c>
       <c r="D1107" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1107" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1107" t="str">
-        <v>Bulgaria</v>
+        <v>РФ</v>
       </c>
       <c r="G1107">
-        <v>46857</v>
+        <v>46898</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>VOYNOV LTD</v>
+        <v>Инновационно-внедренческий центр радиационной стерилизации Уральского Федерального Университета имени первого Президента России Б.Н.Ельцина</v>
       </c>
       <c r="B1108" t="str">
-        <v/>
+        <v>ФГАОУ ВО</v>
       </c>
       <c r="C1108" t="str">
-        <v/>
+        <v>6660003190</v>
       </c>
       <c r="D1108" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1108" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1108" t="str">
-        <v>Bulgaria</v>
+        <v>РФ</v>
       </c>
       <c r="G1108">
-        <v>46899</v>
+        <v>46898</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>ADS Sea center LTD.</v>
+        <v>КАМА</v>
       </c>
       <c r="B1109" t="str">
-        <v/>
+        <v>АО</v>
       </c>
       <c r="C1109" t="str">
-        <v/>
+        <v>1650404549</v>
       </c>
       <c r="D1109" t="str">
-        <v>UKAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1109" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1109" t="str">
-        <v>Bulgaria</v>
+        <v>РФ</v>
       </c>
       <c r="G1109">
-        <v>46824</v>
+        <v>46901</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>Инновационно-внедренческий центр радиационной стерилизации Уральского Федерального Университета имени первого Президента России Б.Н.Ельцина</v>
+        <v>КАМА</v>
       </c>
       <c r="B1110" t="str">
-        <v>ФГАОУ ВО</v>
+        <v>АО</v>
       </c>
       <c r="C1110" t="str">
-        <v>6660003190</v>
+        <v>1650404549</v>
       </c>
       <c r="D1110" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1110" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1110" t="str">
         <v>РФ</v>
       </c>
       <c r="G1110">
-        <v>46898</v>
+        <v>46901</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>Инновационно-внедренческий центр радиационной стерилизации Уральского Федерального Университета имени первого Президента России Б.Н.Ельцина</v>
+        <v>КАМА</v>
       </c>
       <c r="B1111" t="str">
-        <v>ФГАОУ ВО</v>
+        <v>АО</v>
       </c>
       <c r="C1111" t="str">
-        <v>6660003190</v>
+        <v>1650404549</v>
       </c>
       <c r="D1111" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1111" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1111" t="str">
         <v>РФ</v>
       </c>
       <c r="G1111">
-        <v>46898</v>
+        <v>46902</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>КАМА</v>
+        <v>Интэко Тюбинг</v>
       </c>
       <c r="B1112" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1112" t="str">
-        <v>1650404549</v>
+        <v>1646043628</v>
       </c>
       <c r="D1112" t="str">
-        <v>ESYD (IAF)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1112" t="str">
         <v>ISO 9001:2015</v>
@@ -25975,18 +25975,18 @@
         <v>РФ</v>
       </c>
       <c r="G1112">
-        <v>46901</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>КАМА</v>
+        <v>Интэко Тюбинг</v>
       </c>
       <c r="B1113" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1113" t="str">
-        <v>1650404549</v>
+        <v>1646043628</v>
       </c>
       <c r="D1113" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -25998,30 +25998,30 @@
         <v>РФ</v>
       </c>
       <c r="G1113">
-        <v>46901</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>КАМА</v>
+        <v>Интэко Тюбинг</v>
       </c>
       <c r="B1114" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1114" t="str">
-        <v>1650404549</v>
+        <v>1646043629</v>
       </c>
       <c r="D1114" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1114" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1114" t="str">
         <v>РФ</v>
       </c>
       <c r="G1114">
-        <v>46902</v>
+        <v>46944</v>
       </c>
     </row>
     <row r="1115">
@@ -26032,65 +26032,65 @@
         <v>ООО</v>
       </c>
       <c r="C1115" t="str">
-        <v>1646043628</v>
+        <v>1646043629</v>
       </c>
       <c r="D1115" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1115" t="str">
-        <v>ISO 9001:2015</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1115" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1115">
-        <v>46982</v>
+      <c r="G1115" t="str">
+        <v/>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>Интэко Тюбинг</v>
+        <v>Никольская Консалтинг</v>
       </c>
       <c r="B1116" t="str">
         <v>ООО</v>
       </c>
       <c r="C1116" t="str">
-        <v>1646043628</v>
+        <v>9710096350</v>
       </c>
       <c r="D1116" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1116" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 37001:2016</v>
       </c>
       <c r="F1116" t="str">
         <v>РФ</v>
       </c>
       <c r="G1116">
-        <v>46982</v>
+        <v>46935</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>Интэко Тюбинг</v>
+        <v>Никольская Консалтинг</v>
       </c>
       <c r="B1117" t="str">
         <v>ООО</v>
       </c>
       <c r="C1117" t="str">
-        <v>1646043629</v>
+        <v>9710096350</v>
       </c>
       <c r="D1117" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1117" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 37001:2016</v>
       </c>
       <c r="F1117" t="str">
         <v>РФ</v>
       </c>
       <c r="G1117">
-        <v>46944</v>
+        <v>46935</v>
       </c>
     </row>
     <row r="1118">
@@ -26107,13 +26107,13 @@
         <v>IAS (IAF)</v>
       </c>
       <c r="E1118" t="str">
-        <v>ISO 37001:2016</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1118" t="str">
         <v>РФ</v>
       </c>
       <c r="G1118">
-        <v>46935</v>
+        <v>47105</v>
       </c>
     </row>
     <row r="1119">
@@ -26130,13 +26130,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1119" t="str">
-        <v>ISO 37001:2016</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1119" t="str">
         <v>РФ</v>
       </c>
       <c r="G1119">
-        <v>46935</v>
+        <v>47105</v>
       </c>
     </row>
     <row r="1120">
@@ -26150,10 +26150,10 @@
         <v>9710096350</v>
       </c>
       <c r="D1120" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1120" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ГОСТ Р ИСО/МЭК 27001-2021</v>
       </c>
       <c r="F1120" t="str">
         <v>РФ</v>
@@ -26164,85 +26164,85 @@
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>Никольская Консалтинг</v>
+        <v>Майнинг Элемент</v>
       </c>
       <c r="B1121" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1121" t="str">
-        <v>9710096350</v>
+        <v>7810982090</v>
       </c>
       <c r="D1121" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1121" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1121" t="str">
         <v>РФ</v>
       </c>
       <c r="G1121">
-        <v>47105</v>
+        <v>47025</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>Никольская Консалтинг</v>
+        <v>Майнинг Элемент</v>
       </c>
       <c r="B1122" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1122" t="str">
-        <v>9710096350</v>
+        <v>7810982090</v>
       </c>
       <c r="D1122" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1122" t="str">
-        <v>ГОСТ Р ИСО/МЭК 27001-2021</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1122" t="str">
         <v>РФ</v>
       </c>
       <c r="G1122">
-        <v>47105</v>
+        <v>47025</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>Майнинг Элемент</v>
+        <v>Гротекс</v>
       </c>
       <c r="B1123" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1123" t="str">
-        <v>7810982090</v>
+        <v>7814459396</v>
       </c>
       <c r="D1123" t="str">
-        <v>ESYD (IAF)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1123" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1123" t="str">
         <v>РФ</v>
       </c>
       <c r="G1123">
-        <v>47025</v>
+        <v>46913</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>Майнинг Элемент</v>
+        <v>НПП КуйбышевТелеком - Метрология</v>
       </c>
       <c r="B1124" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1124" t="str">
-        <v>7810982090</v>
+        <v>6312102369</v>
       </c>
       <c r="D1124" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1124" t="str">
         <v>ISO 9001:2015</v>
@@ -26251,30 +26251,30 @@
         <v>РФ</v>
       </c>
       <c r="G1124">
-        <v>47025</v>
+        <v>46958</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>Гротекс</v>
+        <v>НПП КуйбышевТелеком - Метрология</v>
       </c>
       <c r="B1125" t="str">
         <v>ООО</v>
       </c>
       <c r="C1125" t="str">
-        <v>7814459396</v>
+        <v>6312102369</v>
       </c>
       <c r="D1125" t="str">
-        <v>IAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1125" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1125" t="str">
         <v>РФ</v>
       </c>
       <c r="G1125">
-        <v>46913</v>
+        <v>46958</v>
       </c>
     </row>
     <row r="1126">
@@ -26291,13 +26291,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1126" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1126" t="str">
         <v>РФ</v>
       </c>
       <c r="G1126">
-        <v>46958</v>
+        <v>46960</v>
       </c>
     </row>
     <row r="1127">
@@ -26311,10 +26311,10 @@
         <v>6312102369</v>
       </c>
       <c r="D1127" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1127" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1127" t="str">
         <v>РФ</v>
@@ -26334,16 +26334,16 @@
         <v>6312102369</v>
       </c>
       <c r="D1128" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1128" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1128" t="str">
         <v>РФ</v>
       </c>
       <c r="G1128">
-        <v>46960</v>
+        <v>46958</v>
       </c>
     </row>
     <row r="1129">
@@ -26360,13 +26360,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1129" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1129" t="str">
         <v>РФ</v>
       </c>
       <c r="G1129">
-        <v>46958</v>
+        <v>46960</v>
       </c>
     </row>
     <row r="1130">
@@ -26380,16 +26380,16 @@
         <v>6312102369</v>
       </c>
       <c r="D1130" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1130" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1130" t="str">
         <v>РФ</v>
       </c>
       <c r="G1130">
-        <v>46958</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1131">
@@ -26400,19 +26400,19 @@
         <v>ООО</v>
       </c>
       <c r="C1131" t="str">
-        <v>6312102369</v>
+        <v>6312102370</v>
       </c>
       <c r="D1131" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1131" t="str">
-        <v>ISO 45001:2018</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1131" t="str">
         <v>РФ</v>
       </c>
       <c r="G1131">
-        <v>46960</v>
+        <v>46819</v>
       </c>
     </row>
     <row r="1132">
@@ -26423,42 +26423,42 @@
         <v>ООО</v>
       </c>
       <c r="C1132" t="str">
-        <v>6312102369</v>
+        <v>6312102370</v>
       </c>
       <c r="D1132" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1132" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1132" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1132">
-        <v>47039</v>
+      <c r="G1132" t="str">
+        <v/>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>НПП КуйбышевТелеком - Метрология</v>
+        <v>"Tengri Tyres"</v>
       </c>
       <c r="B1133" t="str">
-        <v>ООО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1133" t="str">
-        <v>6312102370</v>
+        <v>201040014370</v>
       </c>
       <c r="D1133" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1133" t="str">
-        <v>S.QS.07-2024</v>
+        <v>IATF 16949:2016</v>
       </c>
       <c r="F1133" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1133">
-        <v>46819</v>
+        <v>46949</v>
       </c>
     </row>
     <row r="1134">
@@ -26472,39 +26472,39 @@
         <v>201040014370</v>
       </c>
       <c r="D1134" t="str">
-        <v>UKAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1134" t="str">
-        <v>IATF 16949:2016</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1134" t="str">
         <v>KZ</v>
       </c>
       <c r="G1134">
-        <v>46949</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>"Tengri Tyres"</v>
+        <v>ГЕРС Технолоджи</v>
       </c>
       <c r="B1135" t="str">
-        <v>ТОО</v>
+        <v>ООО</v>
       </c>
       <c r="C1135" t="str">
-        <v>201040014370</v>
+        <v>5050085880</v>
       </c>
       <c r="D1135" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1135" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1135" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1135">
-        <v>47110</v>
+        <v>46991</v>
       </c>
     </row>
     <row r="1136">
@@ -26518,7 +26518,7 @@
         <v>5050085880</v>
       </c>
       <c r="D1136" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1136" t="str">
         <v>ISO 9001:2015</v>
@@ -26532,48 +26532,48 @@
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>ГЕРС Технолоджи</v>
+        <v>"Учебно-методический центр" Федеральной службы по экологическому, технологическому и атомному надзору</v>
       </c>
       <c r="B1137" t="str">
-        <v>ООО</v>
+        <v>ФГБОУ ДПО</v>
       </c>
       <c r="C1137" t="str">
-        <v>5050085880</v>
+        <v>7723320277</v>
       </c>
       <c r="D1137" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1137" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1137" t="str">
         <v>РФ</v>
       </c>
       <c r="G1137">
-        <v>46991</v>
+        <v>46952</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>"Учебно-методический центр" Федеральной службы по экологическому, технологическому и атомному надзору</v>
+        <v>ЭЛЕКТРОПИТАНИЕ</v>
       </c>
       <c r="B1138" t="str">
-        <v>ФГБОУ ДПО</v>
+        <v>ООО НПЦ</v>
       </c>
       <c r="C1138" t="str">
-        <v>7723320277</v>
+        <v>583503532636</v>
       </c>
       <c r="D1138" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1138" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1138" t="str">
         <v>РФ</v>
       </c>
       <c r="G1138">
-        <v>46952</v>
+        <v>46948</v>
       </c>
     </row>
     <row r="1139">
@@ -26587,7 +26587,7 @@
         <v>583503532636</v>
       </c>
       <c r="D1139" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1139" t="str">
         <v>ISO 9001:2015</v>
@@ -26601,16 +26601,16 @@
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>ЭЛЕКТРОПИТАНИЕ</v>
+        <v>АМПРЕСС</v>
       </c>
       <c r="B1140" t="str">
-        <v>ООО НПЦ</v>
+        <v>ООО</v>
       </c>
       <c r="C1140" t="str">
-        <v>583503532636</v>
+        <v>632127272251</v>
       </c>
       <c r="D1140" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1140" t="str">
         <v>ISO 9001:2015</v>
@@ -26633,7 +26633,7 @@
         <v>632127272251</v>
       </c>
       <c r="D1141" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1141" t="str">
         <v>ISO 9001:2015</v>
@@ -26653,19 +26653,19 @@
         <v>ООО</v>
       </c>
       <c r="C1142" t="str">
-        <v>632127272251</v>
+        <v>6382061691</v>
       </c>
       <c r="D1142" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1142" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1142" t="str">
         <v>РФ</v>
       </c>
       <c r="G1142">
-        <v>46948</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="1143">
@@ -26679,50 +26679,50 @@
         <v>6382061691</v>
       </c>
       <c r="D1143" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1143" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1143" t="str">
         <v>РФ</v>
       </c>
       <c r="G1143">
-        <v>46212</v>
+        <v>47010</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>АМПРЕСС</v>
+        <v>Научно-производственная фирма "Моссар"</v>
       </c>
       <c r="B1144" t="str">
         <v>ООО</v>
       </c>
       <c r="C1144" t="str">
-        <v>6382061691</v>
+        <v>6454073547</v>
       </c>
       <c r="D1144" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1144" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1144" t="str">
         <v>РФ</v>
       </c>
       <c r="G1144">
-        <v>47010</v>
+        <v>47166</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>Научно-производственная фирма "Моссар"</v>
+        <v>Восход ПЛЮС</v>
       </c>
       <c r="B1145" t="str">
         <v>ООО</v>
       </c>
       <c r="C1145" t="str">
-        <v>6454073547</v>
+        <v>7724383865</v>
       </c>
       <c r="D1145" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -26734,30 +26734,30 @@
         <v>РФ</v>
       </c>
       <c r="G1145">
-        <v>47166</v>
+        <v>46987</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>Восход ПЛЮС</v>
+        <v>Научно-производственная фирма "БИОСС"</v>
       </c>
       <c r="B1146" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1146" t="str">
-        <v>7724383865</v>
+        <v>7735126570</v>
       </c>
       <c r="D1146" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1146" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1146" t="str">
         <v>РФ</v>
       </c>
       <c r="G1146">
-        <v>46987</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1147">
@@ -26771,7 +26771,7 @@
         <v>7735126570</v>
       </c>
       <c r="D1147" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1147" t="str">
         <v>ISO 13485:2016</v>
@@ -26794,39 +26794,39 @@
         <v>7735126570</v>
       </c>
       <c r="D1148" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1148" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1148" t="str">
         <v>РФ</v>
       </c>
       <c r="G1148">
-        <v>47039</v>
+        <v>47063</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>Научно-производственная фирма "БИОСС"</v>
+        <v>РСтартер</v>
       </c>
       <c r="B1149" t="str">
         <v>АО</v>
       </c>
       <c r="C1149" t="str">
-        <v>7735126570</v>
+        <v>5258156241</v>
       </c>
       <c r="D1149" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1149" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1149" t="str">
         <v>РФ</v>
       </c>
       <c r="G1149">
-        <v>47063</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="1150">
@@ -26840,16 +26840,16 @@
         <v>5258156241</v>
       </c>
       <c r="D1150" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1150" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1150" t="str">
         <v>РФ</v>
       </c>
       <c r="G1150">
-        <v>46177</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1151">
@@ -26863,16 +26863,16 @@
         <v>5258156241</v>
       </c>
       <c r="D1151" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1151" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1151" t="str">
         <v>РФ</v>
       </c>
       <c r="G1151">
-        <v>46982</v>
+        <v>46983</v>
       </c>
     </row>
     <row r="1152">
@@ -26886,7 +26886,7 @@
         <v>5258156241</v>
       </c>
       <c r="D1152" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1152" t="str">
         <v>ISO 9001:2015</v>
@@ -26900,82 +26900,82 @@
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>РСтартер</v>
+        <v>ЕТС Трейд</v>
       </c>
       <c r="B1153" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1153" t="str">
-        <v>5258156241</v>
+        <v>7224069315</v>
       </c>
       <c r="D1153" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1153" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1153" t="str">
         <v>РФ</v>
       </c>
       <c r="G1153">
-        <v>46983</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>ЕТС Трейд</v>
+        <v>НПП Тасма</v>
       </c>
       <c r="B1154" t="str">
         <v>ООО</v>
       </c>
       <c r="C1154" t="str">
-        <v>7224069315</v>
+        <v>1658105396</v>
       </c>
       <c r="D1154" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1154" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1154" t="str">
         <v>РФ</v>
       </c>
       <c r="G1154">
-        <v>46996</v>
+        <v>46998</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>НПП Тасма</v>
+        <v>Завод Красный Якорь</v>
       </c>
       <c r="B1155" t="str">
-        <v>ООО</v>
+        <v>ПАО</v>
       </c>
       <c r="C1155" t="str">
-        <v>1658105396</v>
+        <v>5257005049</v>
       </c>
       <c r="D1155" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1155" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1155" t="str">
         <v>РФ</v>
       </c>
       <c r="G1155">
-        <v>46998</v>
+        <v>46602</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>Завод Красный Якорь</v>
+        <v>Морское грузовое бюро</v>
       </c>
       <c r="B1156" t="str">
-        <v>ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1156" t="str">
-        <v>5257005049</v>
+        <v>4705063303</v>
       </c>
       <c r="D1156" t="str">
         <v>ESYD (IAF)</v>
@@ -26987,18 +26987,18 @@
         <v>РФ</v>
       </c>
       <c r="G1156">
-        <v>46602</v>
+        <v>46649</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>Морское грузовое бюро</v>
+        <v>GRETIMYBE</v>
       </c>
       <c r="B1157" t="str">
-        <v>ООО</v>
+        <v>UAB</v>
       </c>
       <c r="C1157" t="str">
-        <v>4705063303</v>
+        <v>LT 415578811</v>
       </c>
       <c r="D1157" t="str">
         <v>ESYD (IAF)</v>
@@ -27007,21 +27007,21 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1157" t="str">
-        <v>РФ</v>
+        <v>Lithuania</v>
       </c>
       <c r="G1157">
-        <v>46649</v>
+        <v>46652</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>GRETIMYBE</v>
+        <v>Санрайз</v>
       </c>
       <c r="B1158" t="str">
-        <v>UAB</v>
+        <v>ООО</v>
       </c>
       <c r="C1158" t="str">
-        <v>LT 415578811</v>
+        <v>7825449671</v>
       </c>
       <c r="D1158" t="str">
         <v>ESYD (IAF)</v>
@@ -27033,7 +27033,7 @@
         <v>Lithuania</v>
       </c>
       <c r="G1158">
-        <v>46652</v>
+        <v>46897</v>
       </c>
     </row>
     <row r="1159">
@@ -27050,36 +27050,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1159" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1159" t="str">
-        <v>Lithuania</v>
+        <v>РФ</v>
       </c>
       <c r="G1159">
-        <v>46897</v>
+        <v>46899</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>Санрайз</v>
+        <v>Архангельский фанерный завод</v>
       </c>
       <c r="B1160" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1160" t="str">
-        <v>7825449671</v>
+        <v>2903004722</v>
       </c>
       <c r="D1160" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1160" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1160" t="str">
         <v>РФ</v>
       </c>
       <c r="G1160">
-        <v>46899</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="1161">
@@ -27096,7 +27096,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1161" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1161" t="str">
         <v>РФ</v>
@@ -27119,7 +27119,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1162" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1162" t="str">
         <v>РФ</v>
@@ -27130,19 +27130,19 @@
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>Архангельский фанерный завод</v>
+        <v>Академия бизнеса</v>
       </c>
       <c r="B1163" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1163" t="str">
-        <v>2903004722</v>
+        <v>7801499948</v>
       </c>
       <c r="D1163" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1163" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1163" t="str">
         <v>РФ</v>
@@ -27153,13 +27153,13 @@
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>Академия бизнеса</v>
+        <v>ИЦ "Технохим"</v>
       </c>
       <c r="B1164" t="str">
-        <v>ООО</v>
+        <v>ЗАО</v>
       </c>
       <c r="C1164" t="str">
-        <v>7801499948</v>
+        <v>7813348421</v>
       </c>
       <c r="D1164" t="str">
         <v>ESYD (IAF)</v>
@@ -27171,18 +27171,18 @@
         <v>РФ</v>
       </c>
       <c r="G1164">
-        <v>46750</v>
+        <v>46450</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>ИЦ "Технохим"</v>
+        <v>НПП "СЗГП"</v>
       </c>
       <c r="B1165" t="str">
         <v>ЗАО</v>
       </c>
       <c r="C1165" t="str">
-        <v>7813348421</v>
+        <v>7813385303</v>
       </c>
       <c r="D1165" t="str">
         <v>ESYD (IAF)</v>
@@ -27194,18 +27194,18 @@
         <v>РФ</v>
       </c>
       <c r="G1165">
-        <v>46450</v>
+        <v>46775</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>НПП "СЗГП"</v>
+        <v>Сыктывкарский ликеро-водочный завод</v>
       </c>
       <c r="B1166" t="str">
-        <v>ЗАО</v>
+        <v>АО</v>
       </c>
       <c r="C1166" t="str">
-        <v>7813385303</v>
+        <v>1101205623</v>
       </c>
       <c r="D1166" t="str">
         <v>ESYD (IAF)</v>
@@ -27217,7 +27217,7 @@
         <v>РФ</v>
       </c>
       <c r="G1166">
-        <v>46775</v>
+        <v>46906</v>
       </c>
     </row>
     <row r="1167">
@@ -27234,47 +27234,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1167" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1167" t="str">
         <v>РФ</v>
       </c>
       <c r="G1167">
-        <v>46906</v>
+        <v>46909</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>Сыктывкарский ликеро-водочный завод</v>
+        <v>Ижевский электромеханический завод "Купол"</v>
       </c>
       <c r="B1168" t="str">
         <v>АО</v>
       </c>
       <c r="C1168" t="str">
-        <v>1101205623</v>
+        <v>1831083343</v>
       </c>
       <c r="D1168" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1168" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1168" t="str">
         <v>РФ</v>
       </c>
       <c r="G1168">
-        <v>46909</v>
+        <v>46980</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>Ижевский электромеханический завод "Купол"</v>
+        <v>Арзамасский филиал ООО "Сен-Гобен Строительная Продукция Рус"</v>
       </c>
       <c r="B1169" t="str">
-        <v>АО</v>
+        <v/>
       </c>
       <c r="C1169" t="str">
-        <v>1831083343</v>
+        <v>5011020537</v>
       </c>
       <c r="D1169" t="str">
         <v>ESYD (IAF)</v>
@@ -27286,18 +27286,18 @@
         <v>РФ</v>
       </c>
       <c r="G1169">
-        <v>46980</v>
+        <v>47086</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>Арзамасский филиал ООО "Сен-Гобен Строительная Продукция Рус"</v>
+        <v>Белэнергомаш- БЗЭМ</v>
       </c>
       <c r="B1170" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1170" t="str">
-        <v>5011020537</v>
+        <v>3123315768</v>
       </c>
       <c r="D1170" t="str">
         <v>ESYD (IAF)</v>
@@ -27309,7 +27309,7 @@
         <v>РФ</v>
       </c>
       <c r="G1170">
-        <v>47086</v>
+        <v>46409</v>
       </c>
     </row>
     <row r="1171">
@@ -27326,13 +27326,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1171" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1171" t="str">
         <v>РФ</v>
       </c>
       <c r="G1171">
-        <v>46409</v>
+        <v>46411</v>
       </c>
     </row>
     <row r="1172">
@@ -27349,7 +27349,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1172" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1172" t="str">
         <v>РФ</v>
@@ -27360,25 +27360,25 @@
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>Белэнергомаш- БЗЭМ</v>
+        <v>Калужский научно-исследовательский радиотехнический институт</v>
       </c>
       <c r="B1173" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1173" t="str">
-        <v>3123315768</v>
+        <v>4007017378</v>
       </c>
       <c r="D1173" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1173" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1173" t="str">
         <v>РФ</v>
       </c>
       <c r="G1173">
-        <v>46411</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="1174">
@@ -27395,47 +27395,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1174" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1174" t="str">
         <v>РФ</v>
       </c>
       <c r="G1174">
-        <v>46317</v>
+        <v>46433</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>Калужский научно-исследовательский радиотехнический институт</v>
+        <v>НПП "БАСЭТ"</v>
       </c>
       <c r="B1175" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1175" t="str">
-        <v>4007017378</v>
+        <v>269001177</v>
       </c>
       <c r="D1175" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1175" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1175" t="str">
         <v>РФ</v>
       </c>
       <c r="G1175">
-        <v>46433</v>
+        <v>46488</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>НПП "БАСЭТ"</v>
+        <v>НПП "Петролайн-А"</v>
       </c>
       <c r="B1176" t="str">
         <v>ООО</v>
       </c>
       <c r="C1176" t="str">
-        <v>269001177</v>
+        <v>1650081440</v>
       </c>
       <c r="D1176" t="str">
         <v>ESYD (IAF)</v>
@@ -27447,18 +27447,18 @@
         <v>РФ</v>
       </c>
       <c r="G1176">
-        <v>46488</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>НПП "Петролайн-А"</v>
+        <v>ООО "Энергоспецмонтаж"</v>
       </c>
       <c r="B1177" t="str">
         <v>ООО</v>
       </c>
       <c r="C1177" t="str">
-        <v>1650081440</v>
+        <v>1837006602</v>
       </c>
       <c r="D1177" t="str">
         <v>ESYD (IAF)</v>
@@ -27470,18 +27470,18 @@
         <v>РФ</v>
       </c>
       <c r="G1177">
-        <v>46165</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>ООО "Энергоспецмонтаж"</v>
+        <v>НИКИМТ-АТОМСТРОЙ</v>
       </c>
       <c r="B1178" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1178" t="str">
-        <v>1837006602</v>
+        <v>7715719854</v>
       </c>
       <c r="D1178" t="str">
         <v>ESYD (IAF)</v>
@@ -27493,7 +27493,7 @@
         <v>РФ</v>
       </c>
       <c r="G1178">
-        <v>46214</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="1179">
@@ -27510,13 +27510,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1179" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1179" t="str">
         <v>РФ</v>
       </c>
       <c r="G1179">
-        <v>46244</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="1180">
@@ -27533,70 +27533,70 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1180" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1180" t="str">
         <v>РФ</v>
       </c>
       <c r="G1180">
-        <v>46265</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>НИКИМТ-АТОМСТРОЙ</v>
+        <v>Карбофер Метсервис</v>
       </c>
       <c r="B1181" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1181" t="str">
-        <v>7715719854</v>
+        <v>3662148389</v>
       </c>
       <c r="D1181" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1181" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1181" t="str">
         <v>РФ</v>
       </c>
       <c r="G1181">
-        <v>46326</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>Карбофер Метсервис</v>
+        <v>Белая Дача Волга</v>
       </c>
       <c r="B1182" t="str">
         <v>ООО</v>
       </c>
       <c r="C1182" t="str">
-        <v>3662148389</v>
+        <v>5027307207</v>
       </c>
       <c r="D1182" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1182" t="str">
-        <v>ISO 9001:2015</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1182" t="str">
         <v>РФ</v>
       </c>
       <c r="G1182">
-        <v>46229</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>Белая Дача Волга</v>
+        <v>Воплощение</v>
       </c>
       <c r="B1183" t="str">
         <v>ООО</v>
       </c>
       <c r="C1183" t="str">
-        <v>5027307207</v>
+        <v>7106077126</v>
       </c>
       <c r="D1183" t="str">
         <v>ESYD (IAF)</v>
@@ -27608,18 +27608,18 @@
         <v>РФ</v>
       </c>
       <c r="G1183">
-        <v>46212</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>Воплощение</v>
+        <v>Красный маяк</v>
       </c>
       <c r="B1184" t="str">
         <v>ООО</v>
       </c>
       <c r="C1184" t="str">
-        <v>7106077126</v>
+        <v>7609027393</v>
       </c>
       <c r="D1184" t="str">
         <v>ESYD (IAF)</v>
@@ -27631,18 +27631,18 @@
         <v>РФ</v>
       </c>
       <c r="G1184">
-        <v>46200</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>Красный маяк</v>
+        <v>АПК Астраханский</v>
       </c>
       <c r="B1185" t="str">
         <v>ООО</v>
       </c>
       <c r="C1185" t="str">
-        <v>7609027393</v>
+        <v>3023008925</v>
       </c>
       <c r="D1185" t="str">
         <v>ESYD (IAF)</v>
@@ -27654,7 +27654,7 @@
         <v>РФ</v>
       </c>
       <c r="G1185">
-        <v>46290</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="1186">
@@ -27671,7 +27671,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1186" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>GRASP</v>
       </c>
       <c r="F1186" t="str">
         <v>РФ</v>
@@ -27694,70 +27694,70 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1187" t="str">
-        <v>GRASP</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1187" t="str">
         <v>РФ</v>
       </c>
       <c r="G1187">
-        <v>46284</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="str">
-        <v>АПК Астраханский</v>
+        <v>НУЦ "Качество"</v>
       </c>
       <c r="B1188" t="str">
         <v>ООО</v>
       </c>
       <c r="C1188" t="str">
-        <v>3023008925</v>
+        <v>7715552355</v>
       </c>
       <c r="D1188" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1188" t="str">
-        <v>FSSC 22000</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1188" t="str">
         <v>РФ</v>
       </c>
       <c r="G1188">
-        <v>46311</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="str">
-        <v>НУЦ "Качество"</v>
+        <v>BLESS S.R.</v>
       </c>
       <c r="B1189" t="str">
         <v>ООО</v>
       </c>
       <c r="C1189" t="str">
-        <v>7715552355</v>
+        <v>309422741</v>
       </c>
       <c r="D1189" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1189" t="str">
-        <v>ISO 9001:2015</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1189" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1189">
-        <v>46228</v>
+        <v>UZ</v>
+      </c>
+      <c r="G1189" t="str">
+        <v>Сертификат еще не выдан</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="str">
-        <v>BLESS S.R.</v>
+        <v>Иотова А.А.</v>
       </c>
       <c r="B1190" t="str">
-        <v>ООО</v>
+        <v>ИП</v>
       </c>
       <c r="C1190" t="str">
-        <v>309422741</v>
+        <v>500702017601</v>
       </c>
       <c r="D1190" t="str">
         <v>ESYD (IAF)</v>
@@ -27766,21 +27766,21 @@
         <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1190" t="str">
-        <v>UZ</v>
-      </c>
-      <c r="G1190" t="str">
-        <v>Сертификат еще не выдан</v>
+        <v>РФ</v>
+      </c>
+      <c r="G1190">
+        <v>46247</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="str">
-        <v>Иотова А.А.</v>
+        <v>Сунгатов Разиль</v>
       </c>
       <c r="B1191" t="str">
         <v>ИП</v>
       </c>
       <c r="C1191" t="str">
-        <v>500702017601</v>
+        <v>300902421774</v>
       </c>
       <c r="D1191" t="str">
         <v>ESYD (IAF)</v>
@@ -27792,18 +27792,18 @@
         <v>РФ</v>
       </c>
       <c r="G1191">
-        <v>46247</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="str">
-        <v>Сунгатов Разиль</v>
+        <v>Веселый агроном</v>
       </c>
       <c r="B1192" t="str">
-        <v>ИП</v>
+        <v>ООО</v>
       </c>
       <c r="C1192" t="str">
-        <v>300902421774</v>
+        <v>5007082611</v>
       </c>
       <c r="D1192" t="str">
         <v>ESYD (IAF)</v>
@@ -27815,41 +27815,41 @@
         <v>РФ</v>
       </c>
       <c r="G1192">
-        <v>46304</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="str">
-        <v>Веселый агроном</v>
+        <v>"Пятигорский "Импульс"</v>
       </c>
       <c r="B1193" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1193" t="str">
-        <v>5007082611</v>
+        <v>2632005656</v>
       </c>
       <c r="D1193" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1193" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1193" t="str">
         <v>РФ</v>
       </c>
       <c r="G1193">
-        <v>46289</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="str">
-        <v>"Пятигорский "Импульс"</v>
+        <v>"Швабе"</v>
       </c>
       <c r="B1194" t="str">
-        <v>ОАО</v>
+        <v>АО</v>
       </c>
       <c r="C1194" t="str">
-        <v>2632005656</v>
+        <v>7717671799</v>
       </c>
       <c r="D1194" t="str">
         <v>ESYD (IAF)</v>
@@ -27861,18 +27861,18 @@
         <v>РФ</v>
       </c>
       <c r="G1194">
-        <v>46341</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="str">
-        <v>"Швабе"</v>
+        <v>"ПИТЕРАТОММАШ"</v>
       </c>
       <c r="B1195" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1195" t="str">
-        <v>7717671799</v>
+        <v>7805658638</v>
       </c>
       <c r="D1195" t="str">
         <v>ESYD (IAF)</v>
@@ -27884,18 +27884,18 @@
         <v>РФ</v>
       </c>
       <c r="G1195">
-        <v>46320</v>
+        <v>46422</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="str">
-        <v>"ПИТЕРАТОММАШ"</v>
+        <v>"Морской лабораторый комплекс"</v>
       </c>
       <c r="B1196" t="str">
         <v>ООО</v>
       </c>
       <c r="C1196" t="str">
-        <v>7805658638</v>
+        <v>7816640696</v>
       </c>
       <c r="D1196" t="str">
         <v>ESYD (IAF)</v>
@@ -27907,64 +27907,64 @@
         <v>РФ</v>
       </c>
       <c r="G1196">
-        <v>46422</v>
+        <v>46409</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="str">
-        <v>"Морской лабораторый комплекс"</v>
+        <v>«Байкальская энергетическая компания»</v>
       </c>
       <c r="B1197" t="str">
         <v>ООО</v>
       </c>
       <c r="C1197" t="str">
-        <v>7816640696</v>
+        <v>3808229774</v>
       </c>
       <c r="D1197" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1197" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1197" t="str">
         <v>РФ</v>
       </c>
       <c r="G1197">
-        <v>46409</v>
+        <v>46375</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="str">
-        <v>«Байкальская энергетическая компания»</v>
+        <v>"Транснефть-Диаскан"</v>
       </c>
       <c r="B1198" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1198" t="str">
-        <v>3808229774</v>
+        <v>5072703668</v>
       </c>
       <c r="D1198" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1198" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1198" t="str">
         <v>РФ</v>
       </c>
       <c r="G1198">
-        <v>46375</v>
+        <v>46482</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="str">
-        <v>"Транснефть-Диаскан"</v>
+        <v>"С-плюс"</v>
       </c>
       <c r="B1199" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1199" t="str">
-        <v>5072703668</v>
+        <v>7720325407</v>
       </c>
       <c r="D1199" t="str">
         <v>ESYD (IAF)</v>
@@ -27976,18 +27976,18 @@
         <v>РФ</v>
       </c>
       <c r="G1199">
-        <v>46482</v>
+        <v>46674</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="str">
-        <v>"С-плюс"</v>
+        <v>"ЦНИИМФ"</v>
       </c>
       <c r="B1200" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1200" t="str">
-        <v>7720325407</v>
+        <v>7815001288</v>
       </c>
       <c r="D1200" t="str">
         <v>ESYD (IAF)</v>
@@ -27999,18 +27999,18 @@
         <v>РФ</v>
       </c>
       <c r="G1200">
-        <v>46674</v>
+        <v>46514</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="str">
-        <v>"ЦНИИМФ"</v>
+        <v>"ВЗПП - Микрон"</v>
       </c>
       <c r="B1201" t="str">
         <v>АО</v>
       </c>
       <c r="C1201" t="str">
-        <v>7815001288</v>
+        <v>3661020890</v>
       </c>
       <c r="D1201" t="str">
         <v>ESYD (IAF)</v>
@@ -28022,18 +28022,18 @@
         <v>РФ</v>
       </c>
       <c r="G1201">
-        <v>46514</v>
+        <v>46598</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="str">
-        <v>"ВЗПП - Микрон"</v>
+        <v>Ostec Enterprise Ltd.</v>
       </c>
       <c r="B1202" t="str">
-        <v>АО</v>
+        <v/>
       </c>
       <c r="C1202" t="str">
-        <v>3661020890</v>
+        <v>7731480806</v>
       </c>
       <c r="D1202" t="str">
         <v>ESYD (IAF)</v>
@@ -28045,53 +28045,53 @@
         <v>РФ</v>
       </c>
       <c r="G1202">
-        <v>46598</v>
+        <v>46593</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="str">
-        <v>Ostec Enterprise Ltd.</v>
+        <v>«Национальный расчетный депозитарий»</v>
       </c>
       <c r="B1203" t="str">
-        <v/>
+        <v>НКО АО</v>
       </c>
       <c r="C1203" t="str">
-        <v>7731480806</v>
+        <v>7702165310</v>
       </c>
       <c r="D1203" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1203" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1203" t="str">
         <v>РФ</v>
       </c>
       <c r="G1203">
-        <v>46593</v>
+        <v>46724</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="str">
-        <v>«Национальный расчетный депозитарий»</v>
+        <v>"Томарина"</v>
       </c>
       <c r="B1204" t="str">
-        <v>НКО АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1204" t="str">
-        <v>7702165310</v>
+        <v>3000008541</v>
       </c>
       <c r="D1204" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1204" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1204" t="str">
         <v>РФ</v>
       </c>
       <c r="G1204">
-        <v>46724</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="1205">
@@ -28108,7 +28108,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1205" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>GRASP</v>
       </c>
       <c r="F1205" t="str">
         <v>РФ</v>
@@ -28131,70 +28131,70 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1206" t="str">
-        <v>GRASP</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1206" t="str">
         <v>РФ</v>
       </c>
       <c r="G1206">
-        <v>46323</v>
+        <v>46744</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="str">
-        <v>"Томарина"</v>
+        <v>"АгроНеро"</v>
       </c>
       <c r="B1207" t="str">
         <v>ООО</v>
       </c>
       <c r="C1207" t="str">
-        <v>3000008541</v>
+        <v>6140040847</v>
       </c>
       <c r="D1207" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1207" t="str">
-        <v>FSSC 22000</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1207" t="str">
         <v>РФ</v>
       </c>
       <c r="G1207">
-        <v>46744</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="str">
-        <v>"АгроНеро"</v>
+        <v>"Новгородская аккумуляторная компания"</v>
       </c>
       <c r="B1208" t="str">
         <v>ООО</v>
       </c>
       <c r="C1208" t="str">
-        <v>6140040847</v>
+        <v>5321073271</v>
       </c>
       <c r="D1208" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1208" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1208" t="str">
         <v>РФ</v>
       </c>
       <c r="G1208">
-        <v>46356</v>
+        <v>46653</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="str">
-        <v>"Новгородская аккумуляторная компания"</v>
+        <v>"Метровагонмаш"</v>
       </c>
       <c r="B1209" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1209" t="str">
-        <v>5321073271</v>
+        <v>5029006702</v>
       </c>
       <c r="D1209" t="str">
         <v>ESYD (IAF)</v>
@@ -28206,18 +28206,18 @@
         <v>РФ</v>
       </c>
       <c r="G1209">
-        <v>46653</v>
+        <v>46767</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="str">
-        <v>"Метровагонмаш"</v>
+        <v>"Клиническая стоматологическая поликлиника №12"</v>
       </c>
       <c r="B1210" t="str">
-        <v>АО</v>
+        <v>ГАУЗ</v>
       </c>
       <c r="C1210" t="str">
-        <v>5029006702</v>
+        <v>3448009146</v>
       </c>
       <c r="D1210" t="str">
         <v>ESYD (IAF)</v>
@@ -28229,18 +28229,18 @@
         <v>РФ</v>
       </c>
       <c r="G1210">
-        <v>46767</v>
+        <v>46888</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="str">
-        <v>"Клиническая стоматологическая поликлиника №12"</v>
+        <v>«Кримиан Фэмили Киль»</v>
       </c>
       <c r="B1211" t="str">
-        <v>ГАУЗ</v>
+        <v>ООО</v>
       </c>
       <c r="C1211" t="str">
-        <v>3448009146</v>
+        <v>2315230925</v>
       </c>
       <c r="D1211" t="str">
         <v>ESYD (IAF)</v>
@@ -28252,18 +28252,18 @@
         <v>РФ</v>
       </c>
       <c r="G1211">
-        <v>46888</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="str">
-        <v>«Кримиан Фэмили Киль»</v>
+        <v>Производственная компания "Велам-Рус"</v>
       </c>
       <c r="B1212" t="str">
         <v>ООО</v>
       </c>
       <c r="C1212" t="str">
-        <v>2315230925</v>
+        <v>5258105399</v>
       </c>
       <c r="D1212" t="str">
         <v>ESYD (IAF)</v>
@@ -28275,30 +28275,30 @@
         <v>РФ</v>
       </c>
       <c r="G1212">
-        <v>46750</v>
+        <v>46775</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="str">
-        <v>Производственная компания "Велам-Рус"</v>
+        <v>"Уралэлектромедь"</v>
       </c>
       <c r="B1213" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1213" t="str">
-        <v>5258105399</v>
+        <v>6606003385</v>
       </c>
       <c r="D1213" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1213" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1213" t="str">
         <v>РФ</v>
       </c>
       <c r="G1213">
-        <v>46775</v>
+        <v>46380</v>
       </c>
     </row>
     <row r="1214">
@@ -28315,47 +28315,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1214" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1214" t="str">
         <v>РФ</v>
       </c>
       <c r="G1214">
-        <v>46380</v>
+        <v>46367</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="str">
-        <v>"Уралэлектромедь"</v>
+        <v>«YETA»</v>
       </c>
       <c r="B1215" t="str">
-        <v>АО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1215" t="str">
-        <v>6606003385</v>
+        <v>221040014631</v>
       </c>
       <c r="D1215" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1215" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1215" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1215">
-        <v>46367</v>
+        <v>46733</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="str">
-        <v>«YETA»</v>
+        <v>"Academy of Civil Aviation"</v>
       </c>
       <c r="B1216" t="str">
-        <v>ТОО</v>
+        <v>JSC</v>
       </c>
       <c r="C1216" t="str">
-        <v>221040014631</v>
+        <v>010840003460</v>
       </c>
       <c r="D1216" t="str">
         <v>ESYD (IAF)</v>
@@ -28367,12 +28367,12 @@
         <v>KZ</v>
       </c>
       <c r="G1216">
-        <v>46733</v>
+        <v>46747</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="str">
-        <v>"Academy of Civil Aviation"</v>
+        <v>JSC "Academy of Civil Aviation"</v>
       </c>
       <c r="B1217" t="str">
         <v>JSC</v>
@@ -28381,73 +28381,73 @@
         <v>010840003460</v>
       </c>
       <c r="D1217" t="str">
-        <v>ESYD (IAF)</v>
+        <v>n/a</v>
       </c>
       <c r="E1217" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 21001</v>
       </c>
       <c r="F1217" t="str">
         <v>KZ</v>
       </c>
       <c r="G1217">
-        <v>46747</v>
+        <v>46744</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="str">
-        <v>JSC "Academy of Civil Aviation"</v>
+        <v>«АзияАгроФуд»</v>
       </c>
       <c r="B1218" t="str">
-        <v>JSC</v>
+        <v>АО</v>
       </c>
       <c r="C1218" t="str">
-        <v>010840003460</v>
+        <v>050740003177</v>
       </c>
       <c r="D1218" t="str">
-        <v>n/a</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1218" t="str">
-        <v>ISO 21001</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1218" t="str">
         <v>KZ</v>
       </c>
-      <c r="G1218">
-        <v>46744</v>
+      <c r="G1218" t="str">
+        <v/>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="str">
-        <v>«АзияАгроФуд»</v>
+        <v>«Каменск-Уральский металлургический завод» (ПАО «КУМЗ»)</v>
       </c>
       <c r="B1219" t="str">
-        <v>АО</v>
+        <v>ПАО</v>
       </c>
       <c r="C1219" t="str">
-        <v>050740003177</v>
+        <v>6665002150</v>
       </c>
       <c r="D1219" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1219" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1219" t="str">
-        <v>KZ</v>
-      </c>
-      <c r="G1219" t="str">
-        <v/>
+        <v>РФ</v>
+      </c>
+      <c r="G1219">
+        <v>47102</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="str">
-        <v>«Каменск-Уральский металлургический завод» (ПАО «КУМЗ»)</v>
+        <v>"СЛАВДОМ"</v>
       </c>
       <c r="B1220" t="str">
-        <v>ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1220" t="str">
-        <v>6665002150</v>
+        <v>7806528328</v>
       </c>
       <c r="D1220" t="str">
         <v>ESYD (IAF)</v>
@@ -28459,18 +28459,18 @@
         <v>РФ</v>
       </c>
       <c r="G1220">
-        <v>47102</v>
+        <v>46871</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="str">
-        <v>"СЛАВДОМ"</v>
+        <v>«ГАБИОНЫ МАККАФЕРРИ СНГ»</v>
       </c>
       <c r="B1221" t="str">
         <v>ООО</v>
       </c>
       <c r="C1221" t="str">
-        <v>7806528328</v>
+        <v>7722187777</v>
       </c>
       <c r="D1221" t="str">
         <v>ESYD (IAF)</v>
@@ -28482,30 +28482,30 @@
         <v>РФ</v>
       </c>
       <c r="G1221">
-        <v>46871</v>
+        <v>46474</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="str">
-        <v>«ГАБИОНЫ МАККАФЕРРИ СНГ»</v>
+        <v>"Коломенский завод"</v>
       </c>
       <c r="B1222" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1222" t="str">
-        <v>7722187777</v>
+        <v>5022013517</v>
       </c>
       <c r="D1222" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1222" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1222" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1222">
-        <v>46474</v>
+      <c r="G1222" t="str">
+        <v>Сертификат еще не выдан</v>
       </c>
     </row>
     <row r="1223">
@@ -28522,7 +28522,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1223" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1223" t="str">
         <v>РФ</v>
@@ -28533,36 +28533,36 @@
     </row>
     <row r="1224">
       <c r="A1224" t="str">
-        <v>"Коломенский завод"</v>
+        <v>"ENERGOBEST"</v>
       </c>
       <c r="B1224" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1224" t="str">
-        <v>5022013517</v>
+        <v>301418434</v>
       </c>
       <c r="D1224" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1224" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1224" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1224" t="str">
-        <v>Сертификат еще не выдан</v>
+        <v>UZ</v>
+      </c>
+      <c r="G1224">
+        <v>46846</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="str">
-        <v>"ENERGOBEST"</v>
+        <v>«PRIME TOWER GROUP»</v>
       </c>
       <c r="B1225" t="str">
         <v>ООО</v>
       </c>
       <c r="C1225" t="str">
-        <v>301418434</v>
+        <v>303879121</v>
       </c>
       <c r="D1225" t="str">
         <v>ESYD (IAF)</v>
@@ -28574,18 +28574,18 @@
         <v>UZ</v>
       </c>
       <c r="G1225">
-        <v>46846</v>
+        <v>46838</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="str">
-        <v>«PRIME TOWER GROUP»</v>
+        <v>«GEOTEC»</v>
       </c>
       <c r="B1226" t="str">
-        <v>ООО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1226" t="str">
-        <v>303879121</v>
+        <v>061240002175</v>
       </c>
       <c r="D1226" t="str">
         <v>ESYD (IAF)</v>
@@ -28594,21 +28594,21 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1226" t="str">
-        <v>UZ</v>
+        <v>KZ</v>
       </c>
       <c r="G1226">
-        <v>46838</v>
+        <v>46859</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="str">
-        <v>«GEOTEC»</v>
+        <v>«Узэлектроаппарат-Электрощит»</v>
       </c>
       <c r="B1227" t="str">
-        <v>ТОО</v>
+        <v>АО</v>
       </c>
       <c r="C1227" t="str">
-        <v>061240002175</v>
+        <v>201052167</v>
       </c>
       <c r="D1227" t="str">
         <v>ESYD (IAF)</v>
@@ -28617,10 +28617,10 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1227" t="str">
-        <v>KZ</v>
+        <v>UZ</v>
       </c>
       <c r="G1227">
-        <v>46859</v>
+        <v>46892</v>
       </c>
     </row>
     <row r="1228">
@@ -28637,13 +28637,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1228" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1228" t="str">
         <v>UZ</v>
       </c>
       <c r="G1228">
-        <v>46892</v>
+        <v>46889</v>
       </c>
     </row>
     <row r="1229">
@@ -28660,36 +28660,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1229" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1229" t="str">
         <v>UZ</v>
       </c>
       <c r="G1229">
-        <v>46889</v>
+        <v>46892</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="str">
-        <v>«Узэлектроаппарат-Электрощит»</v>
+        <v>"Трастбанк"</v>
       </c>
       <c r="B1230" t="str">
-        <v>АО</v>
+        <v>ЧАБ</v>
       </c>
       <c r="C1230" t="str">
-        <v>201052167</v>
+        <v>201055090</v>
       </c>
       <c r="D1230" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1230" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1230" t="str">
         <v>UZ</v>
       </c>
       <c r="G1230">
-        <v>46892</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="1231">
@@ -28706,36 +28706,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1231" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 37001:2016</v>
       </c>
       <c r="F1231" t="str">
         <v>UZ</v>
       </c>
       <c r="G1231">
-        <v>46996</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="str">
-        <v>"Трастбанк"</v>
+        <v>"Каспийский трубопроводный консорциум-Р"</v>
       </c>
       <c r="B1232" t="str">
-        <v>ЧАБ</v>
+        <v>АО</v>
       </c>
       <c r="C1232" t="str">
-        <v>201055090</v>
+        <v>2310040800</v>
       </c>
       <c r="D1232" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1232" t="str">
-        <v>ISO 37001:2016</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1232" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1232">
-        <v>47039</v>
+        <v>46961</v>
       </c>
     </row>
     <row r="1233">
@@ -28752,7 +28752,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1233" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1233" t="str">
         <v>РФ</v>
@@ -28763,48 +28763,48 @@
     </row>
     <row r="1234">
       <c r="A1234" t="str">
-        <v>"Каспийский трубопроводный консорциум-Р"</v>
+        <v>"АСТОР"</v>
       </c>
       <c r="B1234" t="str">
         <v>АО</v>
       </c>
       <c r="C1234" t="str">
-        <v>2310040800</v>
+        <v>4703015840</v>
       </c>
       <c r="D1234" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1234" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1234" t="str">
         <v>РФ</v>
       </c>
       <c r="G1234">
-        <v>46961</v>
+        <v>47056</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="str">
-        <v>"АСТОР"</v>
+        <v>"AIR MARAKANDA"</v>
       </c>
       <c r="B1235" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1235" t="str">
-        <v>4703015840</v>
+        <v>307280842</v>
       </c>
       <c r="D1235" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1235" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1235" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1235">
-        <v>47056</v>
+        <v>46993</v>
       </c>
     </row>
     <row r="1236">
@@ -28821,36 +28821,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1236" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1236" t="str">
         <v>UZ</v>
       </c>
       <c r="G1236">
-        <v>46993</v>
+        <v>47005</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="str">
-        <v>"AIR MARAKANDA"</v>
+        <v>Частное производственное унитарное предприятие "НТП "Центр"</v>
       </c>
       <c r="B1237" t="str">
-        <v>ООО</v>
+        <v>Частное производственное унитарное предприятие</v>
       </c>
       <c r="C1237" t="str">
-        <v>307280842</v>
+        <v>700010977</v>
       </c>
       <c r="D1237" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1237" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1237" t="str">
-        <v>UZ</v>
+        <v>РБ</v>
       </c>
       <c r="G1237">
-        <v>47005</v>
+        <v>47045</v>
       </c>
     </row>
     <row r="1238">
@@ -28864,7 +28864,7 @@
         <v>700010977</v>
       </c>
       <c r="D1238" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1238" t="str">
         <v>ISO 9001:2015</v>
@@ -28878,16 +28878,16 @@
     </row>
     <row r="1239">
       <c r="A1239" t="str">
-        <v>Частное производственное унитарное предприятие "НТП "Центр"</v>
+        <v>Silicon Materials Inc.</v>
       </c>
       <c r="B1239" t="str">
-        <v>Частное производственное унитарное предприятие</v>
+        <v/>
       </c>
       <c r="C1239" t="str">
-        <v>700010977</v>
+        <v>EIN 25-1681874</v>
       </c>
       <c r="D1239" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1239" t="str">
         <v>ISO 9001:2015</v>
@@ -28895,19 +28895,19 @@
       <c r="F1239" t="str">
         <v>РБ</v>
       </c>
-      <c r="G1239">
-        <v>47045</v>
+      <c r="G1239" t="str">
+        <v>Сертификат еще не выдан</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="str">
-        <v>Silicon Materials Inc.</v>
+        <v>"CLOUPARD"</v>
       </c>
       <c r="B1240" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1240" t="str">
-        <v>EIN 25-1681874</v>
+        <v>310143054</v>
       </c>
       <c r="D1240" t="str">
         <v>ESYD (IAF)</v>
@@ -28916,7 +28916,7 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1240" t="str">
-        <v>РБ</v>
+        <v>UZ</v>
       </c>
       <c r="G1240" t="str">
         <v>Сертификат еще не выдан</v>
@@ -28936,7 +28936,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1241" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1241" t="str">
         <v>UZ</v>
@@ -28947,13 +28947,13 @@
     </row>
     <row r="1242">
       <c r="A1242" t="str">
-        <v>"CLOUPARD"</v>
+        <v>"Н-ТЕХ"</v>
       </c>
       <c r="B1242" t="str">
         <v>ООО</v>
       </c>
       <c r="C1242" t="str">
-        <v>310143054</v>
+        <v>7813283686</v>
       </c>
       <c r="D1242" t="str">
         <v>ESYD (IAF)</v>
@@ -28962,44 +28962,44 @@
         <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1242" t="str">
-        <v>UZ</v>
-      </c>
-      <c r="G1242" t="str">
-        <v>Сертификат еще не выдан</v>
+        <v>РФ</v>
+      </c>
+      <c r="G1242">
+        <v>47055</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="str">
-        <v>"Н-ТЕХ"</v>
+        <v>"СММ"</v>
       </c>
       <c r="B1243" t="str">
-        <v>ООО</v>
+        <v>ЗАО</v>
       </c>
       <c r="C1243" t="str">
-        <v>7813283686</v>
+        <v>7826136294</v>
       </c>
       <c r="D1243" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1243" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1243" t="str">
         <v>РФ</v>
       </c>
       <c r="G1243">
-        <v>47055</v>
+        <v>47012</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="str">
-        <v>"СММ"</v>
+        <v>"Ifoda Agro Kimyo Himoya"</v>
       </c>
       <c r="B1244" t="str">
-        <v>ЗАО</v>
+        <v>СП ООО</v>
       </c>
       <c r="C1244" t="str">
-        <v>7826136294</v>
+        <v>314010020917</v>
       </c>
       <c r="D1244" t="str">
         <v>ESYD (IAF)</v>
@@ -29008,10 +29008,10 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1244" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1244">
-        <v>47012</v>
+        <v>47074</v>
       </c>
     </row>
     <row r="1245">
@@ -29028,36 +29028,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1245" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1245" t="str">
         <v>UZ</v>
       </c>
       <c r="G1245">
-        <v>47074</v>
+        <v>47073</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="str">
-        <v>"Ifoda Agro Kimyo Himoya"</v>
+        <v>ZTE Investment</v>
       </c>
       <c r="B1246" t="str">
-        <v>СП ООО</v>
+        <v>ИП ООО</v>
       </c>
       <c r="C1246" t="str">
-        <v>314010020917</v>
+        <v>20662083</v>
       </c>
       <c r="D1246" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1246" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1246" t="str">
         <v>UZ</v>
       </c>
       <c r="G1246">
-        <v>47073</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="1247">
@@ -29074,13 +29074,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1247" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1247" t="str">
         <v>UZ</v>
       </c>
       <c r="G1247">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="1248">
@@ -29097,47 +29097,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1248" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1248" t="str">
         <v>UZ</v>
       </c>
       <c r="G1248">
-        <v>47055</v>
+        <v>47056</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="str">
-        <v>ZTE Investment</v>
+        <v>«Интраком»</v>
       </c>
       <c r="B1249" t="str">
-        <v>ИП ООО</v>
+        <v>ООО</v>
       </c>
       <c r="C1249" t="str">
-        <v>20662083</v>
+        <v>6612059795</v>
       </c>
       <c r="D1249" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1249" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1249" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1249">
-        <v>47056</v>
+        <v>47031</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="str">
-        <v>«Интраком»</v>
+        <v>«КФ-АВТО»</v>
       </c>
       <c r="B1250" t="str">
         <v>ООО</v>
       </c>
       <c r="C1250" t="str">
-        <v>6612059795</v>
+        <v>692142686</v>
       </c>
       <c r="D1250" t="str">
         <v>ESYD (IAF)</v>
@@ -29146,44 +29146,44 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1250" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1250">
-        <v>47031</v>
+        <v>47048</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="str">
-        <v>«КФ-АВТО»</v>
+        <v>"Авалон Джус"</v>
       </c>
       <c r="B1251" t="str">
         <v>ООО</v>
       </c>
       <c r="C1251" t="str">
-        <v>692142686</v>
+        <v>2310215472</v>
       </c>
       <c r="D1251" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1251" t="str">
-        <v>ISO 9001:2015</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1251" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1251">
-        <v>47048</v>
+        <v>47106</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="str">
-        <v>"Авалон Джус"</v>
+        <v>"Компания Алтын Казык"</v>
       </c>
       <c r="B1252" t="str">
-        <v>ООО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1252" t="str">
-        <v>2310215472</v>
+        <v>060640000339</v>
       </c>
       <c r="D1252" t="str">
         <v>ESYD (IAF)</v>
@@ -29192,21 +29192,21 @@
         <v>FSSC 22000</v>
       </c>
       <c r="F1252" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1252">
-        <v>47106</v>
+        <v>46484</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="str">
-        <v>"Компания Алтын Казык"</v>
+        <v>"ASL OYNA"</v>
       </c>
       <c r="B1253" t="str">
-        <v>ТОО</v>
+        <v>ООО</v>
       </c>
       <c r="C1253" t="str">
-        <v>060640000339</v>
+        <v>203554782</v>
       </c>
       <c r="D1253" t="str">
         <v>ESYD (IAF)</v>
@@ -29215,21 +29215,21 @@
         <v>FSSC 22000</v>
       </c>
       <c r="F1253" t="str">
-        <v>KZ</v>
+        <v>UZ</v>
       </c>
       <c r="G1253">
-        <v>46484</v>
+        <v>46971</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="str">
-        <v>"ASL OYNA"</v>
+        <v>“PENG SHENG CHARM”</v>
       </c>
       <c r="B1254" t="str">
-        <v>ООО</v>
+        <v>ИП ООО</v>
       </c>
       <c r="C1254" t="str">
-        <v>203554782</v>
+        <v>301647292</v>
       </c>
       <c r="D1254" t="str">
         <v>ESYD (IAF)</v>
@@ -29241,18 +29241,18 @@
         <v>UZ</v>
       </c>
       <c r="G1254">
-        <v>46971</v>
+        <v>46945</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="str">
-        <v>“PENG SHENG CHARM”</v>
+        <v>«TASH-PET»</v>
       </c>
       <c r="B1255" t="str">
-        <v>ИП ООО</v>
+        <v>ООО</v>
       </c>
       <c r="C1255" t="str">
-        <v>301647292</v>
+        <v>300939824</v>
       </c>
       <c r="D1255" t="str">
         <v>ESYD (IAF)</v>
@@ -29264,41 +29264,41 @@
         <v>UZ</v>
       </c>
       <c r="G1255">
-        <v>46945</v>
+        <v>47016</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="str">
-        <v>«TASH-PET»</v>
+        <v>Тяжпрессмаш</v>
       </c>
       <c r="B1256" t="str">
-        <v>ООО</v>
+        <v>ПАО</v>
       </c>
       <c r="C1256" t="str">
-        <v>300939824</v>
+        <v>6229009163</v>
       </c>
       <c r="D1256" t="str">
-        <v>ESYD (IAF)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1256" t="str">
-        <v>FSSC 22000</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1256" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1256">
-        <v>47016</v>
+        <v>46655</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="str">
-        <v>Тяжпрессмаш</v>
+        <v>Завод Лоджикруф</v>
       </c>
       <c r="B1257" t="str">
-        <v>ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1257" t="str">
-        <v>6229009163</v>
+        <v>6230054971</v>
       </c>
       <c r="D1257" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29310,18 +29310,18 @@
         <v>РФ</v>
       </c>
       <c r="G1257">
-        <v>46655</v>
+        <v>46668</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="str">
-        <v>Завод Лоджикруф</v>
+        <v>СОЛВО</v>
       </c>
       <c r="B1258" t="str">
         <v>ООО</v>
       </c>
       <c r="C1258" t="str">
-        <v>6230054971</v>
+        <v>7825064174</v>
       </c>
       <c r="D1258" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29333,18 +29333,18 @@
         <v>РФ</v>
       </c>
       <c r="G1258">
-        <v>46668</v>
+        <v>46683</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="str">
-        <v>СОЛВО</v>
+        <v>Воскресенский филиал ООО "Завод Технофлекс"</v>
       </c>
       <c r="B1259" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1259" t="str">
-        <v>7825064174</v>
+        <v>6229024796</v>
       </c>
       <c r="D1259" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29356,18 +29356,18 @@
         <v>РФ</v>
       </c>
       <c r="G1259">
-        <v>46683</v>
+        <v>46719</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="str">
-        <v>Воскресенский филиал ООО "Завод Технофлекс"</v>
+        <v>НПФ Ракурс</v>
       </c>
       <c r="B1260" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1260" t="str">
-        <v>6229024796</v>
+        <v>7812041998</v>
       </c>
       <c r="D1260" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29379,18 +29379,18 @@
         <v>РФ</v>
       </c>
       <c r="G1260">
-        <v>46719</v>
+        <v>46731</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="str">
-        <v>НПФ Ракурс</v>
+        <v>Светлана-Рентген</v>
       </c>
       <c r="B1261" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1261" t="str">
-        <v>7812041998</v>
+        <v>7805026364</v>
       </c>
       <c r="D1261" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29402,18 +29402,18 @@
         <v>РФ</v>
       </c>
       <c r="G1261">
-        <v>46731</v>
+        <v>46825</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="str">
-        <v>Светлана-Рентген</v>
+        <v>ЗАВОД ТУРБИННЫХ ЗАПЧАСТЕЙ</v>
       </c>
       <c r="B1262" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1262" t="str">
-        <v>7805026364</v>
+        <v>7814656732</v>
       </c>
       <c r="D1262" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29425,7 +29425,7 @@
         <v>РФ</v>
       </c>
       <c r="G1262">
-        <v>46825</v>
+        <v>46856</v>
       </c>
     </row>
     <row r="1263">
@@ -29439,39 +29439,39 @@
         <v>7814656732</v>
       </c>
       <c r="D1263" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1263" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1263" t="str">
         <v>РФ</v>
       </c>
       <c r="G1263">
-        <v>46856</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="str">
-        <v>ЗАВОД ТУРБИННЫХ ЗАПЧАСТЕЙ</v>
+        <v>Петроаналитика</v>
       </c>
       <c r="B1264" t="str">
         <v>ООО</v>
       </c>
       <c r="C1264" t="str">
-        <v>7814656732</v>
+        <v>7805523334</v>
       </c>
       <c r="D1264" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1264" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1264" t="str">
         <v>РФ</v>
       </c>
       <c r="G1264">
-        <v>46520</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="1265">
@@ -29485,39 +29485,39 @@
         <v>7805523334</v>
       </c>
       <c r="D1265" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1265" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1265" t="str">
         <v>РФ</v>
       </c>
       <c r="G1265">
-        <v>46934</v>
+        <v>47111</v>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="str">
-        <v>Петроаналитика</v>
+        <v>Химсталькомплект (ХСК)</v>
       </c>
       <c r="B1266" t="str">
         <v>ООО</v>
       </c>
       <c r="C1266" t="str">
-        <v>7805523334</v>
+        <v>7422046285</v>
       </c>
       <c r="D1266" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EGAC (QME)</v>
       </c>
       <c r="E1266" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1266" t="str">
         <v>РФ</v>
       </c>
       <c r="G1266">
-        <v>47111</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="1267">
@@ -29531,73 +29531,73 @@
         <v>7422046285</v>
       </c>
       <c r="D1267" t="str">
-        <v>EGAC (QME)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1267" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1267" t="str">
         <v>РФ</v>
       </c>
       <c r="G1267">
-        <v>46265</v>
+        <v>46808</v>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="str">
-        <v>Химсталькомплект (ХСК)</v>
+        <v>Группа компаний "ЛЮМЭКС Инструментс"</v>
       </c>
       <c r="B1268" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1268" t="str">
-        <v>7422046285</v>
+        <v>7801472150</v>
       </c>
       <c r="D1268" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>JASANZ (SAI Global)</v>
       </c>
       <c r="E1268" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1268" t="str">
         <v>РФ</v>
       </c>
       <c r="G1268">
-        <v>46808</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="str">
-        <v>Группа компаний "ЛЮМЭКС Инструментс"</v>
+        <v>СИЭЛ</v>
       </c>
       <c r="B1269" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1269" t="str">
-        <v>7801472150</v>
+        <v>7810742885</v>
       </c>
       <c r="D1269" t="str">
-        <v>JASANZ (SAI Global)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1269" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1269" t="str">
         <v>РФ</v>
       </c>
       <c r="G1269">
-        <v>46278</v>
+        <v>46673</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="str">
-        <v>СИЭЛ</v>
+        <v>Газпром диагностика</v>
       </c>
       <c r="B1270" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1270" t="str">
-        <v>7810742885</v>
+        <v>4345083100</v>
       </c>
       <c r="D1270" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -29609,18 +29609,18 @@
         <v>РФ</v>
       </c>
       <c r="G1270">
-        <v>46673</v>
+        <v>47102</v>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="str">
-        <v>Газпром диагностика</v>
+        <v>БП Морские Системы</v>
       </c>
       <c r="B1271" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1271" t="str">
-        <v>4345083100</v>
+        <v>7801726319</v>
       </c>
       <c r="D1271" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -29632,21 +29632,21 @@
         <v>РФ</v>
       </c>
       <c r="G1271">
-        <v>47102</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="str">
-        <v>БП Морские Системы</v>
+        <v>Статус</v>
       </c>
       <c r="B1272" t="str">
         <v>ООО</v>
       </c>
       <c r="C1272" t="str">
-        <v>7801726319</v>
+        <v>7413025257</v>
       </c>
       <c r="D1272" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1272" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -29655,18 +29655,18 @@
         <v>РФ</v>
       </c>
       <c r="G1272">
-        <v>46520</v>
+        <v>46927</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="str">
-        <v>Статус</v>
+        <v>ТЭК-Консалтинг</v>
       </c>
       <c r="B1273" t="str">
         <v>ООО</v>
       </c>
       <c r="C1273" t="str">
-        <v>7413025257</v>
+        <v>7804185393</v>
       </c>
       <c r="D1273" t="str">
         <v>РОСАТОМРЕГИСТР</v>
@@ -29678,18 +29678,18 @@
         <v>РФ</v>
       </c>
       <c r="G1273">
-        <v>46927</v>
+        <v>46898</v>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="str">
-        <v>ТЭК-Консалтинг</v>
+        <v>ГидроТехАтом</v>
       </c>
       <c r="B1274" t="str">
         <v>ООО</v>
       </c>
       <c r="C1274" t="str">
-        <v>7804185393</v>
+        <v>1831123035</v>
       </c>
       <c r="D1274" t="str">
         <v>РОСАТОМРЕГИСТР</v>
@@ -29701,21 +29701,21 @@
         <v>РФ</v>
       </c>
       <c r="G1274">
-        <v>46898</v>
+        <v>47168</v>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="str">
-        <v>ГидроТехАтом</v>
+        <v>НАМИ инновационные компоненты</v>
       </c>
       <c r="B1275" t="str">
         <v>ООО</v>
       </c>
       <c r="C1275" t="str">
-        <v>1831123035</v>
+        <v>6330056813</v>
       </c>
       <c r="D1275" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1275" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -29724,7 +29724,7 @@
         <v>РФ</v>
       </c>
       <c r="G1275">
-        <v>47168</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1276">
@@ -29738,39 +29738,39 @@
         <v>6330056813</v>
       </c>
       <c r="D1276" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1276" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1276" t="str">
         <v>РФ</v>
       </c>
       <c r="G1276">
-        <v>47039</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="str">
-        <v>НАМИ инновационные компоненты</v>
+        <v>Европейский мужчина и его здоровье</v>
       </c>
       <c r="B1277" t="str">
         <v>ООО</v>
       </c>
       <c r="C1277" t="str">
-        <v>6330056813</v>
+        <v>7811447106</v>
       </c>
       <c r="D1277" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1277" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1277" t="str">
         <v>РФ</v>
       </c>
       <c r="G1277">
-        <v>46303</v>
+        <v>47115</v>
       </c>
     </row>
     <row r="1278">
@@ -29784,7 +29784,7 @@
         <v>7811447106</v>
       </c>
       <c r="D1278" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1278" t="str">
         <v>ISO 9001:2015</v>
@@ -29798,16 +29798,16 @@
     </row>
     <row r="1279">
       <c r="A1279" t="str">
-        <v>Европейский мужчина и его здоровье</v>
+        <v>Газпром Линде Инжиниринг (ГЛ Инжиниринг)</v>
       </c>
       <c r="B1279" t="str">
         <v>ООО</v>
       </c>
       <c r="C1279" t="str">
-        <v>7811447106</v>
+        <v>0266023912</v>
       </c>
       <c r="D1279" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1279" t="str">
         <v>ISO 9001:2015</v>
@@ -29816,7 +29816,7 @@
         <v>РФ</v>
       </c>
       <c r="G1279">
-        <v>47115</v>
+        <v>47025</v>
       </c>
     </row>
     <row r="1280">
@@ -29830,7 +29830,7 @@
         <v>0266023912</v>
       </c>
       <c r="D1280" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1280" t="str">
         <v>ISO 9001:2015</v>
@@ -29853,10 +29853,10 @@
         <v>0266023912</v>
       </c>
       <c r="D1281" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1281" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1281" t="str">
         <v>РФ</v>
@@ -29876,7 +29876,7 @@
         <v>0266023912</v>
       </c>
       <c r="D1282" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1282" t="str">
         <v>ISO 14001:2015</v>
@@ -29899,10 +29899,10 @@
         <v>0266023912</v>
       </c>
       <c r="D1283" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1283" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1283" t="str">
         <v>РФ</v>
@@ -29922,7 +29922,7 @@
         <v>0266023912</v>
       </c>
       <c r="D1284" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1284" t="str">
         <v>ISO 45001:2018</v>
@@ -29945,16 +29945,16 @@
         <v>0266023912</v>
       </c>
       <c r="D1285" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1285" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1285" t="str">
         <v>РФ</v>
       </c>
       <c r="G1285">
-        <v>47025</v>
+        <v>47023</v>
       </c>
     </row>
     <row r="1286">
@@ -29971,7 +29971,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1286" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р ИСО 14001-2016</v>
       </c>
       <c r="F1286" t="str">
         <v>РФ</v>
@@ -29994,7 +29994,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1287" t="str">
-        <v>ГОСТ Р ИСО 14001-2016</v>
+        <v>ГОСТ Р ИСО 45001-2020</v>
       </c>
       <c r="F1287" t="str">
         <v>РФ</v>
@@ -30014,39 +30014,39 @@
         <v>0266023912</v>
       </c>
       <c r="D1288" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1288" t="str">
-        <v>ГОСТ Р ИСО 45001-2020</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1288" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1288">
-        <v>47023</v>
+      <c r="G1288" t="str">
+        <v/>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="str">
-        <v>Газпром Линде Инжиниринг (ГЛ Инжиниринг)</v>
+        <v>Сарштедт</v>
       </c>
       <c r="B1289" t="str">
         <v>ООО</v>
       </c>
       <c r="C1289" t="str">
-        <v>0266023912</v>
+        <v>6037008575</v>
       </c>
       <c r="D1289" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>NABCB (IAF)</v>
       </c>
       <c r="E1289" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1289" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1289" t="str">
-        <v/>
+      <c r="G1289">
+        <v>47076</v>
       </c>
     </row>
     <row r="1290">
@@ -30060,7 +30060,7 @@
         <v>6037008575</v>
       </c>
       <c r="D1290" t="str">
-        <v>NABCB (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1290" t="str">
         <v>ISO 13485:2016</v>
@@ -30083,39 +30083,39 @@
         <v>6037008575</v>
       </c>
       <c r="D1291" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1291" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1291" t="str">
         <v>РФ</v>
       </c>
       <c r="G1291">
-        <v>47076</v>
+        <v>46748</v>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="str">
-        <v>Сарштедт</v>
+        <v>Бора Пак</v>
       </c>
       <c r="B1292" t="str">
         <v>ООО</v>
       </c>
       <c r="C1292" t="str">
-        <v>6037008575</v>
+        <v>6315626314</v>
       </c>
       <c r="D1292" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1292" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1292" t="str">
         <v>РФ</v>
       </c>
       <c r="G1292">
-        <v>46748</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="1293">
@@ -30129,16 +30129,16 @@
         <v>6315626314</v>
       </c>
       <c r="D1293" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1293" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1293" t="str">
         <v>РФ</v>
       </c>
       <c r="G1293">
-        <v>46274</v>
+        <v>47086</v>
       </c>
     </row>
     <row r="1294">
@@ -30155,7 +30155,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1294" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1294" t="str">
         <v>РФ</v>
@@ -30166,16 +30166,16 @@
     </row>
     <row r="1295">
       <c r="A1295" t="str">
-        <v>Бора Пак</v>
+        <v>Научно-производственный центр Горноспасательные технологии</v>
       </c>
       <c r="B1295" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1295" t="str">
-        <v>6315626314</v>
+        <v>6672163631</v>
       </c>
       <c r="D1295" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1295" t="str">
         <v>ISO 9001:2015</v>
@@ -30184,7 +30184,7 @@
         <v>РФ</v>
       </c>
       <c r="G1295">
-        <v>47086</v>
+        <v>47070</v>
       </c>
     </row>
     <row r="1296">
@@ -30198,7 +30198,7 @@
         <v>6672163631</v>
       </c>
       <c r="D1296" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1296" t="str">
         <v>ISO 9001:2015</v>
@@ -30212,7 +30212,7 @@
     </row>
     <row r="1297">
       <c r="A1297" t="str">
-        <v>Научно-производственный центр Горноспасательные технологии</v>
+        <v>Научно-производственный центр "Горноспасательные технологии"</v>
       </c>
       <c r="B1297" t="str">
         <v>АО</v>
@@ -30221,39 +30221,39 @@
         <v>6672163631</v>
       </c>
       <c r="D1297" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1297" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1297" t="str">
         <v>РФ</v>
       </c>
       <c r="G1297">
-        <v>47070</v>
+        <v>47100</v>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="str">
-        <v>Научно-производственный центр "Горноспасательные технологии"</v>
+        <v>Джойсон Сейфти Системс Рус</v>
       </c>
       <c r="B1298" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1298" t="str">
-        <v>6672163631</v>
+        <v>7325097407</v>
       </c>
       <c r="D1298" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1298" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1298" t="str">
         <v>РФ</v>
       </c>
       <c r="G1298">
-        <v>47100</v>
+        <v>47097</v>
       </c>
     </row>
     <row r="1299">
@@ -30267,7 +30267,7 @@
         <v>7325097407</v>
       </c>
       <c r="D1299" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1299" t="str">
         <v>ISO 9001:2015</v>
@@ -30290,16 +30290,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1300" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1300" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1300" t="str">
         <v>РФ</v>
       </c>
       <c r="G1300">
-        <v>47097</v>
+        <v>47166</v>
       </c>
     </row>
     <row r="1301">
@@ -30313,7 +30313,7 @@
         <v>7325097407</v>
       </c>
       <c r="D1301" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1301" t="str">
         <v>ISO 14001:2015</v>
@@ -30336,10 +30336,10 @@
         <v>7325097407</v>
       </c>
       <c r="D1302" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1302" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1302" t="str">
         <v>РФ</v>
@@ -30359,7 +30359,7 @@
         <v>7325097407</v>
       </c>
       <c r="D1303" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1303" t="str">
         <v>ISO 45001:2018</v>
@@ -30382,16 +30382,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1304" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1304" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1304" t="str">
         <v>РФ</v>
       </c>
       <c r="G1304">
-        <v>47166</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1305">
@@ -30405,16 +30405,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1305" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1305" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1305" t="str">
         <v>РФ</v>
       </c>
       <c r="G1305">
-        <v>46982</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="1306">
@@ -30428,39 +30428,39 @@
         <v>7325097407</v>
       </c>
       <c r="D1306" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1306" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1306" t="str">
         <v>РФ</v>
       </c>
       <c r="G1306">
-        <v>46178</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="str">
-        <v>Джойсон Сейфти Системс Рус</v>
+        <v>ТЛТ ПРОФ</v>
       </c>
       <c r="B1307" t="str">
         <v>ООО</v>
       </c>
       <c r="C1307" t="str">
-        <v>7325097407</v>
+        <v>6321273480</v>
       </c>
       <c r="D1307" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1307" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1307" t="str">
         <v>РФ</v>
       </c>
       <c r="G1307">
-        <v>46982</v>
+        <v>46844</v>
       </c>
     </row>
     <row r="1308">
@@ -30474,7 +30474,7 @@
         <v>6321273480</v>
       </c>
       <c r="D1308" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1308" t="str">
         <v>ISO 9001:2015</v>
@@ -30488,16 +30488,16 @@
     </row>
     <row r="1309">
       <c r="A1309" t="str">
-        <v>ТЛТ ПРОФ</v>
+        <v>ТрансАвтоСвет</v>
       </c>
       <c r="B1309" t="str">
         <v>ООО</v>
       </c>
       <c r="C1309" t="str">
-        <v>6321273480</v>
+        <v>7328075313</v>
       </c>
       <c r="D1309" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1309" t="str">
         <v>ISO 9001:2015</v>
@@ -30506,7 +30506,7 @@
         <v>РФ</v>
       </c>
       <c r="G1309">
-        <v>46844</v>
+        <v>47046</v>
       </c>
     </row>
     <row r="1310">
@@ -30520,7 +30520,7 @@
         <v>7328075313</v>
       </c>
       <c r="D1310" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1310" t="str">
         <v>ISO 9001:2015</v>
@@ -30534,16 +30534,16 @@
     </row>
     <row r="1311">
       <c r="A1311" t="str">
-        <v>ТрансАвтоСвет</v>
+        <v>Борский стекольный завод</v>
       </c>
       <c r="B1311" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1311" t="str">
-        <v>7328075313</v>
+        <v>5246002261</v>
       </c>
       <c r="D1311" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1311" t="str">
         <v>ISO 9001:2015</v>
@@ -30552,7 +30552,7 @@
         <v>РФ</v>
       </c>
       <c r="G1311">
-        <v>47046</v>
+        <v>47066</v>
       </c>
     </row>
     <row r="1312">
@@ -30566,7 +30566,7 @@
         <v>5246002261</v>
       </c>
       <c r="D1312" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1312" t="str">
         <v>ISO 9001:2015</v>
@@ -30589,16 +30589,16 @@
         <v>5246002261</v>
       </c>
       <c r="D1313" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1313" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1313" t="str">
         <v>РФ</v>
       </c>
       <c r="G1313">
-        <v>47066</v>
+        <v>46634</v>
       </c>
     </row>
     <row r="1314">
@@ -30612,7 +30612,7 @@
         <v>5246002261</v>
       </c>
       <c r="D1314" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1314" t="str">
         <v>ISO 14001:2015</v>
@@ -30635,10 +30635,10 @@
         <v>5246002261</v>
       </c>
       <c r="D1315" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1315" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1315" t="str">
         <v>РФ</v>
@@ -30658,7 +30658,7 @@
         <v>5246002261</v>
       </c>
       <c r="D1316" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1316" t="str">
         <v>ISO 45001:2018</v>
@@ -30681,39 +30681,39 @@
         <v>5246002261</v>
       </c>
       <c r="D1317" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1317" t="str">
-        <v>ISO 45001:2018</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1317" t="str">
         <v>РФ</v>
       </c>
       <c r="G1317">
-        <v>46634</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="str">
-        <v>Борский стекольный завод</v>
+        <v>ПРОМЭНЕРГОКОМПЛЕКТ</v>
       </c>
       <c r="B1318" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1318" t="str">
-        <v>5246002261</v>
+        <v>5262222391</v>
       </c>
       <c r="D1318" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1318" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1318" t="str">
         <v>РФ</v>
       </c>
       <c r="G1318">
-        <v>46255</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1319">
@@ -30727,10 +30727,10 @@
         <v>5262222391</v>
       </c>
       <c r="D1319" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ECA (APAC)</v>
       </c>
       <c r="E1319" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1319" t="str">
         <v>РФ</v>
@@ -30741,94 +30741,94 @@
     </row>
     <row r="1320">
       <c r="A1320" t="str">
-        <v>ПРОМЭНЕРГОКОМПЛЕКТ</v>
+        <v>НПФ "Евродеталь"</v>
       </c>
       <c r="B1320" t="str">
         <v>ООО</v>
       </c>
       <c r="C1320" t="str">
-        <v>5262222391</v>
+        <v>1834054140</v>
       </c>
       <c r="D1320" t="str">
-        <v>ECA (APAC)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1320" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1320" t="str">
         <v>РФ</v>
       </c>
       <c r="G1320">
-        <v>47039</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="str">
-        <v>НПФ "Евродеталь"</v>
+        <v>АйСиЭл Системные Технологии</v>
       </c>
       <c r="B1321" t="str">
         <v>ООО</v>
       </c>
       <c r="C1321" t="str">
-        <v>1834054140</v>
+        <v>1615012203</v>
       </c>
       <c r="D1321" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1321" t="str">
-        <v>16949: 2016</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1321" t="str">
         <v>РФ</v>
       </c>
       <c r="G1321">
-        <v>46323</v>
+        <v>47094</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="str">
-        <v>АйСиЭл Системные Технологии</v>
+        <v>МЕДИН-Н</v>
       </c>
       <c r="B1322" t="str">
         <v>ООО</v>
       </c>
       <c r="C1322" t="str">
-        <v>1615012203</v>
+        <v>6662112620</v>
       </c>
       <c r="D1322" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1322" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1322" t="str">
         <v>РФ</v>
       </c>
       <c r="G1322">
-        <v>47094</v>
+        <v>47073</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="str">
-        <v>МЕДИН-Н</v>
+        <v>МЕТТЕХ</v>
       </c>
       <c r="B1323" t="str">
         <v>ООО</v>
       </c>
       <c r="C1323" t="str">
-        <v>6662112620</v>
+        <v>7806591143</v>
       </c>
       <c r="D1323" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1323" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1323" t="str">
         <v>РФ</v>
       </c>
       <c r="G1323">
-        <v>47073</v>
+        <v>47112</v>
       </c>
     </row>
     <row r="1324">
@@ -30842,7 +30842,7 @@
         <v>7806591143</v>
       </c>
       <c r="D1324" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1324" t="str">
         <v>ISO 9001:2015</v>
@@ -30856,82 +30856,82 @@
     </row>
     <row r="1325">
       <c r="A1325" t="str">
-        <v>МЕТТЕХ</v>
+        <v>Birinchi rezinotexnika zavodi</v>
       </c>
       <c r="B1325" t="str">
-        <v>ООО</v>
+        <v>ИП ООО</v>
       </c>
       <c r="C1325" t="str">
-        <v>7806591143</v>
+        <v>301938570</v>
       </c>
       <c r="D1325" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1325" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1325" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1325">
-        <v>47112</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="str">
-        <v>Birinchi rezinotexnika zavodi</v>
+        <v>Тюменский завод ЗСГ</v>
       </c>
       <c r="B1326" t="str">
-        <v>ИП ООО</v>
+        <v>ООО</v>
       </c>
       <c r="C1326" t="str">
-        <v>301938570</v>
+        <v>7203412108</v>
       </c>
       <c r="D1326" t="str">
-        <v>ESYD (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1326" t="str">
-        <v>ISO 45001:2018</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1326" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1326">
-        <v>47110</v>
+        <v>47074</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="str">
-        <v>Тюменский завод ЗСГ</v>
+        <v>Электронмаш Инжиниринг</v>
       </c>
       <c r="B1327" t="str">
         <v>ООО</v>
       </c>
       <c r="C1327" t="str">
-        <v>7203412108</v>
+        <v>7802428812</v>
       </c>
       <c r="D1327" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1327" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1327" t="str">
         <v>РФ</v>
       </c>
       <c r="G1327">
-        <v>47074</v>
+        <v>46731</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="str">
-        <v>Электронмаш Инжиниринг</v>
+        <v>Нефтегаздеталь</v>
       </c>
       <c r="B1328" t="str">
         <v>ООО</v>
       </c>
       <c r="C1328" t="str">
-        <v>7802428812</v>
+        <v>3661081734</v>
       </c>
       <c r="D1328" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -30943,30 +30943,30 @@
         <v>РФ</v>
       </c>
       <c r="G1328">
-        <v>46731</v>
+        <v>47001</v>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="str">
-        <v>Нефтегаздеталь</v>
+        <v>Богословский кабельный завод</v>
       </c>
       <c r="B1329" t="str">
         <v>ООО</v>
       </c>
       <c r="C1329" t="str">
-        <v>3661081734</v>
+        <v>6617026384</v>
       </c>
       <c r="D1329" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1329" t="str">
-        <v>S.QS.07-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1329" t="str">
         <v>РФ</v>
       </c>
       <c r="G1329">
-        <v>47001</v>
+        <v>47087</v>
       </c>
     </row>
     <row r="1330">
@@ -30980,7 +30980,7 @@
         <v>6617026384</v>
       </c>
       <c r="D1330" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1330" t="str">
         <v>ISO 9001:2015</v>
@@ -30994,16 +30994,16 @@
     </row>
     <row r="1331">
       <c r="A1331" t="str">
-        <v>Богословский кабельный завод</v>
+        <v>Аутолив</v>
       </c>
       <c r="B1331" t="str">
         <v>ООО</v>
       </c>
       <c r="C1331" t="str">
-        <v>6617026384</v>
+        <v>4703105420</v>
       </c>
       <c r="D1331" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1331" t="str">
         <v>ISO 9001:2015</v>
@@ -31026,7 +31026,7 @@
         <v>4703105420</v>
       </c>
       <c r="D1332" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1332" t="str">
         <v>ISO 9001:2015</v>
@@ -31052,13 +31052,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1333" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1333" t="str">
         <v>РФ</v>
       </c>
       <c r="G1333">
-        <v>47087</v>
+        <v>47101</v>
       </c>
     </row>
     <row r="1334">
@@ -31072,39 +31072,39 @@
         <v>4703105420</v>
       </c>
       <c r="D1334" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1334" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1334" t="str">
         <v>РФ</v>
       </c>
       <c r="G1334">
-        <v>47101</v>
+        <v>45980</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="str">
-        <v>Аутолив</v>
+        <v>ASTEL</v>
       </c>
       <c r="B1335" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1335" t="str">
-        <v>4703105420</v>
+        <v>11140001666</v>
       </c>
       <c r="D1335" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1335" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1335" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1335">
-        <v>45980</v>
+        <v>46629</v>
       </c>
     </row>
     <row r="1336">
@@ -31121,13 +31121,13 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1336" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 27001:2013</v>
       </c>
       <c r="F1336" t="str">
         <v>KZ</v>
       </c>
       <c r="G1336">
-        <v>46629</v>
+        <v>46643</v>
       </c>
     </row>
     <row r="1337">
@@ -31144,7 +31144,7 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1337" t="str">
-        <v>ISO 27001:2013</v>
+        <v>ISO 20000-1:2018</v>
       </c>
       <c r="F1337" t="str">
         <v>KZ</v>
@@ -31155,48 +31155,48 @@
     </row>
     <row r="1338">
       <c r="A1338" t="str">
-        <v>ASTEL</v>
+        <v>Федеральное государственное бюджетное образовательное учреждение высшего образования «Тульский государственный педагогический университет им. Л.Н. Толстого», Научно-исследовательский институт химических, фармацевтических и биотехнологий, Научно-производственный центр</v>
       </c>
       <c r="B1338" t="str">
-        <v>АО</v>
+        <v>ФГБОУ ВО</v>
       </c>
       <c r="C1338" t="str">
-        <v>11140001666</v>
+        <v>7107030811</v>
       </c>
       <c r="D1338" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1338" t="str">
-        <v>ISO 20000-1:2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1338" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1338">
-        <v>46643</v>
+        <v>47101</v>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="str">
-        <v>Федеральное государственное бюджетное образовательное учреждение высшего образования «Тульский государственный педагогический университет им. Л.Н. Толстого», Научно-исследовательский институт химических, фармацевтических и биотехнологий, Научно-производственный центр</v>
+        <v>«УЗЛЫ И МЕХАНИЗМЫ КУЗОВА АВТОМОБИЛЯ» (ООО «УМКА»)</v>
       </c>
       <c r="B1339" t="str">
-        <v>ФГБОУ ВО</v>
+        <v>ООО</v>
       </c>
       <c r="C1339" t="str">
-        <v>7107030811</v>
+        <v>6382061684</v>
       </c>
       <c r="D1339" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1339" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1339" t="str">
         <v>РФ</v>
       </c>
       <c r="G1339">
-        <v>47101</v>
+        <v>47094</v>
       </c>
     </row>
     <row r="1340">
@@ -31210,7 +31210,7 @@
         <v>6382061684</v>
       </c>
       <c r="D1340" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1340" t="str">
         <v>ISO 9001:2015</v>
@@ -31233,16 +31233,16 @@
         <v>6382061684</v>
       </c>
       <c r="D1341" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1341" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1341" t="str">
         <v>РФ</v>
       </c>
       <c r="G1341">
-        <v>47094</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="1342">
@@ -31256,39 +31256,39 @@
         <v>6382061684</v>
       </c>
       <c r="D1342" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1342" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1342" t="str">
         <v>РФ</v>
       </c>
       <c r="G1342">
-        <v>46318</v>
+        <v>47175</v>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="str">
-        <v>«УЗЛЫ И МЕХАНИЗМЫ КУЗОВА АВТОМОБИЛЯ» (ООО «УМКА»)</v>
+        <v>РУСАЛ Ачинский Глиноземный Комбинат</v>
       </c>
       <c r="B1343" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1343" t="str">
-        <v>6382061684</v>
+        <v>2443005570</v>
       </c>
       <c r="D1343" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1343" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1343" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1343">
-        <v>47175</v>
+      <c r="G1343" t="str">
+        <v/>
       </c>
     </row>
     <row r="1344">
@@ -31302,7 +31302,7 @@
         <v>2443005570</v>
       </c>
       <c r="D1344" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1344" t="str">
         <v>ISO 9001:2015</v>
@@ -31325,16 +31325,16 @@
         <v>2443005570</v>
       </c>
       <c r="D1345" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1345" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1345" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1345" t="str">
-        <v/>
+      <c r="G1345">
+        <v>47097</v>
       </c>
     </row>
     <row r="1346">
@@ -31348,7 +31348,7 @@
         <v>2443005570</v>
       </c>
       <c r="D1346" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1346" t="str">
         <v>ISO 14001:2015</v>
@@ -31371,16 +31371,16 @@
         <v>2443005570</v>
       </c>
       <c r="D1347" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1347" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1347" t="str">
         <v>РФ</v>
       </c>
       <c r="G1347">
-        <v>47097</v>
+        <v>47213</v>
       </c>
     </row>
     <row r="1348">
@@ -31394,7 +31394,7 @@
         <v>2443005570</v>
       </c>
       <c r="D1348" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1348" t="str">
         <v>ISO 45001:2018</v>
@@ -31408,25 +31408,25 @@
     </row>
     <row r="1349">
       <c r="A1349" t="str">
-        <v>РУСАЛ Ачинский Глиноземный Комбинат</v>
+        <v>ENTER STEEL</v>
       </c>
       <c r="B1349" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1349" t="str">
-        <v>2443005570</v>
+        <v>306574437</v>
       </c>
       <c r="D1349" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1349" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1349" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1349">
-        <v>47213</v>
+        <v>UZ</v>
+      </c>
+      <c r="G1349" t="str">
+        <v/>
       </c>
     </row>
     <row r="1350">
@@ -31443,7 +31443,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1350" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1350" t="str">
         <v>UZ</v>
@@ -31466,7 +31466,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1351" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1351" t="str">
         <v>UZ</v>
@@ -31477,19 +31477,19 @@
     </row>
     <row r="1352">
       <c r="A1352" t="str">
-        <v>ENTER STEEL</v>
+        <v>SAVDONI RIVOJLANTIRISH KOMPANIYASI</v>
       </c>
       <c r="B1352" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1352" t="str">
-        <v>306574437</v>
+        <v>306303488</v>
       </c>
       <c r="D1352" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1352" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 37001:2016</v>
       </c>
       <c r="F1352" t="str">
         <v>UZ</v>
@@ -31500,19 +31500,19 @@
     </row>
     <row r="1353">
       <c r="A1353" t="str">
-        <v>SAVDONI RIVOJLANTIRISH KOMPANIYASI</v>
+        <v>Unitel</v>
       </c>
       <c r="B1353" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1353" t="str">
-        <v>306303488</v>
+        <v>201838002</v>
       </c>
       <c r="D1353" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1353" t="str">
-        <v>ISO 37001:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1353" t="str">
         <v>UZ</v>
@@ -31523,22 +31523,22 @@
     </row>
     <row r="1354">
       <c r="A1354" t="str">
-        <v>Unitel</v>
+        <v>«СХП «РАССВЕТ»</v>
       </c>
       <c r="B1354" t="str">
         <v>ООО</v>
       </c>
       <c r="C1354" t="str">
-        <v>201838002</v>
+        <v>2625027835</v>
       </c>
       <c r="D1354" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1354" t="str">
-        <v>ISO 9001:2015</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1354" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1354" t="str">
         <v/>
@@ -31546,19 +31546,19 @@
     </row>
     <row r="1355">
       <c r="A1355" t="str">
-        <v>«СХП «РАССВЕТ»</v>
+        <v>Завод по производству винто-рулевых колонок Сапфир</v>
       </c>
       <c r="B1355" t="str">
         <v>ООО</v>
       </c>
       <c r="C1355" t="str">
-        <v>2625027835</v>
+        <v>2503032563</v>
       </c>
       <c r="D1355" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1355" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1355" t="str">
         <v>РФ</v>
@@ -31569,48 +31569,48 @@
     </row>
     <row r="1356">
       <c r="A1356" t="str">
-        <v>Завод по производству винто-рулевых колонок Сапфир</v>
+        <v>GDC Services and Solutions d.o.o.</v>
       </c>
       <c r="B1356" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1356" t="str">
-        <v>2503032563</v>
+        <v/>
       </c>
       <c r="D1356" t="str">
-        <v>ESYD (IAF)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1356" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1356" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1356" t="str">
-        <v/>
+        <v>Serbia</v>
+      </c>
+      <c r="G1356">
+        <v>47101</v>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="str">
-        <v>GDC Services and Solutions d.o.o.</v>
+        <v>Красноярский металлургический завод ("КраМЗ")</v>
       </c>
       <c r="B1357" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1357" t="str">
-        <v/>
+        <v>2465043748</v>
       </c>
       <c r="D1357" t="str">
-        <v>IAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1357" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1357" t="str">
-        <v>Serbia</v>
+        <v>РФ</v>
       </c>
       <c r="G1357">
-        <v>47101</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="1358">
@@ -31624,7 +31624,7 @@
         <v>2465043748</v>
       </c>
       <c r="D1358" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1358" t="str">
         <v>ISO 9001:2015</v>
@@ -31647,16 +31647,16 @@
         <v>2465043748</v>
       </c>
       <c r="D1359" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1359" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1359" t="str">
         <v>РФ</v>
       </c>
       <c r="G1359">
-        <v>47110</v>
+        <v>47242</v>
       </c>
     </row>
     <row r="1360">
@@ -31670,7 +31670,7 @@
         <v>2465043748</v>
       </c>
       <c r="D1360" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1360" t="str">
         <v>ISO 14001:2015</v>
@@ -31684,25 +31684,25 @@
     </row>
     <row r="1361">
       <c r="A1361" t="str">
-        <v>Красноярский металлургический завод ("КраМЗ")</v>
+        <v>"ЭЛАРА"</v>
       </c>
       <c r="B1361" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1361" t="str">
-        <v>2465043748</v>
+        <v>2129017646</v>
       </c>
       <c r="D1361" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1361" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1361" t="str">
         <v>РФ</v>
       </c>
       <c r="G1361">
-        <v>47242</v>
+        <v>46980</v>
       </c>
     </row>
     <row r="1362">
@@ -31719,59 +31719,59 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1362" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1362" t="str">
         <v>РФ</v>
       </c>
       <c r="G1362">
-        <v>46980</v>
+        <v>46574</v>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="str">
-        <v>"ЭЛАРА"</v>
+        <v>"Газпром проектирование"</v>
       </c>
       <c r="B1363" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1363" t="str">
-        <v>2129017646</v>
+        <v>0560022871</v>
       </c>
       <c r="D1363" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1363" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1363" t="str">
         <v>РФ</v>
       </c>
       <c r="G1363">
-        <v>46574</v>
+        <v>47003</v>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="str">
-        <v>"Газпром проектирование"</v>
+        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
       </c>
       <c r="B1364" t="str">
         <v>ООО</v>
       </c>
       <c r="C1364" t="str">
-        <v>0560022871</v>
+        <v>190918566</v>
       </c>
       <c r="D1364" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1364" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1364" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1364">
-        <v>47003</v>
+        <v>47151</v>
       </c>
     </row>
     <row r="1365">
@@ -31785,7 +31785,7 @@
         <v>190918566</v>
       </c>
       <c r="D1365" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1365" t="str">
         <v>ISO/IEC 27001:2022</v>
@@ -31799,25 +31799,25 @@
     </row>
     <row r="1366">
       <c r="A1366" t="str">
-        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
+        <v>Аутолайт Технолоджи</v>
       </c>
       <c r="B1366" t="str">
         <v>ООО</v>
       </c>
       <c r="C1366" t="str">
-        <v>190918566</v>
+        <v>6230025811</v>
       </c>
       <c r="D1366" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1366" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1366" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1366">
-        <v>47151</v>
+        <v>47179</v>
       </c>
     </row>
     <row r="1367">
@@ -31831,16 +31831,16 @@
         <v>6230025811</v>
       </c>
       <c r="D1367" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1367" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1367" t="str">
         <v>РФ</v>
       </c>
       <c r="G1367">
-        <v>47179</v>
+        <v>47229</v>
       </c>
     </row>
     <row r="1368">
@@ -31854,16 +31854,16 @@
         <v>6230025811</v>
       </c>
       <c r="D1368" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1368" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1368" t="str">
         <v>РФ</v>
       </c>
       <c r="G1368">
-        <v>47229</v>
+        <v>46430</v>
       </c>
     </row>
     <row r="1369">
@@ -31877,39 +31877,39 @@
         <v>6230025811</v>
       </c>
       <c r="D1369" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1369" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1369" t="str">
         <v>РФ</v>
       </c>
       <c r="G1369">
-        <v>46430</v>
+        <v>47179</v>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="str">
-        <v>Аутолайт Технолоджи</v>
+        <v>Инновационный центр КАМАЗ</v>
       </c>
       <c r="B1370" t="str">
         <v>ООО</v>
       </c>
       <c r="C1370" t="str">
-        <v>6230025811</v>
+        <v>7801204062</v>
       </c>
       <c r="D1370" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1370" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1370" t="str">
         <v>РФ</v>
       </c>
       <c r="G1370">
-        <v>47179</v>
+        <v>47286</v>
       </c>
     </row>
     <row r="1371">
@@ -31926,7 +31926,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1371" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1371" t="str">
         <v>РФ</v>
@@ -31937,128 +31937,128 @@
     </row>
     <row r="1372">
       <c r="A1372" t="str">
-        <v>Инновационный центр КАМАЗ</v>
+        <v>АкваПромМеталл</v>
       </c>
       <c r="B1372" t="str">
         <v>ООО</v>
       </c>
       <c r="C1372" t="str">
-        <v>7801204062</v>
+        <v>7807240772</v>
       </c>
       <c r="D1372" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1372" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1372" t="str">
         <v>РФ</v>
       </c>
       <c r="G1372">
-        <v>47286</v>
+        <v>47223</v>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="str">
-        <v>АкваПромМеталл</v>
+        <v>СЗЭМО ЗАВОД ВЕНТИЛЯТОР ТДМ</v>
       </c>
       <c r="B1373" t="str">
         <v>ООО</v>
       </c>
       <c r="C1373" t="str">
-        <v>7807240772</v>
+        <v>7811513824</v>
       </c>
       <c r="D1373" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1373" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1373" t="str">
         <v>РФ</v>
       </c>
       <c r="G1373">
-        <v>47223</v>
+        <v>46810</v>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="str">
-        <v>СЗЭМО ЗАВОД ВЕНТИЛЯТОР ТДМ</v>
+        <v>РЕМОНТНО-МЕХАНИЧЕСКИЙ ЗАВОД ГОРНО-ХИМИЧЕСКОГО КОМБИНАТА (РМЗ ГХК)</v>
       </c>
       <c r="B1374" t="str">
         <v>ООО</v>
       </c>
       <c r="C1374" t="str">
-        <v>7811513824</v>
+        <v>2452201891</v>
       </c>
       <c r="D1374" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1374" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1374" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1374">
-        <v>46810</v>
+      <c r="G1374" t="str">
+        <v/>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="str">
-        <v>РЕМОНТНО-МЕХАНИЧЕСКИЙ ЗАВОД ГОРНО-ХИМИЧЕСКОГО КОМБИНАТА (РМЗ ГХК)</v>
+        <v>Центр диагностики, экспертизы и сертификации (ЦДЭС)</v>
       </c>
       <c r="B1375" t="str">
         <v>ООО</v>
       </c>
       <c r="C1375" t="str">
-        <v>2452201891</v>
+        <v>7839346161</v>
       </c>
       <c r="D1375" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1375" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1375" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1375" t="str">
-        <v/>
+      <c r="G1375">
+        <v>46567</v>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="str">
-        <v>Центр диагностики, экспертизы и сертификации (ЦДЭС)</v>
+        <v>Уральский завод специального арматуростроения (УЗСА)</v>
       </c>
       <c r="B1376" t="str">
         <v>ООО</v>
       </c>
       <c r="C1376" t="str">
-        <v>7839346161</v>
+        <v>7451403608</v>
       </c>
       <c r="D1376" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1376" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1376" t="str">
         <v>РФ</v>
       </c>
       <c r="G1376">
-        <v>46567</v>
+        <v>46900</v>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="str">
-        <v>Уральский завод специального арматуростроения (УЗСА)</v>
+        <v>Угрешский завод трубопроводной арматуры (УЗТПА)</v>
       </c>
       <c r="B1377" t="str">
         <v>ООО</v>
       </c>
       <c r="C1377" t="str">
-        <v>7451403608</v>
+        <v>5056009251</v>
       </c>
       <c r="D1377" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -32073,27 +32073,28 @@
         <v>46900</v>
       </c>
     </row>
-    <row r="1378">
-      <c r="A1378" t="str">
-        <v>Угрешский завод трубопроводной арматуры (УЗТПА)</v>
+    <row r="1378" xml:space="preserve">
+      <c r="A1378" t="str" xml:space="preserve">
+        <v xml:space="preserve">Научно-_x000d_
+производственное объединение специальных материалов (НПО Спецматериалов)</v>
       </c>
       <c r="B1378" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1378" t="str">
-        <v>5056009251</v>
+        <v>7806125671</v>
       </c>
       <c r="D1378" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1378" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1378" t="str">
         <v>РФ</v>
       </c>
       <c r="G1378">
-        <v>46900</v>
+        <v>46709</v>
       </c>
     </row>
     <row r="1379" xml:space="preserve">
@@ -32108,7 +32109,7 @@
         <v>7806125671</v>
       </c>
       <c r="D1379" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1379" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -32117,42 +32118,41 @@
         <v>РФ</v>
       </c>
       <c r="G1379">
-        <v>46709</v>
-      </c>
-    </row>
-    <row r="1380" xml:space="preserve">
-      <c r="A1380" t="str" xml:space="preserve">
-        <v xml:space="preserve">Научно-_x000d_
-производственное объединение специальных материалов (НПО Спецматериалов)</v>
+        <v>46655</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="str">
+        <v>Специализированная инжиниринговая компания Севзапмонтажавтоматика (СЗМА СПИК)</v>
       </c>
       <c r="B1380" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1380" t="str">
-        <v>7806125671</v>
+        <v>7801715500</v>
       </c>
       <c r="D1380" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1380" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1380" t="str">
         <v>РФ</v>
       </c>
       <c r="G1380">
-        <v>46655</v>
+        <v>46921</v>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="str">
-        <v>Специализированная инжиниринговая компания Севзапмонтажавтоматика (СЗМА СПИК)</v>
+        <v>Тосненский механический завод (ТоМеЗ)</v>
       </c>
       <c r="B1381" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1381" t="str">
-        <v>7801715500</v>
+        <v>4716002824</v>
       </c>
       <c r="D1381" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -32164,21 +32164,21 @@
         <v>РФ</v>
       </c>
       <c r="G1381">
-        <v>46921</v>
+        <v>46619</v>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="str">
-        <v>Тосненский механический завод (ТоМеЗ)</v>
+        <v>Трубопроводные покрытия и технологии (ТПТ)</v>
       </c>
       <c r="B1382" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1382" t="str">
-        <v>4716002824</v>
+        <v>3435308501</v>
       </c>
       <c r="D1382" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>EGAC (QME)</v>
       </c>
       <c r="E1382" t="str">
         <v>ISO 9001:2015</v>
@@ -32187,30 +32187,30 @@
         <v>РФ</v>
       </c>
       <c r="G1382">
-        <v>46619</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="str">
-        <v>Трубопроводные покрытия и технологии (ТПТ)</v>
+        <v>Гродно Азот, филиал Завод Химволокно</v>
       </c>
       <c r="B1383" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1383" t="str">
-        <v>3435308501</v>
+        <v>7707083893</v>
       </c>
       <c r="D1383" t="str">
-        <v>EGAC (QME)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1383" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1383" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1383">
-        <v>46272</v>
+        <v>47270</v>
       </c>
     </row>
     <row r="1384">
@@ -32224,7 +32224,7 @@
         <v>7707083893</v>
       </c>
       <c r="D1384" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1384" t="str">
         <v>ISO 9001:2015</v>
@@ -32238,7 +32238,7 @@
     </row>
     <row r="1385">
       <c r="A1385" t="str">
-        <v>Гродно Азот, филиал Завод Химволокно</v>
+        <v>филиал "Завод Химволокно", ОАО "Гродно Азот",</v>
       </c>
       <c r="B1385" t="str">
         <v>ОАО</v>
@@ -32250,53 +32250,53 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1385" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1385" t="str">
         <v>РБ</v>
       </c>
       <c r="G1385">
-        <v>47270</v>
+        <v>47308</v>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="str">
-        <v>филиал "Завод Химволокно", ОАО "Гродно Азот",</v>
+        <v>АВТОКОЛОРИТ</v>
       </c>
       <c r="B1386" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1386" t="str">
-        <v>7707083893</v>
+        <v>6320092604</v>
       </c>
       <c r="D1386" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1386" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1386" t="str">
-        <v>РБ</v>
-      </c>
-      <c r="G1386">
-        <v>47308</v>
+        <v>РФ</v>
+      </c>
+      <c r="G1386" t="str">
+        <v/>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="str">
-        <v>АВТОКОЛОРИТ</v>
+        <v>ХЕНДЭ СТИЛ РУС</v>
       </c>
       <c r="B1387" t="str">
         <v>ООО</v>
       </c>
       <c r="C1387" t="str">
-        <v>6320092604</v>
+        <v>7813442054</v>
       </c>
       <c r="D1387" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1387" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1387" t="str">
         <v>РФ</v>
@@ -32319,7 +32319,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1388" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1388" t="str">
         <v>РФ</v>
@@ -32330,71 +32330,71 @@
     </row>
     <row r="1389">
       <c r="A1389" t="str">
-        <v>ХЕНДЭ СТИЛ РУС</v>
+        <v>"Рикор Электроникс"</v>
       </c>
       <c r="B1389" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1389" t="str">
-        <v>7813442054</v>
+        <v>5243001622</v>
       </c>
       <c r="D1389" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1389" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1389" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1389" t="str">
-        <v/>
+      <c r="G1389">
+        <v>46521</v>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="str">
-        <v>"Рикор Электроникс"</v>
+        <v>Сваркер</v>
       </c>
       <c r="B1390" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1390" t="str">
-        <v>5243001622</v>
+        <v>6686156088</v>
       </c>
       <c r="D1390" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1390" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1390" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1390">
-        <v>46521</v>
+      <c r="G1390" t="str">
+        <v/>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="str">
-        <v>Сваркер</v>
+        <v>Научно-исследовательский институт биотехнологий (НИИ БиоТех) ФГБОУ ВО СамГМУ Минздрава России</v>
       </c>
       <c r="B1391" t="str">
-        <v>ООО</v>
+        <v>ФГБОУ ВО</v>
       </c>
       <c r="C1391" t="str">
-        <v>6686156088</v>
+        <v>6317002858</v>
       </c>
       <c r="D1391" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1391" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1391" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1391" t="str">
-        <v/>
+      <c r="G1391">
+        <v>47314</v>
       </c>
     </row>
     <row r="1392">
@@ -32408,7 +32408,7 @@
         <v>6317002858</v>
       </c>
       <c r="D1392" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1392" t="str">
         <v>ISO 13485:2016</v>
@@ -32422,25 +32422,25 @@
     </row>
     <row r="1393">
       <c r="A1393" t="str">
-        <v>Научно-исследовательский институт биотехнологий (НИИ БиоТех) ФГБОУ ВО СамГМУ Минздрава России</v>
+        <v>КрасАвиа</v>
       </c>
       <c r="B1393" t="str">
-        <v>ФГБОУ ВО</v>
+        <v>АО</v>
       </c>
       <c r="C1393" t="str">
-        <v>6317002858</v>
+        <v>2465177981</v>
       </c>
       <c r="D1393" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1393" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1393" t="str">
         <v>РФ</v>
       </c>
       <c r="G1393">
-        <v>47314</v>
+        <v>47299</v>
       </c>
     </row>
     <row r="1394">
@@ -32454,7 +32454,7 @@
         <v>2465177981</v>
       </c>
       <c r="D1394" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1394" t="str">
         <v>ISO 9001:2015</v>
@@ -32468,30 +32468,306 @@
     </row>
     <row r="1395">
       <c r="A1395" t="str">
-        <v>КрасАвиа</v>
+        <v>Стальимпэкс</v>
       </c>
       <c r="B1395" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1395" t="str">
+        <v>7017447537</v>
+      </c>
+      <c r="D1395" t="str">
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
+      </c>
+      <c r="E1395" t="str">
+        <v>СТО Газпром 9001-2018</v>
+      </c>
+      <c r="F1395" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1395">
+        <v>47116</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="str">
+        <v>Автоматизация-Метрология-Эксперт</v>
+      </c>
+      <c r="B1396" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1396" t="str">
+        <v>0276115746</v>
+      </c>
+      <c r="D1396" t="str">
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
+      </c>
+      <c r="E1396" t="str">
+        <v>СТО Газпром 9001-2018</v>
+      </c>
+      <c r="F1396" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1396" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="str">
+        <v>Автоматизация-Метрология-эксперт</v>
+      </c>
+      <c r="B1397" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1397" t="str">
+        <v>0276115746</v>
+      </c>
+      <c r="D1397" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1397" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1397" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1397" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="str">
+        <v>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "НИЖЕГОРОДСКИЙ ЗАВОД ТЕПЛООБМЕННОГО ОБОРУДОВАНИЯ"</v>
+      </c>
+      <c r="B1398" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1398" t="str">
+        <v>5261068838</v>
+      </c>
+      <c r="D1398" t="str">
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
+      </c>
+      <c r="E1398" t="str">
+        <v>СТО Газпром 9001-2018</v>
+      </c>
+      <c r="F1398" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1398" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="str">
+        <v>Технопром</v>
+      </c>
+      <c r="B1399" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1399" t="str">
+        <v>7731637278</v>
+      </c>
+      <c r="D1399" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1399" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1399" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1399">
+        <v>47026</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="str">
+        <v>Пергам-Инжиниринг</v>
+      </c>
+      <c r="B1400" t="str">
         <v>АО</v>
       </c>
-      <c r="C1395" t="str">
-        <v>2465177981</v>
-      </c>
-      <c r="D1395" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
-      </c>
-      <c r="E1395" t="str">
-        <v>ISO 9001:2015</v>
-      </c>
-      <c r="F1395" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1395">
-        <v>47299</v>
+      <c r="C1400" t="str">
+        <v>7713226814</v>
+      </c>
+      <c r="D1400" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1400" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1400" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1400">
+        <v>47085</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="str">
+        <v>Газ-проект-Инжиниринг</v>
+      </c>
+      <c r="B1401" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1401" t="str">
+        <v>278096584</v>
+      </c>
+      <c r="D1401" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1401" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1401" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1401">
+        <v>47089</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="str">
+        <v>Инжиниринговая компания Интэко</v>
+      </c>
+      <c r="B1402" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1402" t="str">
+        <v>276121517</v>
+      </c>
+      <c r="D1402" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1402" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1402" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1402">
+        <v>47092</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="str">
+        <v>ЕвроМет</v>
+      </c>
+      <c r="B1403" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1403" t="str">
+        <v>7826046940</v>
+      </c>
+      <c r="D1403" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1403" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1403" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1403">
+        <v>47161</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="str">
+        <v>Краснодарский завод Нефтемаш</v>
+      </c>
+      <c r="B1404" t="str">
+        <v>АО</v>
+      </c>
+      <c r="C1404" t="str">
+        <v>2308026372</v>
+      </c>
+      <c r="D1404" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1404" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1404" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1404">
+        <v>47190</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="str">
+        <v>НТЦ ЗЭРС</v>
+      </c>
+      <c r="B1405" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1405" t="str">
+        <v>6229024740</v>
+      </c>
+      <c r="D1405" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1405" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1405" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1405" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="str">
+        <v>КасторИнжиниринг</v>
+      </c>
+      <c r="B1406" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1406" t="str">
+        <v>5612079207</v>
+      </c>
+      <c r="D1406" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1406" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1406" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1406" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="str">
+        <v>МК Энерго</v>
+      </c>
+      <c r="B1407" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1407" t="str">
+        <v>7731587806</v>
+      </c>
+      <c r="D1407" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1407" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1407" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1407" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1395"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1407"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -17785,7 +17785,7 @@
         <v>РБ</v>
       </c>
       <c r="G756">
-        <v>46199</v>
+        <v>46547</v>
       </c>
     </row>
     <row r="757">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -10976,7 +10976,7 @@
         <v>РФ</v>
       </c>
       <c r="G460">
-        <v>46226</v>
+        <v>47322</v>
       </c>
     </row>
     <row r="461">
@@ -10999,7 +10999,7 @@
         <v>РФ</v>
       </c>
       <c r="G461">
-        <v>46226</v>
+        <v>47322</v>
       </c>
     </row>
     <row r="462">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -18821,8 +18821,8 @@
       <c r="F801" t="str">
         <v>РФ</v>
       </c>
-      <c r="G801" t="str">
-        <v/>
+      <c r="G801">
+        <v>47328</v>
       </c>
     </row>
     <row r="802">
@@ -18844,8 +18844,8 @@
       <c r="F802" t="str">
         <v>РФ</v>
       </c>
-      <c r="G802" t="str">
-        <v/>
+      <c r="G802">
+        <v>47328</v>
       </c>
     </row>
     <row r="803">
@@ -18867,8 +18867,8 @@
       <c r="F803" t="str">
         <v>РФ</v>
       </c>
-      <c r="G803" t="str">
-        <v/>
+      <c r="G803">
+        <v>47328</v>
       </c>
     </row>
     <row r="804">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1395"/>
+  <dimension ref="A1:G1397"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -32489,9 +32489,55 @@
         <v/>
       </c>
     </row>
+    <row r="1396">
+      <c r="A1396" t="str">
+        <v>Урал-Технологические системы покрытий (Урал-ТСП)</v>
+      </c>
+      <c r="B1396" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1396" t="str">
+        <v>261034621</v>
+      </c>
+      <c r="D1396" t="str">
+        <v>O’ZAKK (IAF)</v>
+      </c>
+      <c r="E1396" t="str">
+        <v>ISO 9001:2015</v>
+      </c>
+      <c r="F1396" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1396">
+        <v>47327</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="str">
+        <v>Урал-Технологические системы покрытий (Урал-ТСП)</v>
+      </c>
+      <c r="B1397" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1397" t="str">
+        <v>261034621</v>
+      </c>
+      <c r="D1397" t="str">
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+      </c>
+      <c r="E1397" t="str">
+        <v>ISO 9001:2015</v>
+      </c>
+      <c r="F1397" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1397">
+        <v>47327</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1395"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1397"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -994,7 +994,7 @@
         <v>РФ</v>
       </c>
       <c r="G26">
-        <v>46164</v>
+        <v>46528</v>
       </c>
     </row>
     <row r="27">
@@ -12678,7 +12678,7 @@
         <v>РФ</v>
       </c>
       <c r="G534">
-        <v>46211</v>
+        <v>46575</v>
       </c>
     </row>
     <row r="535">
@@ -13713,7 +13713,7 @@
         <v>РФ</v>
       </c>
       <c r="G579">
-        <v>46156</v>
+        <v>46513</v>
       </c>
     </row>
     <row r="580">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -1569,7 +1569,7 @@
         <v>РФ</v>
       </c>
       <c r="G51">
-        <v>46192</v>
+        <v>46542</v>
       </c>
     </row>
     <row r="52">
@@ -1592,7 +1592,7 @@
         <v>РФ</v>
       </c>
       <c r="G52">
-        <v>46192</v>
+        <v>46542</v>
       </c>
     </row>
     <row r="53">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -6531,7 +6531,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E267" t="str">
-        <v>ГОСТ Р 58139-2018</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F267" t="str">
         <v>РФ</v>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -32278,8 +32278,8 @@
       <c r="F1386" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1386" t="str">
-        <v/>
+      <c r="G1386">
+        <v>47343</v>
       </c>
     </row>
     <row r="1387">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -32278,8 +32278,8 @@
       <c r="F1386" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1386">
-        <v>47343</v>
+      <c r="G1386" t="str">
+        <v/>
       </c>
     </row>
     <row r="1387">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -32209,8 +32209,8 @@
       <c r="F1383" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1383" t="str">
-        <v/>
+      <c r="G1383">
+        <v>47350</v>
       </c>
     </row>
     <row r="1384">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -32024,8 +32024,8 @@
       <c r="F1375" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1375">
-        <v>47350</v>
+      <c r="G1375" t="str">
+        <v/>
       </c>
     </row>
     <row r="1376">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -6459,7 +6459,7 @@
         <v>500227068</v>
       </c>
       <c r="D264" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ECA (APAC)</v>
       </c>
       <c r="E264" t="str">
         <v>ISO 9001:2015</v>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -6813,7 +6813,7 @@
         <v>РФ</v>
       </c>
       <c r="G279">
-        <v>46198</v>
+        <v>46563</v>
       </c>
     </row>
     <row r="280">
@@ -32047,8 +32047,8 @@
       <c r="F1376" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1376" t="str">
-        <v/>
+      <c r="G1376">
+        <v>47357</v>
       </c>
     </row>
     <row r="1377">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1393"/>
+  <dimension ref="A1:G1392"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14012,7 +14012,7 @@
         <v>РФ</v>
       </c>
       <c r="G592">
-        <v>46263</v>
+        <v>47359</v>
       </c>
     </row>
     <row r="593">
@@ -26370,25 +26370,25 @@
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>Восход ПЛЮС</v>
+        <v>Научно-производственная фирма "БИОСС"</v>
       </c>
       <c r="B1130" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1130" t="str">
-        <v>7724383865</v>
+        <v>7735126570</v>
       </c>
       <c r="D1130" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1130" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1130" t="str">
         <v>РФ</v>
       </c>
       <c r="G1130">
-        <v>46987</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1131">
@@ -26402,7 +26402,7 @@
         <v>7735126570</v>
       </c>
       <c r="D1131" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1131" t="str">
         <v>ISO 13485:2016</v>
@@ -26425,39 +26425,39 @@
         <v>7735126570</v>
       </c>
       <c r="D1132" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1132" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1132" t="str">
         <v>РФ</v>
       </c>
       <c r="G1132">
-        <v>47039</v>
+        <v>47063</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>Научно-производственная фирма "БИОСС"</v>
+        <v>РСтартер</v>
       </c>
       <c r="B1133" t="str">
         <v>АО</v>
       </c>
       <c r="C1133" t="str">
-        <v>7735126570</v>
+        <v>5258156241</v>
       </c>
       <c r="D1133" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1133" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1133" t="str">
         <v>РФ</v>
       </c>
       <c r="G1133">
-        <v>47063</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="1134">
@@ -26471,16 +26471,16 @@
         <v>5258156241</v>
       </c>
       <c r="D1134" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1134" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1134" t="str">
         <v>РФ</v>
       </c>
       <c r="G1134">
-        <v>46177</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1135">
@@ -26494,16 +26494,16 @@
         <v>5258156241</v>
       </c>
       <c r="D1135" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1135" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1135" t="str">
         <v>РФ</v>
       </c>
       <c r="G1135">
-        <v>46982</v>
+        <v>46983</v>
       </c>
     </row>
     <row r="1136">
@@ -26517,7 +26517,7 @@
         <v>5258156241</v>
       </c>
       <c r="D1136" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1136" t="str">
         <v>ISO 9001:2015</v>
@@ -26531,82 +26531,82 @@
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>РСтартер</v>
+        <v>ЕТС Трейд</v>
       </c>
       <c r="B1137" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1137" t="str">
-        <v>5258156241</v>
+        <v>7224069315</v>
       </c>
       <c r="D1137" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1137" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1137" t="str">
         <v>РФ</v>
       </c>
       <c r="G1137">
-        <v>46983</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>ЕТС Трейд</v>
+        <v>НПП Тасма</v>
       </c>
       <c r="B1138" t="str">
         <v>ООО</v>
       </c>
       <c r="C1138" t="str">
-        <v>7224069315</v>
+        <v>1658105396</v>
       </c>
       <c r="D1138" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1138" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1138" t="str">
         <v>РФ</v>
       </c>
       <c r="G1138">
-        <v>46996</v>
+        <v>46998</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>НПП Тасма</v>
+        <v>Завод Красный Якорь</v>
       </c>
       <c r="B1139" t="str">
-        <v>ООО</v>
+        <v>ПАО</v>
       </c>
       <c r="C1139" t="str">
-        <v>1658105396</v>
+        <v>5257005049</v>
       </c>
       <c r="D1139" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1139" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1139" t="str">
         <v>РФ</v>
       </c>
       <c r="G1139">
-        <v>46998</v>
+        <v>46602</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>Завод Красный Якорь</v>
+        <v>Морское грузовое бюро</v>
       </c>
       <c r="B1140" t="str">
-        <v>ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1140" t="str">
-        <v>5257005049</v>
+        <v>4705063303</v>
       </c>
       <c r="D1140" t="str">
         <v>ESYD (IAF)</v>
@@ -26618,18 +26618,18 @@
         <v>РФ</v>
       </c>
       <c r="G1140">
-        <v>46602</v>
+        <v>46649</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>Морское грузовое бюро</v>
+        <v>GRETIMYBE</v>
       </c>
       <c r="B1141" t="str">
-        <v>ООО</v>
+        <v>UAB</v>
       </c>
       <c r="C1141" t="str">
-        <v>4705063303</v>
+        <v>LT 415578811</v>
       </c>
       <c r="D1141" t="str">
         <v>ESYD (IAF)</v>
@@ -26638,21 +26638,21 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1141" t="str">
-        <v>РФ</v>
+        <v>Lithuania</v>
       </c>
       <c r="G1141">
-        <v>46649</v>
+        <v>46652</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>GRETIMYBE</v>
+        <v>Санрайз</v>
       </c>
       <c r="B1142" t="str">
-        <v>UAB</v>
+        <v>ООО</v>
       </c>
       <c r="C1142" t="str">
-        <v>LT 415578811</v>
+        <v>7825449671</v>
       </c>
       <c r="D1142" t="str">
         <v>ESYD (IAF)</v>
@@ -26664,7 +26664,7 @@
         <v>Lithuania</v>
       </c>
       <c r="G1142">
-        <v>46652</v>
+        <v>46897</v>
       </c>
     </row>
     <row r="1143">
@@ -26681,36 +26681,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1143" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1143" t="str">
-        <v>Lithuania</v>
+        <v>РФ</v>
       </c>
       <c r="G1143">
-        <v>46897</v>
+        <v>46899</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>Санрайз</v>
+        <v>Архангельский фанерный завод</v>
       </c>
       <c r="B1144" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1144" t="str">
-        <v>7825449671</v>
+        <v>2903004722</v>
       </c>
       <c r="D1144" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1144" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1144" t="str">
         <v>РФ</v>
       </c>
       <c r="G1144">
-        <v>46899</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="1145">
@@ -26727,7 +26727,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1145" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1145" t="str">
         <v>РФ</v>
@@ -26750,7 +26750,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1146" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1146" t="str">
         <v>РФ</v>
@@ -26761,19 +26761,19 @@
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>Архангельский фанерный завод</v>
+        <v>Академия бизнеса</v>
       </c>
       <c r="B1147" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1147" t="str">
-        <v>2903004722</v>
+        <v>7801499948</v>
       </c>
       <c r="D1147" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1147" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1147" t="str">
         <v>РФ</v>
@@ -26784,13 +26784,13 @@
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>Академия бизнеса</v>
+        <v>ИЦ "Технохим"</v>
       </c>
       <c r="B1148" t="str">
-        <v>ООО</v>
+        <v>ЗАО</v>
       </c>
       <c r="C1148" t="str">
-        <v>7801499948</v>
+        <v>7813348421</v>
       </c>
       <c r="D1148" t="str">
         <v>ESYD (IAF)</v>
@@ -26802,18 +26802,18 @@
         <v>РФ</v>
       </c>
       <c r="G1148">
-        <v>46750</v>
+        <v>46450</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>ИЦ "Технохим"</v>
+        <v>НПП "СЗГП"</v>
       </c>
       <c r="B1149" t="str">
         <v>ЗАО</v>
       </c>
       <c r="C1149" t="str">
-        <v>7813348421</v>
+        <v>7813385303</v>
       </c>
       <c r="D1149" t="str">
         <v>ESYD (IAF)</v>
@@ -26825,18 +26825,18 @@
         <v>РФ</v>
       </c>
       <c r="G1149">
-        <v>46450</v>
+        <v>46775</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>НПП "СЗГП"</v>
+        <v>Сыктывкарский ликеро-водочный завод</v>
       </c>
       <c r="B1150" t="str">
-        <v>ЗАО</v>
+        <v>АО</v>
       </c>
       <c r="C1150" t="str">
-        <v>7813385303</v>
+        <v>1101205623</v>
       </c>
       <c r="D1150" t="str">
         <v>ESYD (IAF)</v>
@@ -26848,7 +26848,7 @@
         <v>РФ</v>
       </c>
       <c r="G1150">
-        <v>46775</v>
+        <v>46906</v>
       </c>
     </row>
     <row r="1151">
@@ -26865,47 +26865,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1151" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1151" t="str">
         <v>РФ</v>
       </c>
       <c r="G1151">
-        <v>46906</v>
+        <v>46909</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>Сыктывкарский ликеро-водочный завод</v>
+        <v>Ижевский электромеханический завод "Купол"</v>
       </c>
       <c r="B1152" t="str">
         <v>АО</v>
       </c>
       <c r="C1152" t="str">
-        <v>1101205623</v>
+        <v>1831083343</v>
       </c>
       <c r="D1152" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1152" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1152" t="str">
         <v>РФ</v>
       </c>
       <c r="G1152">
-        <v>46909</v>
+        <v>46980</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>Ижевский электромеханический завод "Купол"</v>
+        <v>Арзамасский филиал ООО "Сен-Гобен Строительная Продукция Рус"</v>
       </c>
       <c r="B1153" t="str">
-        <v>АО</v>
+        <v/>
       </c>
       <c r="C1153" t="str">
-        <v>1831083343</v>
+        <v>5011020537</v>
       </c>
       <c r="D1153" t="str">
         <v>ESYD (IAF)</v>
@@ -26917,18 +26917,18 @@
         <v>РФ</v>
       </c>
       <c r="G1153">
-        <v>46980</v>
+        <v>47086</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>Арзамасский филиал ООО "Сен-Гобен Строительная Продукция Рус"</v>
+        <v>Белэнергомаш- БЗЭМ</v>
       </c>
       <c r="B1154" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1154" t="str">
-        <v>5011020537</v>
+        <v>3123315768</v>
       </c>
       <c r="D1154" t="str">
         <v>ESYD (IAF)</v>
@@ -26940,7 +26940,7 @@
         <v>РФ</v>
       </c>
       <c r="G1154">
-        <v>47086</v>
+        <v>46409</v>
       </c>
     </row>
     <row r="1155">
@@ -26957,13 +26957,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1155" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1155" t="str">
         <v>РФ</v>
       </c>
       <c r="G1155">
-        <v>46409</v>
+        <v>46411</v>
       </c>
     </row>
     <row r="1156">
@@ -26980,7 +26980,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1156" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1156" t="str">
         <v>РФ</v>
@@ -26991,25 +26991,25 @@
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>Белэнергомаш- БЗЭМ</v>
+        <v>Калужский научно-исследовательский радиотехнический институт</v>
       </c>
       <c r="B1157" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1157" t="str">
-        <v>3123315768</v>
+        <v>4007017378</v>
       </c>
       <c r="D1157" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1157" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1157" t="str">
         <v>РФ</v>
       </c>
       <c r="G1157">
-        <v>46411</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="1158">
@@ -27026,47 +27026,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1158" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1158" t="str">
         <v>РФ</v>
       </c>
       <c r="G1158">
-        <v>46317</v>
+        <v>46433</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>Калужский научно-исследовательский радиотехнический институт</v>
+        <v>НПП "БАСЭТ"</v>
       </c>
       <c r="B1159" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1159" t="str">
-        <v>4007017378</v>
+        <v>269001177</v>
       </c>
       <c r="D1159" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1159" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1159" t="str">
         <v>РФ</v>
       </c>
       <c r="G1159">
-        <v>46433</v>
+        <v>46488</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>НПП "БАСЭТ"</v>
+        <v>НПП "Петролайн-А"</v>
       </c>
       <c r="B1160" t="str">
         <v>ООО</v>
       </c>
       <c r="C1160" t="str">
-        <v>269001177</v>
+        <v>1650081440</v>
       </c>
       <c r="D1160" t="str">
         <v>ESYD (IAF)</v>
@@ -27078,18 +27078,18 @@
         <v>РФ</v>
       </c>
       <c r="G1160">
-        <v>46488</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>НПП "Петролайн-А"</v>
+        <v>ООО "Энергоспецмонтаж"</v>
       </c>
       <c r="B1161" t="str">
         <v>ООО</v>
       </c>
       <c r="C1161" t="str">
-        <v>1650081440</v>
+        <v>1837006602</v>
       </c>
       <c r="D1161" t="str">
         <v>ESYD (IAF)</v>
@@ -27101,18 +27101,18 @@
         <v>РФ</v>
       </c>
       <c r="G1161">
-        <v>46165</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>ООО "Энергоспецмонтаж"</v>
+        <v>НИКИМТ-АТОМСТРОЙ</v>
       </c>
       <c r="B1162" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1162" t="str">
-        <v>1837006602</v>
+        <v>7715719854</v>
       </c>
       <c r="D1162" t="str">
         <v>ESYD (IAF)</v>
@@ -27124,7 +27124,7 @@
         <v>РФ</v>
       </c>
       <c r="G1162">
-        <v>46214</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="1163">
@@ -27141,13 +27141,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1163" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1163" t="str">
         <v>РФ</v>
       </c>
       <c r="G1163">
-        <v>46244</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="1164">
@@ -27164,70 +27164,70 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1164" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1164" t="str">
         <v>РФ</v>
       </c>
       <c r="G1164">
-        <v>46265</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>НИКИМТ-АТОМСТРОЙ</v>
+        <v>Карбофер Метсервис</v>
       </c>
       <c r="B1165" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1165" t="str">
-        <v>7715719854</v>
+        <v>3662148389</v>
       </c>
       <c r="D1165" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1165" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1165" t="str">
         <v>РФ</v>
       </c>
       <c r="G1165">
-        <v>46326</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>Карбофер Метсервис</v>
+        <v>Белая Дача Волга</v>
       </c>
       <c r="B1166" t="str">
         <v>ООО</v>
       </c>
       <c r="C1166" t="str">
-        <v>3662148389</v>
+        <v>5027307207</v>
       </c>
       <c r="D1166" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1166" t="str">
-        <v>ISO 9001:2015</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1166" t="str">
         <v>РФ</v>
       </c>
       <c r="G1166">
-        <v>46229</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>Белая Дача Волга</v>
+        <v>Воплощение</v>
       </c>
       <c r="B1167" t="str">
         <v>ООО</v>
       </c>
       <c r="C1167" t="str">
-        <v>5027307207</v>
+        <v>7106077126</v>
       </c>
       <c r="D1167" t="str">
         <v>ESYD (IAF)</v>
@@ -27239,18 +27239,18 @@
         <v>РФ</v>
       </c>
       <c r="G1167">
-        <v>46212</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>Воплощение</v>
+        <v>Красный маяк</v>
       </c>
       <c r="B1168" t="str">
         <v>ООО</v>
       </c>
       <c r="C1168" t="str">
-        <v>7106077126</v>
+        <v>7609027393</v>
       </c>
       <c r="D1168" t="str">
         <v>ESYD (IAF)</v>
@@ -27262,18 +27262,18 @@
         <v>РФ</v>
       </c>
       <c r="G1168">
-        <v>46200</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>Красный маяк</v>
+        <v>АПК Астраханский</v>
       </c>
       <c r="B1169" t="str">
         <v>ООО</v>
       </c>
       <c r="C1169" t="str">
-        <v>7609027393</v>
+        <v>3023008925</v>
       </c>
       <c r="D1169" t="str">
         <v>ESYD (IAF)</v>
@@ -27285,7 +27285,7 @@
         <v>РФ</v>
       </c>
       <c r="G1169">
-        <v>46290</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="1170">
@@ -27302,7 +27302,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1170" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>GRASP</v>
       </c>
       <c r="F1170" t="str">
         <v>РФ</v>
@@ -27325,70 +27325,70 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1171" t="str">
-        <v>GRASP</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1171" t="str">
         <v>РФ</v>
       </c>
       <c r="G1171">
-        <v>46284</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>АПК Астраханский</v>
+        <v>НУЦ "Качество"</v>
       </c>
       <c r="B1172" t="str">
         <v>ООО</v>
       </c>
       <c r="C1172" t="str">
-        <v>3023008925</v>
+        <v>7715552355</v>
       </c>
       <c r="D1172" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1172" t="str">
-        <v>FSSC 22000</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1172" t="str">
         <v>РФ</v>
       </c>
       <c r="G1172">
-        <v>46311</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>НУЦ "Качество"</v>
+        <v>BLESS S.R.</v>
       </c>
       <c r="B1173" t="str">
         <v>ООО</v>
       </c>
       <c r="C1173" t="str">
-        <v>7715552355</v>
+        <v>309422741</v>
       </c>
       <c r="D1173" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1173" t="str">
-        <v>ISO 9001:2015</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1173" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1173">
-        <v>46228</v>
+        <v>UZ</v>
+      </c>
+      <c r="G1173" t="str">
+        <v>Сертификат еще не выдан</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>BLESS S.R.</v>
+        <v>Иотова А.А.</v>
       </c>
       <c r="B1174" t="str">
-        <v>ООО</v>
+        <v>ИП</v>
       </c>
       <c r="C1174" t="str">
-        <v>309422741</v>
+        <v>500702017601</v>
       </c>
       <c r="D1174" t="str">
         <v>ESYD (IAF)</v>
@@ -27397,21 +27397,21 @@
         <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1174" t="str">
-        <v>UZ</v>
-      </c>
-      <c r="G1174" t="str">
-        <v>Сертификат еще не выдан</v>
+        <v>РФ</v>
+      </c>
+      <c r="G1174">
+        <v>46247</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>Иотова А.А.</v>
+        <v>Сунгатов Разиль</v>
       </c>
       <c r="B1175" t="str">
         <v>ИП</v>
       </c>
       <c r="C1175" t="str">
-        <v>500702017601</v>
+        <v>300902421774</v>
       </c>
       <c r="D1175" t="str">
         <v>ESYD (IAF)</v>
@@ -27423,18 +27423,18 @@
         <v>РФ</v>
       </c>
       <c r="G1175">
-        <v>46247</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>Сунгатов Разиль</v>
+        <v>Веселый агроном</v>
       </c>
       <c r="B1176" t="str">
-        <v>ИП</v>
+        <v>ООО</v>
       </c>
       <c r="C1176" t="str">
-        <v>300902421774</v>
+        <v>5007082611</v>
       </c>
       <c r="D1176" t="str">
         <v>ESYD (IAF)</v>
@@ -27446,41 +27446,41 @@
         <v>РФ</v>
       </c>
       <c r="G1176">
-        <v>46304</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>Веселый агроном</v>
+        <v>"Пятигорский "Импульс"</v>
       </c>
       <c r="B1177" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1177" t="str">
-        <v>5007082611</v>
+        <v>2632005656</v>
       </c>
       <c r="D1177" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1177" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1177" t="str">
         <v>РФ</v>
       </c>
       <c r="G1177">
-        <v>46289</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>"Пятигорский "Импульс"</v>
+        <v>"Швабе"</v>
       </c>
       <c r="B1178" t="str">
-        <v>ОАО</v>
+        <v>АО</v>
       </c>
       <c r="C1178" t="str">
-        <v>2632005656</v>
+        <v>7717671799</v>
       </c>
       <c r="D1178" t="str">
         <v>ESYD (IAF)</v>
@@ -27492,18 +27492,18 @@
         <v>РФ</v>
       </c>
       <c r="G1178">
-        <v>46341</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>"Швабе"</v>
+        <v>"ПИТЕРАТОММАШ"</v>
       </c>
       <c r="B1179" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1179" t="str">
-        <v>7717671799</v>
+        <v>7805658638</v>
       </c>
       <c r="D1179" t="str">
         <v>ESYD (IAF)</v>
@@ -27515,18 +27515,18 @@
         <v>РФ</v>
       </c>
       <c r="G1179">
-        <v>46320</v>
+        <v>46422</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>"ПИТЕРАТОММАШ"</v>
+        <v>"Морской лабораторый комплекс"</v>
       </c>
       <c r="B1180" t="str">
         <v>ООО</v>
       </c>
       <c r="C1180" t="str">
-        <v>7805658638</v>
+        <v>7816640696</v>
       </c>
       <c r="D1180" t="str">
         <v>ESYD (IAF)</v>
@@ -27538,64 +27538,64 @@
         <v>РФ</v>
       </c>
       <c r="G1180">
-        <v>46422</v>
+        <v>46409</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>"Морской лабораторый комплекс"</v>
+        <v>«Байкальская энергетическая компания»</v>
       </c>
       <c r="B1181" t="str">
         <v>ООО</v>
       </c>
       <c r="C1181" t="str">
-        <v>7816640696</v>
+        <v>3808229774</v>
       </c>
       <c r="D1181" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1181" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1181" t="str">
         <v>РФ</v>
       </c>
       <c r="G1181">
-        <v>46409</v>
+        <v>46375</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>«Байкальская энергетическая компания»</v>
+        <v>"Транснефть-Диаскан"</v>
       </c>
       <c r="B1182" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1182" t="str">
-        <v>3808229774</v>
+        <v>5072703668</v>
       </c>
       <c r="D1182" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1182" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1182" t="str">
         <v>РФ</v>
       </c>
       <c r="G1182">
-        <v>46375</v>
+        <v>46482</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>"Транснефть-Диаскан"</v>
+        <v>"С-плюс"</v>
       </c>
       <c r="B1183" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1183" t="str">
-        <v>5072703668</v>
+        <v>7720325407</v>
       </c>
       <c r="D1183" t="str">
         <v>ESYD (IAF)</v>
@@ -27607,18 +27607,18 @@
         <v>РФ</v>
       </c>
       <c r="G1183">
-        <v>46482</v>
+        <v>46674</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>"С-плюс"</v>
+        <v>"ЦНИИМФ"</v>
       </c>
       <c r="B1184" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1184" t="str">
-        <v>7720325407</v>
+        <v>7815001288</v>
       </c>
       <c r="D1184" t="str">
         <v>ESYD (IAF)</v>
@@ -27630,18 +27630,18 @@
         <v>РФ</v>
       </c>
       <c r="G1184">
-        <v>46674</v>
+        <v>46514</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>"ЦНИИМФ"</v>
+        <v>"ВЗПП - Микрон"</v>
       </c>
       <c r="B1185" t="str">
         <v>АО</v>
       </c>
       <c r="C1185" t="str">
-        <v>7815001288</v>
+        <v>3661020890</v>
       </c>
       <c r="D1185" t="str">
         <v>ESYD (IAF)</v>
@@ -27653,18 +27653,18 @@
         <v>РФ</v>
       </c>
       <c r="G1185">
-        <v>46514</v>
+        <v>46598</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>"ВЗПП - Микрон"</v>
+        <v>Ostec Enterprise Ltd.</v>
       </c>
       <c r="B1186" t="str">
-        <v>АО</v>
+        <v/>
       </c>
       <c r="C1186" t="str">
-        <v>3661020890</v>
+        <v>7731480806</v>
       </c>
       <c r="D1186" t="str">
         <v>ESYD (IAF)</v>
@@ -27676,53 +27676,53 @@
         <v>РФ</v>
       </c>
       <c r="G1186">
-        <v>46598</v>
+        <v>46593</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="str">
-        <v>Ostec Enterprise Ltd.</v>
+        <v>«Национальный расчетный депозитарий»</v>
       </c>
       <c r="B1187" t="str">
-        <v/>
+        <v>НКО АО</v>
       </c>
       <c r="C1187" t="str">
-        <v>7731480806</v>
+        <v>7702165310</v>
       </c>
       <c r="D1187" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1187" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1187" t="str">
         <v>РФ</v>
       </c>
       <c r="G1187">
-        <v>46593</v>
+        <v>46724</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="str">
-        <v>«Национальный расчетный депозитарий»</v>
+        <v>"Томарина"</v>
       </c>
       <c r="B1188" t="str">
-        <v>НКО АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1188" t="str">
-        <v>7702165310</v>
+        <v>3000008541</v>
       </c>
       <c r="D1188" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1188" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1188" t="str">
         <v>РФ</v>
       </c>
       <c r="G1188">
-        <v>46724</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="1189">
@@ -27739,7 +27739,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1189" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>GRASP</v>
       </c>
       <c r="F1189" t="str">
         <v>РФ</v>
@@ -27762,70 +27762,70 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1190" t="str">
-        <v>GRASP</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1190" t="str">
         <v>РФ</v>
       </c>
       <c r="G1190">
-        <v>46323</v>
+        <v>46744</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="str">
-        <v>"Томарина"</v>
+        <v>"АгроНеро"</v>
       </c>
       <c r="B1191" t="str">
         <v>ООО</v>
       </c>
       <c r="C1191" t="str">
-        <v>3000008541</v>
+        <v>6140040847</v>
       </c>
       <c r="D1191" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1191" t="str">
-        <v>FSSC 22000</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1191" t="str">
         <v>РФ</v>
       </c>
       <c r="G1191">
-        <v>46744</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="str">
-        <v>"АгроНеро"</v>
+        <v>"Новгородская аккумуляторная компания"</v>
       </c>
       <c r="B1192" t="str">
         <v>ООО</v>
       </c>
       <c r="C1192" t="str">
-        <v>6140040847</v>
+        <v>5321073271</v>
       </c>
       <c r="D1192" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1192" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1192" t="str">
         <v>РФ</v>
       </c>
       <c r="G1192">
-        <v>46356</v>
+        <v>46653</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="str">
-        <v>"Новгородская аккумуляторная компания"</v>
+        <v>"Метровагонмаш"</v>
       </c>
       <c r="B1193" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1193" t="str">
-        <v>5321073271</v>
+        <v>5029006702</v>
       </c>
       <c r="D1193" t="str">
         <v>ESYD (IAF)</v>
@@ -27837,18 +27837,18 @@
         <v>РФ</v>
       </c>
       <c r="G1193">
-        <v>46653</v>
+        <v>46767</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="str">
-        <v>"Метровагонмаш"</v>
+        <v>"Клиническая стоматологическая поликлиника №12"</v>
       </c>
       <c r="B1194" t="str">
-        <v>АО</v>
+        <v>ГАУЗ</v>
       </c>
       <c r="C1194" t="str">
-        <v>5029006702</v>
+        <v>3448009146</v>
       </c>
       <c r="D1194" t="str">
         <v>ESYD (IAF)</v>
@@ -27860,18 +27860,18 @@
         <v>РФ</v>
       </c>
       <c r="G1194">
-        <v>46767</v>
+        <v>46888</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="str">
-        <v>"Клиническая стоматологическая поликлиника №12"</v>
+        <v>«Кримиан Фэмили Киль»</v>
       </c>
       <c r="B1195" t="str">
-        <v>ГАУЗ</v>
+        <v>ООО</v>
       </c>
       <c r="C1195" t="str">
-        <v>3448009146</v>
+        <v>2315230925</v>
       </c>
       <c r="D1195" t="str">
         <v>ESYD (IAF)</v>
@@ -27883,18 +27883,18 @@
         <v>РФ</v>
       </c>
       <c r="G1195">
-        <v>46888</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="str">
-        <v>«Кримиан Фэмили Киль»</v>
+        <v>Производственная компания "Велам-Рус"</v>
       </c>
       <c r="B1196" t="str">
         <v>ООО</v>
       </c>
       <c r="C1196" t="str">
-        <v>2315230925</v>
+        <v>5258105399</v>
       </c>
       <c r="D1196" t="str">
         <v>ESYD (IAF)</v>
@@ -27906,30 +27906,30 @@
         <v>РФ</v>
       </c>
       <c r="G1196">
-        <v>46750</v>
+        <v>46775</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="str">
-        <v>Производственная компания "Велам-Рус"</v>
+        <v>"Уралэлектромедь"</v>
       </c>
       <c r="B1197" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1197" t="str">
-        <v>5258105399</v>
+        <v>6606003385</v>
       </c>
       <c r="D1197" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1197" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1197" t="str">
         <v>РФ</v>
       </c>
       <c r="G1197">
-        <v>46775</v>
+        <v>46380</v>
       </c>
     </row>
     <row r="1198">
@@ -27946,47 +27946,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1198" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1198" t="str">
         <v>РФ</v>
       </c>
       <c r="G1198">
-        <v>46380</v>
+        <v>46367</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="str">
-        <v>"Уралэлектромедь"</v>
+        <v>«YETA»</v>
       </c>
       <c r="B1199" t="str">
-        <v>АО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1199" t="str">
-        <v>6606003385</v>
+        <v>221040014631</v>
       </c>
       <c r="D1199" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1199" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1199" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1199">
-        <v>46367</v>
+        <v>46733</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="str">
-        <v>«YETA»</v>
+        <v>"Academy of Civil Aviation"</v>
       </c>
       <c r="B1200" t="str">
-        <v>ТОО</v>
+        <v>JSC</v>
       </c>
       <c r="C1200" t="str">
-        <v>221040014631</v>
+        <v>010840003460</v>
       </c>
       <c r="D1200" t="str">
         <v>ESYD (IAF)</v>
@@ -27998,12 +27998,12 @@
         <v>KZ</v>
       </c>
       <c r="G1200">
-        <v>46733</v>
+        <v>46747</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="str">
-        <v>"Academy of Civil Aviation"</v>
+        <v>JSC "Academy of Civil Aviation"</v>
       </c>
       <c r="B1201" t="str">
         <v>JSC</v>
@@ -28012,73 +28012,73 @@
         <v>010840003460</v>
       </c>
       <c r="D1201" t="str">
-        <v>ESYD (IAF)</v>
+        <v>n/a</v>
       </c>
       <c r="E1201" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 21001</v>
       </c>
       <c r="F1201" t="str">
         <v>KZ</v>
       </c>
       <c r="G1201">
-        <v>46747</v>
+        <v>46744</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="str">
-        <v>JSC "Academy of Civil Aviation"</v>
+        <v>«АзияАгроФуд»</v>
       </c>
       <c r="B1202" t="str">
-        <v>JSC</v>
+        <v>АО</v>
       </c>
       <c r="C1202" t="str">
-        <v>010840003460</v>
+        <v>050740003177</v>
       </c>
       <c r="D1202" t="str">
-        <v>n/a</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1202" t="str">
-        <v>ISO 21001</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1202" t="str">
         <v>KZ</v>
       </c>
-      <c r="G1202">
-        <v>46744</v>
+      <c r="G1202" t="str">
+        <v/>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="str">
-        <v>«АзияАгроФуд»</v>
+        <v>«Каменск-Уральский металлургический завод» (ПАО «КУМЗ»)</v>
       </c>
       <c r="B1203" t="str">
-        <v>АО</v>
+        <v>ПАО</v>
       </c>
       <c r="C1203" t="str">
-        <v>050740003177</v>
+        <v>6665002150</v>
       </c>
       <c r="D1203" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1203" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1203" t="str">
-        <v>KZ</v>
-      </c>
-      <c r="G1203" t="str">
-        <v/>
+        <v>РФ</v>
+      </c>
+      <c r="G1203">
+        <v>47102</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="str">
-        <v>«Каменск-Уральский металлургический завод» (ПАО «КУМЗ»)</v>
+        <v>"СЛАВДОМ"</v>
       </c>
       <c r="B1204" t="str">
-        <v>ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1204" t="str">
-        <v>6665002150</v>
+        <v>7806528328</v>
       </c>
       <c r="D1204" t="str">
         <v>ESYD (IAF)</v>
@@ -28090,18 +28090,18 @@
         <v>РФ</v>
       </c>
       <c r="G1204">
-        <v>47102</v>
+        <v>46871</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="str">
-        <v>"СЛАВДОМ"</v>
+        <v>«ГАБИОНЫ МАККАФЕРРИ СНГ»</v>
       </c>
       <c r="B1205" t="str">
         <v>ООО</v>
       </c>
       <c r="C1205" t="str">
-        <v>7806528328</v>
+        <v>7722187777</v>
       </c>
       <c r="D1205" t="str">
         <v>ESYD (IAF)</v>
@@ -28113,30 +28113,30 @@
         <v>РФ</v>
       </c>
       <c r="G1205">
-        <v>46871</v>
+        <v>46474</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="str">
-        <v>«ГАБИОНЫ МАККАФЕРРИ СНГ»</v>
+        <v>"Коломенский завод"</v>
       </c>
       <c r="B1206" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1206" t="str">
-        <v>7722187777</v>
+        <v>5022013517</v>
       </c>
       <c r="D1206" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1206" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1206" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1206">
-        <v>46474</v>
+      <c r="G1206" t="str">
+        <v>Сертификат еще не выдан</v>
       </c>
     </row>
     <row r="1207">
@@ -28153,7 +28153,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1207" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1207" t="str">
         <v>РФ</v>
@@ -28164,36 +28164,36 @@
     </row>
     <row r="1208">
       <c r="A1208" t="str">
-        <v>"Коломенский завод"</v>
+        <v>"ENERGOBEST"</v>
       </c>
       <c r="B1208" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1208" t="str">
-        <v>5022013517</v>
+        <v>301418434</v>
       </c>
       <c r="D1208" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1208" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1208" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1208" t="str">
-        <v>Сертификат еще не выдан</v>
+        <v>UZ</v>
+      </c>
+      <c r="G1208">
+        <v>46846</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="str">
-        <v>"ENERGOBEST"</v>
+        <v>«PRIME TOWER GROUP»</v>
       </c>
       <c r="B1209" t="str">
         <v>ООО</v>
       </c>
       <c r="C1209" t="str">
-        <v>301418434</v>
+        <v>303879121</v>
       </c>
       <c r="D1209" t="str">
         <v>ESYD (IAF)</v>
@@ -28205,18 +28205,18 @@
         <v>UZ</v>
       </c>
       <c r="G1209">
-        <v>46846</v>
+        <v>46838</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="str">
-        <v>«PRIME TOWER GROUP»</v>
+        <v>«GEOTEC»</v>
       </c>
       <c r="B1210" t="str">
-        <v>ООО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1210" t="str">
-        <v>303879121</v>
+        <v>061240002175</v>
       </c>
       <c r="D1210" t="str">
         <v>ESYD (IAF)</v>
@@ -28225,21 +28225,21 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1210" t="str">
-        <v>UZ</v>
+        <v>KZ</v>
       </c>
       <c r="G1210">
-        <v>46838</v>
+        <v>46859</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="str">
-        <v>«GEOTEC»</v>
+        <v>«Узэлектроаппарат-Электрощит»</v>
       </c>
       <c r="B1211" t="str">
-        <v>ТОО</v>
+        <v>АО</v>
       </c>
       <c r="C1211" t="str">
-        <v>061240002175</v>
+        <v>201052167</v>
       </c>
       <c r="D1211" t="str">
         <v>ESYD (IAF)</v>
@@ -28248,10 +28248,10 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1211" t="str">
-        <v>KZ</v>
+        <v>UZ</v>
       </c>
       <c r="G1211">
-        <v>46859</v>
+        <v>46892</v>
       </c>
     </row>
     <row r="1212">
@@ -28268,13 +28268,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1212" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1212" t="str">
         <v>UZ</v>
       </c>
       <c r="G1212">
-        <v>46892</v>
+        <v>46889</v>
       </c>
     </row>
     <row r="1213">
@@ -28291,36 +28291,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1213" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1213" t="str">
         <v>UZ</v>
       </c>
       <c r="G1213">
-        <v>46889</v>
+        <v>46892</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="str">
-        <v>«Узэлектроаппарат-Электрощит»</v>
+        <v>"Трастбанк"</v>
       </c>
       <c r="B1214" t="str">
-        <v>АО</v>
+        <v>ЧАБ</v>
       </c>
       <c r="C1214" t="str">
-        <v>201052167</v>
+        <v>201055090</v>
       </c>
       <c r="D1214" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1214" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1214" t="str">
         <v>UZ</v>
       </c>
       <c r="G1214">
-        <v>46892</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="1215">
@@ -28337,36 +28337,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1215" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 37001:2016</v>
       </c>
       <c r="F1215" t="str">
         <v>UZ</v>
       </c>
       <c r="G1215">
-        <v>46996</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="str">
-        <v>"Трастбанк"</v>
+        <v>"Каспийский трубопроводный консорциум-Р"</v>
       </c>
       <c r="B1216" t="str">
-        <v>ЧАБ</v>
+        <v>АО</v>
       </c>
       <c r="C1216" t="str">
-        <v>201055090</v>
+        <v>2310040800</v>
       </c>
       <c r="D1216" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1216" t="str">
-        <v>ISO 37001:2016</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1216" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1216">
-        <v>47039</v>
+        <v>46961</v>
       </c>
     </row>
     <row r="1217">
@@ -28383,7 +28383,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1217" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1217" t="str">
         <v>РФ</v>
@@ -28394,48 +28394,48 @@
     </row>
     <row r="1218">
       <c r="A1218" t="str">
-        <v>"Каспийский трубопроводный консорциум-Р"</v>
+        <v>"АСТОР"</v>
       </c>
       <c r="B1218" t="str">
         <v>АО</v>
       </c>
       <c r="C1218" t="str">
-        <v>2310040800</v>
+        <v>4703015840</v>
       </c>
       <c r="D1218" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1218" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1218" t="str">
         <v>РФ</v>
       </c>
       <c r="G1218">
-        <v>46961</v>
+        <v>47056</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="str">
-        <v>"АСТОР"</v>
+        <v>"AIR MARAKANDA"</v>
       </c>
       <c r="B1219" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1219" t="str">
-        <v>4703015840</v>
+        <v>307280842</v>
       </c>
       <c r="D1219" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1219" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1219" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1219">
-        <v>47056</v>
+        <v>46993</v>
       </c>
     </row>
     <row r="1220">
@@ -28452,36 +28452,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1220" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1220" t="str">
         <v>UZ</v>
       </c>
       <c r="G1220">
-        <v>46993</v>
+        <v>47005</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="str">
-        <v>"AIR MARAKANDA"</v>
+        <v>Частное производственное унитарное предприятие "НТП "Центр"</v>
       </c>
       <c r="B1221" t="str">
-        <v>ООО</v>
+        <v>Частное производственное унитарное предприятие</v>
       </c>
       <c r="C1221" t="str">
-        <v>307280842</v>
+        <v>700010977</v>
       </c>
       <c r="D1221" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1221" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1221" t="str">
-        <v>UZ</v>
+        <v>РБ</v>
       </c>
       <c r="G1221">
-        <v>47005</v>
+        <v>47045</v>
       </c>
     </row>
     <row r="1222">
@@ -28495,7 +28495,7 @@
         <v>700010977</v>
       </c>
       <c r="D1222" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1222" t="str">
         <v>ISO 9001:2015</v>
@@ -28509,16 +28509,16 @@
     </row>
     <row r="1223">
       <c r="A1223" t="str">
-        <v>Частное производственное унитарное предприятие "НТП "Центр"</v>
+        <v>Silicon Materials Inc.</v>
       </c>
       <c r="B1223" t="str">
-        <v>Частное производственное унитарное предприятие</v>
+        <v/>
       </c>
       <c r="C1223" t="str">
-        <v>700010977</v>
+        <v>EIN 25-1681874</v>
       </c>
       <c r="D1223" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1223" t="str">
         <v>ISO 9001:2015</v>
@@ -28526,19 +28526,19 @@
       <c r="F1223" t="str">
         <v>РБ</v>
       </c>
-      <c r="G1223">
-        <v>47045</v>
+      <c r="G1223" t="str">
+        <v>Сертификат еще не выдан</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="str">
-        <v>Silicon Materials Inc.</v>
+        <v>"CLOUPARD"</v>
       </c>
       <c r="B1224" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1224" t="str">
-        <v>EIN 25-1681874</v>
+        <v>310143054</v>
       </c>
       <c r="D1224" t="str">
         <v>ESYD (IAF)</v>
@@ -28547,7 +28547,7 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1224" t="str">
-        <v>РБ</v>
+        <v>UZ</v>
       </c>
       <c r="G1224" t="str">
         <v>Сертификат еще не выдан</v>
@@ -28567,7 +28567,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1225" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1225" t="str">
         <v>UZ</v>
@@ -28578,13 +28578,13 @@
     </row>
     <row r="1226">
       <c r="A1226" t="str">
-        <v>"CLOUPARD"</v>
+        <v>"Н-ТЕХ"</v>
       </c>
       <c r="B1226" t="str">
         <v>ООО</v>
       </c>
       <c r="C1226" t="str">
-        <v>310143054</v>
+        <v>7813283686</v>
       </c>
       <c r="D1226" t="str">
         <v>ESYD (IAF)</v>
@@ -28593,44 +28593,44 @@
         <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1226" t="str">
-        <v>UZ</v>
-      </c>
-      <c r="G1226" t="str">
-        <v>Сертификат еще не выдан</v>
+        <v>РФ</v>
+      </c>
+      <c r="G1226">
+        <v>47055</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="str">
-        <v>"Н-ТЕХ"</v>
+        <v>"СММ"</v>
       </c>
       <c r="B1227" t="str">
-        <v>ООО</v>
+        <v>ЗАО</v>
       </c>
       <c r="C1227" t="str">
-        <v>7813283686</v>
+        <v>7826136294</v>
       </c>
       <c r="D1227" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1227" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1227" t="str">
         <v>РФ</v>
       </c>
       <c r="G1227">
-        <v>47055</v>
+        <v>47012</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="str">
-        <v>"СММ"</v>
+        <v>"Ifoda Agro Kimyo Himoya"</v>
       </c>
       <c r="B1228" t="str">
-        <v>ЗАО</v>
+        <v>СП ООО</v>
       </c>
       <c r="C1228" t="str">
-        <v>7826136294</v>
+        <v>314010020917</v>
       </c>
       <c r="D1228" t="str">
         <v>ESYD (IAF)</v>
@@ -28639,10 +28639,10 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1228" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1228">
-        <v>47012</v>
+        <v>47074</v>
       </c>
     </row>
     <row r="1229">
@@ -28659,36 +28659,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1229" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1229" t="str">
         <v>UZ</v>
       </c>
       <c r="G1229">
-        <v>47074</v>
+        <v>47073</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="str">
-        <v>"Ifoda Agro Kimyo Himoya"</v>
+        <v>ZTE Investment</v>
       </c>
       <c r="B1230" t="str">
-        <v>СП ООО</v>
+        <v>ИП ООО</v>
       </c>
       <c r="C1230" t="str">
-        <v>314010020917</v>
+        <v>20662083</v>
       </c>
       <c r="D1230" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1230" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1230" t="str">
         <v>UZ</v>
       </c>
       <c r="G1230">
-        <v>47073</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="1231">
@@ -28705,13 +28705,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1231" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1231" t="str">
         <v>UZ</v>
       </c>
       <c r="G1231">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="1232">
@@ -28728,47 +28728,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1232" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1232" t="str">
         <v>UZ</v>
       </c>
       <c r="G1232">
-        <v>47055</v>
+        <v>47056</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="str">
-        <v>ZTE Investment</v>
+        <v>«Интраком»</v>
       </c>
       <c r="B1233" t="str">
-        <v>ИП ООО</v>
+        <v>ООО</v>
       </c>
       <c r="C1233" t="str">
-        <v>20662083</v>
+        <v>6612059795</v>
       </c>
       <c r="D1233" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1233" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1233" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1233">
-        <v>47056</v>
+        <v>47031</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="str">
-        <v>«Интраком»</v>
+        <v>«КФ-АВТО»</v>
       </c>
       <c r="B1234" t="str">
         <v>ООО</v>
       </c>
       <c r="C1234" t="str">
-        <v>6612059795</v>
+        <v>692142686</v>
       </c>
       <c r="D1234" t="str">
         <v>ESYD (IAF)</v>
@@ -28777,44 +28777,44 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1234" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1234">
-        <v>47031</v>
+        <v>47048</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="str">
-        <v>«КФ-АВТО»</v>
+        <v>"Авалон Джус"</v>
       </c>
       <c r="B1235" t="str">
         <v>ООО</v>
       </c>
       <c r="C1235" t="str">
-        <v>692142686</v>
+        <v>2310215472</v>
       </c>
       <c r="D1235" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1235" t="str">
-        <v>ISO 9001:2015</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1235" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1235">
-        <v>47048</v>
+        <v>47106</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="str">
-        <v>"Авалон Джус"</v>
+        <v>"Компания Алтын Казык"</v>
       </c>
       <c r="B1236" t="str">
-        <v>ООО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1236" t="str">
-        <v>2310215472</v>
+        <v>060640000339</v>
       </c>
       <c r="D1236" t="str">
         <v>ESYD (IAF)</v>
@@ -28823,21 +28823,21 @@
         <v>FSSC 22000</v>
       </c>
       <c r="F1236" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1236">
-        <v>47106</v>
+        <v>46484</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="str">
-        <v>"Компания Алтын Казык"</v>
+        <v>"ASL OYNA"</v>
       </c>
       <c r="B1237" t="str">
-        <v>ТОО</v>
+        <v>ООО</v>
       </c>
       <c r="C1237" t="str">
-        <v>060640000339</v>
+        <v>203554782</v>
       </c>
       <c r="D1237" t="str">
         <v>ESYD (IAF)</v>
@@ -28846,21 +28846,21 @@
         <v>FSSC 22000</v>
       </c>
       <c r="F1237" t="str">
-        <v>KZ</v>
+        <v>UZ</v>
       </c>
       <c r="G1237">
-        <v>46484</v>
+        <v>46971</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="str">
-        <v>"ASL OYNA"</v>
+        <v>“PENG SHENG CHARM”</v>
       </c>
       <c r="B1238" t="str">
-        <v>ООО</v>
+        <v>ИП ООО</v>
       </c>
       <c r="C1238" t="str">
-        <v>203554782</v>
+        <v>301647292</v>
       </c>
       <c r="D1238" t="str">
         <v>ESYD (IAF)</v>
@@ -28872,18 +28872,18 @@
         <v>UZ</v>
       </c>
       <c r="G1238">
-        <v>46971</v>
+        <v>46945</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="str">
-        <v>“PENG SHENG CHARM”</v>
+        <v>«TASH-PET»</v>
       </c>
       <c r="B1239" t="str">
-        <v>ИП ООО</v>
+        <v>ООО</v>
       </c>
       <c r="C1239" t="str">
-        <v>301647292</v>
+        <v>300939824</v>
       </c>
       <c r="D1239" t="str">
         <v>ESYD (IAF)</v>
@@ -28895,41 +28895,41 @@
         <v>UZ</v>
       </c>
       <c r="G1239">
-        <v>46945</v>
+        <v>47016</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="str">
-        <v>«TASH-PET»</v>
+        <v>Тяжпрессмаш</v>
       </c>
       <c r="B1240" t="str">
-        <v>ООО</v>
+        <v>ПАО</v>
       </c>
       <c r="C1240" t="str">
-        <v>300939824</v>
+        <v>6229009163</v>
       </c>
       <c r="D1240" t="str">
-        <v>ESYD (IAF)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1240" t="str">
-        <v>FSSC 22000</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1240" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1240">
-        <v>47016</v>
+        <v>46655</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="str">
-        <v>Тяжпрессмаш</v>
+        <v>Завод Лоджикруф</v>
       </c>
       <c r="B1241" t="str">
-        <v>ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1241" t="str">
-        <v>6229009163</v>
+        <v>6230054971</v>
       </c>
       <c r="D1241" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -28941,18 +28941,18 @@
         <v>РФ</v>
       </c>
       <c r="G1241">
-        <v>46655</v>
+        <v>46668</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="str">
-        <v>Завод Лоджикруф</v>
+        <v>СОЛВО</v>
       </c>
       <c r="B1242" t="str">
         <v>ООО</v>
       </c>
       <c r="C1242" t="str">
-        <v>6230054971</v>
+        <v>7825064174</v>
       </c>
       <c r="D1242" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -28964,18 +28964,18 @@
         <v>РФ</v>
       </c>
       <c r="G1242">
-        <v>46668</v>
+        <v>46683</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="str">
-        <v>СОЛВО</v>
+        <v>Воскресенский филиал ООО "Завод Технофлекс"</v>
       </c>
       <c r="B1243" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1243" t="str">
-        <v>7825064174</v>
+        <v>6229024796</v>
       </c>
       <c r="D1243" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -28987,18 +28987,18 @@
         <v>РФ</v>
       </c>
       <c r="G1243">
-        <v>46683</v>
+        <v>46719</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="str">
-        <v>Воскресенский филиал ООО "Завод Технофлекс"</v>
+        <v>НПФ Ракурс</v>
       </c>
       <c r="B1244" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1244" t="str">
-        <v>6229024796</v>
+        <v>7812041998</v>
       </c>
       <c r="D1244" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29010,18 +29010,18 @@
         <v>РФ</v>
       </c>
       <c r="G1244">
-        <v>46719</v>
+        <v>46731</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="str">
-        <v>НПФ Ракурс</v>
+        <v>Светлана-Рентген</v>
       </c>
       <c r="B1245" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1245" t="str">
-        <v>7812041998</v>
+        <v>7805026364</v>
       </c>
       <c r="D1245" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29033,18 +29033,18 @@
         <v>РФ</v>
       </c>
       <c r="G1245">
-        <v>46731</v>
+        <v>46825</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="str">
-        <v>Светлана-Рентген</v>
+        <v>ЗАВОД ТУРБИННЫХ ЗАПЧАСТЕЙ</v>
       </c>
       <c r="B1246" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1246" t="str">
-        <v>7805026364</v>
+        <v>7814656732</v>
       </c>
       <c r="D1246" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29056,7 +29056,7 @@
         <v>РФ</v>
       </c>
       <c r="G1246">
-        <v>46825</v>
+        <v>46856</v>
       </c>
     </row>
     <row r="1247">
@@ -29070,39 +29070,39 @@
         <v>7814656732</v>
       </c>
       <c r="D1247" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1247" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1247" t="str">
         <v>РФ</v>
       </c>
       <c r="G1247">
-        <v>46856</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="str">
-        <v>ЗАВОД ТУРБИННЫХ ЗАПЧАСТЕЙ</v>
+        <v>Петроаналитика</v>
       </c>
       <c r="B1248" t="str">
         <v>ООО</v>
       </c>
       <c r="C1248" t="str">
-        <v>7814656732</v>
+        <v>7805523334</v>
       </c>
       <c r="D1248" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1248" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1248" t="str">
         <v>РФ</v>
       </c>
       <c r="G1248">
-        <v>46520</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="1249">
@@ -29116,39 +29116,39 @@
         <v>7805523334</v>
       </c>
       <c r="D1249" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1249" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1249" t="str">
         <v>РФ</v>
       </c>
       <c r="G1249">
-        <v>46934</v>
+        <v>47111</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="str">
-        <v>Петроаналитика</v>
+        <v>Химсталькомплект (ХСК)</v>
       </c>
       <c r="B1250" t="str">
         <v>ООО</v>
       </c>
       <c r="C1250" t="str">
-        <v>7805523334</v>
+        <v>7422046285</v>
       </c>
       <c r="D1250" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EGAC (QME)</v>
       </c>
       <c r="E1250" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1250" t="str">
         <v>РФ</v>
       </c>
       <c r="G1250">
-        <v>47111</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="1251">
@@ -29162,73 +29162,73 @@
         <v>7422046285</v>
       </c>
       <c r="D1251" t="str">
-        <v>EGAC (QME)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1251" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1251" t="str">
         <v>РФ</v>
       </c>
       <c r="G1251">
-        <v>46265</v>
+        <v>46808</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="str">
-        <v>Химсталькомплект (ХСК)</v>
+        <v>Группа компаний "ЛЮМЭКС Инструментс"</v>
       </c>
       <c r="B1252" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1252" t="str">
-        <v>7422046285</v>
+        <v>7801472150</v>
       </c>
       <c r="D1252" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>JASANZ (SAI Global)</v>
       </c>
       <c r="E1252" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1252" t="str">
         <v>РФ</v>
       </c>
       <c r="G1252">
-        <v>46808</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="str">
-        <v>Группа компаний "ЛЮМЭКС Инструментс"</v>
+        <v>СИЭЛ</v>
       </c>
       <c r="B1253" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1253" t="str">
-        <v>7801472150</v>
+        <v>7810742885</v>
       </c>
       <c r="D1253" t="str">
-        <v>JASANZ (SAI Global)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1253" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1253" t="str">
         <v>РФ</v>
       </c>
       <c r="G1253">
-        <v>46278</v>
+        <v>46673</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="str">
-        <v>СИЭЛ</v>
+        <v>Газпром диагностика</v>
       </c>
       <c r="B1254" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1254" t="str">
-        <v>7810742885</v>
+        <v>4345083100</v>
       </c>
       <c r="D1254" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -29240,18 +29240,18 @@
         <v>РФ</v>
       </c>
       <c r="G1254">
-        <v>46673</v>
+        <v>47102</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="str">
-        <v>Газпром диагностика</v>
+        <v>БП Морские Системы</v>
       </c>
       <c r="B1255" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1255" t="str">
-        <v>4345083100</v>
+        <v>7801726319</v>
       </c>
       <c r="D1255" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -29263,21 +29263,21 @@
         <v>РФ</v>
       </c>
       <c r="G1255">
-        <v>47102</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="str">
-        <v>БП Морские Системы</v>
+        <v>Статус</v>
       </c>
       <c r="B1256" t="str">
         <v>ООО</v>
       </c>
       <c r="C1256" t="str">
-        <v>7801726319</v>
+        <v>7413025257</v>
       </c>
       <c r="D1256" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1256" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -29286,18 +29286,18 @@
         <v>РФ</v>
       </c>
       <c r="G1256">
-        <v>46520</v>
+        <v>46927</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="str">
-        <v>Статус</v>
+        <v>ТЭК-Консалтинг</v>
       </c>
       <c r="B1257" t="str">
         <v>ООО</v>
       </c>
       <c r="C1257" t="str">
-        <v>7413025257</v>
+        <v>7804185393</v>
       </c>
       <c r="D1257" t="str">
         <v>РОСАТОМРЕГИСТР</v>
@@ -29309,18 +29309,18 @@
         <v>РФ</v>
       </c>
       <c r="G1257">
-        <v>46927</v>
+        <v>46898</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="str">
-        <v>ТЭК-Консалтинг</v>
+        <v>ГидроТехАтом</v>
       </c>
       <c r="B1258" t="str">
         <v>ООО</v>
       </c>
       <c r="C1258" t="str">
-        <v>7804185393</v>
+        <v>1831123035</v>
       </c>
       <c r="D1258" t="str">
         <v>РОСАТОМРЕГИСТР</v>
@@ -29332,21 +29332,21 @@
         <v>РФ</v>
       </c>
       <c r="G1258">
-        <v>46898</v>
+        <v>47168</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="str">
-        <v>ГидроТехАтом</v>
+        <v>НАМИ инновационные компоненты</v>
       </c>
       <c r="B1259" t="str">
         <v>ООО</v>
       </c>
       <c r="C1259" t="str">
-        <v>1831123035</v>
+        <v>6330056813</v>
       </c>
       <c r="D1259" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1259" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -29355,7 +29355,7 @@
         <v>РФ</v>
       </c>
       <c r="G1259">
-        <v>47168</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1260">
@@ -29369,39 +29369,39 @@
         <v>6330056813</v>
       </c>
       <c r="D1260" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1260" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1260" t="str">
         <v>РФ</v>
       </c>
       <c r="G1260">
-        <v>47039</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="str">
-        <v>НАМИ инновационные компоненты</v>
+        <v>Европейский мужчина и его здоровье</v>
       </c>
       <c r="B1261" t="str">
         <v>ООО</v>
       </c>
       <c r="C1261" t="str">
-        <v>6330056813</v>
+        <v>7811447106</v>
       </c>
       <c r="D1261" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1261" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1261" t="str">
         <v>РФ</v>
       </c>
       <c r="G1261">
-        <v>46303</v>
+        <v>47115</v>
       </c>
     </row>
     <row r="1262">
@@ -29415,7 +29415,7 @@
         <v>7811447106</v>
       </c>
       <c r="D1262" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1262" t="str">
         <v>ISO 9001:2015</v>
@@ -29429,16 +29429,16 @@
     </row>
     <row r="1263">
       <c r="A1263" t="str">
-        <v>Европейский мужчина и его здоровье</v>
+        <v>Газпром Линде Инжиниринг (ГЛ Инжиниринг)</v>
       </c>
       <c r="B1263" t="str">
         <v>ООО</v>
       </c>
       <c r="C1263" t="str">
-        <v>7811447106</v>
+        <v>0266023912</v>
       </c>
       <c r="D1263" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1263" t="str">
         <v>ISO 9001:2015</v>
@@ -29447,7 +29447,7 @@
         <v>РФ</v>
       </c>
       <c r="G1263">
-        <v>47115</v>
+        <v>47025</v>
       </c>
     </row>
     <row r="1264">
@@ -29461,7 +29461,7 @@
         <v>0266023912</v>
       </c>
       <c r="D1264" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1264" t="str">
         <v>ISO 9001:2015</v>
@@ -29484,10 +29484,10 @@
         <v>0266023912</v>
       </c>
       <c r="D1265" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1265" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1265" t="str">
         <v>РФ</v>
@@ -29507,7 +29507,7 @@
         <v>0266023912</v>
       </c>
       <c r="D1266" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1266" t="str">
         <v>ISO 14001:2015</v>
@@ -29530,10 +29530,10 @@
         <v>0266023912</v>
       </c>
       <c r="D1267" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1267" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1267" t="str">
         <v>РФ</v>
@@ -29553,7 +29553,7 @@
         <v>0266023912</v>
       </c>
       <c r="D1268" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1268" t="str">
         <v>ISO 45001:2018</v>
@@ -29576,16 +29576,16 @@
         <v>0266023912</v>
       </c>
       <c r="D1269" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1269" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1269" t="str">
         <v>РФ</v>
       </c>
       <c r="G1269">
-        <v>47025</v>
+        <v>47023</v>
       </c>
     </row>
     <row r="1270">
@@ -29602,7 +29602,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1270" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р ИСО 14001-2016</v>
       </c>
       <c r="F1270" t="str">
         <v>РФ</v>
@@ -29625,7 +29625,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1271" t="str">
-        <v>ГОСТ Р ИСО 14001-2016</v>
+        <v>ГОСТ Р ИСО 45001-2020</v>
       </c>
       <c r="F1271" t="str">
         <v>РФ</v>
@@ -29645,39 +29645,39 @@
         <v>0266023912</v>
       </c>
       <c r="D1272" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1272" t="str">
-        <v>ГОСТ Р ИСО 45001-2020</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1272" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1272">
-        <v>47023</v>
+      <c r="G1272" t="str">
+        <v/>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="str">
-        <v>Газпром Линде Инжиниринг (ГЛ Инжиниринг)</v>
+        <v>Сарштедт</v>
       </c>
       <c r="B1273" t="str">
         <v>ООО</v>
       </c>
       <c r="C1273" t="str">
-        <v>0266023912</v>
+        <v>6037008575</v>
       </c>
       <c r="D1273" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>NABCB (IAF)</v>
       </c>
       <c r="E1273" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1273" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1273" t="str">
-        <v/>
+      <c r="G1273">
+        <v>47076</v>
       </c>
     </row>
     <row r="1274">
@@ -29691,7 +29691,7 @@
         <v>6037008575</v>
       </c>
       <c r="D1274" t="str">
-        <v>NABCB (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1274" t="str">
         <v>ISO 13485:2016</v>
@@ -29714,39 +29714,39 @@
         <v>6037008575</v>
       </c>
       <c r="D1275" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1275" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1275" t="str">
         <v>РФ</v>
       </c>
       <c r="G1275">
-        <v>47076</v>
+        <v>46748</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="str">
-        <v>Сарштедт</v>
+        <v>Бора Пак</v>
       </c>
       <c r="B1276" t="str">
         <v>ООО</v>
       </c>
       <c r="C1276" t="str">
-        <v>6037008575</v>
+        <v>6315626314</v>
       </c>
       <c r="D1276" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1276" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1276" t="str">
         <v>РФ</v>
       </c>
       <c r="G1276">
-        <v>46748</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="1277">
@@ -29760,16 +29760,16 @@
         <v>6315626314</v>
       </c>
       <c r="D1277" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1277" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1277" t="str">
         <v>РФ</v>
       </c>
       <c r="G1277">
-        <v>46274</v>
+        <v>47086</v>
       </c>
     </row>
     <row r="1278">
@@ -29786,7 +29786,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1278" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1278" t="str">
         <v>РФ</v>
@@ -29797,16 +29797,16 @@
     </row>
     <row r="1279">
       <c r="A1279" t="str">
-        <v>Бора Пак</v>
+        <v>Научно-производственный центр Горноспасательные технологии</v>
       </c>
       <c r="B1279" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1279" t="str">
-        <v>6315626314</v>
+        <v>6672163631</v>
       </c>
       <c r="D1279" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1279" t="str">
         <v>ISO 9001:2015</v>
@@ -29815,7 +29815,7 @@
         <v>РФ</v>
       </c>
       <c r="G1279">
-        <v>47086</v>
+        <v>47070</v>
       </c>
     </row>
     <row r="1280">
@@ -29829,7 +29829,7 @@
         <v>6672163631</v>
       </c>
       <c r="D1280" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1280" t="str">
         <v>ISO 9001:2015</v>
@@ -29843,7 +29843,7 @@
     </row>
     <row r="1281">
       <c r="A1281" t="str">
-        <v>Научно-производственный центр Горноспасательные технологии</v>
+        <v>Научно-производственный центр "Горноспасательные технологии"</v>
       </c>
       <c r="B1281" t="str">
         <v>АО</v>
@@ -29852,39 +29852,39 @@
         <v>6672163631</v>
       </c>
       <c r="D1281" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1281" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1281" t="str">
         <v>РФ</v>
       </c>
       <c r="G1281">
-        <v>47070</v>
+        <v>47100</v>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="str">
-        <v>Научно-производственный центр "Горноспасательные технологии"</v>
+        <v>Джойсон Сейфти Системс Рус</v>
       </c>
       <c r="B1282" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1282" t="str">
-        <v>6672163631</v>
+        <v>7325097407</v>
       </c>
       <c r="D1282" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1282" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1282" t="str">
         <v>РФ</v>
       </c>
       <c r="G1282">
-        <v>47100</v>
+        <v>47097</v>
       </c>
     </row>
     <row r="1283">
@@ -29898,7 +29898,7 @@
         <v>7325097407</v>
       </c>
       <c r="D1283" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1283" t="str">
         <v>ISO 9001:2015</v>
@@ -29921,16 +29921,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1284" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1284" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1284" t="str">
         <v>РФ</v>
       </c>
       <c r="G1284">
-        <v>47097</v>
+        <v>47166</v>
       </c>
     </row>
     <row r="1285">
@@ -29944,7 +29944,7 @@
         <v>7325097407</v>
       </c>
       <c r="D1285" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1285" t="str">
         <v>ISO 14001:2015</v>
@@ -29967,10 +29967,10 @@
         <v>7325097407</v>
       </c>
       <c r="D1286" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1286" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1286" t="str">
         <v>РФ</v>
@@ -29990,7 +29990,7 @@
         <v>7325097407</v>
       </c>
       <c r="D1287" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1287" t="str">
         <v>ISO 45001:2018</v>
@@ -30013,16 +30013,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1288" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1288" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1288" t="str">
         <v>РФ</v>
       </c>
       <c r="G1288">
-        <v>47166</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1289">
@@ -30036,16 +30036,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1289" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1289" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1289" t="str">
         <v>РФ</v>
       </c>
       <c r="G1289">
-        <v>46982</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="1290">
@@ -30059,39 +30059,39 @@
         <v>7325097407</v>
       </c>
       <c r="D1290" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1290" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1290" t="str">
         <v>РФ</v>
       </c>
       <c r="G1290">
-        <v>46178</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="str">
-        <v>Джойсон Сейфти Системс Рус</v>
+        <v>ТЛТ ПРОФ</v>
       </c>
       <c r="B1291" t="str">
         <v>ООО</v>
       </c>
       <c r="C1291" t="str">
-        <v>7325097407</v>
+        <v>6321273480</v>
       </c>
       <c r="D1291" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1291" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1291" t="str">
         <v>РФ</v>
       </c>
       <c r="G1291">
-        <v>46982</v>
+        <v>46844</v>
       </c>
     </row>
     <row r="1292">
@@ -30105,7 +30105,7 @@
         <v>6321273480</v>
       </c>
       <c r="D1292" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1292" t="str">
         <v>ISO 9001:2015</v>
@@ -30119,16 +30119,16 @@
     </row>
     <row r="1293">
       <c r="A1293" t="str">
-        <v>ТЛТ ПРОФ</v>
+        <v>ТрансАвтоСвет</v>
       </c>
       <c r="B1293" t="str">
         <v>ООО</v>
       </c>
       <c r="C1293" t="str">
-        <v>6321273480</v>
+        <v>7328075313</v>
       </c>
       <c r="D1293" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1293" t="str">
         <v>ISO 9001:2015</v>
@@ -30137,7 +30137,7 @@
         <v>РФ</v>
       </c>
       <c r="G1293">
-        <v>46844</v>
+        <v>47046</v>
       </c>
     </row>
     <row r="1294">
@@ -30151,7 +30151,7 @@
         <v>7328075313</v>
       </c>
       <c r="D1294" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1294" t="str">
         <v>ISO 9001:2015</v>
@@ -30165,16 +30165,16 @@
     </row>
     <row r="1295">
       <c r="A1295" t="str">
-        <v>ТрансАвтоСвет</v>
+        <v>Борский стекольный завод</v>
       </c>
       <c r="B1295" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1295" t="str">
-        <v>7328075313</v>
+        <v>5246002261</v>
       </c>
       <c r="D1295" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1295" t="str">
         <v>ISO 9001:2015</v>
@@ -30183,7 +30183,7 @@
         <v>РФ</v>
       </c>
       <c r="G1295">
-        <v>47046</v>
+        <v>47066</v>
       </c>
     </row>
     <row r="1296">
@@ -30197,7 +30197,7 @@
         <v>5246002261</v>
       </c>
       <c r="D1296" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1296" t="str">
         <v>ISO 9001:2015</v>
@@ -30220,16 +30220,16 @@
         <v>5246002261</v>
       </c>
       <c r="D1297" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1297" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1297" t="str">
         <v>РФ</v>
       </c>
       <c r="G1297">
-        <v>47066</v>
+        <v>46634</v>
       </c>
     </row>
     <row r="1298">
@@ -30243,7 +30243,7 @@
         <v>5246002261</v>
       </c>
       <c r="D1298" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1298" t="str">
         <v>ISO 14001:2015</v>
@@ -30266,10 +30266,10 @@
         <v>5246002261</v>
       </c>
       <c r="D1299" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1299" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1299" t="str">
         <v>РФ</v>
@@ -30289,7 +30289,7 @@
         <v>5246002261</v>
       </c>
       <c r="D1300" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1300" t="str">
         <v>ISO 45001:2018</v>
@@ -30312,39 +30312,39 @@
         <v>5246002261</v>
       </c>
       <c r="D1301" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1301" t="str">
-        <v>ISO 45001:2018</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1301" t="str">
         <v>РФ</v>
       </c>
       <c r="G1301">
-        <v>46634</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="str">
-        <v>Борский стекольный завод</v>
+        <v>ПРОМЭНЕРГОКОМПЛЕКТ</v>
       </c>
       <c r="B1302" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1302" t="str">
-        <v>5246002261</v>
+        <v>5262222391</v>
       </c>
       <c r="D1302" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1302" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1302" t="str">
         <v>РФ</v>
       </c>
       <c r="G1302">
-        <v>46255</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1303">
@@ -30358,10 +30358,10 @@
         <v>5262222391</v>
       </c>
       <c r="D1303" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ECA (APAC)</v>
       </c>
       <c r="E1303" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1303" t="str">
         <v>РФ</v>
@@ -30372,94 +30372,94 @@
     </row>
     <row r="1304">
       <c r="A1304" t="str">
-        <v>ПРОМЭНЕРГОКОМПЛЕКТ</v>
+        <v>НПФ "Евродеталь"</v>
       </c>
       <c r="B1304" t="str">
         <v>ООО</v>
       </c>
       <c r="C1304" t="str">
-        <v>5262222391</v>
+        <v>1834054140</v>
       </c>
       <c r="D1304" t="str">
-        <v>ECA (APAC)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1304" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1304" t="str">
         <v>РФ</v>
       </c>
       <c r="G1304">
-        <v>47039</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="str">
-        <v>НПФ "Евродеталь"</v>
+        <v>АйСиЭл Системные Технологии</v>
       </c>
       <c r="B1305" t="str">
         <v>ООО</v>
       </c>
       <c r="C1305" t="str">
-        <v>1834054140</v>
+        <v>1615012203</v>
       </c>
       <c r="D1305" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1305" t="str">
-        <v>16949: 2016</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1305" t="str">
         <v>РФ</v>
       </c>
       <c r="G1305">
-        <v>46323</v>
+        <v>47094</v>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="str">
-        <v>АйСиЭл Системные Технологии</v>
+        <v>МЕДИН-Н</v>
       </c>
       <c r="B1306" t="str">
         <v>ООО</v>
       </c>
       <c r="C1306" t="str">
-        <v>1615012203</v>
+        <v>6662112620</v>
       </c>
       <c r="D1306" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1306" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1306" t="str">
         <v>РФ</v>
       </c>
       <c r="G1306">
-        <v>47094</v>
+        <v>47073</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="str">
-        <v>МЕДИН-Н</v>
+        <v>МЕТТЕХ</v>
       </c>
       <c r="B1307" t="str">
         <v>ООО</v>
       </c>
       <c r="C1307" t="str">
-        <v>6662112620</v>
+        <v>7806591143</v>
       </c>
       <c r="D1307" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1307" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1307" t="str">
         <v>РФ</v>
       </c>
       <c r="G1307">
-        <v>47073</v>
+        <v>47112</v>
       </c>
     </row>
     <row r="1308">
@@ -30473,7 +30473,7 @@
         <v>7806591143</v>
       </c>
       <c r="D1308" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1308" t="str">
         <v>ISO 9001:2015</v>
@@ -30487,82 +30487,82 @@
     </row>
     <row r="1309">
       <c r="A1309" t="str">
-        <v>МЕТТЕХ</v>
+        <v>Birinchi rezinotexnika zavodi</v>
       </c>
       <c r="B1309" t="str">
-        <v>ООО</v>
+        <v>ИП ООО</v>
       </c>
       <c r="C1309" t="str">
-        <v>7806591143</v>
+        <v>301938570</v>
       </c>
       <c r="D1309" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1309" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1309" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1309">
-        <v>47112</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="str">
-        <v>Birinchi rezinotexnika zavodi</v>
+        <v>Тюменский завод ЗСГ</v>
       </c>
       <c r="B1310" t="str">
-        <v>ИП ООО</v>
+        <v>ООО</v>
       </c>
       <c r="C1310" t="str">
-        <v>301938570</v>
+        <v>7203412108</v>
       </c>
       <c r="D1310" t="str">
-        <v>ESYD (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1310" t="str">
-        <v>ISO 45001:2018</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1310" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1310">
-        <v>47110</v>
+        <v>47074</v>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="str">
-        <v>Тюменский завод ЗСГ</v>
+        <v>Электронмаш Инжиниринг</v>
       </c>
       <c r="B1311" t="str">
         <v>ООО</v>
       </c>
       <c r="C1311" t="str">
-        <v>7203412108</v>
+        <v>7802428812</v>
       </c>
       <c r="D1311" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1311" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1311" t="str">
         <v>РФ</v>
       </c>
       <c r="G1311">
-        <v>47074</v>
+        <v>46731</v>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="str">
-        <v>Электронмаш Инжиниринг</v>
+        <v>Нефтегаздеталь</v>
       </c>
       <c r="B1312" t="str">
         <v>ООО</v>
       </c>
       <c r="C1312" t="str">
-        <v>7802428812</v>
+        <v>3661081734</v>
       </c>
       <c r="D1312" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -30574,30 +30574,30 @@
         <v>РФ</v>
       </c>
       <c r="G1312">
-        <v>46731</v>
+        <v>47001</v>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="str">
-        <v>Нефтегаздеталь</v>
+        <v>Богословский кабельный завод</v>
       </c>
       <c r="B1313" t="str">
         <v>ООО</v>
       </c>
       <c r="C1313" t="str">
-        <v>3661081734</v>
+        <v>6617026384</v>
       </c>
       <c r="D1313" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1313" t="str">
-        <v>S.QS.07-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1313" t="str">
         <v>РФ</v>
       </c>
       <c r="G1313">
-        <v>47001</v>
+        <v>47087</v>
       </c>
     </row>
     <row r="1314">
@@ -30611,7 +30611,7 @@
         <v>6617026384</v>
       </c>
       <c r="D1314" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1314" t="str">
         <v>ISO 9001:2015</v>
@@ -30625,16 +30625,16 @@
     </row>
     <row r="1315">
       <c r="A1315" t="str">
-        <v>Богословский кабельный завод</v>
+        <v>Аутолив</v>
       </c>
       <c r="B1315" t="str">
         <v>ООО</v>
       </c>
       <c r="C1315" t="str">
-        <v>6617026384</v>
+        <v>4703105420</v>
       </c>
       <c r="D1315" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1315" t="str">
         <v>ISO 9001:2015</v>
@@ -30657,7 +30657,7 @@
         <v>4703105420</v>
       </c>
       <c r="D1316" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1316" t="str">
         <v>ISO 9001:2015</v>
@@ -30683,13 +30683,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1317" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1317" t="str">
         <v>РФ</v>
       </c>
       <c r="G1317">
-        <v>47087</v>
+        <v>47101</v>
       </c>
     </row>
     <row r="1318">
@@ -30703,39 +30703,39 @@
         <v>4703105420</v>
       </c>
       <c r="D1318" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1318" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1318" t="str">
         <v>РФ</v>
       </c>
       <c r="G1318">
-        <v>47101</v>
+        <v>45980</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="str">
-        <v>Аутолив</v>
+        <v>ASTEL</v>
       </c>
       <c r="B1319" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1319" t="str">
-        <v>4703105420</v>
+        <v>11140001666</v>
       </c>
       <c r="D1319" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1319" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1319" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1319">
-        <v>45980</v>
+        <v>46629</v>
       </c>
     </row>
     <row r="1320">
@@ -30752,13 +30752,13 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1320" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 27001:2013</v>
       </c>
       <c r="F1320" t="str">
         <v>KZ</v>
       </c>
       <c r="G1320">
-        <v>46629</v>
+        <v>46643</v>
       </c>
     </row>
     <row r="1321">
@@ -30775,7 +30775,7 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1321" t="str">
-        <v>ISO 27001:2013</v>
+        <v>ISO 20000-1:2018</v>
       </c>
       <c r="F1321" t="str">
         <v>KZ</v>
@@ -30786,48 +30786,48 @@
     </row>
     <row r="1322">
       <c r="A1322" t="str">
-        <v>ASTEL</v>
+        <v>Федеральное государственное бюджетное образовательное учреждение высшего образования «Тульский государственный педагогический университет им. Л.Н. Толстого», Научно-исследовательский институт химических, фармацевтических и биотехнологий, Научно-производственный центр</v>
       </c>
       <c r="B1322" t="str">
-        <v>АО</v>
+        <v>ФГБОУ ВО</v>
       </c>
       <c r="C1322" t="str">
-        <v>11140001666</v>
+        <v>7107030811</v>
       </c>
       <c r="D1322" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1322" t="str">
-        <v>ISO 20000-1:2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1322" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1322">
-        <v>46643</v>
+        <v>47101</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="str">
-        <v>Федеральное государственное бюджетное образовательное учреждение высшего образования «Тульский государственный педагогический университет им. Л.Н. Толстого», Научно-исследовательский институт химических, фармацевтических и биотехнологий, Научно-производственный центр</v>
+        <v>«УЗЛЫ И МЕХАНИЗМЫ КУЗОВА АВТОМОБИЛЯ» (ООО «УМКА»)</v>
       </c>
       <c r="B1323" t="str">
-        <v>ФГБОУ ВО</v>
+        <v>ООО</v>
       </c>
       <c r="C1323" t="str">
-        <v>7107030811</v>
+        <v>6382061684</v>
       </c>
       <c r="D1323" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1323" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1323" t="str">
         <v>РФ</v>
       </c>
       <c r="G1323">
-        <v>47101</v>
+        <v>47094</v>
       </c>
     </row>
     <row r="1324">
@@ -30841,7 +30841,7 @@
         <v>6382061684</v>
       </c>
       <c r="D1324" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1324" t="str">
         <v>ISO 9001:2015</v>
@@ -30864,16 +30864,16 @@
         <v>6382061684</v>
       </c>
       <c r="D1325" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1325" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1325" t="str">
         <v>РФ</v>
       </c>
       <c r="G1325">
-        <v>47094</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="1326">
@@ -30887,39 +30887,39 @@
         <v>6382061684</v>
       </c>
       <c r="D1326" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1326" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1326" t="str">
         <v>РФ</v>
       </c>
       <c r="G1326">
-        <v>46318</v>
+        <v>47175</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="str">
-        <v>«УЗЛЫ И МЕХАНИЗМЫ КУЗОВА АВТОМОБИЛЯ» (ООО «УМКА»)</v>
+        <v>РУСАЛ Ачинский Глиноземный Комбинат</v>
       </c>
       <c r="B1327" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1327" t="str">
-        <v>6382061684</v>
+        <v>2443005570</v>
       </c>
       <c r="D1327" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1327" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1327" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1327">
-        <v>47175</v>
+      <c r="G1327" t="str">
+        <v/>
       </c>
     </row>
     <row r="1328">
@@ -30933,7 +30933,7 @@
         <v>2443005570</v>
       </c>
       <c r="D1328" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1328" t="str">
         <v>ISO 9001:2015</v>
@@ -30956,16 +30956,16 @@
         <v>2443005570</v>
       </c>
       <c r="D1329" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1329" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1329" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1329" t="str">
-        <v/>
+      <c r="G1329">
+        <v>47097</v>
       </c>
     </row>
     <row r="1330">
@@ -30979,7 +30979,7 @@
         <v>2443005570</v>
       </c>
       <c r="D1330" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1330" t="str">
         <v>ISO 14001:2015</v>
@@ -31002,16 +31002,16 @@
         <v>2443005570</v>
       </c>
       <c r="D1331" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1331" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1331" t="str">
         <v>РФ</v>
       </c>
       <c r="G1331">
-        <v>47097</v>
+        <v>47213</v>
       </c>
     </row>
     <row r="1332">
@@ -31025,7 +31025,7 @@
         <v>2443005570</v>
       </c>
       <c r="D1332" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1332" t="str">
         <v>ISO 45001:2018</v>
@@ -31039,25 +31039,25 @@
     </row>
     <row r="1333">
       <c r="A1333" t="str">
-        <v>РУСАЛ Ачинский Глиноземный Комбинат</v>
+        <v>ENTER STEEL</v>
       </c>
       <c r="B1333" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1333" t="str">
-        <v>2443005570</v>
+        <v>306574437</v>
       </c>
       <c r="D1333" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1333" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1333" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1333">
-        <v>47213</v>
+        <v>UZ</v>
+      </c>
+      <c r="G1333" t="str">
+        <v/>
       </c>
     </row>
     <row r="1334">
@@ -31074,7 +31074,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1334" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1334" t="str">
         <v>UZ</v>
@@ -31097,7 +31097,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1335" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1335" t="str">
         <v>UZ</v>
@@ -31108,19 +31108,19 @@
     </row>
     <row r="1336">
       <c r="A1336" t="str">
-        <v>ENTER STEEL</v>
+        <v>SAVDONI RIVOJLANTIRISH KOMPANIYASI</v>
       </c>
       <c r="B1336" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1336" t="str">
-        <v>306574437</v>
+        <v>306303488</v>
       </c>
       <c r="D1336" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1336" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 37001:2016</v>
       </c>
       <c r="F1336" t="str">
         <v>UZ</v>
@@ -31131,19 +31131,19 @@
     </row>
     <row r="1337">
       <c r="A1337" t="str">
-        <v>SAVDONI RIVOJLANTIRISH KOMPANIYASI</v>
+        <v>Unitel</v>
       </c>
       <c r="B1337" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1337" t="str">
-        <v>306303488</v>
+        <v>201838002</v>
       </c>
       <c r="D1337" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1337" t="str">
-        <v>ISO 37001:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1337" t="str">
         <v>UZ</v>
@@ -31154,22 +31154,22 @@
     </row>
     <row r="1338">
       <c r="A1338" t="str">
-        <v>Unitel</v>
+        <v>«СХП «РАССВЕТ»</v>
       </c>
       <c r="B1338" t="str">
         <v>ООО</v>
       </c>
       <c r="C1338" t="str">
-        <v>201838002</v>
+        <v>2625027835</v>
       </c>
       <c r="D1338" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1338" t="str">
-        <v>ISO 9001:2015</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1338" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1338" t="str">
         <v/>
@@ -31177,19 +31177,19 @@
     </row>
     <row r="1339">
       <c r="A1339" t="str">
-        <v>«СХП «РАССВЕТ»</v>
+        <v>Завод по производству винто-рулевых колонок Сапфир</v>
       </c>
       <c r="B1339" t="str">
         <v>ООО</v>
       </c>
       <c r="C1339" t="str">
-        <v>2625027835</v>
+        <v>2503032563</v>
       </c>
       <c r="D1339" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1339" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1339" t="str">
         <v>РФ</v>
@@ -31200,48 +31200,48 @@
     </row>
     <row r="1340">
       <c r="A1340" t="str">
-        <v>Завод по производству винто-рулевых колонок Сапфир</v>
+        <v>GDC Services and Solutions d.o.o.</v>
       </c>
       <c r="B1340" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1340" t="str">
-        <v>2503032563</v>
+        <v/>
       </c>
       <c r="D1340" t="str">
-        <v>ESYD (IAF)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1340" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1340" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1340" t="str">
-        <v/>
+        <v>Serbia</v>
+      </c>
+      <c r="G1340">
+        <v>47101</v>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="str">
-        <v>GDC Services and Solutions d.o.o.</v>
+        <v>Красноярский металлургический завод ("КраМЗ")</v>
       </c>
       <c r="B1341" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1341" t="str">
-        <v/>
+        <v>2465043748</v>
       </c>
       <c r="D1341" t="str">
-        <v>IAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1341" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1341" t="str">
-        <v>Serbia</v>
+        <v>РФ</v>
       </c>
       <c r="G1341">
-        <v>47101</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="1342">
@@ -31255,7 +31255,7 @@
         <v>2465043748</v>
       </c>
       <c r="D1342" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1342" t="str">
         <v>ISO 9001:2015</v>
@@ -31278,16 +31278,16 @@
         <v>2465043748</v>
       </c>
       <c r="D1343" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1343" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1343" t="str">
         <v>РФ</v>
       </c>
       <c r="G1343">
-        <v>47110</v>
+        <v>47242</v>
       </c>
     </row>
     <row r="1344">
@@ -31301,7 +31301,7 @@
         <v>2465043748</v>
       </c>
       <c r="D1344" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1344" t="str">
         <v>ISO 14001:2015</v>
@@ -31315,25 +31315,25 @@
     </row>
     <row r="1345">
       <c r="A1345" t="str">
-        <v>Красноярский металлургический завод ("КраМЗ")</v>
+        <v>"ЭЛАРА"</v>
       </c>
       <c r="B1345" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1345" t="str">
-        <v>2465043748</v>
+        <v>2129017646</v>
       </c>
       <c r="D1345" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1345" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1345" t="str">
         <v>РФ</v>
       </c>
       <c r="G1345">
-        <v>47242</v>
+        <v>46980</v>
       </c>
     </row>
     <row r="1346">
@@ -31350,59 +31350,59 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1346" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1346" t="str">
         <v>РФ</v>
       </c>
       <c r="G1346">
-        <v>46980</v>
+        <v>46574</v>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="str">
-        <v>"ЭЛАРА"</v>
+        <v>"Газпром проектирование"</v>
       </c>
       <c r="B1347" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1347" t="str">
-        <v>2129017646</v>
+        <v>0560022871</v>
       </c>
       <c r="D1347" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1347" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1347" t="str">
         <v>РФ</v>
       </c>
       <c r="G1347">
-        <v>46574</v>
+        <v>47003</v>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="str">
-        <v>"Газпром проектирование"</v>
+        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
       </c>
       <c r="B1348" t="str">
         <v>ООО</v>
       </c>
       <c r="C1348" t="str">
-        <v>0560022871</v>
+        <v>190918566</v>
       </c>
       <c r="D1348" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1348" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1348" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1348">
-        <v>47003</v>
+        <v>47151</v>
       </c>
     </row>
     <row r="1349">
@@ -31416,7 +31416,7 @@
         <v>190918566</v>
       </c>
       <c r="D1349" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1349" t="str">
         <v>ISO/IEC 27001:2022</v>
@@ -31430,25 +31430,25 @@
     </row>
     <row r="1350">
       <c r="A1350" t="str">
-        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
+        <v>Аутолайт Технолоджи</v>
       </c>
       <c r="B1350" t="str">
         <v>ООО</v>
       </c>
       <c r="C1350" t="str">
-        <v>190918566</v>
+        <v>6230025811</v>
       </c>
       <c r="D1350" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1350" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1350" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1350">
-        <v>47151</v>
+        <v>47179</v>
       </c>
     </row>
     <row r="1351">
@@ -31462,16 +31462,16 @@
         <v>6230025811</v>
       </c>
       <c r="D1351" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1351" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1351" t="str">
         <v>РФ</v>
       </c>
       <c r="G1351">
-        <v>47179</v>
+        <v>47229</v>
       </c>
     </row>
     <row r="1352">
@@ -31485,16 +31485,16 @@
         <v>6230025811</v>
       </c>
       <c r="D1352" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1352" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1352" t="str">
         <v>РФ</v>
       </c>
       <c r="G1352">
-        <v>47229</v>
+        <v>46430</v>
       </c>
     </row>
     <row r="1353">
@@ -31508,39 +31508,39 @@
         <v>6230025811</v>
       </c>
       <c r="D1353" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1353" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1353" t="str">
         <v>РФ</v>
       </c>
       <c r="G1353">
-        <v>46430</v>
+        <v>47179</v>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="str">
-        <v>Аутолайт Технолоджи</v>
+        <v>Инновационный центр КАМАЗ</v>
       </c>
       <c r="B1354" t="str">
         <v>ООО</v>
       </c>
       <c r="C1354" t="str">
-        <v>6230025811</v>
+        <v>7801204062</v>
       </c>
       <c r="D1354" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1354" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1354" t="str">
         <v>РФ</v>
       </c>
       <c r="G1354">
-        <v>47179</v>
+        <v>47286</v>
       </c>
     </row>
     <row r="1355">
@@ -31557,7 +31557,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1355" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1355" t="str">
         <v>РФ</v>
@@ -31568,128 +31568,128 @@
     </row>
     <row r="1356">
       <c r="A1356" t="str">
-        <v>Инновационный центр КАМАЗ</v>
+        <v>АкваПромМеталл</v>
       </c>
       <c r="B1356" t="str">
         <v>ООО</v>
       </c>
       <c r="C1356" t="str">
-        <v>7801204062</v>
+        <v>7807240772</v>
       </c>
       <c r="D1356" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1356" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1356" t="str">
         <v>РФ</v>
       </c>
       <c r="G1356">
-        <v>47286</v>
+        <v>47223</v>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="str">
-        <v>АкваПромМеталл</v>
+        <v>СЗЭМО ЗАВОД ВЕНТИЛЯТОР ТДМ</v>
       </c>
       <c r="B1357" t="str">
         <v>ООО</v>
       </c>
       <c r="C1357" t="str">
-        <v>7807240772</v>
+        <v>7811513824</v>
       </c>
       <c r="D1357" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1357" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1357" t="str">
         <v>РФ</v>
       </c>
       <c r="G1357">
-        <v>47223</v>
+        <v>46810</v>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="str">
-        <v>СЗЭМО ЗАВОД ВЕНТИЛЯТОР ТДМ</v>
+        <v>РЕМОНТНО-МЕХАНИЧЕСКИЙ ЗАВОД ГОРНО-ХИМИЧЕСКОГО КОМБИНАТА (РМЗ ГХК)</v>
       </c>
       <c r="B1358" t="str">
         <v>ООО</v>
       </c>
       <c r="C1358" t="str">
-        <v>7811513824</v>
+        <v>2452201891</v>
       </c>
       <c r="D1358" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1358" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1358" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1358">
-        <v>46810</v>
+      <c r="G1358" t="str">
+        <v/>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="str">
-        <v>РЕМОНТНО-МЕХАНИЧЕСКИЙ ЗАВОД ГОРНО-ХИМИЧЕСКОГО КОМБИНАТА (РМЗ ГХК)</v>
+        <v>Центр диагностики, экспертизы и сертификации (ЦДЭС)</v>
       </c>
       <c r="B1359" t="str">
         <v>ООО</v>
       </c>
       <c r="C1359" t="str">
-        <v>2452201891</v>
+        <v>7839346161</v>
       </c>
       <c r="D1359" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1359" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1359" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1359" t="str">
-        <v/>
+      <c r="G1359">
+        <v>46567</v>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="str">
-        <v>Центр диагностики, экспертизы и сертификации (ЦДЭС)</v>
+        <v>Уральский завод специального арматуростроения (УЗСА)</v>
       </c>
       <c r="B1360" t="str">
         <v>ООО</v>
       </c>
       <c r="C1360" t="str">
-        <v>7839346161</v>
+        <v>7451403608</v>
       </c>
       <c r="D1360" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1360" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1360" t="str">
         <v>РФ</v>
       </c>
       <c r="G1360">
-        <v>46567</v>
+        <v>46900</v>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="str">
-        <v>Уральский завод специального арматуростроения (УЗСА)</v>
+        <v>Угрешский завод трубопроводной арматуры (УЗТПА)</v>
       </c>
       <c r="B1361" t="str">
         <v>ООО</v>
       </c>
       <c r="C1361" t="str">
-        <v>7451403608</v>
+        <v>5056009251</v>
       </c>
       <c r="D1361" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -31704,27 +31704,28 @@
         <v>46900</v>
       </c>
     </row>
-    <row r="1362">
-      <c r="A1362" t="str">
-        <v>Угрешский завод трубопроводной арматуры (УЗТПА)</v>
+    <row r="1362" xml:space="preserve">
+      <c r="A1362" t="str" xml:space="preserve">
+        <v xml:space="preserve">Научно-_x000d_
+производственное объединение специальных материалов (НПО Спецматериалов)</v>
       </c>
       <c r="B1362" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1362" t="str">
-        <v>5056009251</v>
+        <v>7806125671</v>
       </c>
       <c r="D1362" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1362" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1362" t="str">
         <v>РФ</v>
       </c>
       <c r="G1362">
-        <v>46900</v>
+        <v>46709</v>
       </c>
     </row>
     <row r="1363" xml:space="preserve">
@@ -31739,7 +31740,7 @@
         <v>7806125671</v>
       </c>
       <c r="D1363" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1363" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -31748,42 +31749,41 @@
         <v>РФ</v>
       </c>
       <c r="G1363">
-        <v>46709</v>
-      </c>
-    </row>
-    <row r="1364" xml:space="preserve">
-      <c r="A1364" t="str" xml:space="preserve">
-        <v xml:space="preserve">Научно-_x000d_
-производственное объединение специальных материалов (НПО Спецматериалов)</v>
+        <v>46655</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="str">
+        <v>Специализированная инжиниринговая компания Севзапмонтажавтоматика (СЗМА СПИК)</v>
       </c>
       <c r="B1364" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1364" t="str">
-        <v>7806125671</v>
+        <v>7801715500</v>
       </c>
       <c r="D1364" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1364" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1364" t="str">
         <v>РФ</v>
       </c>
       <c r="G1364">
-        <v>46655</v>
+        <v>46921</v>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="str">
-        <v>Специализированная инжиниринговая компания Севзапмонтажавтоматика (СЗМА СПИК)</v>
+        <v>Тосненский механический завод (ТоМеЗ)</v>
       </c>
       <c r="B1365" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1365" t="str">
-        <v>7801715500</v>
+        <v>4716002824</v>
       </c>
       <c r="D1365" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -31795,21 +31795,21 @@
         <v>РФ</v>
       </c>
       <c r="G1365">
-        <v>46921</v>
+        <v>46619</v>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="str">
-        <v>Тосненский механический завод (ТоМеЗ)</v>
+        <v>Трубопроводные покрытия и технологии (ТПТ)</v>
       </c>
       <c r="B1366" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1366" t="str">
-        <v>4716002824</v>
+        <v>3435308501</v>
       </c>
       <c r="D1366" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>EGAC (QME)</v>
       </c>
       <c r="E1366" t="str">
         <v>ISO 9001:2015</v>
@@ -31818,30 +31818,30 @@
         <v>РФ</v>
       </c>
       <c r="G1366">
-        <v>46619</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="str">
-        <v>Трубопроводные покрытия и технологии (ТПТ)</v>
+        <v>Гродно Азот, филиал Завод Химволокно</v>
       </c>
       <c r="B1367" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1367" t="str">
-        <v>3435308501</v>
+        <v>7707083893</v>
       </c>
       <c r="D1367" t="str">
-        <v>EGAC (QME)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1367" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1367" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1367">
-        <v>46272</v>
+        <v>47270</v>
       </c>
     </row>
     <row r="1368">
@@ -31855,7 +31855,7 @@
         <v>7707083893</v>
       </c>
       <c r="D1368" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1368" t="str">
         <v>ISO 9001:2015</v>
@@ -31869,7 +31869,7 @@
     </row>
     <row r="1369">
       <c r="A1369" t="str">
-        <v>Гродно Азот, филиал Завод Химволокно</v>
+        <v>филиал "Завод Химволокно", ОАО "Гродно Азот"</v>
       </c>
       <c r="B1369" t="str">
         <v>ОАО</v>
@@ -31881,13 +31881,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1369" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1369" t="str">
         <v>РБ</v>
       </c>
       <c r="G1369">
-        <v>47270</v>
+        <v>47308</v>
       </c>
     </row>
     <row r="1370">
@@ -31901,56 +31901,56 @@
         <v>7707083893</v>
       </c>
       <c r="D1370" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1370" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1370" t="str">
         <v>РБ</v>
       </c>
       <c r="G1370">
-        <v>47308</v>
+        <v>46492</v>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="str">
-        <v>филиал "Завод Химволокно", ОАО "Гродно Азот"</v>
+        <v>АВТОКОЛОРИТ</v>
       </c>
       <c r="B1371" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1371" t="str">
-        <v>7707083893</v>
+        <v>6320092604</v>
       </c>
       <c r="D1371" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1371" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1371" t="str">
-        <v>РБ</v>
-      </c>
-      <c r="G1371">
-        <v>46492</v>
+        <v>РФ</v>
+      </c>
+      <c r="G1371" t="str">
+        <v/>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="str">
-        <v>АВТОКОЛОРИТ</v>
+        <v>ХЕНДЭ СТИЛ РУС</v>
       </c>
       <c r="B1372" t="str">
         <v>ООО</v>
       </c>
       <c r="C1372" t="str">
-        <v>6320092604</v>
+        <v>7813442054</v>
       </c>
       <c r="D1372" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1372" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1372" t="str">
         <v>РФ</v>
@@ -31973,7 +31973,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1373" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1373" t="str">
         <v>РФ</v>
@@ -31984,71 +31984,71 @@
     </row>
     <row r="1374">
       <c r="A1374" t="str">
-        <v>ХЕНДЭ СТИЛ РУС</v>
+        <v>"Рикор Электроникс"</v>
       </c>
       <c r="B1374" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1374" t="str">
-        <v>7813442054</v>
+        <v>5243001622</v>
       </c>
       <c r="D1374" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1374" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1374" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1374" t="str">
-        <v/>
+      <c r="G1374">
+        <v>46521</v>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="str">
-        <v>"Рикор Электроникс"</v>
+        <v>Сваркер</v>
       </c>
       <c r="B1375" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1375" t="str">
-        <v>5243001622</v>
+        <v>6686156088</v>
       </c>
       <c r="D1375" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1375" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1375" t="str">
         <v>РФ</v>
       </c>
       <c r="G1375">
-        <v>46521</v>
+        <v>47357</v>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="str">
-        <v>Сваркер</v>
+        <v>Научно-исследовательский институт биотехнологий (НИИ БиоТех) ФГБОУ ВО СамГМУ Минздрава России</v>
       </c>
       <c r="B1376" t="str">
-        <v>ООО</v>
+        <v>ФГБОУ ВО</v>
       </c>
       <c r="C1376" t="str">
-        <v>6686156088</v>
+        <v>6317002858</v>
       </c>
       <c r="D1376" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1376" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1376" t="str">
         <v>РФ</v>
       </c>
       <c r="G1376">
-        <v>47357</v>
+        <v>47319</v>
       </c>
     </row>
     <row r="1377">
@@ -32062,7 +32062,7 @@
         <v>6317002858</v>
       </c>
       <c r="D1377" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1377" t="str">
         <v>ISO 13485:2016</v>
@@ -32076,25 +32076,25 @@
     </row>
     <row r="1378">
       <c r="A1378" t="str">
-        <v>Научно-исследовательский институт биотехнологий (НИИ БиоТех) ФГБОУ ВО СамГМУ Минздрава России</v>
+        <v>КрасАвиа</v>
       </c>
       <c r="B1378" t="str">
-        <v>ФГБОУ ВО</v>
+        <v>АО</v>
       </c>
       <c r="C1378" t="str">
-        <v>6317002858</v>
+        <v>2465177981</v>
       </c>
       <c r="D1378" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1378" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1378" t="str">
         <v>РФ</v>
       </c>
       <c r="G1378">
-        <v>47319</v>
+        <v>47299</v>
       </c>
     </row>
     <row r="1379">
@@ -32108,7 +32108,7 @@
         <v>2465177981</v>
       </c>
       <c r="D1379" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1379" t="str">
         <v>ISO 9001:2015</v>
@@ -32122,36 +32122,36 @@
     </row>
     <row r="1380">
       <c r="A1380" t="str">
-        <v>КрасАвиа</v>
+        <v>Стальимпэкс</v>
       </c>
       <c r="B1380" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1380" t="str">
-        <v>2465177981</v>
+        <v>7017447537</v>
       </c>
       <c r="D1380" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1380" t="str">
-        <v>ISO 9001:2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1380" t="str">
         <v>РФ</v>
       </c>
       <c r="G1380">
-        <v>47299</v>
+        <v>47116</v>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="str">
-        <v>Стальимпэкс</v>
+        <v>Автоматизация-Метрология-Эксперт</v>
       </c>
       <c r="B1381" t="str">
         <v>ООО</v>
       </c>
       <c r="C1381" t="str">
-        <v>7017447537</v>
+        <v>0276115746</v>
       </c>
       <c r="D1381" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -32162,13 +32162,13 @@
       <c r="F1381" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1381">
-        <v>47116</v>
+      <c r="G1381" t="str">
+        <v/>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="str">
-        <v>Автоматизация-Метрология-Эксперт</v>
+        <v>Автоматизация-Метрология-эксперт</v>
       </c>
       <c r="B1382" t="str">
         <v>ООО</v>
@@ -32177,10 +32177,10 @@
         <v>0276115746</v>
       </c>
       <c r="D1382" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1382" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1382" t="str">
         <v>РФ</v>
@@ -32191,19 +32191,19 @@
     </row>
     <row r="1383">
       <c r="A1383" t="str">
-        <v>Автоматизация-Метрология-эксперт</v>
+        <v>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "НИЖЕГОРОДСКИЙ ЗАВОД ТЕПЛООБМЕННОГО ОБОРУДОВАНИЯ"</v>
       </c>
       <c r="B1383" t="str">
         <v>ООО</v>
       </c>
       <c r="C1383" t="str">
-        <v>0276115746</v>
+        <v>5261068838</v>
       </c>
       <c r="D1383" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1383" t="str">
-        <v>S.QS.07-2024</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1383" t="str">
         <v>РФ</v>
@@ -32214,36 +32214,36 @@
     </row>
     <row r="1384">
       <c r="A1384" t="str">
-        <v>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "НИЖЕГОРОДСКИЙ ЗАВОД ТЕПЛООБМЕННОГО ОБОРУДОВАНИЯ"</v>
+        <v>Технопром</v>
       </c>
       <c r="B1384" t="str">
         <v>ООО</v>
       </c>
       <c r="C1384" t="str">
-        <v>5261068838</v>
+        <v>7731637278</v>
       </c>
       <c r="D1384" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1384" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1384" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1384" t="str">
-        <v/>
+      <c r="G1384">
+        <v>47026</v>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="str">
-        <v>Технопром</v>
+        <v>Пергам-Инжиниринг</v>
       </c>
       <c r="B1385" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1385" t="str">
-        <v>7731637278</v>
+        <v>7713226814</v>
       </c>
       <c r="D1385" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32255,18 +32255,18 @@
         <v>РФ</v>
       </c>
       <c r="G1385">
-        <v>47026</v>
+        <v>47085</v>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="str">
-        <v>Пергам-Инжиниринг</v>
+        <v>Газ-проект-Инжиниринг</v>
       </c>
       <c r="B1386" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1386" t="str">
-        <v>7713226814</v>
+        <v>278096584</v>
       </c>
       <c r="D1386" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32278,18 +32278,18 @@
         <v>РФ</v>
       </c>
       <c r="G1386">
-        <v>47085</v>
+        <v>47089</v>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="str">
-        <v>Газ-проект-Инжиниринг</v>
+        <v>Инжиниринговая компания Интэко</v>
       </c>
       <c r="B1387" t="str">
         <v>ООО</v>
       </c>
       <c r="C1387" t="str">
-        <v>278096584</v>
+        <v>276121517</v>
       </c>
       <c r="D1387" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32301,18 +32301,18 @@
         <v>РФ</v>
       </c>
       <c r="G1387">
-        <v>47089</v>
+        <v>47092</v>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="str">
-        <v>Инжиниринговая компания Интэко</v>
+        <v>ЕвроМет</v>
       </c>
       <c r="B1388" t="str">
         <v>ООО</v>
       </c>
       <c r="C1388" t="str">
-        <v>276121517</v>
+        <v>7826046940</v>
       </c>
       <c r="D1388" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32324,18 +32324,18 @@
         <v>РФ</v>
       </c>
       <c r="G1388">
-        <v>47092</v>
+        <v>47161</v>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="str">
-        <v>ЕвроМет</v>
+        <v>Краснодарский завод Нефтемаш</v>
       </c>
       <c r="B1389" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1389" t="str">
-        <v>7826046940</v>
+        <v>2308026372</v>
       </c>
       <c r="D1389" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32347,18 +32347,18 @@
         <v>РФ</v>
       </c>
       <c r="G1389">
-        <v>47161</v>
+        <v>47190</v>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="str">
-        <v>Краснодарский завод Нефтемаш</v>
+        <v>НТЦ ЗЭРС</v>
       </c>
       <c r="B1390" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1390" t="str">
-        <v>2308026372</v>
+        <v>6229024740</v>
       </c>
       <c r="D1390" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32369,19 +32369,19 @@
       <c r="F1390" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1390">
-        <v>47190</v>
+      <c r="G1390" t="str">
+        <v/>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="str">
-        <v>НТЦ ЗЭРС</v>
+        <v>КасторИнжиниринг</v>
       </c>
       <c r="B1391" t="str">
         <v>ООО</v>
       </c>
       <c r="C1391" t="str">
-        <v>6229024740</v>
+        <v>5612079207</v>
       </c>
       <c r="D1391" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32398,13 +32398,13 @@
     </row>
     <row r="1392">
       <c r="A1392" t="str">
-        <v>КасторИнжиниринг</v>
+        <v>МК Энерго</v>
       </c>
       <c r="B1392" t="str">
         <v>ООО</v>
       </c>
       <c r="C1392" t="str">
-        <v>5612079207</v>
+        <v>7731587806</v>
       </c>
       <c r="D1392" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32419,32 +32419,9 @@
         <v/>
       </c>
     </row>
-    <row r="1393">
-      <c r="A1393" t="str">
-        <v>МК Энерго</v>
-      </c>
-      <c r="B1393" t="str">
-        <v>ООО</v>
-      </c>
-      <c r="C1393" t="str">
-        <v>7731587806</v>
-      </c>
-      <c r="D1393" t="str">
-        <v>СДС АНО ИНТИ</v>
-      </c>
-      <c r="E1393" t="str">
-        <v>S.QS.07-2024</v>
-      </c>
-      <c r="F1393" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1393" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1393"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1392"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1392"/>
+  <dimension ref="A1:G1393"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -23320,7 +23320,7 @@
         <v>7801223114</v>
       </c>
       <c r="D997" t="str">
-        <v>UKAS (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E997" t="str">
         <v>ISO 13485:2016</v>
@@ -23329,41 +23329,41 @@
         <v>РФ</v>
       </c>
       <c r="G997">
-        <v>46622</v>
+        <v>47348</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>Айрос-Систем</v>
+        <v>Ассоциация Медицины и Аналитики</v>
       </c>
       <c r="B998" t="str">
         <v>ООО</v>
       </c>
       <c r="C998" t="str">
-        <v>7804691720</v>
+        <v>7801223114</v>
       </c>
       <c r="D998" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E998" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F998" t="str">
         <v>РФ</v>
       </c>
       <c r="G998">
-        <v>46622</v>
+        <v>47348</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>БорМаш</v>
+        <v>Айрос-Систем</v>
       </c>
       <c r="B999" t="str">
         <v>ООО</v>
       </c>
       <c r="C999" t="str">
-        <v>3604011804</v>
+        <v>7804691720</v>
       </c>
       <c r="D999" t="str">
         <v>UKAS (IAF)</v>
@@ -23375,7 +23375,7 @@
         <v>РФ</v>
       </c>
       <c r="G999">
-        <v>46625</v>
+        <v>46622</v>
       </c>
     </row>
     <row r="1000">
@@ -23389,50 +23389,50 @@
         <v>3604011804</v>
       </c>
       <c r="D1000" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1000" t="str">
-        <v>S.QS.01-2020</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1000" t="str">
         <v>РФ</v>
       </c>
       <c r="G1000">
-        <v>46474</v>
+        <v>46625</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>FELUCCA MARITIME SERVICES</v>
+        <v>БорМаш</v>
       </c>
       <c r="B1001" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1001" t="str">
-        <v/>
+        <v>3604011804</v>
       </c>
       <c r="D1001" t="str">
-        <v>UKAS (IAF)</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1001" t="str">
-        <v>ISO 9001:2015</v>
+        <v>S.QS.01-2020</v>
       </c>
       <c r="F1001" t="str">
-        <v>UAE</v>
+        <v>РФ</v>
       </c>
       <c r="G1001">
-        <v>46654</v>
+        <v>46474</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>ОБЪЕДИНЕННАЯ КОМПАНИЯ РУСАЛ АНОДНАЯ ФАБРИКА</v>
+        <v>FELUCCA MARITIME SERVICES</v>
       </c>
       <c r="B1002" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1002" t="str">
-        <v>7709788673</v>
+        <v/>
       </c>
       <c r="D1002" t="str">
         <v>UKAS (IAF)</v>
@@ -23441,33 +23441,33 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1002" t="str">
-        <v>РФ</v>
+        <v>UAE</v>
       </c>
       <c r="G1002">
-        <v>46597</v>
+        <v>46654</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>Мегатехника СПб</v>
+        <v>ОБЪЕДИНЕННАЯ КОМПАНИЯ РУСАЛ АНОДНАЯ ФАБРИКА</v>
       </c>
       <c r="B1003" t="str">
         <v>ООО</v>
       </c>
       <c r="C1003" t="str">
-        <v>7801399929</v>
+        <v>7709788673</v>
       </c>
       <c r="D1003" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1003" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1003" t="str">
         <v>РФ</v>
       </c>
       <c r="G1003">
-        <v>46793</v>
+        <v>46597</v>
       </c>
     </row>
     <row r="1004">
@@ -23481,16 +23481,16 @@
         <v>7801399929</v>
       </c>
       <c r="D1004" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1004" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1004" t="str">
         <v>РФ</v>
       </c>
       <c r="G1004">
-        <v>46773</v>
+        <v>46793</v>
       </c>
     </row>
     <row r="1005">
@@ -23504,7 +23504,7 @@
         <v>7801399929</v>
       </c>
       <c r="D1005" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1005" t="str">
         <v>ISO 9001:2015</v>
@@ -23518,45 +23518,45 @@
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>ORIENT BULKER EXPRESS SHIP MANAGEMENT</v>
+        <v>Мегатехника СПб</v>
       </c>
       <c r="B1006" t="str">
-        <v>LLC</v>
+        <v>ООО</v>
       </c>
       <c r="C1006" t="str">
-        <v/>
+        <v>7801399929</v>
       </c>
       <c r="D1006" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1006" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1006" t="str">
-        <v>UAE</v>
+        <v>РФ</v>
       </c>
       <c r="G1006">
-        <v>46669</v>
+        <v>46773</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>НАУЧНО-ПРОИЗВОДСТВЕННОЕ ПРЕДПРИЯТИЕ «РАДАР ММС»</v>
+        <v>ORIENT BULKER EXPRESS SHIP MANAGEMENT</v>
       </c>
       <c r="B1007" t="str">
-        <v>АО</v>
+        <v>LLC</v>
       </c>
       <c r="C1007" t="str">
-        <v>7814027653</v>
+        <v/>
       </c>
       <c r="D1007" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1007" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1007" t="str">
-        <v>РФ</v>
+        <v>UAE</v>
       </c>
       <c r="G1007">
         <v>46669</v>
@@ -23573,16 +23573,16 @@
         <v>7814027653</v>
       </c>
       <c r="D1008" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1008" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1008" t="str">
         <v>РФ</v>
       </c>
       <c r="G1008">
-        <v>46260</v>
+        <v>46669</v>
       </c>
     </row>
     <row r="1009">
@@ -23596,108 +23596,108 @@
         <v>7814027653</v>
       </c>
       <c r="D1009" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1009" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1009" t="str">
         <v>РФ</v>
       </c>
       <c r="G1009">
-        <v>46710</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>СКТ-сервис</v>
+        <v>НАУЧНО-ПРОИЗВОДСТВЕННОЕ ПРЕДПРИЯТИЕ «РАДАР ММС»</v>
       </c>
       <c r="B1010" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1010" t="str">
-        <v>6027207282</v>
+        <v>7814027653</v>
       </c>
       <c r="D1010" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1010" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1010" t="str">
         <v>РФ</v>
       </c>
       <c r="G1010">
-        <v>46864</v>
+        <v>46710</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>Общество с ограниченной ответственностью "ИЛМАКС" Завод по производству строительных материалов</v>
+        <v>СКТ-сервис</v>
       </c>
       <c r="B1011" t="str">
         <v>ООО</v>
       </c>
       <c r="C1011" t="str">
-        <v>100070995</v>
+        <v>6027207282</v>
       </c>
       <c r="D1011" t="str">
-        <v>UKAS (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1011" t="str">
-        <v>ISO 9001:2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1011" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1011">
-        <v>46729</v>
+        <v>46864</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>Кандрашин А.В</v>
+        <v>Общество с ограниченной ответственностью "ИЛМАКС" Завод по производству строительных материалов</v>
       </c>
       <c r="B1012" t="str">
-        <v>ИП</v>
+        <v>ООО</v>
       </c>
       <c r="C1012" t="str">
-        <v>632106359952</v>
+        <v>100070995</v>
       </c>
       <c r="D1012" t="str">
-        <v>EGAC (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1012" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1012" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1012">
-        <v>46730</v>
+        <v>46729</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>Шумихинский завод подшипниковых иглороликов</v>
+        <v>Кандрашин А.В</v>
       </c>
       <c r="B1013" t="str">
-        <v>ОАО</v>
+        <v>ИП</v>
       </c>
       <c r="C1013" t="str">
-        <v>4524000693</v>
+        <v>632106359952</v>
       </c>
       <c r="D1013" t="str">
-        <v>EADAS</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1013" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1013" t="str">
         <v>РФ</v>
       </c>
       <c r="G1013">
-        <v>46227</v>
+        <v>46730</v>
       </c>
     </row>
     <row r="1014">
@@ -23711,50 +23711,50 @@
         <v>4524000693</v>
       </c>
       <c r="D1014" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1014" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1014" t="str">
         <v>РФ</v>
       </c>
       <c r="G1014">
-        <v>46717</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>СМТ</v>
+        <v>Шумихинский завод подшипниковых иглороликов</v>
       </c>
       <c r="B1015" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1015" t="str">
-        <v>7838510490</v>
+        <v>4524000693</v>
       </c>
       <c r="D1015" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1015" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1015" t="str">
         <v>РФ</v>
       </c>
       <c r="G1015">
-        <v>46575</v>
+        <v>46717</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>Технология</v>
+        <v>СМТ</v>
       </c>
       <c r="B1016" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1016" t="str">
-        <v>1828007328</v>
+        <v>7838510490</v>
       </c>
       <c r="D1016" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -23766,64 +23766,64 @@
         <v>РФ</v>
       </c>
       <c r="G1016">
-        <v>46866</v>
+        <v>46575</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>Steam Line Middle East Shipping</v>
+        <v>Технология</v>
       </c>
       <c r="B1017" t="str">
-        <v/>
+        <v>АО</v>
       </c>
       <c r="C1017" t="str">
-        <v/>
+        <v>1828007328</v>
       </c>
       <c r="D1017" t="str">
-        <v>UKAS (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1017" t="str">
-        <v>ISO 9001:2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1017" t="str">
-        <v>UAE</v>
+        <v>РФ</v>
       </c>
       <c r="G1017">
-        <v>46719</v>
+        <v>46866</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>Верейский механический завод</v>
+        <v>Steam Line Middle East Shipping</v>
       </c>
       <c r="B1018" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1018" t="str">
-        <v>5030090040</v>
+        <v/>
       </c>
       <c r="D1018" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1018" t="str">
-        <v>S.QS.01-2020</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1018" t="str">
-        <v>РФ</v>
+        <v>UAE</v>
       </c>
       <c r="G1018">
-        <v>46362</v>
+        <v>46719</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>ТМС-групп</v>
+        <v>Верейский механический завод</v>
       </c>
       <c r="B1019" t="str">
         <v>ООО</v>
       </c>
       <c r="C1019" t="str">
-        <v>1644034949</v>
+        <v>5030090040</v>
       </c>
       <c r="D1019" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -23835,41 +23835,41 @@
         <v>РФ</v>
       </c>
       <c r="G1019">
-        <v>46467</v>
+        <v>46362</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>Титан-Энерго</v>
+        <v>ТМС-групп</v>
       </c>
       <c r="B1020" t="str">
         <v>ООО</v>
       </c>
       <c r="C1020" t="str">
-        <v>8610024374</v>
+        <v>1644034949</v>
       </c>
       <c r="D1020" t="str">
         <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1020" t="str">
-        <v>S.QS.07-2024</v>
+        <v>S.QS.01-2020</v>
       </c>
       <c r="F1020" t="str">
         <v>РФ</v>
       </c>
       <c r="G1020">
-        <v>46699</v>
+        <v>46467</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>СРЗ</v>
+        <v>Титан-Энерго</v>
       </c>
       <c r="B1021" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1021" t="str">
-        <v>6317126596</v>
+        <v>8610024374</v>
       </c>
       <c r="D1021" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -23881,53 +23881,53 @@
         <v>РФ</v>
       </c>
       <c r="G1021">
-        <v>46692</v>
+        <v>46699</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>ПСА</v>
+        <v>СРЗ</v>
       </c>
       <c r="B1022" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1022" t="str">
-        <v>7017462729</v>
+        <v>6317126596</v>
       </c>
       <c r="D1022" t="str">
         <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1022" t="str">
-        <v>S.QS.01-2020</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1022" t="str">
         <v>РФ</v>
       </c>
       <c r="G1022">
-        <v>46502</v>
+        <v>46692</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>ГК «ЛИМАН»</v>
+        <v>ПСА</v>
       </c>
       <c r="B1023" t="str">
         <v>ООО</v>
       </c>
       <c r="C1023" t="str">
-        <v>7811438750</v>
+        <v>7017462729</v>
       </c>
       <c r="D1023" t="str">
-        <v>ESYD (IAF)</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1023" t="str">
-        <v>ISO 9001:2015</v>
+        <v>S.QS.01-2020</v>
       </c>
       <c r="F1023" t="str">
         <v>РФ</v>
       </c>
       <c r="G1023">
-        <v>46837</v>
+        <v>46502</v>
       </c>
     </row>
     <row r="1024">
@@ -23941,7 +23941,7 @@
         <v>7811438750</v>
       </c>
       <c r="D1024" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1024" t="str">
         <v>ISO 9001:2015</v>
@@ -23955,76 +23955,76 @@
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>ЗМК-Сибирь</v>
+        <v>ГК «ЛИМАН»</v>
       </c>
       <c r="B1025" t="str">
         <v>ООО</v>
       </c>
       <c r="C1025" t="str">
-        <v>5505217893</v>
+        <v>7811438750</v>
       </c>
       <c r="D1025" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1025" t="str">
-        <v>S.QS.01-2020</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1025" t="str">
         <v>РФ</v>
       </c>
       <c r="G1025">
-        <v>46440</v>
+        <v>46837</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>Б2Б центр</v>
+        <v>ЗМК-Сибирь</v>
       </c>
       <c r="B1026" t="str">
         <v>ООО</v>
       </c>
       <c r="C1026" t="str">
-        <v>5034051080</v>
+        <v>5505217893</v>
       </c>
       <c r="D1026" t="str">
         <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1026" t="str">
-        <v>S.QS.07-2024</v>
+        <v>S.QS.01-2020</v>
       </c>
       <c r="F1026" t="str">
         <v>РФ</v>
       </c>
       <c r="G1026">
-        <v>46677</v>
+        <v>46440</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>Nikolov S.r.l.</v>
+        <v>Б2Б центр</v>
       </c>
       <c r="B1027" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1027" t="str">
-        <v/>
+        <v>5034051080</v>
       </c>
       <c r="D1027" t="str">
-        <v>Accredia</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1027" t="str">
-        <v>ISO 9001:2015</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1027" t="str">
-        <v>IT</v>
+        <v>РФ</v>
       </c>
       <c r="G1027">
-        <v>46769</v>
+        <v>46677</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>M C G 8 LLC</v>
+        <v>Nikolov S.r.l.</v>
       </c>
       <c r="B1028" t="str">
         <v/>
@@ -24033,62 +24033,62 @@
         <v/>
       </c>
       <c r="D1028" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Accredia</v>
       </c>
       <c r="E1028" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1028" t="str">
-        <v>Georgia</v>
+        <v>IT</v>
       </c>
       <c r="G1028">
-        <v>46766</v>
+        <v>46769</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>ТДМК</v>
+        <v>M C G 8 LLC</v>
       </c>
       <c r="B1029" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1029" t="str">
-        <v>6321191904</v>
+        <v/>
       </c>
       <c r="D1029" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1029" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1029" t="str">
-        <v>РФ</v>
+        <v>Georgia</v>
       </c>
       <c r="G1029">
-        <v>46760</v>
+        <v>46766</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>НаноМед</v>
+        <v>ТДМК</v>
       </c>
       <c r="B1030" t="str">
         <v>ООО</v>
       </c>
       <c r="C1030" t="str">
-        <v>5837044394</v>
+        <v>6321191904</v>
       </c>
       <c r="D1030" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1030" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1030" t="str">
         <v>РФ</v>
       </c>
       <c r="G1030">
-        <v>46781</v>
+        <v>46760</v>
       </c>
     </row>
     <row r="1031">
@@ -24102,7 +24102,7 @@
         <v>5837044394</v>
       </c>
       <c r="D1031" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1031" t="str">
         <v>ISO 13485:2016</v>
@@ -24125,16 +24125,16 @@
         <v>5837044394</v>
       </c>
       <c r="D1032" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1032" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1032" t="str">
         <v>РФ</v>
       </c>
       <c r="G1032">
-        <v>46822</v>
+        <v>46781</v>
       </c>
     </row>
     <row r="1033">
@@ -24148,7 +24148,7 @@
         <v>5837044394</v>
       </c>
       <c r="D1033" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1033" t="str">
         <v>ГОСТ ISO 13485-2017</v>
@@ -24162,25 +24162,25 @@
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>ТЕХНОЛОГИЧЕСКИЕ ПЛЕНКИ</v>
+        <v>НаноМед</v>
       </c>
       <c r="B1034" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1034" t="str">
-        <v>5246058666</v>
+        <v>5837044394</v>
       </c>
       <c r="D1034" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1034" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1034" t="str">
         <v>РФ</v>
       </c>
       <c r="G1034">
-        <v>47112</v>
+        <v>46822</v>
       </c>
     </row>
     <row r="1035">
@@ -24194,7 +24194,7 @@
         <v>5246058666</v>
       </c>
       <c r="D1035" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1035" t="str">
         <v>ISO 9001:2015</v>
@@ -24208,48 +24208,48 @@
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>Шарпинская</v>
+        <v>ТЕХНОЛОГИЧЕСКИЕ ПЛЕНКИ</v>
       </c>
       <c r="B1036" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1036" t="str">
-        <v>3801142563</v>
+        <v>5246058666</v>
       </c>
       <c r="D1036" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1036" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1036" t="str">
         <v>РФ</v>
       </c>
       <c r="G1036">
-        <v>46736</v>
+        <v>47112</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>Автогидроусилитель</v>
+        <v>Шарпинская</v>
       </c>
       <c r="B1037" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1037" t="str">
-        <v>600009233</v>
+        <v>3801142563</v>
       </c>
       <c r="D1037" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1037" t="str">
-        <v>IATF 16949:2016</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1037" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1037">
-        <v>46597</v>
+        <v>46736</v>
       </c>
     </row>
     <row r="1038">
@@ -24263,39 +24263,39 @@
         <v>600009233</v>
       </c>
       <c r="D1038" t="str">
-        <v>EADAS</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1038" t="str">
-        <v>16949: 2016</v>
+        <v>IATF 16949:2016</v>
       </c>
       <c r="F1038" t="str">
         <v>РБ</v>
       </c>
       <c r="G1038">
-        <v>46101</v>
+        <v>46597</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>ЛАДАПЛАСТ-Т</v>
+        <v>Автогидроусилитель</v>
       </c>
       <c r="B1039" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1039" t="str">
-        <v>6321231498</v>
+        <v>600009233</v>
       </c>
       <c r="D1039" t="str">
-        <v>EGAC (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1039" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1039" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1039">
-        <v>46731</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="1040">
@@ -24309,50 +24309,50 @@
         <v>6321231498</v>
       </c>
       <c r="D1040" t="str">
-        <v>EADAS</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1040" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1040" t="str">
         <v>РФ</v>
       </c>
       <c r="G1040">
-        <v>46318</v>
+        <v>46731</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>АксТим</v>
+        <v>ЛАДАПЛАСТ-Т</v>
       </c>
       <c r="B1041" t="str">
         <v>ООО</v>
       </c>
       <c r="C1041" t="str">
-        <v>7705476338</v>
+        <v>6321231498</v>
       </c>
       <c r="D1041" t="str">
-        <v>ESYD (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1041" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1041" t="str">
         <v>РФ</v>
       </c>
       <c r="G1041">
-        <v>47038</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>АксТим Тех</v>
+        <v>АксТим</v>
       </c>
       <c r="B1042" t="str">
         <v>ООО</v>
       </c>
       <c r="C1042" t="str">
-        <v>6950259732</v>
+        <v>7705476338</v>
       </c>
       <c r="D1042" t="str">
         <v>ESYD (IAF)</v>
@@ -24369,13 +24369,13 @@
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>Аксеникс Инновации</v>
+        <v>АксТим Тех</v>
       </c>
       <c r="B1043" t="str">
         <v>ООО</v>
       </c>
       <c r="C1043" t="str">
-        <v>9731109240</v>
+        <v>6950259732</v>
       </c>
       <c r="D1043" t="str">
         <v>ESYD (IAF)</v>
@@ -24392,13 +24392,13 @@
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>Аксеникс Нейрокод</v>
+        <v>Аксеникс Инновации</v>
       </c>
       <c r="B1044" t="str">
         <v>ООО</v>
       </c>
       <c r="C1044" t="str">
-        <v>9731136116</v>
+        <v>9731109240</v>
       </c>
       <c r="D1044" t="str">
         <v>ESYD (IAF)</v>
@@ -24415,13 +24415,13 @@
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>Аксеникс Инсайт</v>
+        <v>Аксеникс Нейрокод</v>
       </c>
       <c r="B1045" t="str">
         <v>ООО</v>
       </c>
       <c r="C1045" t="str">
-        <v>9731121783</v>
+        <v>9731136116</v>
       </c>
       <c r="D1045" t="str">
         <v>ESYD (IAF)</v>
@@ -24433,21 +24433,21 @@
         <v>РФ</v>
       </c>
       <c r="G1045">
-        <v>47041</v>
+        <v>47038</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>АксТим</v>
+        <v>Аксеникс Инсайт</v>
       </c>
       <c r="B1046" t="str">
         <v>ООО</v>
       </c>
       <c r="C1046" t="str">
-        <v>7705476338</v>
+        <v>9731121783</v>
       </c>
       <c r="D1046" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1046" t="str">
         <v>ISO/IEC 27001:2022</v>
@@ -24456,18 +24456,18 @@
         <v>РФ</v>
       </c>
       <c r="G1046">
-        <v>47038</v>
+        <v>47041</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>АксТим Тех</v>
+        <v>АксТим</v>
       </c>
       <c r="B1047" t="str">
         <v>ООО</v>
       </c>
       <c r="C1047" t="str">
-        <v>6950259732</v>
+        <v>7705476338</v>
       </c>
       <c r="D1047" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -24484,13 +24484,13 @@
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>Аксеникс Инновации</v>
+        <v>АксТим Тех</v>
       </c>
       <c r="B1048" t="str">
         <v>ООО</v>
       </c>
       <c r="C1048" t="str">
-        <v>9731109240</v>
+        <v>6950259732</v>
       </c>
       <c r="D1048" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -24507,13 +24507,13 @@
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>Аксеникс Нейрокод</v>
+        <v>Аксеникс Инновации</v>
       </c>
       <c r="B1049" t="str">
         <v>ООО</v>
       </c>
       <c r="C1049" t="str">
-        <v>9731136116</v>
+        <v>9731109240</v>
       </c>
       <c r="D1049" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -24530,13 +24530,13 @@
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>Аксеникс Инсайт</v>
+        <v>Аксеникс Нейрокод</v>
       </c>
       <c r="B1050" t="str">
         <v>ООО</v>
       </c>
       <c r="C1050" t="str">
-        <v>9731121783</v>
+        <v>9731136116</v>
       </c>
       <c r="D1050" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
@@ -24548,30 +24548,30 @@
         <v>РФ</v>
       </c>
       <c r="G1050">
-        <v>47041</v>
+        <v>47038</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>КАТЮША ПРИНТ</v>
+        <v>Аксеникс Инсайт</v>
       </c>
       <c r="B1051" t="str">
         <v>ООО</v>
       </c>
       <c r="C1051" t="str">
-        <v>9703037297</v>
+        <v>9731121783</v>
       </c>
       <c r="D1051" t="str">
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1051" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1051" t="str">
         <v>РФ</v>
       </c>
       <c r="G1051">
-        <v>46729</v>
+        <v>47041</v>
       </c>
     </row>
     <row r="1052">
@@ -24585,7 +24585,7 @@
         <v>9703037297</v>
       </c>
       <c r="D1052" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1052" t="str">
         <v>ISO 9001:2015</v>
@@ -24608,39 +24608,39 @@
         <v>9703037297</v>
       </c>
       <c r="D1053" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1053" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1053" t="str">
         <v>РФ</v>
       </c>
       <c r="G1053">
-        <v>46787</v>
+        <v>46729</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>НПП Спектр-ТП</v>
+        <v>КАТЮША ПРИНТ</v>
       </c>
       <c r="B1054" t="str">
         <v>ООО</v>
       </c>
       <c r="C1054" t="str">
-        <v>6415003465</v>
+        <v>9703037297</v>
       </c>
       <c r="D1054" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1054" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1054" t="str">
         <v>РФ</v>
       </c>
       <c r="G1054">
-        <v>46744</v>
+        <v>46787</v>
       </c>
     </row>
     <row r="1055">
@@ -24654,10 +24654,10 @@
         <v>6415003465</v>
       </c>
       <c r="D1055" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1055" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1055" t="str">
         <v>РФ</v>
@@ -24677,10 +24677,10 @@
         <v>6415003465</v>
       </c>
       <c r="D1056" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1056" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1056" t="str">
         <v>РФ</v>
@@ -24703,7 +24703,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1057" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1057" t="str">
         <v>РФ</v>
@@ -24714,25 +24714,25 @@
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>ВМПАВТО</v>
+        <v>НПП Спектр-ТП</v>
       </c>
       <c r="B1058" t="str">
         <v>ООО</v>
       </c>
       <c r="C1058" t="str">
-        <v>7814069526</v>
+        <v>6415003465</v>
       </c>
       <c r="D1058" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1058" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1058" t="str">
         <v>РФ</v>
       </c>
       <c r="G1058">
-        <v>46849</v>
+        <v>46744</v>
       </c>
     </row>
     <row r="1059">
@@ -24746,7 +24746,7 @@
         <v>7814069526</v>
       </c>
       <c r="D1059" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1059" t="str">
         <v>ISO 9001:2015</v>
@@ -24760,16 +24760,16 @@
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>смазка.ру</v>
+        <v>ВМПАВТО</v>
       </c>
       <c r="B1060" t="str">
         <v>ООО</v>
       </c>
       <c r="C1060" t="str">
-        <v>7805276082</v>
+        <v>7814069526</v>
       </c>
       <c r="D1060" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1060" t="str">
         <v>ISO 9001:2015</v>
@@ -24778,7 +24778,7 @@
         <v>РФ</v>
       </c>
       <c r="G1060">
-        <v>46846</v>
+        <v>46849</v>
       </c>
     </row>
     <row r="1061">
@@ -24792,7 +24792,7 @@
         <v>7805276082</v>
       </c>
       <c r="D1061" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1061" t="str">
         <v>ISO 9001:2015</v>
@@ -24806,16 +24806,16 @@
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>Лайтинг Солюшнс</v>
+        <v>смазка.ру</v>
       </c>
       <c r="B1062" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1062" t="str">
-        <v>7720906560</v>
+        <v>7805276082</v>
       </c>
       <c r="D1062" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1062" t="str">
         <v>ISO 9001:2015</v>
@@ -24824,7 +24824,7 @@
         <v>РФ</v>
       </c>
       <c r="G1062">
-        <v>46806</v>
+        <v>46846</v>
       </c>
     </row>
     <row r="1063">
@@ -24838,7 +24838,7 @@
         <v>7720906560</v>
       </c>
       <c r="D1063" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1063" t="str">
         <v>ISO 9001:2015</v>
@@ -24861,39 +24861,39 @@
         <v>7720906560</v>
       </c>
       <c r="D1064" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1064" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1064" t="str">
         <v>РФ</v>
       </c>
       <c r="G1064">
-        <v>46423</v>
+        <v>46806</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>"АРТ ДЕКО БИЛД" ЕООД</v>
+        <v>Лайтинг Солюшнс</v>
       </c>
       <c r="B1065" t="str">
-        <v/>
+        <v>АО</v>
       </c>
       <c r="C1065" t="str">
-        <v/>
+        <v>7720906560</v>
       </c>
       <c r="D1065" t="str">
-        <v>IAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1065" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1065" t="str">
-        <v>Bulgaria</v>
+        <v>РФ</v>
       </c>
       <c r="G1065">
-        <v>46788</v>
+        <v>46423</v>
       </c>
     </row>
     <row r="1066">
@@ -24910,13 +24910,13 @@
         <v>IAS (IAF)</v>
       </c>
       <c r="E1066" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1066" t="str">
         <v>Bulgaria</v>
       </c>
       <c r="G1066">
-        <v>46787</v>
+        <v>46788</v>
       </c>
     </row>
     <row r="1067">
@@ -24933,7 +24933,7 @@
         <v>IAS (IAF)</v>
       </c>
       <c r="E1067" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1067" t="str">
         <v>Bulgaria</v>
@@ -24944,48 +24944,48 @@
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>Предприятие "Трубопласт"</v>
+        <v>"АРТ ДЕКО БИЛД" ЕООД</v>
       </c>
       <c r="B1068" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1068" t="str">
-        <v>6661044752</v>
+        <v/>
       </c>
       <c r="D1068" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1068" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1068" t="str">
-        <v>РФ</v>
+        <v>Bulgaria</v>
       </c>
       <c r="G1068">
-        <v>46857</v>
+        <v>46787</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>"Карачевский завод "Электродеталь"</v>
+        <v>Предприятие "Трубопласт"</v>
       </c>
       <c r="B1069" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1069" t="str">
-        <v>3254511340</v>
+        <v>6661044752</v>
       </c>
       <c r="D1069" t="str">
-        <v>ESYD (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1069" t="str">
-        <v>ISO 9001:2015</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1069" t="str">
         <v>РФ</v>
       </c>
       <c r="G1069">
-        <v>47033</v>
+        <v>46857</v>
       </c>
     </row>
     <row r="1070">
@@ -24999,7 +24999,7 @@
         <v>3254511340</v>
       </c>
       <c r="D1070" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1070" t="str">
         <v>ISO 9001:2015</v>
@@ -25022,16 +25022,16 @@
         <v>3254511340</v>
       </c>
       <c r="D1071" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1071" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1071" t="str">
         <v>РФ</v>
       </c>
       <c r="G1071">
-        <v>46206</v>
+        <v>47033</v>
       </c>
     </row>
     <row r="1072">
@@ -25045,16 +25045,16 @@
         <v>3254511340</v>
       </c>
       <c r="D1072" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1072" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1072" t="str">
         <v>РФ</v>
       </c>
       <c r="G1072">
-        <v>47035</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="1073">
@@ -25071,7 +25071,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1073" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1073" t="str">
         <v>РФ</v>
@@ -25082,25 +25082,25 @@
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>QazAlPack</v>
+        <v>"Карачевский завод "Электродеталь"</v>
       </c>
       <c r="B1074" t="str">
-        <v>LLP</v>
+        <v>АО</v>
       </c>
       <c r="C1074" t="str">
-        <v>191140029675</v>
+        <v>3254511340</v>
       </c>
       <c r="D1074" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1074" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1074" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1074">
-        <v>46823</v>
+        <v>47035</v>
       </c>
     </row>
     <row r="1075">
@@ -25117,13 +25117,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1075" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1075" t="str">
         <v>KZ</v>
       </c>
       <c r="G1075">
-        <v>46824</v>
+        <v>46823</v>
       </c>
     </row>
     <row r="1076">
@@ -25140,7 +25140,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1076" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1076" t="str">
         <v>KZ</v>
@@ -25163,36 +25163,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1077" t="str">
-        <v>FSSC 22000</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1077" t="str">
         <v>KZ</v>
       </c>
       <c r="G1077">
-        <v>46891</v>
+        <v>46824</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>Транспортные интерьерные системы</v>
+        <v>QazAlPack</v>
       </c>
       <c r="B1078" t="str">
-        <v>ООО</v>
+        <v>LLP</v>
       </c>
       <c r="C1078" t="str">
-        <v>6230126270</v>
+        <v>191140029675</v>
       </c>
       <c r="D1078" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1078" t="str">
-        <v>ISO 9001:2015</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1078" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1078">
-        <v>47049</v>
+        <v>46891</v>
       </c>
     </row>
     <row r="1079">
@@ -25206,7 +25206,7 @@
         <v>6230126270</v>
       </c>
       <c r="D1079" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1079" t="str">
         <v>ISO 9001:2015</v>
@@ -25229,16 +25229,16 @@
         <v>6230126270</v>
       </c>
       <c r="D1080" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1080" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1080" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1080" t="str">
-        <v>с 2026 года</v>
+      <c r="G1080">
+        <v>47049</v>
       </c>
     </row>
     <row r="1081">
@@ -25252,27 +25252,27 @@
         <v>6230126270</v>
       </c>
       <c r="D1081" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1081" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1081" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1081">
-        <v>47039</v>
+      <c r="G1081" t="str">
+        <v>с 2026 года</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>СмартЭмСис</v>
+        <v>Транспортные интерьерные системы</v>
       </c>
       <c r="B1082" t="str">
         <v>ООО</v>
       </c>
       <c r="C1082" t="str">
-        <v>7725781700</v>
+        <v>6230126270</v>
       </c>
       <c r="D1082" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -25284,18 +25284,18 @@
         <v>РФ</v>
       </c>
       <c r="G1082">
-        <v>47035</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>ТехноТерм-Саратов</v>
+        <v>СмартЭмСис</v>
       </c>
       <c r="B1083" t="str">
         <v>ООО</v>
       </c>
       <c r="C1083" t="str">
-        <v>6453132158</v>
+        <v>7725781700</v>
       </c>
       <c r="D1083" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -25307,18 +25307,18 @@
         <v>РФ</v>
       </c>
       <c r="G1083">
-        <v>46983</v>
+        <v>47035</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>Энергия М</v>
+        <v>ТехноТерм-Саратов</v>
       </c>
       <c r="B1084" t="str">
         <v>ООО</v>
       </c>
       <c r="C1084" t="str">
-        <v>7736365613</v>
+        <v>6453132158</v>
       </c>
       <c r="D1084" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -25330,30 +25330,30 @@
         <v>РФ</v>
       </c>
       <c r="G1084">
-        <v>46941</v>
+        <v>46983</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>ЛП-Трим</v>
+        <v>Энергия М</v>
       </c>
       <c r="B1085" t="str">
         <v>ООО</v>
       </c>
       <c r="C1085" t="str">
-        <v>6321173535</v>
+        <v>7736365613</v>
       </c>
       <c r="D1085" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1085" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1085" t="str">
         <v>РФ</v>
       </c>
       <c r="G1085">
-        <v>46877</v>
+        <v>46941</v>
       </c>
     </row>
     <row r="1086">
@@ -25367,16 +25367,16 @@
         <v>6321173535</v>
       </c>
       <c r="D1086" t="str">
-        <v>EADAS</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1086" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1086" t="str">
         <v>РФ</v>
       </c>
       <c r="G1086">
-        <v>46478</v>
+        <v>46877</v>
       </c>
     </row>
     <row r="1087">
@@ -25390,44 +25390,44 @@
         <v>6321173535</v>
       </c>
       <c r="D1087" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1087" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1087" t="str">
         <v>РФ</v>
       </c>
       <c r="G1087">
-        <v>46877</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>“TRIDAN” Ltd.</v>
+        <v>ЛП-Трим</v>
       </c>
       <c r="B1088" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1088" t="str">
-        <v/>
+        <v>6321173535</v>
       </c>
       <c r="D1088" t="str">
-        <v>UKAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1088" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1088" t="str">
-        <v>Bulgaria</v>
+        <v>РФ</v>
       </c>
       <c r="G1088">
-        <v>46907</v>
+        <v>46877</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>VOYNOV LTD</v>
+        <v>“TRIDAN” Ltd.</v>
       </c>
       <c r="B1089" t="str">
         <v/>
@@ -25445,7 +25445,7 @@
         <v>Bulgaria</v>
       </c>
       <c r="G1089">
-        <v>46857</v>
+        <v>46907</v>
       </c>
     </row>
     <row r="1090">
@@ -25462,18 +25462,18 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1090" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1090" t="str">
         <v>Bulgaria</v>
       </c>
       <c r="G1090">
-        <v>46899</v>
+        <v>46857</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>ADS Sea center LTD.</v>
+        <v>VOYNOV LTD</v>
       </c>
       <c r="B1091" t="str">
         <v/>
@@ -25485,36 +25485,36 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1091" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1091" t="str">
         <v>Bulgaria</v>
       </c>
       <c r="G1091">
-        <v>46824</v>
+        <v>46899</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>Инновационно-внедренческий центр радиационной стерилизации Уральского Федерального Университета имени первого Президента России Б.Н.Ельцина</v>
+        <v>ADS Sea center LTD.</v>
       </c>
       <c r="B1092" t="str">
-        <v>ФГАОУ ВО</v>
+        <v/>
       </c>
       <c r="C1092" t="str">
-        <v>6660003190</v>
+        <v/>
       </c>
       <c r="D1092" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1092" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1092" t="str">
-        <v>РФ</v>
+        <v>Bulgaria</v>
       </c>
       <c r="G1092">
-        <v>46898</v>
+        <v>46824</v>
       </c>
     </row>
     <row r="1093">
@@ -25528,7 +25528,7 @@
         <v>6660003190</v>
       </c>
       <c r="D1093" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1093" t="str">
         <v>ГОСТ ISO 13485-2017</v>
@@ -25542,25 +25542,25 @@
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>КАМА</v>
+        <v>Инновационно-внедренческий центр радиационной стерилизации Уральского Федерального Университета имени первого Президента России Б.Н.Ельцина</v>
       </c>
       <c r="B1094" t="str">
-        <v>АО</v>
+        <v>ФГАОУ ВО</v>
       </c>
       <c r="C1094" t="str">
-        <v>1650404549</v>
+        <v>6660003190</v>
       </c>
       <c r="D1094" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1094" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1094" t="str">
         <v>РФ</v>
       </c>
       <c r="G1094">
-        <v>46901</v>
+        <v>46898</v>
       </c>
     </row>
     <row r="1095">
@@ -25574,7 +25574,7 @@
         <v>1650404549</v>
       </c>
       <c r="D1095" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1095" t="str">
         <v>ISO 9001:2015</v>
@@ -25597,39 +25597,39 @@
         <v>1650404549</v>
       </c>
       <c r="D1096" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1096" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1096" t="str">
         <v>РФ</v>
       </c>
       <c r="G1096">
-        <v>46902</v>
+        <v>46901</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>Интэко Тюбинг</v>
+        <v>КАМА</v>
       </c>
       <c r="B1097" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1097" t="str">
-        <v>1646043628</v>
+        <v>1650404549</v>
       </c>
       <c r="D1097" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1097" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1097" t="str">
         <v>РФ</v>
       </c>
       <c r="G1097">
-        <v>46982</v>
+        <v>46902</v>
       </c>
     </row>
     <row r="1098">
@@ -25643,7 +25643,7 @@
         <v>1646043628</v>
       </c>
       <c r="D1098" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1098" t="str">
         <v>ISO 9001:2015</v>
@@ -25663,19 +25663,19 @@
         <v>ООО</v>
       </c>
       <c r="C1099" t="str">
-        <v>1646043629</v>
+        <v>1646043628</v>
       </c>
       <c r="D1099" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1099" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1099" t="str">
         <v>РФ</v>
       </c>
       <c r="G1099">
-        <v>46944</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1100">
@@ -25689,39 +25689,39 @@
         <v>1646043629</v>
       </c>
       <c r="D1100" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1100" t="str">
-        <v>S.QS.07-2024</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1100" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1100" t="str">
-        <v/>
+      <c r="G1100">
+        <v>46944</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>Никольская Консалтинг</v>
+        <v>Интэко Тюбинг</v>
       </c>
       <c r="B1101" t="str">
         <v>ООО</v>
       </c>
       <c r="C1101" t="str">
-        <v>9710096350</v>
+        <v>1646043629</v>
       </c>
       <c r="D1101" t="str">
-        <v>IAS (IAF)</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1101" t="str">
-        <v>ISO 37001:2016</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1101" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1101">
-        <v>46935</v>
+      <c r="G1101" t="str">
+        <v/>
       </c>
     </row>
     <row r="1102">
@@ -25735,7 +25735,7 @@
         <v>9710096350</v>
       </c>
       <c r="D1102" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1102" t="str">
         <v>ISO 37001:2016</v>
@@ -25758,16 +25758,16 @@
         <v>9710096350</v>
       </c>
       <c r="D1103" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1103" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 37001:2016</v>
       </c>
       <c r="F1103" t="str">
         <v>РФ</v>
       </c>
       <c r="G1103">
-        <v>47105</v>
+        <v>46935</v>
       </c>
     </row>
     <row r="1104">
@@ -25781,7 +25781,7 @@
         <v>9710096350</v>
       </c>
       <c r="D1104" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1104" t="str">
         <v>ISO/IEC 27001:2022</v>
@@ -25807,7 +25807,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1105" t="str">
-        <v>ГОСТ Р ИСО/МЭК 27001-2021</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1105" t="str">
         <v>РФ</v>
@@ -25818,25 +25818,25 @@
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>Майнинг Элемент</v>
+        <v>Никольская Консалтинг</v>
       </c>
       <c r="B1106" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1106" t="str">
-        <v>7810982090</v>
+        <v>9710096350</v>
       </c>
       <c r="D1106" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1106" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО/МЭК 27001-2021</v>
       </c>
       <c r="F1106" t="str">
         <v>РФ</v>
       </c>
       <c r="G1106">
-        <v>47025</v>
+        <v>47105</v>
       </c>
     </row>
     <row r="1107">
@@ -25850,7 +25850,7 @@
         <v>7810982090</v>
       </c>
       <c r="D1107" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1107" t="str">
         <v>ISO 9001:2015</v>
@@ -25864,48 +25864,48 @@
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>Гротекс</v>
+        <v>Майнинг Элемент</v>
       </c>
       <c r="B1108" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1108" t="str">
-        <v>7814459396</v>
+        <v>7810982090</v>
       </c>
       <c r="D1108" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1108" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1108" t="str">
         <v>РФ</v>
       </c>
       <c r="G1108">
-        <v>46913</v>
+        <v>47025</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>НПП КуйбышевТелеком - Метрология</v>
+        <v>Гротекс</v>
       </c>
       <c r="B1109" t="str">
         <v>ООО</v>
       </c>
       <c r="C1109" t="str">
-        <v>6312102369</v>
+        <v>7814459396</v>
       </c>
       <c r="D1109" t="str">
-        <v>ESYD (IAF)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1109" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1109" t="str">
         <v>РФ</v>
       </c>
       <c r="G1109">
-        <v>46958</v>
+        <v>46913</v>
       </c>
     </row>
     <row r="1110">
@@ -25922,7 +25922,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1110" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1110" t="str">
         <v>РФ</v>
@@ -25945,13 +25945,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1111" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1111" t="str">
         <v>РФ</v>
       </c>
       <c r="G1111">
-        <v>46960</v>
+        <v>46958</v>
       </c>
     </row>
     <row r="1112">
@@ -25965,16 +25965,16 @@
         <v>6312102369</v>
       </c>
       <c r="D1112" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1112" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1112" t="str">
         <v>РФ</v>
       </c>
       <c r="G1112">
-        <v>46958</v>
+        <v>46960</v>
       </c>
     </row>
     <row r="1113">
@@ -25991,7 +25991,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1113" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1113" t="str">
         <v>РФ</v>
@@ -26014,13 +26014,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1114" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1114" t="str">
         <v>РФ</v>
       </c>
       <c r="G1114">
-        <v>46960</v>
+        <v>46958</v>
       </c>
     </row>
     <row r="1115">
@@ -26034,16 +26034,16 @@
         <v>6312102369</v>
       </c>
       <c r="D1115" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1115" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1115" t="str">
         <v>РФ</v>
       </c>
       <c r="G1115">
-        <v>47039</v>
+        <v>46960</v>
       </c>
     </row>
     <row r="1116">
@@ -26054,19 +26054,19 @@
         <v>ООО</v>
       </c>
       <c r="C1116" t="str">
-        <v>6312102370</v>
+        <v>6312102369</v>
       </c>
       <c r="D1116" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1116" t="str">
-        <v>S.QS.07-2024</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1116" t="str">
         <v>РФ</v>
       </c>
       <c r="G1116">
-        <v>46819</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1117">
@@ -26080,39 +26080,39 @@
         <v>6312102370</v>
       </c>
       <c r="D1117" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1117" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1117" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1117" t="str">
-        <v/>
+      <c r="G1117">
+        <v>46819</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>"Tengri Tyres"</v>
+        <v>НПП КуйбышевТелеком - Метрология</v>
       </c>
       <c r="B1118" t="str">
-        <v>ТОО</v>
+        <v>ООО</v>
       </c>
       <c r="C1118" t="str">
-        <v>201040014370</v>
+        <v>6312102370</v>
       </c>
       <c r="D1118" t="str">
-        <v>UKAS (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1118" t="str">
-        <v>IATF 16949:2016</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1118" t="str">
-        <v>KZ</v>
-      </c>
-      <c r="G1118">
-        <v>46949</v>
+        <v>РФ</v>
+      </c>
+      <c r="G1118" t="str">
+        <v/>
       </c>
     </row>
     <row r="1119">
@@ -26126,39 +26126,39 @@
         <v>201040014370</v>
       </c>
       <c r="D1119" t="str">
-        <v>ESYD (IAF)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1119" t="str">
-        <v>ISO 45001:2018</v>
+        <v>IATF 16949:2016</v>
       </c>
       <c r="F1119" t="str">
         <v>KZ</v>
       </c>
       <c r="G1119">
-        <v>47110</v>
+        <v>46949</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>ГЕРС Технолоджи</v>
+        <v>"Tengri Tyres"</v>
       </c>
       <c r="B1120" t="str">
-        <v>ООО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1120" t="str">
-        <v>5050085880</v>
+        <v>201040014370</v>
       </c>
       <c r="D1120" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1120" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1120" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1120">
-        <v>46991</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="1121">
@@ -26172,7 +26172,7 @@
         <v>5050085880</v>
       </c>
       <c r="D1121" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1121" t="str">
         <v>ISO 9001:2015</v>
@@ -26186,48 +26186,48 @@
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>"Учебно-методический центр" Федеральной службы по экологическому, технологическому и атомному надзору</v>
+        <v>ГЕРС Технолоджи</v>
       </c>
       <c r="B1122" t="str">
-        <v>ФГБОУ ДПО</v>
+        <v>ООО</v>
       </c>
       <c r="C1122" t="str">
-        <v>7723320277</v>
+        <v>5050085880</v>
       </c>
       <c r="D1122" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1122" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1122" t="str">
         <v>РФ</v>
       </c>
       <c r="G1122">
-        <v>46952</v>
+        <v>46991</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>ЭЛЕКТРОПИТАНИЕ</v>
+        <v>"Учебно-методический центр" Федеральной службы по экологическому, технологическому и атомному надзору</v>
       </c>
       <c r="B1123" t="str">
-        <v>ООО НПЦ</v>
+        <v>ФГБОУ ДПО</v>
       </c>
       <c r="C1123" t="str">
-        <v>583503532636</v>
+        <v>7723320277</v>
       </c>
       <c r="D1123" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1123" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1123" t="str">
         <v>РФ</v>
       </c>
       <c r="G1123">
-        <v>46948</v>
+        <v>46952</v>
       </c>
     </row>
     <row r="1124">
@@ -26241,7 +26241,7 @@
         <v>583503532636</v>
       </c>
       <c r="D1124" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1124" t="str">
         <v>ISO 9001:2015</v>
@@ -26255,16 +26255,16 @@
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>АМПРЕСС</v>
+        <v>ЭЛЕКТРОПИТАНИЕ</v>
       </c>
       <c r="B1125" t="str">
-        <v>ООО</v>
+        <v>ООО НПЦ</v>
       </c>
       <c r="C1125" t="str">
-        <v>632127272251</v>
+        <v>583503532636</v>
       </c>
       <c r="D1125" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1125" t="str">
         <v>ISO 9001:2015</v>
@@ -26287,7 +26287,7 @@
         <v>632127272251</v>
       </c>
       <c r="D1126" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1126" t="str">
         <v>ISO 9001:2015</v>
@@ -26307,19 +26307,19 @@
         <v>ООО</v>
       </c>
       <c r="C1127" t="str">
-        <v>6382061691</v>
+        <v>632127272251</v>
       </c>
       <c r="D1127" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1127" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1127" t="str">
         <v>РФ</v>
       </c>
       <c r="G1127">
-        <v>46212</v>
+        <v>46948</v>
       </c>
     </row>
     <row r="1128">
@@ -26333,62 +26333,62 @@
         <v>6382061691</v>
       </c>
       <c r="D1128" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1128" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1128" t="str">
         <v>РФ</v>
       </c>
       <c r="G1128">
-        <v>47010</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>Научно-производственная фирма "Моссар"</v>
+        <v>АМПРЕСС</v>
       </c>
       <c r="B1129" t="str">
         <v>ООО</v>
       </c>
       <c r="C1129" t="str">
-        <v>6454073547</v>
+        <v>6382061691</v>
       </c>
       <c r="D1129" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1129" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1129" t="str">
         <v>РФ</v>
       </c>
       <c r="G1129">
-        <v>47166</v>
+        <v>47010</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>Научно-производственная фирма "БИОСС"</v>
+        <v>Научно-производственная фирма "Моссар"</v>
       </c>
       <c r="B1130" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1130" t="str">
-        <v>7735126570</v>
+        <v>6454073547</v>
       </c>
       <c r="D1130" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1130" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1130" t="str">
         <v>РФ</v>
       </c>
       <c r="G1130">
-        <v>47039</v>
+        <v>47166</v>
       </c>
     </row>
     <row r="1131">
@@ -26402,7 +26402,7 @@
         <v>7735126570</v>
       </c>
       <c r="D1131" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1131" t="str">
         <v>ISO 13485:2016</v>
@@ -26425,39 +26425,39 @@
         <v>7735126570</v>
       </c>
       <c r="D1132" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1132" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1132" t="str">
         <v>РФ</v>
       </c>
       <c r="G1132">
-        <v>47063</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>РСтартер</v>
+        <v>Научно-производственная фирма "БИОСС"</v>
       </c>
       <c r="B1133" t="str">
         <v>АО</v>
       </c>
       <c r="C1133" t="str">
-        <v>5258156241</v>
+        <v>7735126570</v>
       </c>
       <c r="D1133" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1133" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1133" t="str">
         <v>РФ</v>
       </c>
       <c r="G1133">
-        <v>46177</v>
+        <v>47063</v>
       </c>
     </row>
     <row r="1134">
@@ -26471,16 +26471,16 @@
         <v>5258156241</v>
       </c>
       <c r="D1134" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1134" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1134" t="str">
         <v>РФ</v>
       </c>
       <c r="G1134">
-        <v>46982</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="1135">
@@ -26494,16 +26494,16 @@
         <v>5258156241</v>
       </c>
       <c r="D1135" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1135" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1135" t="str">
         <v>РФ</v>
       </c>
       <c r="G1135">
-        <v>46983</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1136">
@@ -26517,7 +26517,7 @@
         <v>5258156241</v>
       </c>
       <c r="D1136" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1136" t="str">
         <v>ISO 9001:2015</v>
@@ -26531,82 +26531,82 @@
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>ЕТС Трейд</v>
+        <v>РСтартер</v>
       </c>
       <c r="B1137" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1137" t="str">
-        <v>7224069315</v>
+        <v>5258156241</v>
       </c>
       <c r="D1137" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1137" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1137" t="str">
         <v>РФ</v>
       </c>
       <c r="G1137">
-        <v>46996</v>
+        <v>46983</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>НПП Тасма</v>
+        <v>ЕТС Трейд</v>
       </c>
       <c r="B1138" t="str">
         <v>ООО</v>
       </c>
       <c r="C1138" t="str">
-        <v>1658105396</v>
+        <v>7224069315</v>
       </c>
       <c r="D1138" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1138" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1138" t="str">
         <v>РФ</v>
       </c>
       <c r="G1138">
-        <v>46998</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>Завод Красный Якорь</v>
+        <v>НПП Тасма</v>
       </c>
       <c r="B1139" t="str">
-        <v>ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1139" t="str">
-        <v>5257005049</v>
+        <v>1658105396</v>
       </c>
       <c r="D1139" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1139" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1139" t="str">
         <v>РФ</v>
       </c>
       <c r="G1139">
-        <v>46602</v>
+        <v>46998</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>Морское грузовое бюро</v>
+        <v>Завод Красный Якорь</v>
       </c>
       <c r="B1140" t="str">
-        <v>ООО</v>
+        <v>ПАО</v>
       </c>
       <c r="C1140" t="str">
-        <v>4705063303</v>
+        <v>5257005049</v>
       </c>
       <c r="D1140" t="str">
         <v>ESYD (IAF)</v>
@@ -26618,18 +26618,18 @@
         <v>РФ</v>
       </c>
       <c r="G1140">
-        <v>46649</v>
+        <v>46602</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>GRETIMYBE</v>
+        <v>Морское грузовое бюро</v>
       </c>
       <c r="B1141" t="str">
-        <v>UAB</v>
+        <v>ООО</v>
       </c>
       <c r="C1141" t="str">
-        <v>LT 415578811</v>
+        <v>4705063303</v>
       </c>
       <c r="D1141" t="str">
         <v>ESYD (IAF)</v>
@@ -26638,21 +26638,21 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1141" t="str">
-        <v>Lithuania</v>
+        <v>РФ</v>
       </c>
       <c r="G1141">
-        <v>46652</v>
+        <v>46649</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>Санрайз</v>
+        <v>GRETIMYBE</v>
       </c>
       <c r="B1142" t="str">
-        <v>ООО</v>
+        <v>UAB</v>
       </c>
       <c r="C1142" t="str">
-        <v>7825449671</v>
+        <v>LT 415578811</v>
       </c>
       <c r="D1142" t="str">
         <v>ESYD (IAF)</v>
@@ -26664,7 +26664,7 @@
         <v>Lithuania</v>
       </c>
       <c r="G1142">
-        <v>46897</v>
+        <v>46652</v>
       </c>
     </row>
     <row r="1143">
@@ -26681,36 +26681,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1143" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1143" t="str">
-        <v>РФ</v>
+        <v>Lithuania</v>
       </c>
       <c r="G1143">
-        <v>46899</v>
+        <v>46897</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>Архангельский фанерный завод</v>
+        <v>Санрайз</v>
       </c>
       <c r="B1144" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1144" t="str">
-        <v>2903004722</v>
+        <v>7825449671</v>
       </c>
       <c r="D1144" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1144" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1144" t="str">
         <v>РФ</v>
       </c>
       <c r="G1144">
-        <v>46750</v>
+        <v>46899</v>
       </c>
     </row>
     <row r="1145">
@@ -26727,7 +26727,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1145" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1145" t="str">
         <v>РФ</v>
@@ -26750,7 +26750,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1146" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1146" t="str">
         <v>РФ</v>
@@ -26761,19 +26761,19 @@
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>Академия бизнеса</v>
+        <v>Архангельский фанерный завод</v>
       </c>
       <c r="B1147" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1147" t="str">
-        <v>7801499948</v>
+        <v>2903004722</v>
       </c>
       <c r="D1147" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1147" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1147" t="str">
         <v>РФ</v>
@@ -26784,13 +26784,13 @@
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>ИЦ "Технохим"</v>
+        <v>Академия бизнеса</v>
       </c>
       <c r="B1148" t="str">
-        <v>ЗАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1148" t="str">
-        <v>7813348421</v>
+        <v>7801499948</v>
       </c>
       <c r="D1148" t="str">
         <v>ESYD (IAF)</v>
@@ -26802,18 +26802,18 @@
         <v>РФ</v>
       </c>
       <c r="G1148">
-        <v>46450</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>НПП "СЗГП"</v>
+        <v>ИЦ "Технохим"</v>
       </c>
       <c r="B1149" t="str">
         <v>ЗАО</v>
       </c>
       <c r="C1149" t="str">
-        <v>7813385303</v>
+        <v>7813348421</v>
       </c>
       <c r="D1149" t="str">
         <v>ESYD (IAF)</v>
@@ -26825,18 +26825,18 @@
         <v>РФ</v>
       </c>
       <c r="G1149">
-        <v>46775</v>
+        <v>46450</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>Сыктывкарский ликеро-водочный завод</v>
+        <v>НПП "СЗГП"</v>
       </c>
       <c r="B1150" t="str">
-        <v>АО</v>
+        <v>ЗАО</v>
       </c>
       <c r="C1150" t="str">
-        <v>1101205623</v>
+        <v>7813385303</v>
       </c>
       <c r="D1150" t="str">
         <v>ESYD (IAF)</v>
@@ -26848,7 +26848,7 @@
         <v>РФ</v>
       </c>
       <c r="G1150">
-        <v>46906</v>
+        <v>46775</v>
       </c>
     </row>
     <row r="1151">
@@ -26865,47 +26865,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1151" t="str">
-        <v>ISO 22000:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1151" t="str">
         <v>РФ</v>
       </c>
       <c r="G1151">
-        <v>46909</v>
+        <v>46906</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>Ижевский электромеханический завод "Купол"</v>
+        <v>Сыктывкарский ликеро-водочный завод</v>
       </c>
       <c r="B1152" t="str">
         <v>АО</v>
       </c>
       <c r="C1152" t="str">
-        <v>1831083343</v>
+        <v>1101205623</v>
       </c>
       <c r="D1152" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1152" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 22000:2018</v>
       </c>
       <c r="F1152" t="str">
         <v>РФ</v>
       </c>
       <c r="G1152">
-        <v>46980</v>
+        <v>46909</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>Арзамасский филиал ООО "Сен-Гобен Строительная Продукция Рус"</v>
+        <v>Ижевский электромеханический завод "Купол"</v>
       </c>
       <c r="B1153" t="str">
-        <v/>
+        <v>АО</v>
       </c>
       <c r="C1153" t="str">
-        <v>5011020537</v>
+        <v>1831083343</v>
       </c>
       <c r="D1153" t="str">
         <v>ESYD (IAF)</v>
@@ -26917,18 +26917,18 @@
         <v>РФ</v>
       </c>
       <c r="G1153">
-        <v>47086</v>
+        <v>46980</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>Белэнергомаш- БЗЭМ</v>
+        <v>Арзамасский филиал ООО "Сен-Гобен Строительная Продукция Рус"</v>
       </c>
       <c r="B1154" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1154" t="str">
-        <v>3123315768</v>
+        <v>5011020537</v>
       </c>
       <c r="D1154" t="str">
         <v>ESYD (IAF)</v>
@@ -26940,7 +26940,7 @@
         <v>РФ</v>
       </c>
       <c r="G1154">
-        <v>46409</v>
+        <v>47086</v>
       </c>
     </row>
     <row r="1155">
@@ -26957,13 +26957,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1155" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1155" t="str">
         <v>РФ</v>
       </c>
       <c r="G1155">
-        <v>46411</v>
+        <v>46409</v>
       </c>
     </row>
     <row r="1156">
@@ -26980,7 +26980,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1156" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1156" t="str">
         <v>РФ</v>
@@ -26991,25 +26991,25 @@
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>Калужский научно-исследовательский радиотехнический институт</v>
+        <v>Белэнергомаш- БЗЭМ</v>
       </c>
       <c r="B1157" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1157" t="str">
-        <v>4007017378</v>
+        <v>3123315768</v>
       </c>
       <c r="D1157" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1157" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1157" t="str">
         <v>РФ</v>
       </c>
       <c r="G1157">
-        <v>46317</v>
+        <v>46411</v>
       </c>
     </row>
     <row r="1158">
@@ -27026,47 +27026,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1158" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1158" t="str">
         <v>РФ</v>
       </c>
       <c r="G1158">
-        <v>46433</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>НПП "БАСЭТ"</v>
+        <v>Калужский научно-исследовательский радиотехнический институт</v>
       </c>
       <c r="B1159" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1159" t="str">
-        <v>269001177</v>
+        <v>4007017378</v>
       </c>
       <c r="D1159" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1159" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1159" t="str">
         <v>РФ</v>
       </c>
       <c r="G1159">
-        <v>46488</v>
+        <v>46433</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>НПП "Петролайн-А"</v>
+        <v>НПП "БАСЭТ"</v>
       </c>
       <c r="B1160" t="str">
         <v>ООО</v>
       </c>
       <c r="C1160" t="str">
-        <v>1650081440</v>
+        <v>269001177</v>
       </c>
       <c r="D1160" t="str">
         <v>ESYD (IAF)</v>
@@ -27078,18 +27078,18 @@
         <v>РФ</v>
       </c>
       <c r="G1160">
-        <v>46165</v>
+        <v>46488</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>ООО "Энергоспецмонтаж"</v>
+        <v>НПП "Петролайн-А"</v>
       </c>
       <c r="B1161" t="str">
         <v>ООО</v>
       </c>
       <c r="C1161" t="str">
-        <v>1837006602</v>
+        <v>1650081440</v>
       </c>
       <c r="D1161" t="str">
         <v>ESYD (IAF)</v>
@@ -27101,18 +27101,18 @@
         <v>РФ</v>
       </c>
       <c r="G1161">
-        <v>46214</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>НИКИМТ-АТОМСТРОЙ</v>
+        <v>ООО "Энергоспецмонтаж"</v>
       </c>
       <c r="B1162" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1162" t="str">
-        <v>7715719854</v>
+        <v>1837006602</v>
       </c>
       <c r="D1162" t="str">
         <v>ESYD (IAF)</v>
@@ -27124,7 +27124,7 @@
         <v>РФ</v>
       </c>
       <c r="G1162">
-        <v>46244</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="1163">
@@ -27141,13 +27141,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1163" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1163" t="str">
         <v>РФ</v>
       </c>
       <c r="G1163">
-        <v>46265</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="1164">
@@ -27164,70 +27164,70 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1164" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1164" t="str">
         <v>РФ</v>
       </c>
       <c r="G1164">
-        <v>46326</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>Карбофер Метсервис</v>
+        <v>НИКИМТ-АТОМСТРОЙ</v>
       </c>
       <c r="B1165" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1165" t="str">
-        <v>3662148389</v>
+        <v>7715719854</v>
       </c>
       <c r="D1165" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1165" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1165" t="str">
         <v>РФ</v>
       </c>
       <c r="G1165">
-        <v>46229</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>Белая Дача Волга</v>
+        <v>Карбофер Метсервис</v>
       </c>
       <c r="B1166" t="str">
         <v>ООО</v>
       </c>
       <c r="C1166" t="str">
-        <v>5027307207</v>
+        <v>3662148389</v>
       </c>
       <c r="D1166" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1166" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1166" t="str">
         <v>РФ</v>
       </c>
       <c r="G1166">
-        <v>46212</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>Воплощение</v>
+        <v>Белая Дача Волга</v>
       </c>
       <c r="B1167" t="str">
         <v>ООО</v>
       </c>
       <c r="C1167" t="str">
-        <v>7106077126</v>
+        <v>5027307207</v>
       </c>
       <c r="D1167" t="str">
         <v>ESYD (IAF)</v>
@@ -27239,18 +27239,18 @@
         <v>РФ</v>
       </c>
       <c r="G1167">
-        <v>46200</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>Красный маяк</v>
+        <v>Воплощение</v>
       </c>
       <c r="B1168" t="str">
         <v>ООО</v>
       </c>
       <c r="C1168" t="str">
-        <v>7609027393</v>
+        <v>7106077126</v>
       </c>
       <c r="D1168" t="str">
         <v>ESYD (IAF)</v>
@@ -27262,18 +27262,18 @@
         <v>РФ</v>
       </c>
       <c r="G1168">
-        <v>46290</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>АПК Астраханский</v>
+        <v>Красный маяк</v>
       </c>
       <c r="B1169" t="str">
         <v>ООО</v>
       </c>
       <c r="C1169" t="str">
-        <v>3023008925</v>
+        <v>7609027393</v>
       </c>
       <c r="D1169" t="str">
         <v>ESYD (IAF)</v>
@@ -27285,7 +27285,7 @@
         <v>РФ</v>
       </c>
       <c r="G1169">
-        <v>46284</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="1170">
@@ -27302,7 +27302,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1170" t="str">
-        <v>GRASP</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1170" t="str">
         <v>РФ</v>
@@ -27325,70 +27325,70 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1171" t="str">
-        <v>FSSC 22000</v>
+        <v>GRASP</v>
       </c>
       <c r="F1171" t="str">
         <v>РФ</v>
       </c>
       <c r="G1171">
-        <v>46311</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>НУЦ "Качество"</v>
+        <v>АПК Астраханский</v>
       </c>
       <c r="B1172" t="str">
         <v>ООО</v>
       </c>
       <c r="C1172" t="str">
-        <v>7715552355</v>
+        <v>3023008925</v>
       </c>
       <c r="D1172" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1172" t="str">
-        <v>ISO 9001:2015</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1172" t="str">
         <v>РФ</v>
       </c>
       <c r="G1172">
-        <v>46228</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>BLESS S.R.</v>
+        <v>НУЦ "Качество"</v>
       </c>
       <c r="B1173" t="str">
         <v>ООО</v>
       </c>
       <c r="C1173" t="str">
-        <v>309422741</v>
+        <v>7715552355</v>
       </c>
       <c r="D1173" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1173" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1173" t="str">
-        <v>UZ</v>
-      </c>
-      <c r="G1173" t="str">
-        <v>Сертификат еще не выдан</v>
+        <v>РФ</v>
+      </c>
+      <c r="G1173">
+        <v>46228</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>Иотова А.А.</v>
+        <v>BLESS S.R.</v>
       </c>
       <c r="B1174" t="str">
-        <v>ИП</v>
+        <v>ООО</v>
       </c>
       <c r="C1174" t="str">
-        <v>500702017601</v>
+        <v>309422741</v>
       </c>
       <c r="D1174" t="str">
         <v>ESYD (IAF)</v>
@@ -27397,21 +27397,21 @@
         <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1174" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1174">
-        <v>46247</v>
+        <v>UZ</v>
+      </c>
+      <c r="G1174" t="str">
+        <v>Сертификат еще не выдан</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>Сунгатов Разиль</v>
+        <v>Иотова А.А.</v>
       </c>
       <c r="B1175" t="str">
         <v>ИП</v>
       </c>
       <c r="C1175" t="str">
-        <v>300902421774</v>
+        <v>500702017601</v>
       </c>
       <c r="D1175" t="str">
         <v>ESYD (IAF)</v>
@@ -27423,18 +27423,18 @@
         <v>РФ</v>
       </c>
       <c r="G1175">
-        <v>46304</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>Веселый агроном</v>
+        <v>Сунгатов Разиль</v>
       </c>
       <c r="B1176" t="str">
-        <v>ООО</v>
+        <v>ИП</v>
       </c>
       <c r="C1176" t="str">
-        <v>5007082611</v>
+        <v>300902421774</v>
       </c>
       <c r="D1176" t="str">
         <v>ESYD (IAF)</v>
@@ -27446,41 +27446,41 @@
         <v>РФ</v>
       </c>
       <c r="G1176">
-        <v>46289</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>"Пятигорский "Импульс"</v>
+        <v>Веселый агроном</v>
       </c>
       <c r="B1177" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1177" t="str">
-        <v>2632005656</v>
+        <v>5007082611</v>
       </c>
       <c r="D1177" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1177" t="str">
-        <v>ISO 9001:2015</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1177" t="str">
         <v>РФ</v>
       </c>
       <c r="G1177">
-        <v>46341</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>"Швабе"</v>
+        <v>"Пятигорский "Импульс"</v>
       </c>
       <c r="B1178" t="str">
-        <v>АО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1178" t="str">
-        <v>7717671799</v>
+        <v>2632005656</v>
       </c>
       <c r="D1178" t="str">
         <v>ESYD (IAF)</v>
@@ -27492,18 +27492,18 @@
         <v>РФ</v>
       </c>
       <c r="G1178">
-        <v>46320</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>"ПИТЕРАТОММАШ"</v>
+        <v>"Швабе"</v>
       </c>
       <c r="B1179" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1179" t="str">
-        <v>7805658638</v>
+        <v>7717671799</v>
       </c>
       <c r="D1179" t="str">
         <v>ESYD (IAF)</v>
@@ -27515,18 +27515,18 @@
         <v>РФ</v>
       </c>
       <c r="G1179">
-        <v>46422</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>"Морской лабораторый комплекс"</v>
+        <v>"ПИТЕРАТОММАШ"</v>
       </c>
       <c r="B1180" t="str">
         <v>ООО</v>
       </c>
       <c r="C1180" t="str">
-        <v>7816640696</v>
+        <v>7805658638</v>
       </c>
       <c r="D1180" t="str">
         <v>ESYD (IAF)</v>
@@ -27538,64 +27538,64 @@
         <v>РФ</v>
       </c>
       <c r="G1180">
-        <v>46409</v>
+        <v>46422</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>«Байкальская энергетическая компания»</v>
+        <v>"Морской лабораторый комплекс"</v>
       </c>
       <c r="B1181" t="str">
         <v>ООО</v>
       </c>
       <c r="C1181" t="str">
-        <v>3808229774</v>
+        <v>7816640696</v>
       </c>
       <c r="D1181" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1181" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1181" t="str">
         <v>РФ</v>
       </c>
       <c r="G1181">
-        <v>46375</v>
+        <v>46409</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>"Транснефть-Диаскан"</v>
+        <v>«Байкальская энергетическая компания»</v>
       </c>
       <c r="B1182" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1182" t="str">
-        <v>5072703668</v>
+        <v>3808229774</v>
       </c>
       <c r="D1182" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1182" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1182" t="str">
         <v>РФ</v>
       </c>
       <c r="G1182">
-        <v>46482</v>
+        <v>46375</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>"С-плюс"</v>
+        <v>"Транснефть-Диаскан"</v>
       </c>
       <c r="B1183" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1183" t="str">
-        <v>7720325407</v>
+        <v>5072703668</v>
       </c>
       <c r="D1183" t="str">
         <v>ESYD (IAF)</v>
@@ -27607,18 +27607,18 @@
         <v>РФ</v>
       </c>
       <c r="G1183">
-        <v>46674</v>
+        <v>46482</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>"ЦНИИМФ"</v>
+        <v>"С-плюс"</v>
       </c>
       <c r="B1184" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1184" t="str">
-        <v>7815001288</v>
+        <v>7720325407</v>
       </c>
       <c r="D1184" t="str">
         <v>ESYD (IAF)</v>
@@ -27630,18 +27630,18 @@
         <v>РФ</v>
       </c>
       <c r="G1184">
-        <v>46514</v>
+        <v>46674</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>"ВЗПП - Микрон"</v>
+        <v>"ЦНИИМФ"</v>
       </c>
       <c r="B1185" t="str">
         <v>АО</v>
       </c>
       <c r="C1185" t="str">
-        <v>3661020890</v>
+        <v>7815001288</v>
       </c>
       <c r="D1185" t="str">
         <v>ESYD (IAF)</v>
@@ -27653,18 +27653,18 @@
         <v>РФ</v>
       </c>
       <c r="G1185">
-        <v>46598</v>
+        <v>46514</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>Ostec Enterprise Ltd.</v>
+        <v>"ВЗПП - Микрон"</v>
       </c>
       <c r="B1186" t="str">
-        <v/>
+        <v>АО</v>
       </c>
       <c r="C1186" t="str">
-        <v>7731480806</v>
+        <v>3661020890</v>
       </c>
       <c r="D1186" t="str">
         <v>ESYD (IAF)</v>
@@ -27676,53 +27676,53 @@
         <v>РФ</v>
       </c>
       <c r="G1186">
-        <v>46593</v>
+        <v>46598</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="str">
-        <v>«Национальный расчетный депозитарий»</v>
+        <v>Ostec Enterprise Ltd.</v>
       </c>
       <c r="B1187" t="str">
-        <v>НКО АО</v>
+        <v/>
       </c>
       <c r="C1187" t="str">
-        <v>7702165310</v>
+        <v>7731480806</v>
       </c>
       <c r="D1187" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1187" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1187" t="str">
         <v>РФ</v>
       </c>
       <c r="G1187">
-        <v>46724</v>
+        <v>46593</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="str">
-        <v>"Томарина"</v>
+        <v>«Национальный расчетный депозитарий»</v>
       </c>
       <c r="B1188" t="str">
-        <v>ООО</v>
+        <v>НКО АО</v>
       </c>
       <c r="C1188" t="str">
-        <v>3000008541</v>
+        <v>7702165310</v>
       </c>
       <c r="D1188" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1188" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1188" t="str">
         <v>РФ</v>
       </c>
       <c r="G1188">
-        <v>46323</v>
+        <v>46724</v>
       </c>
     </row>
     <row r="1189">
@@ -27739,7 +27739,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1189" t="str">
-        <v>GRASP</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1189" t="str">
         <v>РФ</v>
@@ -27762,70 +27762,70 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1190" t="str">
-        <v>FSSC 22000</v>
+        <v>GRASP</v>
       </c>
       <c r="F1190" t="str">
         <v>РФ</v>
       </c>
       <c r="G1190">
-        <v>46744</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="str">
-        <v>"АгроНеро"</v>
+        <v>"Томарина"</v>
       </c>
       <c r="B1191" t="str">
         <v>ООО</v>
       </c>
       <c r="C1191" t="str">
-        <v>6140040847</v>
+        <v>3000008541</v>
       </c>
       <c r="D1191" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1191" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1191" t="str">
         <v>РФ</v>
       </c>
       <c r="G1191">
-        <v>46356</v>
+        <v>46744</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="str">
-        <v>"Новгородская аккумуляторная компания"</v>
+        <v>"АгроНеро"</v>
       </c>
       <c r="B1192" t="str">
         <v>ООО</v>
       </c>
       <c r="C1192" t="str">
-        <v>5321073271</v>
+        <v>6140040847</v>
       </c>
       <c r="D1192" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1192" t="str">
-        <v>ISO 9001:2015</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1192" t="str">
         <v>РФ</v>
       </c>
       <c r="G1192">
-        <v>46653</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="str">
-        <v>"Метровагонмаш"</v>
+        <v>"Новгородская аккумуляторная компания"</v>
       </c>
       <c r="B1193" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1193" t="str">
-        <v>5029006702</v>
+        <v>5321073271</v>
       </c>
       <c r="D1193" t="str">
         <v>ESYD (IAF)</v>
@@ -27837,18 +27837,18 @@
         <v>РФ</v>
       </c>
       <c r="G1193">
-        <v>46767</v>
+        <v>46653</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="str">
-        <v>"Клиническая стоматологическая поликлиника №12"</v>
+        <v>"Метровагонмаш"</v>
       </c>
       <c r="B1194" t="str">
-        <v>ГАУЗ</v>
+        <v>АО</v>
       </c>
       <c r="C1194" t="str">
-        <v>3448009146</v>
+        <v>5029006702</v>
       </c>
       <c r="D1194" t="str">
         <v>ESYD (IAF)</v>
@@ -27860,18 +27860,18 @@
         <v>РФ</v>
       </c>
       <c r="G1194">
-        <v>46888</v>
+        <v>46767</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="str">
-        <v>«Кримиан Фэмили Киль»</v>
+        <v>"Клиническая стоматологическая поликлиника №12"</v>
       </c>
       <c r="B1195" t="str">
-        <v>ООО</v>
+        <v>ГАУЗ</v>
       </c>
       <c r="C1195" t="str">
-        <v>2315230925</v>
+        <v>3448009146</v>
       </c>
       <c r="D1195" t="str">
         <v>ESYD (IAF)</v>
@@ -27883,18 +27883,18 @@
         <v>РФ</v>
       </c>
       <c r="G1195">
-        <v>46750</v>
+        <v>46888</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="str">
-        <v>Производственная компания "Велам-Рус"</v>
+        <v>«Кримиан Фэмили Киль»</v>
       </c>
       <c r="B1196" t="str">
         <v>ООО</v>
       </c>
       <c r="C1196" t="str">
-        <v>5258105399</v>
+        <v>2315230925</v>
       </c>
       <c r="D1196" t="str">
         <v>ESYD (IAF)</v>
@@ -27906,30 +27906,30 @@
         <v>РФ</v>
       </c>
       <c r="G1196">
-        <v>46775</v>
+        <v>46750</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="str">
-        <v>"Уралэлектромедь"</v>
+        <v>Производственная компания "Велам-Рус"</v>
       </c>
       <c r="B1197" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1197" t="str">
-        <v>6606003385</v>
+        <v>5258105399</v>
       </c>
       <c r="D1197" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1197" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1197" t="str">
         <v>РФ</v>
       </c>
       <c r="G1197">
-        <v>46380</v>
+        <v>46775</v>
       </c>
     </row>
     <row r="1198">
@@ -27946,47 +27946,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1198" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1198" t="str">
         <v>РФ</v>
       </c>
       <c r="G1198">
-        <v>46367</v>
+        <v>46380</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="str">
-        <v>«YETA»</v>
+        <v>"Уралэлектромедь"</v>
       </c>
       <c r="B1199" t="str">
-        <v>ТОО</v>
+        <v>АО</v>
       </c>
       <c r="C1199" t="str">
-        <v>221040014631</v>
+        <v>6606003385</v>
       </c>
       <c r="D1199" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1199" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1199" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1199">
-        <v>46733</v>
+        <v>46367</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="str">
-        <v>"Academy of Civil Aviation"</v>
+        <v>«YETA»</v>
       </c>
       <c r="B1200" t="str">
-        <v>JSC</v>
+        <v>ТОО</v>
       </c>
       <c r="C1200" t="str">
-        <v>010840003460</v>
+        <v>221040014631</v>
       </c>
       <c r="D1200" t="str">
         <v>ESYD (IAF)</v>
@@ -27998,12 +27998,12 @@
         <v>KZ</v>
       </c>
       <c r="G1200">
-        <v>46747</v>
+        <v>46733</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="str">
-        <v>JSC "Academy of Civil Aviation"</v>
+        <v>"Academy of Civil Aviation"</v>
       </c>
       <c r="B1201" t="str">
         <v>JSC</v>
@@ -28012,73 +28012,73 @@
         <v>010840003460</v>
       </c>
       <c r="D1201" t="str">
-        <v>n/a</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1201" t="str">
-        <v>ISO 21001</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1201" t="str">
         <v>KZ</v>
       </c>
       <c r="G1201">
-        <v>46744</v>
+        <v>46747</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="str">
-        <v>«АзияАгроФуд»</v>
+        <v>JSC "Academy of Civil Aviation"</v>
       </c>
       <c r="B1202" t="str">
-        <v>АО</v>
+        <v>JSC</v>
       </c>
       <c r="C1202" t="str">
-        <v>050740003177</v>
+        <v>010840003460</v>
       </c>
       <c r="D1202" t="str">
-        <v>ESYD (IAF)</v>
+        <v>n/a</v>
       </c>
       <c r="E1202" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 21001</v>
       </c>
       <c r="F1202" t="str">
         <v>KZ</v>
       </c>
-      <c r="G1202" t="str">
-        <v/>
+      <c r="G1202">
+        <v>46744</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="str">
-        <v>«Каменск-Уральский металлургический завод» (ПАО «КУМЗ»)</v>
+        <v>«АзияАгроФуд»</v>
       </c>
       <c r="B1203" t="str">
-        <v>ПАО</v>
+        <v>АО</v>
       </c>
       <c r="C1203" t="str">
-        <v>6665002150</v>
+        <v>050740003177</v>
       </c>
       <c r="D1203" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1203" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1203" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1203">
-        <v>47102</v>
+        <v>KZ</v>
+      </c>
+      <c r="G1203" t="str">
+        <v/>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="str">
-        <v>"СЛАВДОМ"</v>
+        <v>«Каменск-Уральский металлургический завод» (ПАО «КУМЗ»)</v>
       </c>
       <c r="B1204" t="str">
-        <v>ООО</v>
+        <v>ПАО</v>
       </c>
       <c r="C1204" t="str">
-        <v>7806528328</v>
+        <v>6665002150</v>
       </c>
       <c r="D1204" t="str">
         <v>ESYD (IAF)</v>
@@ -28090,18 +28090,18 @@
         <v>РФ</v>
       </c>
       <c r="G1204">
-        <v>46871</v>
+        <v>47102</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="str">
-        <v>«ГАБИОНЫ МАККАФЕРРИ СНГ»</v>
+        <v>"СЛАВДОМ"</v>
       </c>
       <c r="B1205" t="str">
         <v>ООО</v>
       </c>
       <c r="C1205" t="str">
-        <v>7722187777</v>
+        <v>7806528328</v>
       </c>
       <c r="D1205" t="str">
         <v>ESYD (IAF)</v>
@@ -28113,30 +28113,30 @@
         <v>РФ</v>
       </c>
       <c r="G1205">
-        <v>46474</v>
+        <v>46871</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="str">
-        <v>"Коломенский завод"</v>
+        <v>«ГАБИОНЫ МАККАФЕРРИ СНГ»</v>
       </c>
       <c r="B1206" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1206" t="str">
-        <v>5022013517</v>
+        <v>7722187777</v>
       </c>
       <c r="D1206" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1206" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1206" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1206" t="str">
-        <v>Сертификат еще не выдан</v>
+      <c r="G1206">
+        <v>46474</v>
       </c>
     </row>
     <row r="1207">
@@ -28153,7 +28153,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1207" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1207" t="str">
         <v>РФ</v>
@@ -28164,36 +28164,36 @@
     </row>
     <row r="1208">
       <c r="A1208" t="str">
-        <v>"ENERGOBEST"</v>
+        <v>"Коломенский завод"</v>
       </c>
       <c r="B1208" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1208" t="str">
-        <v>301418434</v>
+        <v>5022013517</v>
       </c>
       <c r="D1208" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1208" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1208" t="str">
-        <v>UZ</v>
-      </c>
-      <c r="G1208">
-        <v>46846</v>
+        <v>РФ</v>
+      </c>
+      <c r="G1208" t="str">
+        <v>Сертификат еще не выдан</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="str">
-        <v>«PRIME TOWER GROUP»</v>
+        <v>"ENERGOBEST"</v>
       </c>
       <c r="B1209" t="str">
         <v>ООО</v>
       </c>
       <c r="C1209" t="str">
-        <v>303879121</v>
+        <v>301418434</v>
       </c>
       <c r="D1209" t="str">
         <v>ESYD (IAF)</v>
@@ -28205,18 +28205,18 @@
         <v>UZ</v>
       </c>
       <c r="G1209">
-        <v>46838</v>
+        <v>46846</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="str">
-        <v>«GEOTEC»</v>
+        <v>«PRIME TOWER GROUP»</v>
       </c>
       <c r="B1210" t="str">
-        <v>ТОО</v>
+        <v>ООО</v>
       </c>
       <c r="C1210" t="str">
-        <v>061240002175</v>
+        <v>303879121</v>
       </c>
       <c r="D1210" t="str">
         <v>ESYD (IAF)</v>
@@ -28225,21 +28225,21 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1210" t="str">
-        <v>KZ</v>
+        <v>UZ</v>
       </c>
       <c r="G1210">
-        <v>46859</v>
+        <v>46838</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="str">
-        <v>«Узэлектроаппарат-Электрощит»</v>
+        <v>«GEOTEC»</v>
       </c>
       <c r="B1211" t="str">
-        <v>АО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1211" t="str">
-        <v>201052167</v>
+        <v>061240002175</v>
       </c>
       <c r="D1211" t="str">
         <v>ESYD (IAF)</v>
@@ -28248,10 +28248,10 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1211" t="str">
-        <v>UZ</v>
+        <v>KZ</v>
       </c>
       <c r="G1211">
-        <v>46892</v>
+        <v>46859</v>
       </c>
     </row>
     <row r="1212">
@@ -28268,13 +28268,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1212" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1212" t="str">
         <v>UZ</v>
       </c>
       <c r="G1212">
-        <v>46889</v>
+        <v>46892</v>
       </c>
     </row>
     <row r="1213">
@@ -28291,36 +28291,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1213" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1213" t="str">
         <v>UZ</v>
       </c>
       <c r="G1213">
-        <v>46892</v>
+        <v>46889</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="str">
-        <v>"Трастбанк"</v>
+        <v>«Узэлектроаппарат-Электрощит»</v>
       </c>
       <c r="B1214" t="str">
-        <v>ЧАБ</v>
+        <v>АО</v>
       </c>
       <c r="C1214" t="str">
-        <v>201055090</v>
+        <v>201052167</v>
       </c>
       <c r="D1214" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1214" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1214" t="str">
         <v>UZ</v>
       </c>
       <c r="G1214">
-        <v>46996</v>
+        <v>46892</v>
       </c>
     </row>
     <row r="1215">
@@ -28337,36 +28337,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1215" t="str">
-        <v>ISO 37001:2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1215" t="str">
         <v>UZ</v>
       </c>
       <c r="G1215">
-        <v>47039</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="str">
-        <v>"Каспийский трубопроводный консорциум-Р"</v>
+        <v>"Трастбанк"</v>
       </c>
       <c r="B1216" t="str">
-        <v>АО</v>
+        <v>ЧАБ</v>
       </c>
       <c r="C1216" t="str">
-        <v>2310040800</v>
+        <v>201055090</v>
       </c>
       <c r="D1216" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1216" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 37001:2016</v>
       </c>
       <c r="F1216" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1216">
-        <v>46961</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1217">
@@ -28383,7 +28383,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1217" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1217" t="str">
         <v>РФ</v>
@@ -28394,48 +28394,48 @@
     </row>
     <row r="1218">
       <c r="A1218" t="str">
-        <v>"АСТОР"</v>
+        <v>"Каспийский трубопроводный консорциум-Р"</v>
       </c>
       <c r="B1218" t="str">
         <v>АО</v>
       </c>
       <c r="C1218" t="str">
-        <v>4703015840</v>
+        <v>2310040800</v>
       </c>
       <c r="D1218" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1218" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1218" t="str">
         <v>РФ</v>
       </c>
       <c r="G1218">
-        <v>47056</v>
+        <v>46961</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="str">
-        <v>"AIR MARAKANDA"</v>
+        <v>"АСТОР"</v>
       </c>
       <c r="B1219" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1219" t="str">
-        <v>307280842</v>
+        <v>4703015840</v>
       </c>
       <c r="D1219" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1219" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1219" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1219">
-        <v>46993</v>
+        <v>47056</v>
       </c>
     </row>
     <row r="1220">
@@ -28452,36 +28452,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1220" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1220" t="str">
         <v>UZ</v>
       </c>
       <c r="G1220">
-        <v>47005</v>
+        <v>46993</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="str">
-        <v>Частное производственное унитарное предприятие "НТП "Центр"</v>
+        <v>"AIR MARAKANDA"</v>
       </c>
       <c r="B1221" t="str">
-        <v>Частное производственное унитарное предприятие</v>
+        <v>ООО</v>
       </c>
       <c r="C1221" t="str">
-        <v>700010977</v>
+        <v>307280842</v>
       </c>
       <c r="D1221" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1221" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1221" t="str">
-        <v>РБ</v>
+        <v>UZ</v>
       </c>
       <c r="G1221">
-        <v>47045</v>
+        <v>47005</v>
       </c>
     </row>
     <row r="1222">
@@ -28495,7 +28495,7 @@
         <v>700010977</v>
       </c>
       <c r="D1222" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1222" t="str">
         <v>ISO 9001:2015</v>
@@ -28509,16 +28509,16 @@
     </row>
     <row r="1223">
       <c r="A1223" t="str">
-        <v>Silicon Materials Inc.</v>
+        <v>Частное производственное унитарное предприятие "НТП "Центр"</v>
       </c>
       <c r="B1223" t="str">
-        <v/>
+        <v>Частное производственное унитарное предприятие</v>
       </c>
       <c r="C1223" t="str">
-        <v>EIN 25-1681874</v>
+        <v>700010977</v>
       </c>
       <c r="D1223" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1223" t="str">
         <v>ISO 9001:2015</v>
@@ -28526,19 +28526,19 @@
       <c r="F1223" t="str">
         <v>РБ</v>
       </c>
-      <c r="G1223" t="str">
-        <v>Сертификат еще не выдан</v>
+      <c r="G1223">
+        <v>47045</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="str">
-        <v>"CLOUPARD"</v>
+        <v>Silicon Materials Inc.</v>
       </c>
       <c r="B1224" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1224" t="str">
-        <v>310143054</v>
+        <v>EIN 25-1681874</v>
       </c>
       <c r="D1224" t="str">
         <v>ESYD (IAF)</v>
@@ -28547,7 +28547,7 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1224" t="str">
-        <v>UZ</v>
+        <v>РБ</v>
       </c>
       <c r="G1224" t="str">
         <v>Сертификат еще не выдан</v>
@@ -28567,7 +28567,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1225" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1225" t="str">
         <v>UZ</v>
@@ -28578,13 +28578,13 @@
     </row>
     <row r="1226">
       <c r="A1226" t="str">
-        <v>"Н-ТЕХ"</v>
+        <v>"CLOUPARD"</v>
       </c>
       <c r="B1226" t="str">
         <v>ООО</v>
       </c>
       <c r="C1226" t="str">
-        <v>7813283686</v>
+        <v>310143054</v>
       </c>
       <c r="D1226" t="str">
         <v>ESYD (IAF)</v>
@@ -28593,44 +28593,44 @@
         <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1226" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1226">
-        <v>47055</v>
+        <v>UZ</v>
+      </c>
+      <c r="G1226" t="str">
+        <v>Сертификат еще не выдан</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="str">
-        <v>"СММ"</v>
+        <v>"Н-ТЕХ"</v>
       </c>
       <c r="B1227" t="str">
-        <v>ЗАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1227" t="str">
-        <v>7826136294</v>
+        <v>7813283686</v>
       </c>
       <c r="D1227" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1227" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1227" t="str">
         <v>РФ</v>
       </c>
       <c r="G1227">
-        <v>47012</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="str">
-        <v>"Ifoda Agro Kimyo Himoya"</v>
+        <v>"СММ"</v>
       </c>
       <c r="B1228" t="str">
-        <v>СП ООО</v>
+        <v>ЗАО</v>
       </c>
       <c r="C1228" t="str">
-        <v>314010020917</v>
+        <v>7826136294</v>
       </c>
       <c r="D1228" t="str">
         <v>ESYD (IAF)</v>
@@ -28639,10 +28639,10 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1228" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1228">
-        <v>47074</v>
+        <v>47012</v>
       </c>
     </row>
     <row r="1229">
@@ -28659,36 +28659,36 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1229" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1229" t="str">
         <v>UZ</v>
       </c>
       <c r="G1229">
-        <v>47073</v>
+        <v>47074</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="str">
-        <v>ZTE Investment</v>
+        <v>"Ifoda Agro Kimyo Himoya"</v>
       </c>
       <c r="B1230" t="str">
-        <v>ИП ООО</v>
+        <v>СП ООО</v>
       </c>
       <c r="C1230" t="str">
-        <v>20662083</v>
+        <v>314010020917</v>
       </c>
       <c r="D1230" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1230" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1230" t="str">
         <v>UZ</v>
       </c>
       <c r="G1230">
-        <v>47054</v>
+        <v>47073</v>
       </c>
     </row>
     <row r="1231">
@@ -28705,13 +28705,13 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1231" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1231" t="str">
         <v>UZ</v>
       </c>
       <c r="G1231">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="1232">
@@ -28728,47 +28728,47 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1232" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1232" t="str">
         <v>UZ</v>
       </c>
       <c r="G1232">
-        <v>47056</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="str">
-        <v>«Интраком»</v>
+        <v>ZTE Investment</v>
       </c>
       <c r="B1233" t="str">
-        <v>ООО</v>
+        <v>ИП ООО</v>
       </c>
       <c r="C1233" t="str">
-        <v>6612059795</v>
+        <v>20662083</v>
       </c>
       <c r="D1233" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1233" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1233" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1233">
-        <v>47031</v>
+        <v>47056</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="str">
-        <v>«КФ-АВТО»</v>
+        <v>«Интраком»</v>
       </c>
       <c r="B1234" t="str">
         <v>ООО</v>
       </c>
       <c r="C1234" t="str">
-        <v>692142686</v>
+        <v>6612059795</v>
       </c>
       <c r="D1234" t="str">
         <v>ESYD (IAF)</v>
@@ -28777,44 +28777,44 @@
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1234" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1234">
-        <v>47048</v>
+        <v>47031</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="str">
-        <v>"Авалон Джус"</v>
+        <v>«КФ-АВТО»</v>
       </c>
       <c r="B1235" t="str">
         <v>ООО</v>
       </c>
       <c r="C1235" t="str">
-        <v>2310215472</v>
+        <v>692142686</v>
       </c>
       <c r="D1235" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1235" t="str">
-        <v>FSSC 22000</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1235" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1235">
-        <v>47106</v>
+        <v>47048</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="str">
-        <v>"Компания Алтын Казык"</v>
+        <v>"Авалон Джус"</v>
       </c>
       <c r="B1236" t="str">
-        <v>ТОО</v>
+        <v>ООО</v>
       </c>
       <c r="C1236" t="str">
-        <v>060640000339</v>
+        <v>2310215472</v>
       </c>
       <c r="D1236" t="str">
         <v>ESYD (IAF)</v>
@@ -28823,21 +28823,21 @@
         <v>FSSC 22000</v>
       </c>
       <c r="F1236" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1236">
-        <v>46484</v>
+        <v>47106</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="str">
-        <v>"ASL OYNA"</v>
+        <v>"Компания Алтын Казык"</v>
       </c>
       <c r="B1237" t="str">
-        <v>ООО</v>
+        <v>ТОО</v>
       </c>
       <c r="C1237" t="str">
-        <v>203554782</v>
+        <v>060640000339</v>
       </c>
       <c r="D1237" t="str">
         <v>ESYD (IAF)</v>
@@ -28846,21 +28846,21 @@
         <v>FSSC 22000</v>
       </c>
       <c r="F1237" t="str">
-        <v>UZ</v>
+        <v>KZ</v>
       </c>
       <c r="G1237">
-        <v>46971</v>
+        <v>46484</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="str">
-        <v>“PENG SHENG CHARM”</v>
+        <v>"ASL OYNA"</v>
       </c>
       <c r="B1238" t="str">
-        <v>ИП ООО</v>
+        <v>ООО</v>
       </c>
       <c r="C1238" t="str">
-        <v>301647292</v>
+        <v>203554782</v>
       </c>
       <c r="D1238" t="str">
         <v>ESYD (IAF)</v>
@@ -28872,18 +28872,18 @@
         <v>UZ</v>
       </c>
       <c r="G1238">
-        <v>46945</v>
+        <v>46971</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="str">
-        <v>«TASH-PET»</v>
+        <v>“PENG SHENG CHARM”</v>
       </c>
       <c r="B1239" t="str">
-        <v>ООО</v>
+        <v>ИП ООО</v>
       </c>
       <c r="C1239" t="str">
-        <v>300939824</v>
+        <v>301647292</v>
       </c>
       <c r="D1239" t="str">
         <v>ESYD (IAF)</v>
@@ -28895,41 +28895,41 @@
         <v>UZ</v>
       </c>
       <c r="G1239">
-        <v>47016</v>
+        <v>46945</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="str">
-        <v>Тяжпрессмаш</v>
+        <v>«TASH-PET»</v>
       </c>
       <c r="B1240" t="str">
-        <v>ПАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1240" t="str">
-        <v>6229009163</v>
+        <v>300939824</v>
       </c>
       <c r="D1240" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1240" t="str">
-        <v>ISO 9001:2015</v>
+        <v>FSSC 22000</v>
       </c>
       <c r="F1240" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1240">
-        <v>46655</v>
+        <v>47016</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="str">
-        <v>Завод Лоджикруф</v>
+        <v>Тяжпрессмаш</v>
       </c>
       <c r="B1241" t="str">
-        <v>ООО</v>
+        <v>ПАО</v>
       </c>
       <c r="C1241" t="str">
-        <v>6230054971</v>
+        <v>6229009163</v>
       </c>
       <c r="D1241" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -28941,18 +28941,18 @@
         <v>РФ</v>
       </c>
       <c r="G1241">
-        <v>46668</v>
+        <v>46655</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="str">
-        <v>СОЛВО</v>
+        <v>Завод Лоджикруф</v>
       </c>
       <c r="B1242" t="str">
         <v>ООО</v>
       </c>
       <c r="C1242" t="str">
-        <v>7825064174</v>
+        <v>6230054971</v>
       </c>
       <c r="D1242" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -28964,18 +28964,18 @@
         <v>РФ</v>
       </c>
       <c r="G1242">
-        <v>46683</v>
+        <v>46668</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="str">
-        <v>Воскресенский филиал ООО "Завод Технофлекс"</v>
+        <v>СОЛВО</v>
       </c>
       <c r="B1243" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1243" t="str">
-        <v>6229024796</v>
+        <v>7825064174</v>
       </c>
       <c r="D1243" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -28987,18 +28987,18 @@
         <v>РФ</v>
       </c>
       <c r="G1243">
-        <v>46719</v>
+        <v>46683</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="str">
-        <v>НПФ Ракурс</v>
+        <v>Воскресенский филиал ООО "Завод Технофлекс"</v>
       </c>
       <c r="B1244" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1244" t="str">
-        <v>7812041998</v>
+        <v>6229024796</v>
       </c>
       <c r="D1244" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29010,18 +29010,18 @@
         <v>РФ</v>
       </c>
       <c r="G1244">
-        <v>46731</v>
+        <v>46719</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="str">
-        <v>Светлана-Рентген</v>
+        <v>НПФ Ракурс</v>
       </c>
       <c r="B1245" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1245" t="str">
-        <v>7805026364</v>
+        <v>7812041998</v>
       </c>
       <c r="D1245" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29033,18 +29033,18 @@
         <v>РФ</v>
       </c>
       <c r="G1245">
-        <v>46825</v>
+        <v>46731</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="str">
-        <v>ЗАВОД ТУРБИННЫХ ЗАПЧАСТЕЙ</v>
+        <v>Светлана-Рентген</v>
       </c>
       <c r="B1246" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1246" t="str">
-        <v>7814656732</v>
+        <v>7805026364</v>
       </c>
       <c r="D1246" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -29056,7 +29056,7 @@
         <v>РФ</v>
       </c>
       <c r="G1246">
-        <v>46856</v>
+        <v>46825</v>
       </c>
     </row>
     <row r="1247">
@@ -29070,39 +29070,39 @@
         <v>7814656732</v>
       </c>
       <c r="D1247" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1247" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1247" t="str">
         <v>РФ</v>
       </c>
       <c r="G1247">
-        <v>46520</v>
+        <v>46856</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="str">
-        <v>Петроаналитика</v>
+        <v>ЗАВОД ТУРБИННЫХ ЗАПЧАСТЕЙ</v>
       </c>
       <c r="B1248" t="str">
         <v>ООО</v>
       </c>
       <c r="C1248" t="str">
-        <v>7805523334</v>
+        <v>7814656732</v>
       </c>
       <c r="D1248" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1248" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1248" t="str">
         <v>РФ</v>
       </c>
       <c r="G1248">
-        <v>46934</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="1249">
@@ -29116,39 +29116,39 @@
         <v>7805523334</v>
       </c>
       <c r="D1249" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1249" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1249" t="str">
         <v>РФ</v>
       </c>
       <c r="G1249">
-        <v>47111</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="str">
-        <v>Химсталькомплект (ХСК)</v>
+        <v>Петроаналитика</v>
       </c>
       <c r="B1250" t="str">
         <v>ООО</v>
       </c>
       <c r="C1250" t="str">
-        <v>7422046285</v>
+        <v>7805523334</v>
       </c>
       <c r="D1250" t="str">
-        <v>EGAC (QME)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1250" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1250" t="str">
         <v>РФ</v>
       </c>
       <c r="G1250">
-        <v>46265</v>
+        <v>47111</v>
       </c>
     </row>
     <row r="1251">
@@ -29162,73 +29162,73 @@
         <v>7422046285</v>
       </c>
       <c r="D1251" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>EGAC (QME)</v>
       </c>
       <c r="E1251" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1251" t="str">
         <v>РФ</v>
       </c>
       <c r="G1251">
-        <v>46808</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="str">
-        <v>Группа компаний "ЛЮМЭКС Инструментс"</v>
+        <v>Химсталькомплект (ХСК)</v>
       </c>
       <c r="B1252" t="str">
-        <v/>
+        <v>ООО</v>
       </c>
       <c r="C1252" t="str">
-        <v>7801472150</v>
+        <v>7422046285</v>
       </c>
       <c r="D1252" t="str">
-        <v>JASANZ (SAI Global)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1252" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1252" t="str">
         <v>РФ</v>
       </c>
       <c r="G1252">
-        <v>46278</v>
+        <v>46808</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="str">
-        <v>СИЭЛ</v>
+        <v>Группа компаний "ЛЮМЭКС Инструментс"</v>
       </c>
       <c r="B1253" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1253" t="str">
-        <v>7810742885</v>
+        <v>7801472150</v>
       </c>
       <c r="D1253" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>JASANZ (SAI Global)</v>
       </c>
       <c r="E1253" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1253" t="str">
         <v>РФ</v>
       </c>
       <c r="G1253">
-        <v>46673</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="str">
-        <v>Газпром диагностика</v>
+        <v>СИЭЛ</v>
       </c>
       <c r="B1254" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1254" t="str">
-        <v>4345083100</v>
+        <v>7810742885</v>
       </c>
       <c r="D1254" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -29240,18 +29240,18 @@
         <v>РФ</v>
       </c>
       <c r="G1254">
-        <v>47102</v>
+        <v>46673</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="str">
-        <v>БП Морские Системы</v>
+        <v>Газпром диагностика</v>
       </c>
       <c r="B1255" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1255" t="str">
-        <v>7801726319</v>
+        <v>4345083100</v>
       </c>
       <c r="D1255" t="str">
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
@@ -29263,21 +29263,21 @@
         <v>РФ</v>
       </c>
       <c r="G1255">
-        <v>46520</v>
+        <v>47102</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="str">
-        <v>Статус</v>
+        <v>БП Морские Системы</v>
       </c>
       <c r="B1256" t="str">
         <v>ООО</v>
       </c>
       <c r="C1256" t="str">
-        <v>7413025257</v>
+        <v>7801726319</v>
       </c>
       <c r="D1256" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1256" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -29286,18 +29286,18 @@
         <v>РФ</v>
       </c>
       <c r="G1256">
-        <v>46927</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="str">
-        <v>ТЭК-Консалтинг</v>
+        <v>Статус</v>
       </c>
       <c r="B1257" t="str">
         <v>ООО</v>
       </c>
       <c r="C1257" t="str">
-        <v>7804185393</v>
+        <v>7413025257</v>
       </c>
       <c r="D1257" t="str">
         <v>РОСАТОМРЕГИСТР</v>
@@ -29309,18 +29309,18 @@
         <v>РФ</v>
       </c>
       <c r="G1257">
-        <v>46898</v>
+        <v>46927</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="str">
-        <v>ГидроТехАтом</v>
+        <v>ТЭК-Консалтинг</v>
       </c>
       <c r="B1258" t="str">
         <v>ООО</v>
       </c>
       <c r="C1258" t="str">
-        <v>1831123035</v>
+        <v>7804185393</v>
       </c>
       <c r="D1258" t="str">
         <v>РОСАТОМРЕГИСТР</v>
@@ -29332,21 +29332,21 @@
         <v>РФ</v>
       </c>
       <c r="G1258">
-        <v>47168</v>
+        <v>46898</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="str">
-        <v>НАМИ инновационные компоненты</v>
+        <v>ГидроТехАтом</v>
       </c>
       <c r="B1259" t="str">
         <v>ООО</v>
       </c>
       <c r="C1259" t="str">
-        <v>6330056813</v>
+        <v>1831123035</v>
       </c>
       <c r="D1259" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1259" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -29355,7 +29355,7 @@
         <v>РФ</v>
       </c>
       <c r="G1259">
-        <v>47039</v>
+        <v>47168</v>
       </c>
     </row>
     <row r="1260">
@@ -29369,39 +29369,39 @@
         <v>6330056813</v>
       </c>
       <c r="D1260" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1260" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1260" t="str">
         <v>РФ</v>
       </c>
       <c r="G1260">
-        <v>46303</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="str">
-        <v>Европейский мужчина и его здоровье</v>
+        <v>НАМИ инновационные компоненты</v>
       </c>
       <c r="B1261" t="str">
         <v>ООО</v>
       </c>
       <c r="C1261" t="str">
-        <v>7811447106</v>
+        <v>6330056813</v>
       </c>
       <c r="D1261" t="str">
-        <v>ESYD (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1261" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1261" t="str">
         <v>РФ</v>
       </c>
       <c r="G1261">
-        <v>47115</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1262">
@@ -29415,7 +29415,7 @@
         <v>7811447106</v>
       </c>
       <c r="D1262" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1262" t="str">
         <v>ISO 9001:2015</v>
@@ -29429,16 +29429,16 @@
     </row>
     <row r="1263">
       <c r="A1263" t="str">
-        <v>Газпром Линде Инжиниринг (ГЛ Инжиниринг)</v>
+        <v>Европейский мужчина и его здоровье</v>
       </c>
       <c r="B1263" t="str">
         <v>ООО</v>
       </c>
       <c r="C1263" t="str">
-        <v>0266023912</v>
+        <v>7811447106</v>
       </c>
       <c r="D1263" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1263" t="str">
         <v>ISO 9001:2015</v>
@@ -29447,7 +29447,7 @@
         <v>РФ</v>
       </c>
       <c r="G1263">
-        <v>47025</v>
+        <v>47115</v>
       </c>
     </row>
     <row r="1264">
@@ -29461,7 +29461,7 @@
         <v>0266023912</v>
       </c>
       <c r="D1264" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1264" t="str">
         <v>ISO 9001:2015</v>
@@ -29484,10 +29484,10 @@
         <v>0266023912</v>
       </c>
       <c r="D1265" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1265" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1265" t="str">
         <v>РФ</v>
@@ -29507,7 +29507,7 @@
         <v>0266023912</v>
       </c>
       <c r="D1266" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1266" t="str">
         <v>ISO 14001:2015</v>
@@ -29530,10 +29530,10 @@
         <v>0266023912</v>
       </c>
       <c r="D1267" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1267" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1267" t="str">
         <v>РФ</v>
@@ -29553,7 +29553,7 @@
         <v>0266023912</v>
       </c>
       <c r="D1268" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1268" t="str">
         <v>ISO 45001:2018</v>
@@ -29576,16 +29576,16 @@
         <v>0266023912</v>
       </c>
       <c r="D1269" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1269" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1269" t="str">
         <v>РФ</v>
       </c>
       <c r="G1269">
-        <v>47023</v>
+        <v>47025</v>
       </c>
     </row>
     <row r="1270">
@@ -29602,7 +29602,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1270" t="str">
-        <v>ГОСТ Р ИСО 14001-2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1270" t="str">
         <v>РФ</v>
@@ -29625,7 +29625,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1271" t="str">
-        <v>ГОСТ Р ИСО 45001-2020</v>
+        <v>ГОСТ Р ИСО 14001-2016</v>
       </c>
       <c r="F1271" t="str">
         <v>РФ</v>
@@ -29645,39 +29645,39 @@
         <v>0266023912</v>
       </c>
       <c r="D1272" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1272" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ГОСТ Р ИСО 45001-2020</v>
       </c>
       <c r="F1272" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1272" t="str">
-        <v/>
+      <c r="G1272">
+        <v>47023</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="str">
-        <v>Сарштедт</v>
+        <v>Газпром Линде Инжиниринг (ГЛ Инжиниринг)</v>
       </c>
       <c r="B1273" t="str">
         <v>ООО</v>
       </c>
       <c r="C1273" t="str">
-        <v>6037008575</v>
+        <v>0266023912</v>
       </c>
       <c r="D1273" t="str">
-        <v>NABCB (IAF)</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1273" t="str">
-        <v>ISO 13485:2016</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1273" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1273">
-        <v>47076</v>
+      <c r="G1273" t="str">
+        <v/>
       </c>
     </row>
     <row r="1274">
@@ -29691,7 +29691,7 @@
         <v>6037008575</v>
       </c>
       <c r="D1274" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>NABCB (IAF)</v>
       </c>
       <c r="E1274" t="str">
         <v>ISO 13485:2016</v>
@@ -29714,39 +29714,39 @@
         <v>6037008575</v>
       </c>
       <c r="D1275" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1275" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1275" t="str">
         <v>РФ</v>
       </c>
       <c r="G1275">
-        <v>46748</v>
+        <v>47076</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="str">
-        <v>Бора Пак</v>
+        <v>Сарштедт</v>
       </c>
       <c r="B1276" t="str">
         <v>ООО</v>
       </c>
       <c r="C1276" t="str">
-        <v>6315626314</v>
+        <v>6037008575</v>
       </c>
       <c r="D1276" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1276" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1276" t="str">
         <v>РФ</v>
       </c>
       <c r="G1276">
-        <v>46274</v>
+        <v>46748</v>
       </c>
     </row>
     <row r="1277">
@@ -29760,16 +29760,16 @@
         <v>6315626314</v>
       </c>
       <c r="D1277" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1277" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1277" t="str">
         <v>РФ</v>
       </c>
       <c r="G1277">
-        <v>47086</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="1278">
@@ -29786,7 +29786,7 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1278" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1278" t="str">
         <v>РФ</v>
@@ -29797,16 +29797,16 @@
     </row>
     <row r="1279">
       <c r="A1279" t="str">
-        <v>Научно-производственный центр Горноспасательные технологии</v>
+        <v>Бора Пак</v>
       </c>
       <c r="B1279" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1279" t="str">
-        <v>6672163631</v>
+        <v>6315626314</v>
       </c>
       <c r="D1279" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1279" t="str">
         <v>ISO 9001:2015</v>
@@ -29815,7 +29815,7 @@
         <v>РФ</v>
       </c>
       <c r="G1279">
-        <v>47070</v>
+        <v>47086</v>
       </c>
     </row>
     <row r="1280">
@@ -29829,7 +29829,7 @@
         <v>6672163631</v>
       </c>
       <c r="D1280" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1280" t="str">
         <v>ISO 9001:2015</v>
@@ -29843,7 +29843,7 @@
     </row>
     <row r="1281">
       <c r="A1281" t="str">
-        <v>Научно-производственный центр "Горноспасательные технологии"</v>
+        <v>Научно-производственный центр Горноспасательные технологии</v>
       </c>
       <c r="B1281" t="str">
         <v>АО</v>
@@ -29852,39 +29852,39 @@
         <v>6672163631</v>
       </c>
       <c r="D1281" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1281" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1281" t="str">
         <v>РФ</v>
       </c>
       <c r="G1281">
-        <v>47100</v>
+        <v>47070</v>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="str">
-        <v>Джойсон Сейфти Системс Рус</v>
+        <v>Научно-производственный центр "Горноспасательные технологии"</v>
       </c>
       <c r="B1282" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1282" t="str">
-        <v>7325097407</v>
+        <v>6672163631</v>
       </c>
       <c r="D1282" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1282" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1282" t="str">
         <v>РФ</v>
       </c>
       <c r="G1282">
-        <v>47097</v>
+        <v>47100</v>
       </c>
     </row>
     <row r="1283">
@@ -29898,7 +29898,7 @@
         <v>7325097407</v>
       </c>
       <c r="D1283" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1283" t="str">
         <v>ISO 9001:2015</v>
@@ -29921,16 +29921,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1284" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1284" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1284" t="str">
         <v>РФ</v>
       </c>
       <c r="G1284">
-        <v>47166</v>
+        <v>47097</v>
       </c>
     </row>
     <row r="1285">
@@ -29944,7 +29944,7 @@
         <v>7325097407</v>
       </c>
       <c r="D1285" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1285" t="str">
         <v>ISO 14001:2015</v>
@@ -29967,10 +29967,10 @@
         <v>7325097407</v>
       </c>
       <c r="D1286" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1286" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1286" t="str">
         <v>РФ</v>
@@ -29990,7 +29990,7 @@
         <v>7325097407</v>
       </c>
       <c r="D1287" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1287" t="str">
         <v>ISO 45001:2018</v>
@@ -30013,16 +30013,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1288" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1288" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1288" t="str">
         <v>РФ</v>
       </c>
       <c r="G1288">
-        <v>46982</v>
+        <v>47166</v>
       </c>
     </row>
     <row r="1289">
@@ -30036,16 +30036,16 @@
         <v>7325097407</v>
       </c>
       <c r="D1289" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1289" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1289" t="str">
         <v>РФ</v>
       </c>
       <c r="G1289">
-        <v>46178</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1290">
@@ -30059,39 +30059,39 @@
         <v>7325097407</v>
       </c>
       <c r="D1290" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1290" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1290" t="str">
         <v>РФ</v>
       </c>
       <c r="G1290">
-        <v>46982</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="str">
-        <v>ТЛТ ПРОФ</v>
+        <v>Джойсон Сейфти Системс Рус</v>
       </c>
       <c r="B1291" t="str">
         <v>ООО</v>
       </c>
       <c r="C1291" t="str">
-        <v>6321273480</v>
+        <v>7325097407</v>
       </c>
       <c r="D1291" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1291" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1291" t="str">
         <v>РФ</v>
       </c>
       <c r="G1291">
-        <v>46844</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="1292">
@@ -30105,7 +30105,7 @@
         <v>6321273480</v>
       </c>
       <c r="D1292" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1292" t="str">
         <v>ISO 9001:2015</v>
@@ -30119,16 +30119,16 @@
     </row>
     <row r="1293">
       <c r="A1293" t="str">
-        <v>ТрансАвтоСвет</v>
+        <v>ТЛТ ПРОФ</v>
       </c>
       <c r="B1293" t="str">
         <v>ООО</v>
       </c>
       <c r="C1293" t="str">
-        <v>7328075313</v>
+        <v>6321273480</v>
       </c>
       <c r="D1293" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1293" t="str">
         <v>ISO 9001:2015</v>
@@ -30137,7 +30137,7 @@
         <v>РФ</v>
       </c>
       <c r="G1293">
-        <v>47046</v>
+        <v>46844</v>
       </c>
     </row>
     <row r="1294">
@@ -30151,7 +30151,7 @@
         <v>7328075313</v>
       </c>
       <c r="D1294" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1294" t="str">
         <v>ISO 9001:2015</v>
@@ -30165,16 +30165,16 @@
     </row>
     <row r="1295">
       <c r="A1295" t="str">
-        <v>Борский стекольный завод</v>
+        <v>ТрансАвтоСвет</v>
       </c>
       <c r="B1295" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1295" t="str">
-        <v>5246002261</v>
+        <v>7328075313</v>
       </c>
       <c r="D1295" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1295" t="str">
         <v>ISO 9001:2015</v>
@@ -30183,7 +30183,7 @@
         <v>РФ</v>
       </c>
       <c r="G1295">
-        <v>47066</v>
+        <v>47046</v>
       </c>
     </row>
     <row r="1296">
@@ -30197,7 +30197,7 @@
         <v>5246002261</v>
       </c>
       <c r="D1296" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1296" t="str">
         <v>ISO 9001:2015</v>
@@ -30220,16 +30220,16 @@
         <v>5246002261</v>
       </c>
       <c r="D1297" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1297" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1297" t="str">
         <v>РФ</v>
       </c>
       <c r="G1297">
-        <v>46634</v>
+        <v>47066</v>
       </c>
     </row>
     <row r="1298">
@@ -30243,7 +30243,7 @@
         <v>5246002261</v>
       </c>
       <c r="D1298" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1298" t="str">
         <v>ISO 14001:2015</v>
@@ -30266,10 +30266,10 @@
         <v>5246002261</v>
       </c>
       <c r="D1299" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1299" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1299" t="str">
         <v>РФ</v>
@@ -30289,7 +30289,7 @@
         <v>5246002261</v>
       </c>
       <c r="D1300" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1300" t="str">
         <v>ISO 45001:2018</v>
@@ -30312,39 +30312,39 @@
         <v>5246002261</v>
       </c>
       <c r="D1301" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1301" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1301" t="str">
         <v>РФ</v>
       </c>
       <c r="G1301">
-        <v>46255</v>
+        <v>46634</v>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="str">
-        <v>ПРОМЭНЕРГОКОМПЛЕКТ</v>
+        <v>Борский стекольный завод</v>
       </c>
       <c r="B1302" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1302" t="str">
-        <v>5262222391</v>
+        <v>5246002261</v>
       </c>
       <c r="D1302" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1302" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1302" t="str">
         <v>РФ</v>
       </c>
       <c r="G1302">
-        <v>47039</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="1303">
@@ -30358,10 +30358,10 @@
         <v>5262222391</v>
       </c>
       <c r="D1303" t="str">
-        <v>ECA (APAC)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1303" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1303" t="str">
         <v>РФ</v>
@@ -30372,94 +30372,94 @@
     </row>
     <row r="1304">
       <c r="A1304" t="str">
-        <v>НПФ "Евродеталь"</v>
+        <v>ПРОМЭНЕРГОКОМПЛЕКТ</v>
       </c>
       <c r="B1304" t="str">
         <v>ООО</v>
       </c>
       <c r="C1304" t="str">
-        <v>1834054140</v>
+        <v>5262222391</v>
       </c>
       <c r="D1304" t="str">
-        <v>EADAS</v>
+        <v>ECA (APAC)</v>
       </c>
       <c r="E1304" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1304" t="str">
         <v>РФ</v>
       </c>
       <c r="G1304">
-        <v>46323</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="str">
-        <v>АйСиЭл Системные Технологии</v>
+        <v>НПФ "Евродеталь"</v>
       </c>
       <c r="B1305" t="str">
         <v>ООО</v>
       </c>
       <c r="C1305" t="str">
-        <v>1615012203</v>
+        <v>1834054140</v>
       </c>
       <c r="D1305" t="str">
-        <v>ESYD (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1305" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1305" t="str">
         <v>РФ</v>
       </c>
       <c r="G1305">
-        <v>47094</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="str">
-        <v>МЕДИН-Н</v>
+        <v>АйСиЭл Системные Технологии</v>
       </c>
       <c r="B1306" t="str">
         <v>ООО</v>
       </c>
       <c r="C1306" t="str">
-        <v>6662112620</v>
+        <v>1615012203</v>
       </c>
       <c r="D1306" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1306" t="str">
-        <v>ГОСТ ISO 13485-2017</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1306" t="str">
         <v>РФ</v>
       </c>
       <c r="G1306">
-        <v>47073</v>
+        <v>47094</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="str">
-        <v>МЕТТЕХ</v>
+        <v>МЕДИН-Н</v>
       </c>
       <c r="B1307" t="str">
         <v>ООО</v>
       </c>
       <c r="C1307" t="str">
-        <v>7806591143</v>
+        <v>6662112620</v>
       </c>
       <c r="D1307" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1307" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ ISO 13485-2017</v>
       </c>
       <c r="F1307" t="str">
         <v>РФ</v>
       </c>
       <c r="G1307">
-        <v>47112</v>
+        <v>47073</v>
       </c>
     </row>
     <row r="1308">
@@ -30473,7 +30473,7 @@
         <v>7806591143</v>
       </c>
       <c r="D1308" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1308" t="str">
         <v>ISO 9001:2015</v>
@@ -30487,82 +30487,82 @@
     </row>
     <row r="1309">
       <c r="A1309" t="str">
-        <v>Birinchi rezinotexnika zavodi</v>
+        <v>МЕТТЕХ</v>
       </c>
       <c r="B1309" t="str">
-        <v>ИП ООО</v>
+        <v>ООО</v>
       </c>
       <c r="C1309" t="str">
-        <v>301938570</v>
+        <v>7806591143</v>
       </c>
       <c r="D1309" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1309" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1309" t="str">
-        <v>UZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1309">
-        <v>47110</v>
+        <v>47112</v>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="str">
-        <v>Тюменский завод ЗСГ</v>
+        <v>Birinchi rezinotexnika zavodi</v>
       </c>
       <c r="B1310" t="str">
-        <v>ООО</v>
+        <v>ИП ООО</v>
       </c>
       <c r="C1310" t="str">
-        <v>7203412108</v>
+        <v>301938570</v>
       </c>
       <c r="D1310" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1310" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1310" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1310">
-        <v>47074</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="str">
-        <v>Электронмаш Инжиниринг</v>
+        <v>Тюменский завод ЗСГ</v>
       </c>
       <c r="B1311" t="str">
         <v>ООО</v>
       </c>
       <c r="C1311" t="str">
-        <v>7802428812</v>
+        <v>7203412108</v>
       </c>
       <c r="D1311" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1311" t="str">
-        <v>S.QS.07-2024</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1311" t="str">
         <v>РФ</v>
       </c>
       <c r="G1311">
-        <v>46731</v>
+        <v>47074</v>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="str">
-        <v>Нефтегаздеталь</v>
+        <v>Электронмаш Инжиниринг</v>
       </c>
       <c r="B1312" t="str">
         <v>ООО</v>
       </c>
       <c r="C1312" t="str">
-        <v>3661081734</v>
+        <v>7802428812</v>
       </c>
       <c r="D1312" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -30574,30 +30574,30 @@
         <v>РФ</v>
       </c>
       <c r="G1312">
-        <v>47001</v>
+        <v>46731</v>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="str">
-        <v>Богословский кабельный завод</v>
+        <v>Нефтегаздеталь</v>
       </c>
       <c r="B1313" t="str">
         <v>ООО</v>
       </c>
       <c r="C1313" t="str">
-        <v>6617026384</v>
+        <v>3661081734</v>
       </c>
       <c r="D1313" t="str">
-        <v>ESYD (IAF)</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1313" t="str">
-        <v>ISO 9001:2015</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1313" t="str">
         <v>РФ</v>
       </c>
       <c r="G1313">
-        <v>47087</v>
+        <v>47001</v>
       </c>
     </row>
     <row r="1314">
@@ -30611,7 +30611,7 @@
         <v>6617026384</v>
       </c>
       <c r="D1314" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1314" t="str">
         <v>ISO 9001:2015</v>
@@ -30625,16 +30625,16 @@
     </row>
     <row r="1315">
       <c r="A1315" t="str">
-        <v>Аутолив</v>
+        <v>Богословский кабельный завод</v>
       </c>
       <c r="B1315" t="str">
         <v>ООО</v>
       </c>
       <c r="C1315" t="str">
-        <v>4703105420</v>
+        <v>6617026384</v>
       </c>
       <c r="D1315" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1315" t="str">
         <v>ISO 9001:2015</v>
@@ -30657,7 +30657,7 @@
         <v>4703105420</v>
       </c>
       <c r="D1316" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1316" t="str">
         <v>ISO 9001:2015</v>
@@ -30683,13 +30683,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1317" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1317" t="str">
         <v>РФ</v>
       </c>
       <c r="G1317">
-        <v>47101</v>
+        <v>47087</v>
       </c>
     </row>
     <row r="1318">
@@ -30703,39 +30703,39 @@
         <v>4703105420</v>
       </c>
       <c r="D1318" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1318" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1318" t="str">
         <v>РФ</v>
       </c>
       <c r="G1318">
-        <v>45980</v>
+        <v>47101</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="str">
-        <v>ASTEL</v>
+        <v>Аутолив</v>
       </c>
       <c r="B1319" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1319" t="str">
-        <v>11140001666</v>
+        <v>4703105420</v>
       </c>
       <c r="D1319" t="str">
-        <v>UKAS (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1319" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1319" t="str">
-        <v>KZ</v>
+        <v>РФ</v>
       </c>
       <c r="G1319">
-        <v>46629</v>
+        <v>45980</v>
       </c>
     </row>
     <row r="1320">
@@ -30752,13 +30752,13 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1320" t="str">
-        <v>ISO 27001:2013</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1320" t="str">
         <v>KZ</v>
       </c>
       <c r="G1320">
-        <v>46643</v>
+        <v>46629</v>
       </c>
     </row>
     <row r="1321">
@@ -30775,7 +30775,7 @@
         <v>UKAS (IAF)</v>
       </c>
       <c r="E1321" t="str">
-        <v>ISO 20000-1:2018</v>
+        <v>ISO 27001:2013</v>
       </c>
       <c r="F1321" t="str">
         <v>KZ</v>
@@ -30786,48 +30786,48 @@
     </row>
     <row r="1322">
       <c r="A1322" t="str">
-        <v>Федеральное государственное бюджетное образовательное учреждение высшего образования «Тульский государственный педагогический университет им. Л.Н. Толстого», Научно-исследовательский институт химических, фармацевтических и биотехнологий, Научно-производственный центр</v>
+        <v>ASTEL</v>
       </c>
       <c r="B1322" t="str">
-        <v>ФГБОУ ВО</v>
+        <v>АО</v>
       </c>
       <c r="C1322" t="str">
-        <v>7107030811</v>
+        <v>11140001666</v>
       </c>
       <c r="D1322" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>UKAS (IAF)</v>
       </c>
       <c r="E1322" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 20000-1:2018</v>
       </c>
       <c r="F1322" t="str">
-        <v>РФ</v>
+        <v>KZ</v>
       </c>
       <c r="G1322">
-        <v>47101</v>
+        <v>46643</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="str">
-        <v>«УЗЛЫ И МЕХАНИЗМЫ КУЗОВА АВТОМОБИЛЯ» (ООО «УМКА»)</v>
+        <v>Федеральное государственное бюджетное образовательное учреждение высшего образования «Тульский государственный педагогический университет им. Л.Н. Толстого», Научно-исследовательский институт химических, фармацевтических и биотехнологий, Научно-производственный центр</v>
       </c>
       <c r="B1323" t="str">
-        <v>ООО</v>
+        <v>ФГБОУ ВО</v>
       </c>
       <c r="C1323" t="str">
-        <v>6382061684</v>
+        <v>7107030811</v>
       </c>
       <c r="D1323" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1323" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1323" t="str">
         <v>РФ</v>
       </c>
       <c r="G1323">
-        <v>47094</v>
+        <v>47101</v>
       </c>
     </row>
     <row r="1324">
@@ -30841,7 +30841,7 @@
         <v>6382061684</v>
       </c>
       <c r="D1324" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1324" t="str">
         <v>ISO 9001:2015</v>
@@ -30864,16 +30864,16 @@
         <v>6382061684</v>
       </c>
       <c r="D1325" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1325" t="str">
-        <v>16949: 2016</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1325" t="str">
         <v>РФ</v>
       </c>
       <c r="G1325">
-        <v>46318</v>
+        <v>47094</v>
       </c>
     </row>
     <row r="1326">
@@ -30887,39 +30887,39 @@
         <v>6382061684</v>
       </c>
       <c r="D1326" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1326" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1326" t="str">
         <v>РФ</v>
       </c>
       <c r="G1326">
-        <v>47175</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="str">
-        <v>РУСАЛ Ачинский Глиноземный Комбинат</v>
+        <v>«УЗЛЫ И МЕХАНИЗМЫ КУЗОВА АВТОМОБИЛЯ» (ООО «УМКА»)</v>
       </c>
       <c r="B1327" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1327" t="str">
-        <v>2443005570</v>
+        <v>6382061684</v>
       </c>
       <c r="D1327" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1327" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1327" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1327" t="str">
-        <v/>
+      <c r="G1327">
+        <v>47175</v>
       </c>
     </row>
     <row r="1328">
@@ -30933,7 +30933,7 @@
         <v>2443005570</v>
       </c>
       <c r="D1328" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1328" t="str">
         <v>ISO 9001:2015</v>
@@ -30956,16 +30956,16 @@
         <v>2443005570</v>
       </c>
       <c r="D1329" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1329" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1329" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1329">
-        <v>47097</v>
+      <c r="G1329" t="str">
+        <v/>
       </c>
     </row>
     <row r="1330">
@@ -30979,7 +30979,7 @@
         <v>2443005570</v>
       </c>
       <c r="D1330" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1330" t="str">
         <v>ISO 14001:2015</v>
@@ -31002,16 +31002,16 @@
         <v>2443005570</v>
       </c>
       <c r="D1331" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1331" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1331" t="str">
         <v>РФ</v>
       </c>
       <c r="G1331">
-        <v>47213</v>
+        <v>47097</v>
       </c>
     </row>
     <row r="1332">
@@ -31025,7 +31025,7 @@
         <v>2443005570</v>
       </c>
       <c r="D1332" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1332" t="str">
         <v>ISO 45001:2018</v>
@@ -31039,25 +31039,25 @@
     </row>
     <row r="1333">
       <c r="A1333" t="str">
-        <v>ENTER STEEL</v>
+        <v>РУСАЛ Ачинский Глиноземный Комбинат</v>
       </c>
       <c r="B1333" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1333" t="str">
-        <v>306574437</v>
+        <v>2443005570</v>
       </c>
       <c r="D1333" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1333" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1333" t="str">
-        <v>UZ</v>
-      </c>
-      <c r="G1333" t="str">
-        <v/>
+        <v>РФ</v>
+      </c>
+      <c r="G1333">
+        <v>47213</v>
       </c>
     </row>
     <row r="1334">
@@ -31074,7 +31074,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1334" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1334" t="str">
         <v>UZ</v>
@@ -31097,7 +31097,7 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1335" t="str">
-        <v>ISO 45001:2018</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1335" t="str">
         <v>UZ</v>
@@ -31108,19 +31108,19 @@
     </row>
     <row r="1336">
       <c r="A1336" t="str">
-        <v>SAVDONI RIVOJLANTIRISH KOMPANIYASI</v>
+        <v>ENTER STEEL</v>
       </c>
       <c r="B1336" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1336" t="str">
-        <v>306303488</v>
+        <v>306574437</v>
       </c>
       <c r="D1336" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1336" t="str">
-        <v>ISO 37001:2016</v>
+        <v>ISO 45001:2018</v>
       </c>
       <c r="F1336" t="str">
         <v>UZ</v>
@@ -31131,19 +31131,19 @@
     </row>
     <row r="1337">
       <c r="A1337" t="str">
-        <v>Unitel</v>
+        <v>SAVDONI RIVOJLANTIRISH KOMPANIYASI</v>
       </c>
       <c r="B1337" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1337" t="str">
-        <v>201838002</v>
+        <v>306303488</v>
       </c>
       <c r="D1337" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1337" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 37001:2016</v>
       </c>
       <c r="F1337" t="str">
         <v>UZ</v>
@@ -31154,22 +31154,22 @@
     </row>
     <row r="1338">
       <c r="A1338" t="str">
-        <v>«СХП «РАССВЕТ»</v>
+        <v>Unitel</v>
       </c>
       <c r="B1338" t="str">
         <v>ООО</v>
       </c>
       <c r="C1338" t="str">
-        <v>2625027835</v>
+        <v>201838002</v>
       </c>
       <c r="D1338" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1338" t="str">
-        <v>GLOBALGAP IFA Smart</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1338" t="str">
-        <v>РФ</v>
+        <v>UZ</v>
       </c>
       <c r="G1338" t="str">
         <v/>
@@ -31177,19 +31177,19 @@
     </row>
     <row r="1339">
       <c r="A1339" t="str">
-        <v>Завод по производству винто-рулевых колонок Сапфир</v>
+        <v>«СХП «РАССВЕТ»</v>
       </c>
       <c r="B1339" t="str">
         <v>ООО</v>
       </c>
       <c r="C1339" t="str">
-        <v>2503032563</v>
+        <v>2625027835</v>
       </c>
       <c r="D1339" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1339" t="str">
-        <v>ISO 9001:2015</v>
+        <v>GLOBALGAP IFA Smart</v>
       </c>
       <c r="F1339" t="str">
         <v>РФ</v>
@@ -31200,48 +31200,48 @@
     </row>
     <row r="1340">
       <c r="A1340" t="str">
-        <v>GDC Services and Solutions d.o.o.</v>
+        <v>Завод по производству винто-рулевых колонок Сапфир</v>
       </c>
       <c r="B1340" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1340" t="str">
+        <v>2503032563</v>
+      </c>
+      <c r="D1340" t="str">
+        <v>ESYD (IAF)</v>
+      </c>
+      <c r="E1340" t="str">
+        <v>ISO 9001:2015</v>
+      </c>
+      <c r="F1340" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1340" t="str">
         <v/>
-      </c>
-      <c r="C1340" t="str">
-        <v/>
-      </c>
-      <c r="D1340" t="str">
-        <v>IAS (IAF)</v>
-      </c>
-      <c r="E1340" t="str">
-        <v>ISO 9001:2015</v>
-      </c>
-      <c r="F1340" t="str">
-        <v>Serbia</v>
-      </c>
-      <c r="G1340">
-        <v>47101</v>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="str">
-        <v>Красноярский металлургический завод ("КраМЗ")</v>
+        <v>GDC Services and Solutions d.o.o.</v>
       </c>
       <c r="B1341" t="str">
-        <v>ООО</v>
+        <v/>
       </c>
       <c r="C1341" t="str">
-        <v>2465043748</v>
+        <v/>
       </c>
       <c r="D1341" t="str">
-        <v>ESYD (IAF)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1341" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1341" t="str">
-        <v>РФ</v>
+        <v>Serbia</v>
       </c>
       <c r="G1341">
-        <v>47110</v>
+        <v>47101</v>
       </c>
     </row>
     <row r="1342">
@@ -31255,7 +31255,7 @@
         <v>2465043748</v>
       </c>
       <c r="D1342" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1342" t="str">
         <v>ISO 9001:2015</v>
@@ -31278,16 +31278,16 @@
         <v>2465043748</v>
       </c>
       <c r="D1343" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1343" t="str">
-        <v>ISO 14001:2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1343" t="str">
         <v>РФ</v>
       </c>
       <c r="G1343">
-        <v>47242</v>
+        <v>47110</v>
       </c>
     </row>
     <row r="1344">
@@ -31301,7 +31301,7 @@
         <v>2465043748</v>
       </c>
       <c r="D1344" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1344" t="str">
         <v>ISO 14001:2015</v>
@@ -31315,25 +31315,25 @@
     </row>
     <row r="1345">
       <c r="A1345" t="str">
-        <v>"ЭЛАРА"</v>
+        <v>Красноярский металлургический завод ("КраМЗ")</v>
       </c>
       <c r="B1345" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1345" t="str">
-        <v>2129017646</v>
+        <v>2465043748</v>
       </c>
       <c r="D1345" t="str">
-        <v>ESYD (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1345" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 14001:2015</v>
       </c>
       <c r="F1345" t="str">
         <v>РФ</v>
       </c>
       <c r="G1345">
-        <v>46980</v>
+        <v>47242</v>
       </c>
     </row>
     <row r="1346">
@@ -31350,59 +31350,59 @@
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1346" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1346" t="str">
         <v>РФ</v>
       </c>
       <c r="G1346">
-        <v>46574</v>
+        <v>46980</v>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="str">
-        <v>"Газпром проектирование"</v>
+        <v>"ЭЛАРА"</v>
       </c>
       <c r="B1347" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1347" t="str">
-        <v>0560022871</v>
+        <v>2129017646</v>
       </c>
       <c r="D1347" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1347" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1347" t="str">
         <v>РФ</v>
       </c>
       <c r="G1347">
-        <v>47003</v>
+        <v>46574</v>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="str">
-        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
+        <v>"Газпром проектирование"</v>
       </c>
       <c r="B1348" t="str">
         <v>ООО</v>
       </c>
       <c r="C1348" t="str">
-        <v>190918566</v>
+        <v>0560022871</v>
       </c>
       <c r="D1348" t="str">
         <v>ESYD (IAF)</v>
       </c>
       <c r="E1348" t="str">
-        <v>ISO/IEC 27001:2022</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1348" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1348">
-        <v>47151</v>
+        <v>47003</v>
       </c>
     </row>
     <row r="1349">
@@ -31416,7 +31416,7 @@
         <v>190918566</v>
       </c>
       <c r="D1349" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1349" t="str">
         <v>ISO/IEC 27001:2022</v>
@@ -31430,25 +31430,25 @@
     </row>
     <row r="1350">
       <c r="A1350" t="str">
-        <v>Аутолайт Технолоджи</v>
+        <v>БЕЛПРОЕКТКОНСАЛТИНГ</v>
       </c>
       <c r="B1350" t="str">
         <v>ООО</v>
       </c>
       <c r="C1350" t="str">
-        <v>6230025811</v>
+        <v>190918566</v>
       </c>
       <c r="D1350" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1350" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO/IEC 27001:2022</v>
       </c>
       <c r="F1350" t="str">
-        <v>РФ</v>
+        <v>РБ</v>
       </c>
       <c r="G1350">
-        <v>47179</v>
+        <v>47151</v>
       </c>
     </row>
     <row r="1351">
@@ -31462,16 +31462,16 @@
         <v>6230025811</v>
       </c>
       <c r="D1351" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1351" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1351" t="str">
         <v>РФ</v>
       </c>
       <c r="G1351">
-        <v>47229</v>
+        <v>47179</v>
       </c>
     </row>
     <row r="1352">
@@ -31485,16 +31485,16 @@
         <v>6230025811</v>
       </c>
       <c r="D1352" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1352" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1352" t="str">
         <v>РФ</v>
       </c>
       <c r="G1352">
-        <v>46430</v>
+        <v>47229</v>
       </c>
     </row>
     <row r="1353">
@@ -31508,39 +31508,39 @@
         <v>6230025811</v>
       </c>
       <c r="D1353" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1353" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1353" t="str">
         <v>РФ</v>
       </c>
       <c r="G1353">
-        <v>47179</v>
+        <v>46430</v>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="str">
-        <v>Инновационный центр КАМАЗ</v>
+        <v>Аутолайт Технолоджи</v>
       </c>
       <c r="B1354" t="str">
         <v>ООО</v>
       </c>
       <c r="C1354" t="str">
-        <v>7801204062</v>
+        <v>6230025811</v>
       </c>
       <c r="D1354" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1354" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1354" t="str">
         <v>РФ</v>
       </c>
       <c r="G1354">
-        <v>47286</v>
+        <v>47179</v>
       </c>
     </row>
     <row r="1355">
@@ -31557,7 +31557,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1355" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1355" t="str">
         <v>РФ</v>
@@ -31568,128 +31568,128 @@
     </row>
     <row r="1356">
       <c r="A1356" t="str">
-        <v>АкваПромМеталл</v>
+        <v>Инновационный центр КАМАЗ</v>
       </c>
       <c r="B1356" t="str">
         <v>ООО</v>
       </c>
       <c r="C1356" t="str">
-        <v>7807240772</v>
+        <v>7801204062</v>
       </c>
       <c r="D1356" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1356" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1356" t="str">
         <v>РФ</v>
       </c>
       <c r="G1356">
-        <v>47223</v>
+        <v>47286</v>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="str">
-        <v>СЗЭМО ЗАВОД ВЕНТИЛЯТОР ТДМ</v>
+        <v>АкваПромМеталл</v>
       </c>
       <c r="B1357" t="str">
         <v>ООО</v>
       </c>
       <c r="C1357" t="str">
-        <v>7811513824</v>
+        <v>7807240772</v>
       </c>
       <c r="D1357" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1357" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1357" t="str">
         <v>РФ</v>
       </c>
       <c r="G1357">
-        <v>46810</v>
+        <v>47223</v>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="str">
-        <v>РЕМОНТНО-МЕХАНИЧЕСКИЙ ЗАВОД ГОРНО-ХИМИЧЕСКОГО КОМБИНАТА (РМЗ ГХК)</v>
+        <v>СЗЭМО ЗАВОД ВЕНТИЛЯТОР ТДМ</v>
       </c>
       <c r="B1358" t="str">
         <v>ООО</v>
       </c>
       <c r="C1358" t="str">
-        <v>2452201891</v>
+        <v>7811513824</v>
       </c>
       <c r="D1358" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1358" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1358" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1358" t="str">
-        <v/>
+      <c r="G1358">
+        <v>46810</v>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="str">
-        <v>Центр диагностики, экспертизы и сертификации (ЦДЭС)</v>
+        <v>РЕМОНТНО-МЕХАНИЧЕСКИЙ ЗАВОД ГОРНО-ХИМИЧЕСКОГО КОМБИНАТА (РМЗ ГХК)</v>
       </c>
       <c r="B1359" t="str">
         <v>ООО</v>
       </c>
       <c r="C1359" t="str">
-        <v>7839346161</v>
+        <v>2452201891</v>
       </c>
       <c r="D1359" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1359" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1359" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1359">
-        <v>46567</v>
+      <c r="G1359" t="str">
+        <v/>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="str">
-        <v>Уральский завод специального арматуростроения (УЗСА)</v>
+        <v>Центр диагностики, экспертизы и сертификации (ЦДЭС)</v>
       </c>
       <c r="B1360" t="str">
         <v>ООО</v>
       </c>
       <c r="C1360" t="str">
-        <v>7451403608</v>
+        <v>7839346161</v>
       </c>
       <c r="D1360" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1360" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1360" t="str">
         <v>РФ</v>
       </c>
       <c r="G1360">
-        <v>46900</v>
+        <v>46567</v>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="str">
-        <v>Угрешский завод трубопроводной арматуры (УЗТПА)</v>
+        <v>Уральский завод специального арматуростроения (УЗСА)</v>
       </c>
       <c r="B1361" t="str">
         <v>ООО</v>
       </c>
       <c r="C1361" t="str">
-        <v>5056009251</v>
+        <v>7451403608</v>
       </c>
       <c r="D1361" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -31704,28 +31704,27 @@
         <v>46900</v>
       </c>
     </row>
-    <row r="1362" xml:space="preserve">
-      <c r="A1362" t="str" xml:space="preserve">
-        <v xml:space="preserve">Научно-_x000d_
-производственное объединение специальных материалов (НПО Спецматериалов)</v>
+    <row r="1362">
+      <c r="A1362" t="str">
+        <v>Угрешский завод трубопроводной арматуры (УЗТПА)</v>
       </c>
       <c r="B1362" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1362" t="str">
-        <v>7806125671</v>
+        <v>5056009251</v>
       </c>
       <c r="D1362" t="str">
-        <v>РОСАТОМРЕГИСТР</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1362" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1362" t="str">
         <v>РФ</v>
       </c>
       <c r="G1362">
-        <v>46709</v>
+        <v>46900</v>
       </c>
     </row>
     <row r="1363" xml:space="preserve">
@@ -31740,7 +31739,7 @@
         <v>7806125671</v>
       </c>
       <c r="D1363" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>РОСАТОМРЕГИСТР</v>
       </c>
       <c r="E1363" t="str">
         <v>ГОСТ Р ИСО 9001-2015</v>
@@ -31749,41 +31748,42 @@
         <v>РФ</v>
       </c>
       <c r="G1363">
+        <v>46709</v>
+      </c>
+    </row>
+    <row r="1364" xml:space="preserve">
+      <c r="A1364" t="str" xml:space="preserve">
+        <v xml:space="preserve">Научно-_x000d_
+производственное объединение специальных материалов (НПО Спецматериалов)</v>
+      </c>
+      <c r="B1364" t="str">
+        <v>АО</v>
+      </c>
+      <c r="C1364" t="str">
+        <v>7806125671</v>
+      </c>
+      <c r="D1364" t="str">
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+      </c>
+      <c r="E1364" t="str">
+        <v>ГОСТ Р ИСО 9001-2015</v>
+      </c>
+      <c r="F1364" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1364">
         <v>46655</v>
-      </c>
-    </row>
-    <row r="1364">
-      <c r="A1364" t="str">
-        <v>Специализированная инжиниринговая компания Севзапмонтажавтоматика (СЗМА СПИК)</v>
-      </c>
-      <c r="B1364" t="str">
-        <v>ООО</v>
-      </c>
-      <c r="C1364" t="str">
-        <v>7801715500</v>
-      </c>
-      <c r="D1364" t="str">
-        <v>O’ZAKK (IAF)</v>
-      </c>
-      <c r="E1364" t="str">
-        <v>ISO 9001:2015</v>
-      </c>
-      <c r="F1364" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1364">
-        <v>46921</v>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="str">
-        <v>Тосненский механический завод (ТоМеЗ)</v>
+        <v>Специализированная инжиниринговая компания Севзапмонтажавтоматика (СЗМА СПИК)</v>
       </c>
       <c r="B1365" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1365" t="str">
-        <v>4716002824</v>
+        <v>7801715500</v>
       </c>
       <c r="D1365" t="str">
         <v>O’ZAKK (IAF)</v>
@@ -31795,21 +31795,21 @@
         <v>РФ</v>
       </c>
       <c r="G1365">
-        <v>46619</v>
+        <v>46921</v>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="str">
-        <v>Трубопроводные покрытия и технологии (ТПТ)</v>
+        <v>Тосненский механический завод (ТоМеЗ)</v>
       </c>
       <c r="B1366" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1366" t="str">
-        <v>3435308501</v>
+        <v>4716002824</v>
       </c>
       <c r="D1366" t="str">
-        <v>EGAC (QME)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1366" t="str">
         <v>ISO 9001:2015</v>
@@ -31818,30 +31818,30 @@
         <v>РФ</v>
       </c>
       <c r="G1366">
-        <v>46272</v>
+        <v>46619</v>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="str">
-        <v>Гродно Азот, филиал Завод Химволокно</v>
+        <v>Трубопроводные покрытия и технологии (ТПТ)</v>
       </c>
       <c r="B1367" t="str">
-        <v>ОАО</v>
+        <v>ООО</v>
       </c>
       <c r="C1367" t="str">
-        <v>7707083893</v>
+        <v>3435308501</v>
       </c>
       <c r="D1367" t="str">
-        <v>O’ZAKK (IAF)</v>
+        <v>EGAC (QME)</v>
       </c>
       <c r="E1367" t="str">
         <v>ISO 9001:2015</v>
       </c>
       <c r="F1367" t="str">
-        <v>РБ</v>
+        <v>РФ</v>
       </c>
       <c r="G1367">
-        <v>47270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="1368">
@@ -31855,7 +31855,7 @@
         <v>7707083893</v>
       </c>
       <c r="D1368" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>O’ZAKK (IAF)</v>
       </c>
       <c r="E1368" t="str">
         <v>ISO 9001:2015</v>
@@ -31869,7 +31869,7 @@
     </row>
     <row r="1369">
       <c r="A1369" t="str">
-        <v>филиал "Завод Химволокно", ОАО "Гродно Азот"</v>
+        <v>Гродно Азот, филиал Завод Химволокно</v>
       </c>
       <c r="B1369" t="str">
         <v>ОАО</v>
@@ -31881,13 +31881,13 @@
         <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1369" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1369" t="str">
         <v>РБ</v>
       </c>
       <c r="G1369">
-        <v>47308</v>
+        <v>47270</v>
       </c>
     </row>
     <row r="1370">
@@ -31901,56 +31901,56 @@
         <v>7707083893</v>
       </c>
       <c r="D1370" t="str">
-        <v>EADAS</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1370" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1370" t="str">
         <v>РБ</v>
       </c>
       <c r="G1370">
-        <v>46492</v>
+        <v>47308</v>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="str">
-        <v>АВТОКОЛОРИТ</v>
+        <v>филиал "Завод Химволокно", ОАО "Гродно Азот"</v>
       </c>
       <c r="B1371" t="str">
-        <v>ООО</v>
+        <v>ОАО</v>
       </c>
       <c r="C1371" t="str">
-        <v>6320092604</v>
+        <v>7707083893</v>
       </c>
       <c r="D1371" t="str">
-        <v>ESYD (IAF)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1371" t="str">
-        <v>ISO 9001:2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1371" t="str">
-        <v>РФ</v>
-      </c>
-      <c r="G1371" t="str">
-        <v/>
+        <v>РБ</v>
+      </c>
+      <c r="G1371">
+        <v>46492</v>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="str">
-        <v>ХЕНДЭ СТИЛ РУС</v>
+        <v>АВТОКОЛОРИТ</v>
       </c>
       <c r="B1372" t="str">
         <v>ООО</v>
       </c>
       <c r="C1372" t="str">
-        <v>7813442054</v>
+        <v>6320092604</v>
       </c>
       <c r="D1372" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>ESYD (IAF)</v>
       </c>
       <c r="E1372" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1372" t="str">
         <v>РФ</v>
@@ -31973,7 +31973,7 @@
         <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1373" t="str">
-        <v>ГОСТ Р 58139-2024</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1373" t="str">
         <v>РФ</v>
@@ -31984,71 +31984,71 @@
     </row>
     <row r="1374">
       <c r="A1374" t="str">
-        <v>"Рикор Электроникс"</v>
+        <v>ХЕНДЭ СТИЛ РУС</v>
       </c>
       <c r="B1374" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1374" t="str">
-        <v>5243001622</v>
+        <v>7813442054</v>
       </c>
       <c r="D1374" t="str">
-        <v>EADAS</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1374" t="str">
-        <v>16949: 2016</v>
+        <v>ГОСТ Р 58139-2024</v>
       </c>
       <c r="F1374" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1374">
-        <v>46521</v>
+      <c r="G1374" t="str">
+        <v/>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="str">
-        <v>Сваркер</v>
+        <v>"Рикор Электроникс"</v>
       </c>
       <c r="B1375" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1375" t="str">
-        <v>6686156088</v>
+        <v>5243001622</v>
       </c>
       <c r="D1375" t="str">
-        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
+        <v>EADAS</v>
       </c>
       <c r="E1375" t="str">
-        <v>ГОСТ Р ИСО 9001-2015</v>
+        <v>16949: 2016</v>
       </c>
       <c r="F1375" t="str">
         <v>РФ</v>
       </c>
       <c r="G1375">
-        <v>47357</v>
+        <v>46521</v>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="str">
-        <v>Научно-исследовательский институт биотехнологий (НИИ БиоТех) ФГБОУ ВО СамГМУ Минздрава России</v>
+        <v>Сваркер</v>
       </c>
       <c r="B1376" t="str">
-        <v>ФГБОУ ВО</v>
+        <v>ООО</v>
       </c>
       <c r="C1376" t="str">
-        <v>6317002858</v>
+        <v>6686156088</v>
       </c>
       <c r="D1376" t="str">
-        <v>IAS (IAF)</v>
+        <v>Федеральная служба по аккредитации (Росаккредитация)</v>
       </c>
       <c r="E1376" t="str">
-        <v>ISO 13485:2016</v>
+        <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F1376" t="str">
         <v>РФ</v>
       </c>
       <c r="G1376">
-        <v>47319</v>
+        <v>47357</v>
       </c>
     </row>
     <row r="1377">
@@ -32062,7 +32062,7 @@
         <v>6317002858</v>
       </c>
       <c r="D1377" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>IAS (IAF)</v>
       </c>
       <c r="E1377" t="str">
         <v>ISO 13485:2016</v>
@@ -32076,25 +32076,25 @@
     </row>
     <row r="1378">
       <c r="A1378" t="str">
-        <v>КрасАвиа</v>
+        <v>Научно-исследовательский институт биотехнологий (НИИ БиоТех) ФГБОУ ВО СамГМУ Минздрава России</v>
       </c>
       <c r="B1378" t="str">
-        <v>АО</v>
+        <v>ФГБОУ ВО</v>
       </c>
       <c r="C1378" t="str">
-        <v>2465177981</v>
+        <v>6317002858</v>
       </c>
       <c r="D1378" t="str">
-        <v>EGAC (IAF)</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1378" t="str">
-        <v>ISO 9001:2015</v>
+        <v>ISO 13485:2016</v>
       </c>
       <c r="F1378" t="str">
         <v>РФ</v>
       </c>
       <c r="G1378">
-        <v>47299</v>
+        <v>47319</v>
       </c>
     </row>
     <row r="1379">
@@ -32108,7 +32108,7 @@
         <v>2465177981</v>
       </c>
       <c r="D1379" t="str">
-        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
+        <v>EGAC (IAF)</v>
       </c>
       <c r="E1379" t="str">
         <v>ISO 9001:2015</v>
@@ -32122,36 +32122,36 @@
     </row>
     <row r="1380">
       <c r="A1380" t="str">
-        <v>Стальимпэкс</v>
+        <v>КрасАвиа</v>
       </c>
       <c r="B1380" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1380" t="str">
-        <v>7017447537</v>
+        <v>2465177981</v>
       </c>
       <c r="D1380" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>Федеральное агентство по техническому регулированию и метрологии РФ (РОССТАНДАРТ)</v>
       </c>
       <c r="E1380" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>ISO 9001:2015</v>
       </c>
       <c r="F1380" t="str">
         <v>РФ</v>
       </c>
       <c r="G1380">
-        <v>47116</v>
+        <v>47299</v>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="str">
-        <v>Автоматизация-Метрология-Эксперт</v>
+        <v>Стальимпэкс</v>
       </c>
       <c r="B1381" t="str">
         <v>ООО</v>
       </c>
       <c r="C1381" t="str">
-        <v>0276115746</v>
+        <v>7017447537</v>
       </c>
       <c r="D1381" t="str">
         <v>СДС ИНТЕРГАЗСЕРТ</v>
@@ -32162,13 +32162,13 @@
       <c r="F1381" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1381" t="str">
-        <v/>
+      <c r="G1381">
+        <v>47116</v>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="str">
-        <v>Автоматизация-Метрология-эксперт</v>
+        <v>Автоматизация-Метрология-Эксперт</v>
       </c>
       <c r="B1382" t="str">
         <v>ООО</v>
@@ -32177,10 +32177,10 @@
         <v>0276115746</v>
       </c>
       <c r="D1382" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1382" t="str">
-        <v>S.QS.07-2024</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1382" t="str">
         <v>РФ</v>
@@ -32191,19 +32191,19 @@
     </row>
     <row r="1383">
       <c r="A1383" t="str">
-        <v>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "НИЖЕГОРОДСКИЙ ЗАВОД ТЕПЛООБМЕННОГО ОБОРУДОВАНИЯ"</v>
+        <v>Автоматизация-Метрология-эксперт</v>
       </c>
       <c r="B1383" t="str">
         <v>ООО</v>
       </c>
       <c r="C1383" t="str">
-        <v>5261068838</v>
+        <v>0276115746</v>
       </c>
       <c r="D1383" t="str">
-        <v>СДС ИНТЕРГАЗСЕРТ</v>
+        <v>СДС АНО ИНТИ</v>
       </c>
       <c r="E1383" t="str">
-        <v>СТО Газпром 9001-2018</v>
+        <v>S.QS.07-2024</v>
       </c>
       <c r="F1383" t="str">
         <v>РФ</v>
@@ -32214,36 +32214,36 @@
     </row>
     <row r="1384">
       <c r="A1384" t="str">
-        <v>Технопром</v>
+        <v>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "НИЖЕГОРОДСКИЙ ЗАВОД ТЕПЛООБМЕННОГО ОБОРУДОВАНИЯ"</v>
       </c>
       <c r="B1384" t="str">
         <v>ООО</v>
       </c>
       <c r="C1384" t="str">
-        <v>7731637278</v>
+        <v>5261068838</v>
       </c>
       <c r="D1384" t="str">
-        <v>СДС АНО ИНТИ</v>
+        <v>СДС ИНТЕРГАЗСЕРТ</v>
       </c>
       <c r="E1384" t="str">
-        <v>S.QS.07-2024</v>
+        <v>СТО Газпром 9001-2018</v>
       </c>
       <c r="F1384" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1384">
-        <v>47026</v>
+      <c r="G1384" t="str">
+        <v/>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="str">
-        <v>Пергам-Инжиниринг</v>
+        <v>Технопром</v>
       </c>
       <c r="B1385" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1385" t="str">
-        <v>7713226814</v>
+        <v>7731637278</v>
       </c>
       <c r="D1385" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32255,18 +32255,18 @@
         <v>РФ</v>
       </c>
       <c r="G1385">
-        <v>47085</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="str">
-        <v>Газ-проект-Инжиниринг</v>
+        <v>Пергам-Инжиниринг</v>
       </c>
       <c r="B1386" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1386" t="str">
-        <v>278096584</v>
+        <v>7713226814</v>
       </c>
       <c r="D1386" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32278,18 +32278,18 @@
         <v>РФ</v>
       </c>
       <c r="G1386">
-        <v>47089</v>
+        <v>47085</v>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="str">
-        <v>Инжиниринговая компания Интэко</v>
+        <v>Газ-проект-Инжиниринг</v>
       </c>
       <c r="B1387" t="str">
         <v>ООО</v>
       </c>
       <c r="C1387" t="str">
-        <v>276121517</v>
+        <v>278096584</v>
       </c>
       <c r="D1387" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32301,18 +32301,18 @@
         <v>РФ</v>
       </c>
       <c r="G1387">
-        <v>47092</v>
+        <v>47089</v>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="str">
-        <v>ЕвроМет</v>
+        <v>Инжиниринговая компания Интэко</v>
       </c>
       <c r="B1388" t="str">
         <v>ООО</v>
       </c>
       <c r="C1388" t="str">
-        <v>7826046940</v>
+        <v>276121517</v>
       </c>
       <c r="D1388" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32324,18 +32324,18 @@
         <v>РФ</v>
       </c>
       <c r="G1388">
-        <v>47161</v>
+        <v>47092</v>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="str">
-        <v>Краснодарский завод Нефтемаш</v>
+        <v>ЕвроМет</v>
       </c>
       <c r="B1389" t="str">
-        <v>АО</v>
+        <v>ООО</v>
       </c>
       <c r="C1389" t="str">
-        <v>2308026372</v>
+        <v>7826046940</v>
       </c>
       <c r="D1389" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32347,18 +32347,18 @@
         <v>РФ</v>
       </c>
       <c r="G1389">
-        <v>47190</v>
+        <v>47161</v>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="str">
-        <v>НТЦ ЗЭРС</v>
+        <v>Краснодарский завод Нефтемаш</v>
       </c>
       <c r="B1390" t="str">
-        <v>ООО</v>
+        <v>АО</v>
       </c>
       <c r="C1390" t="str">
-        <v>6229024740</v>
+        <v>2308026372</v>
       </c>
       <c r="D1390" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32369,19 +32369,19 @@
       <c r="F1390" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1390" t="str">
-        <v/>
+      <c r="G1390">
+        <v>47190</v>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="str">
-        <v>КасторИнжиниринг</v>
+        <v>НТЦ ЗЭРС</v>
       </c>
       <c r="B1391" t="str">
         <v>ООО</v>
       </c>
       <c r="C1391" t="str">
-        <v>5612079207</v>
+        <v>6229024740</v>
       </c>
       <c r="D1391" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32398,13 +32398,13 @@
     </row>
     <row r="1392">
       <c r="A1392" t="str">
-        <v>МК Энерго</v>
+        <v>КасторИнжиниринг</v>
       </c>
       <c r="B1392" t="str">
         <v>ООО</v>
       </c>
       <c r="C1392" t="str">
-        <v>7731587806</v>
+        <v>5612079207</v>
       </c>
       <c r="D1392" t="str">
         <v>СДС АНО ИНТИ</v>
@@ -32419,9 +32419,32 @@
         <v/>
       </c>
     </row>
+    <row r="1393">
+      <c r="A1393" t="str">
+        <v>МК Энерго</v>
+      </c>
+      <c r="B1393" t="str">
+        <v>ООО</v>
+      </c>
+      <c r="C1393" t="str">
+        <v>7731587806</v>
+      </c>
+      <c r="D1393" t="str">
+        <v>СДС АНО ИНТИ</v>
+      </c>
+      <c r="E1393" t="str">
+        <v>S.QS.07-2024</v>
+      </c>
+      <c r="F1393" t="str">
+        <v>РФ</v>
+      </c>
+      <c r="G1393" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1392"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1393"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -18711,7 +18711,7 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>"ДИНАМО - РУСЕВ" ЕООД</v>
+        <v>knfqh</v>
       </c>
       <c r="B797" t="str">
         <v/>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -11344,7 +11344,7 @@
         <v>РФ</v>
       </c>
       <c r="G476">
-        <v>46268</v>
+        <v>47364</v>
       </c>
     </row>
     <row r="477">
